--- a/ipoefgfefs_SLM_Matrix.xlsx
+++ b/ipoefgfefs_SLM_Matrix.xlsx
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -252,6 +252,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -753,7 +754,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>32,768 native (131,072 with YaRN scaling)</t>
+          <t>131,072 full support (32,768 in the default config)</t>
         </is>
       </c>
       <c r="J3" s="5" t="n">
@@ -769,7 +770,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 88.4% | MultiPL-E C++ 63.4% | MBPP 83.5%</t>
+          <t>MultiPL-E C++ 75.6% | HumanEval 88.4% | HumanEval+ 84.1% | MBPP 83.5% | MBPP+ 71.7%</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -815,7 +816,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>32,768 native (131,072 with YaRN scaling)</t>
+          <t>131,072 full support (32,768 in the default config)</t>
         </is>
       </c>
       <c r="J4" s="5" t="n">
@@ -831,7 +832,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 88.4% | MultiPL-E C++ 63.4% | MBPP 83.5%</t>
+          <t>MultiPL-E C++ 75.6% | HumanEval 88.4% | HumanEval+ 84.1% | MBPP 83.5% | MBPP+ 71.7%</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -877,7 +878,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>32,768 native (131,072 with YaRN scaling)</t>
+          <t>131,072 full support (32,768 in the default config)</t>
         </is>
       </c>
       <c r="J5" s="5" t="n">
@@ -893,7 +894,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 88.4% | MultiPL-E C++ 63.4% | MBPP 83.5%</t>
+          <t>MultiPL-E C++ 75.6% | HumanEval 88.4% | HumanEval+ 84.1% | MBPP 83.5% | MBPP+ 71.7%</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -939,7 +940,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>32,768 native (131,072 with YaRN scaling)</t>
+          <t>131,072 full support (32,768 in the default config)</t>
         </is>
       </c>
       <c r="J6" s="5" t="n">
@@ -955,7 +956,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 88.4% | MultiPL-E C++ 63.4% | MBPP 83.5%</t>
+          <t>MultiPL-E C++ 75.6% | HumanEval 88.4% | HumanEval+ 84.1% | MBPP 83.5% | MBPP+ 71.7%</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -1017,7 +1018,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GSM8K 91.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GPQA 56.1% | MGSM 80.6% | DROP 75.5% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
@@ -1079,7 +1080,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GSM8K 91.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GPQA 56.1% | MGSM 80.6% | DROP 75.5% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
@@ -1141,7 +1142,7 @@
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GSM8K 91.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GPQA 56.1% | MGSM 80.6% | DROP 75.5% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N9" s="8" t="inlineStr">
@@ -1203,7 +1204,7 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GSM8K 91.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GPQA 56.1% | MGSM 80.6% | DROP 75.5% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
@@ -1265,7 +1266,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 67.1% | MMLU 65.5% | GSM8K 80.9% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 89.73% | HumanEval+ 86.09% | MMLU 65.54% | GSM8K 80.89% | MATH-500 69.02% | IFEval 74.82% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -1327,7 +1328,7 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 67.1% | MMLU 65.5% | GSM8K 80.9% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 89.73% | HumanEval+ 86.09% | MMLU 65.54% | GSM8K 80.89% | MATH-500 69.02% | IFEval 74.82% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -1389,7 +1390,7 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 67.1% | MMLU 65.5% | GSM8K 80.9% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 89.73% | HumanEval+ 86.09% | MMLU 65.54% | GSM8K 80.89% | MATH-500 69.02% | IFEval 74.82% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
@@ -1451,7 +1452,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 67.1% | MMLU 65.5% | GSM8K 80.9% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 89.73% | HumanEval+ 86.09% | MMLU 65.54% | GSM8K 80.89% | MATH-500 69.02% | IFEval 74.82% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -1513,7 +1514,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 72.6% | MMLU 73.0% | GSM8K 84.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 72.6% (pass@1) | MMLU 69.4% (macro avg) | MMLU-CoT 73.0% | GSM8K 84.5% (8-shot CoT) | MBPP+ 72.8% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
@@ -1575,7 +1576,7 @@
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 72.6% | MMLU 73.0% | GSM8K 84.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 72.6% (pass@1) | MMLU 69.4% (macro avg) | MMLU-CoT 73.0% | GSM8K 84.5% (8-shot CoT) | MBPP+ 72.8% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
@@ -1637,7 +1638,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 72.6% | MMLU 73.0% | GSM8K 84.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 72.6% (pass@1) | MMLU 69.4% (macro avg) | MMLU-CoT 73.0% | GSM8K 84.5% (8-shot CoT) | MBPP+ 72.8% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
@@ -1699,7 +1700,7 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 72.6% | MMLU 73.0% | GSM8K 84.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 72.6% (pass@1) | MMLU 69.4% (macro avg) | MMLU-CoT 73.0% | GSM8K 84.5% (8-shot CoT) | MBPP+ 72.8% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
@@ -1761,7 +1762,7 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 81.1% | MultiPL-E C++ 56.5% | MBPP+ 68.8%</t>
+          <t>MultiPL-E C++ 75.8% | HumanEval 81.1% | MBPP+ 68.8%</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -1823,7 +1824,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 81.1% | MultiPL-E C++ 56.5% | MBPP+ 68.8%</t>
+          <t>MultiPL-E C++ 75.8% | HumanEval 81.1% | MBPP+ 68.8%</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -1885,7 +1886,7 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 81.1% | MultiPL-E C++ 56.5% | MBPP+ 68.8%</t>
+          <t>MultiPL-E C++ 75.8% | HumanEval 81.1% | MBPP+ 68.8%</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -1947,7 +1948,7 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 81.1% | MultiPL-E C++ 56.5% | MBPP+ 68.8%</t>
+          <t>MultiPL-E C++ 75.8% | HumanEval 81.1% | MBPP+ 68.8%</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -2257,7 +2258,7 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 56.1% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 56.1% | MBPP 54.2% | BabelCode-HumanEval C++ 42.2% | BabelCode-MBPP C++ 56.7% | HumanEval single-line infill 68.25% | multi-line infill 20.05%</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -2319,7 +2320,7 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 56.1% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 56.1% | MBPP 54.2% | BabelCode-HumanEval C++ 42.2% | BabelCode-MBPP C++ 56.7% | HumanEval single-line infill 68.25% | multi-line infill 20.05%</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -2381,7 +2382,7 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 56.1% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 56.1% | MBPP 54.2% | BabelCode-HumanEval C++ 42.2% | BabelCode-MBPP C++ 56.7% | HumanEval single-line infill 68.25% | multi-line infill 20.05%</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -2443,7 +2444,7 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 56.1% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 56.1% | MBPP 54.2% | BabelCode-HumanEval C++ 42.2% | BabelCode-MBPP C++ 56.7% | HumanEval single-line infill 68.25% | multi-line infill 20.05%</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -2753,7 +2754,7 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 57.8% | MMLU 63.4% | GSM8K 77.7%</t>
+          <t>MMLU 63.4% (macro avg) | GSM8K 77.7% (8-shot CoT) | HumanEval NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
@@ -2815,7 +2816,7 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 57.8% | MMLU 63.4% | GSM8K 77.7%</t>
+          <t>MMLU 63.4% (macro avg) | GSM8K 77.7% (8-shot CoT) | HumanEval NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -2877,7 +2878,7 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 57.8% | MMLU 63.4% | GSM8K 77.7%</t>
+          <t>MMLU 63.4% (macro avg) | GSM8K 77.7% (8-shot CoT) | HumanEval NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -2939,7 +2940,7 @@
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>HumanEval 57.8% | MMLU 63.4% | GSM8K 77.7%</t>
+          <t>MMLU 63.4% (macro avg) | GSM8K 77.7% (8-shot CoT) | HumanEval NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
@@ -5451,7 +5452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF168"/>
+  <dimension ref="A1:AF216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5739,12 +5740,12 @@
       </c>
       <c r="R3" s="17" t="inlineStr">
         <is>
-          <t>32,768 native (131,072 with YaRN scaling)</t>
+          <t>131,072 full support (32,768 in the default config)</t>
         </is>
       </c>
       <c r="S3" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct - config.json max_position_embeddings = 32768; model card 'Processing Long Texts' section describes YaRN extension to 131072.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct: card states 131,072 full context support with 32,768 as the default configured length. Architecture confirmed: 28 layers, 28 query heads, 4 KV heads (GQA). Params confirmed 7.61B total / 6.53B non-embedding.</t>
         </is>
       </c>
       <c r="T3" s="17" t="n">
@@ -5785,12 +5786,12 @@
       </c>
       <c r="AB3" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 88.4% | MultiPL-E C++ 63.4% | MBPP 83.5%</t>
+          <t>MultiPL-E C++ 75.6% | HumanEval 88.4% | HumanEval+ 84.1% | MBPP 83.5% | MBPP+ 71.7%</t>
         </is>
       </c>
       <c r="AC3" s="15" t="inlineStr">
         <is>
-          <t>HumanEval: qwenlm.github.io/blog/qwen2.5-coder/ (official Qwen blog, results table).  ||  MultiPL-E C++ and MBPP: arxiv 2409.12186, multi-language evaluation section.  ||  CHECK exact table numbers against the PDF before review.</t>
+          <t>VERIFIED 2026-08-10 against arxiv.org/html/2409.12186v3.  ||  MultiPL-E C++ 75.6 = TABLE 17 (per-language MultiPL-E breakdown).  ||  HumanEval 88.4 / HumanEval+ 84.1 / MBPP 83.5 / MBPP+ 71.7 = TABLE 16.  ||  NOTE: the official Qwen blog (qwenlm.github.io/blog/qwen2.5-coder-family/) does NOT publish per-model numbers - the technical report is the only primary source for these.</t>
         </is>
       </c>
       <c r="AD3" s="17" t="inlineStr">
@@ -5805,7 +5806,7 @@
       </c>
       <c r="AF3" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. Benchmarks confirmed against arxiv 2409.12186 Tables 16 and 17.</t>
         </is>
       </c>
     </row>
@@ -5891,12 +5892,12 @@
       </c>
       <c r="R4" s="17" t="inlineStr">
         <is>
-          <t>32,768 native (131,072 with YaRN scaling)</t>
+          <t>131,072 full support (32,768 in the default config)</t>
         </is>
       </c>
       <c r="S4" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct - config.json max_position_embeddings = 32768; model card 'Processing Long Texts' section describes YaRN extension to 131072.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct: card states 131,072 full context support with 32,768 as the default configured length. Architecture confirmed: 28 layers, 28 query heads, 4 KV heads (GQA). Params confirmed 7.61B total / 6.53B non-embedding.</t>
         </is>
       </c>
       <c r="T4" s="17" t="n">
@@ -5937,12 +5938,12 @@
       </c>
       <c r="AB4" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 88.4% | MultiPL-E C++ 63.4% | MBPP 83.5%</t>
+          <t>MultiPL-E C++ 75.6% | HumanEval 88.4% | HumanEval+ 84.1% | MBPP 83.5% | MBPP+ 71.7%</t>
         </is>
       </c>
       <c r="AC4" s="15" t="inlineStr">
         <is>
-          <t>HumanEval: qwenlm.github.io/blog/qwen2.5-coder/ (official Qwen blog, results table).  ||  MultiPL-E C++ and MBPP: arxiv 2409.12186, multi-language evaluation section.  ||  CHECK exact table numbers against the PDF before review.</t>
+          <t>VERIFIED 2026-08-10 against arxiv.org/html/2409.12186v3.  ||  MultiPL-E C++ 75.6 = TABLE 17 (per-language MultiPL-E breakdown).  ||  HumanEval 88.4 / HumanEval+ 84.1 / MBPP 83.5 / MBPP+ 71.7 = TABLE 16.  ||  NOTE: the official Qwen blog (qwenlm.github.io/blog/qwen2.5-coder-family/) does NOT publish per-model numbers - the technical report is the only primary source for these.</t>
         </is>
       </c>
       <c r="AD4" s="17" t="inlineStr">
@@ -5957,7 +5958,7 @@
       </c>
       <c r="AF4" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. Benchmarks confirmed against arxiv 2409.12186 Tables 16 and 17.</t>
         </is>
       </c>
     </row>
@@ -6043,12 +6044,12 @@
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
-          <t>32,768 native (131,072 with YaRN scaling)</t>
+          <t>131,072 full support (32,768 in the default config)</t>
         </is>
       </c>
       <c r="S5" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct - config.json max_position_embeddings = 32768; model card 'Processing Long Texts' section describes YaRN extension to 131072.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct: card states 131,072 full context support with 32,768 as the default configured length. Architecture confirmed: 28 layers, 28 query heads, 4 KV heads (GQA). Params confirmed 7.61B total / 6.53B non-embedding.</t>
         </is>
       </c>
       <c r="T5" s="17" t="n">
@@ -6089,12 +6090,12 @@
       </c>
       <c r="AB5" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 88.4% | MultiPL-E C++ 63.4% | MBPP 83.5%</t>
+          <t>MultiPL-E C++ 75.6% | HumanEval 88.4% | HumanEval+ 84.1% | MBPP 83.5% | MBPP+ 71.7%</t>
         </is>
       </c>
       <c r="AC5" s="15" t="inlineStr">
         <is>
-          <t>HumanEval: qwenlm.github.io/blog/qwen2.5-coder/ (official Qwen blog, results table).  ||  MultiPL-E C++ and MBPP: arxiv 2409.12186, multi-language evaluation section.  ||  CHECK exact table numbers against the PDF before review.</t>
+          <t>VERIFIED 2026-08-10 against arxiv.org/html/2409.12186v3.  ||  MultiPL-E C++ 75.6 = TABLE 17 (per-language MultiPL-E breakdown).  ||  HumanEval 88.4 / HumanEval+ 84.1 / MBPP 83.5 / MBPP+ 71.7 = TABLE 16.  ||  NOTE: the official Qwen blog (qwenlm.github.io/blog/qwen2.5-coder-family/) does NOT publish per-model numbers - the technical report is the only primary source for these.</t>
         </is>
       </c>
       <c r="AD5" s="17" t="inlineStr">
@@ -6109,7 +6110,7 @@
       </c>
       <c r="AF5" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. Benchmarks confirmed against arxiv 2409.12186 Tables 16 and 17.</t>
         </is>
       </c>
     </row>
@@ -6195,12 +6196,12 @@
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
-          <t>32,768 native (131,072 with YaRN scaling)</t>
+          <t>131,072 full support (32,768 in the default config)</t>
         </is>
       </c>
       <c r="S6" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct - config.json max_position_embeddings = 32768; model card 'Processing Long Texts' section describes YaRN extension to 131072.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct: card states 131,072 full context support with 32,768 as the default configured length. Architecture confirmed: 28 layers, 28 query heads, 4 KV heads (GQA). Params confirmed 7.61B total / 6.53B non-embedding.</t>
         </is>
       </c>
       <c r="T6" s="17" t="n">
@@ -6241,12 +6242,12 @@
       </c>
       <c r="AB6" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 88.4% | MultiPL-E C++ 63.4% | MBPP 83.5%</t>
+          <t>MultiPL-E C++ 75.6% | HumanEval 88.4% | HumanEval+ 84.1% | MBPP 83.5% | MBPP+ 71.7%</t>
         </is>
       </c>
       <c r="AC6" s="15" t="inlineStr">
         <is>
-          <t>HumanEval: qwenlm.github.io/blog/qwen2.5-coder/ (official Qwen blog, results table).  ||  MultiPL-E C++ and MBPP: arxiv 2409.12186, multi-language evaluation section.  ||  CHECK exact table numbers against the PDF before review.</t>
+          <t>VERIFIED 2026-08-10 against arxiv.org/html/2409.12186v3.  ||  MultiPL-E C++ 75.6 = TABLE 17 (per-language MultiPL-E breakdown).  ||  HumanEval 88.4 / HumanEval+ 84.1 / MBPP 83.5 / MBPP+ 71.7 = TABLE 16.  ||  NOTE: the official Qwen blog (qwenlm.github.io/blog/qwen2.5-coder-family/) does NOT publish per-model numbers - the technical report is the only primary source for these.</t>
         </is>
       </c>
       <c r="AD6" s="17" t="inlineStr">
@@ -6261,7 +6262,7 @@
       </c>
       <c r="AF6" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. Benchmarks confirmed against arxiv 2409.12186 Tables 16 and 17.</t>
         </is>
       </c>
     </row>
@@ -6321,12 +6322,12 @@
       </c>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1920 x NVIDIA H100-80GB, approx 21 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1920 x NVIDIA H100-80GB, 21 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2412.08905 - training-details section. CHECK: GPU count and duration quoted from memory, confirm against the PDF.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/phi-4 model card, 'Training' section: '1920 H100-80G' for '21 days'.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N7" s="21" t="n">
@@ -6393,12 +6394,12 @@
       </c>
       <c r="AB7" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GSM8K 91.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GPQA 56.1% | MGSM 80.6% | DROP 75.5% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC7" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2412.08905, main results table comparing against GPT-4o-mini and Qwen2.5-14B.  ||  CHECK exact table number.  ||  MultiPL-E C++: genuinely absent from the paper - this is a gap in the published record, not a gap in this research.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/phi-4 model card evaluation table.  ||  CORRECTION: an earlier revision of this sheet listed GSM8K 91.5% - Microsoft does NOT publish GSM8K for Phi-4. The card reports MGSM 80.6% (multilingual grade-school math) instead. The GSM8K figure has been removed as unsourced.  ||  MultiPL-E C++: genuinely absent - a gap in the published record, not in this research.</t>
         </is>
       </c>
       <c r="AD7" s="21" t="inlineStr">
@@ -6413,7 +6414,7 @@
       </c>
       <c r="AF7" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. Benchmarks and training HW confirmed against the phi-4 model card. GSM8K removed as unsourced.</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6474,12 @@
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1920 x NVIDIA H100-80GB, approx 21 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1920 x NVIDIA H100-80GB, 21 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2412.08905 - training-details section. CHECK: GPU count and duration quoted from memory, confirm against the PDF.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/phi-4 model card, 'Training' section: '1920 H100-80G' for '21 days'.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N8" s="21" t="n">
@@ -6545,12 +6546,12 @@
       </c>
       <c r="AB8" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GSM8K 91.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GPQA 56.1% | MGSM 80.6% | DROP 75.5% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC8" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2412.08905, main results table comparing against GPT-4o-mini and Qwen2.5-14B.  ||  CHECK exact table number.  ||  MultiPL-E C++: genuinely absent from the paper - this is a gap in the published record, not a gap in this research.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/phi-4 model card evaluation table.  ||  CORRECTION: an earlier revision of this sheet listed GSM8K 91.5% - Microsoft does NOT publish GSM8K for Phi-4. The card reports MGSM 80.6% (multilingual grade-school math) instead. The GSM8K figure has been removed as unsourced.  ||  MultiPL-E C++: genuinely absent - a gap in the published record, not in this research.</t>
         </is>
       </c>
       <c r="AD8" s="21" t="inlineStr">
@@ -6565,7 +6566,7 @@
       </c>
       <c r="AF8" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. Benchmarks and training HW confirmed against the phi-4 model card. GSM8K removed as unsourced.</t>
         </is>
       </c>
     </row>
@@ -6625,12 +6626,12 @@
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1920 x NVIDIA H100-80GB, approx 21 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1920 x NVIDIA H100-80GB, 21 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2412.08905 - training-details section. CHECK: GPU count and duration quoted from memory, confirm against the PDF.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/phi-4 model card, 'Training' section: '1920 H100-80G' for '21 days'.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N9" s="21" t="n">
@@ -6697,12 +6698,12 @@
       </c>
       <c r="AB9" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GSM8K 91.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GPQA 56.1% | MGSM 80.6% | DROP 75.5% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC9" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2412.08905, main results table comparing against GPT-4o-mini and Qwen2.5-14B.  ||  CHECK exact table number.  ||  MultiPL-E C++: genuinely absent from the paper - this is a gap in the published record, not a gap in this research.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/phi-4 model card evaluation table.  ||  CORRECTION: an earlier revision of this sheet listed GSM8K 91.5% - Microsoft does NOT publish GSM8K for Phi-4. The card reports MGSM 80.6% (multilingual grade-school math) instead. The GSM8K figure has been removed as unsourced.  ||  MultiPL-E C++: genuinely absent - a gap in the published record, not in this research.</t>
         </is>
       </c>
       <c r="AD9" s="21" t="inlineStr">
@@ -6717,7 +6718,7 @@
       </c>
       <c r="AF9" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. Benchmarks and training HW confirmed against the phi-4 model card. GSM8K removed as unsourced.</t>
         </is>
       </c>
     </row>
@@ -6777,12 +6778,12 @@
       </c>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1920 x NVIDIA H100-80GB, approx 21 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1920 x NVIDIA H100-80GB, 21 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2412.08905 - training-details section. CHECK: GPU count and duration quoted from memory, confirm against the PDF.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/phi-4 model card, 'Training' section: '1920 H100-80G' for '21 days'.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N10" s="21" t="n">
@@ -6849,12 +6850,12 @@
       </c>
       <c r="AB10" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GSM8K 91.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 82.6% | MMLU 84.8% | MATH 80.4% | GPQA 56.1% | MGSM 80.6% | DROP 75.5% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC10" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2412.08905, main results table comparing against GPT-4o-mini and Qwen2.5-14B.  ||  CHECK exact table number.  ||  MultiPL-E C++: genuinely absent from the paper - this is a gap in the published record, not a gap in this research.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/phi-4 model card evaluation table.  ||  CORRECTION: an earlier revision of this sheet listed GSM8K 91.5% - Microsoft does NOT publish GSM8K for Phi-4. The card reports MGSM 80.6% (multilingual grade-school math) instead. The GSM8K figure has been removed as unsourced.  ||  MultiPL-E C++: genuinely absent - a gap in the published record, not in this research.</t>
         </is>
       </c>
       <c r="AD10" s="21" t="inlineStr">
@@ -6869,7 +6870,7 @@
       </c>
       <c r="AF10" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. Benchmarks and training HW confirmed against the phi-4 model card. GSM8K removed as unsourced.</t>
         </is>
       </c>
     </row>
@@ -7001,12 +7002,12 @@
       </c>
       <c r="AB11" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 67.1% | MMLU 65.5% | GSM8K 80.9% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 89.73% | HumanEval+ 86.09% | MMLU 65.54% | GSM8K 80.89% | MATH-500 69.02% | IFEval 74.82% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC11" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/ibm-granite/granite-3.3-8b-instruct - model card 'Evaluation Results' table. IBM publishes no arXiv paper for the 3.3 release, so the model card IS the primary source.  ||  CHECK values against the current card - IBM revises these tables between point releases.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/ibm-granite/granite-3.3-8b-instruct model card, 'Evaluation Results' table. IBM publishes no arXiv paper for 3.3, so the card IS the primary source.  ||  CORRECTION: an earlier revision of this sheet stated HumanEval 67.1% - that was WRONG. The published figure is 89.73%, the HIGHEST HumanEval of any model in this sheet.  ||  MultiPL-E C++ genuinely absent - IBM publishes no per-language code breakdown.</t>
         </is>
       </c>
       <c r="AD11" s="17" t="inlineStr">
@@ -7021,7 +7022,7 @@
       </c>
       <c r="AF11" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK against live card. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. HumanEval CORRECTED 67.1 -&gt; 89.73 against the live IBM model card.</t>
         </is>
       </c>
     </row>
@@ -7153,12 +7154,12 @@
       </c>
       <c r="AB12" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 67.1% | MMLU 65.5% | GSM8K 80.9% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 89.73% | HumanEval+ 86.09% | MMLU 65.54% | GSM8K 80.89% | MATH-500 69.02% | IFEval 74.82% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC12" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/ibm-granite/granite-3.3-8b-instruct - model card 'Evaluation Results' table. IBM publishes no arXiv paper for the 3.3 release, so the model card IS the primary source.  ||  CHECK values against the current card - IBM revises these tables between point releases.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/ibm-granite/granite-3.3-8b-instruct model card, 'Evaluation Results' table. IBM publishes no arXiv paper for 3.3, so the card IS the primary source.  ||  CORRECTION: an earlier revision of this sheet stated HumanEval 67.1% - that was WRONG. The published figure is 89.73%, the HIGHEST HumanEval of any model in this sheet.  ||  MultiPL-E C++ genuinely absent - IBM publishes no per-language code breakdown.</t>
         </is>
       </c>
       <c r="AD12" s="17" t="inlineStr">
@@ -7173,7 +7174,7 @@
       </c>
       <c r="AF12" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK against live card. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. HumanEval CORRECTED 67.1 -&gt; 89.73 against the live IBM model card.</t>
         </is>
       </c>
     </row>
@@ -7305,12 +7306,12 @@
       </c>
       <c r="AB13" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 67.1% | MMLU 65.5% | GSM8K 80.9% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 89.73% | HumanEval+ 86.09% | MMLU 65.54% | GSM8K 80.89% | MATH-500 69.02% | IFEval 74.82% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC13" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/ibm-granite/granite-3.3-8b-instruct - model card 'Evaluation Results' table. IBM publishes no arXiv paper for the 3.3 release, so the model card IS the primary source.  ||  CHECK values against the current card - IBM revises these tables between point releases.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/ibm-granite/granite-3.3-8b-instruct model card, 'Evaluation Results' table. IBM publishes no arXiv paper for 3.3, so the card IS the primary source.  ||  CORRECTION: an earlier revision of this sheet stated HumanEval 67.1% - that was WRONG. The published figure is 89.73%, the HIGHEST HumanEval of any model in this sheet.  ||  MultiPL-E C++ genuinely absent - IBM publishes no per-language code breakdown.</t>
         </is>
       </c>
       <c r="AD13" s="17" t="inlineStr">
@@ -7325,7 +7326,7 @@
       </c>
       <c r="AF13" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK against live card. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. HumanEval CORRECTED 67.1 -&gt; 89.73 against the live IBM model card.</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7458,12 @@
       </c>
       <c r="AB14" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 67.1% | MMLU 65.5% | GSM8K 80.9% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 89.73% | HumanEval+ 86.09% | MMLU 65.54% | GSM8K 80.89% | MATH-500 69.02% | IFEval 74.82% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC14" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/ibm-granite/granite-3.3-8b-instruct - model card 'Evaluation Results' table. IBM publishes no arXiv paper for the 3.3 release, so the model card IS the primary source.  ||  CHECK values against the current card - IBM revises these tables between point releases.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/ibm-granite/granite-3.3-8b-instruct model card, 'Evaluation Results' table. IBM publishes no arXiv paper for 3.3, so the card IS the primary source.  ||  CORRECTION: an earlier revision of this sheet stated HumanEval 67.1% - that was WRONG. The published figure is 89.73%, the HIGHEST HumanEval of any model in this sheet.  ||  MultiPL-E C++ genuinely absent - IBM publishes no per-language code breakdown.</t>
         </is>
       </c>
       <c r="AD14" s="17" t="inlineStr">
@@ -7477,7 +7478,7 @@
       </c>
       <c r="AF14" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK against live card. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. HumanEval CORRECTED 67.1 -&gt; 89.73 against the live IBM model card.</t>
         </is>
       </c>
     </row>
@@ -7537,12 +7538,12 @@
       </c>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: NVIDIA H100-80GB. Llama 3 family total 39.3M GPU-hours; 8B share 1.46M GPU-hours  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: NVIDIA H100-80GB (700W TDP). 8B share: 1.46M GPU-hours  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2407.21783 - training-compute table breaking down GPU-hours per model size. CHECK the exact figures and table number.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.1-8B-Instruct model card, 'Training Energy Use' table: 1.46M GPU-hours on H100-80GB, 700W per device.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N15" s="21" t="n">
@@ -7609,12 +7610,12 @@
       </c>
       <c r="AB15" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 72.6% | MMLU 73.0% | GSM8K 84.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 72.6% (pass@1) | MMLU 69.4% (macro avg) | MMLU-CoT 73.0% | GSM8K 84.5% (8-shot CoT) | MBPP+ 72.8% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC15" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2407.21783 - instruction-tuned evaluation tables. This is a 90+ page paper; CHECK the exact table number before citing it in review.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.1-8B-Instruct model card evaluation tables.  ||  CORRECTION: an earlier revision listed MMLU 73.0% without qualification. The card reports TWO figures: MMLU 69.4% (macro average, standard 5-shot) and MMLU-CoT 73.0% (chain-of-thought). Quoting 73.0 as plain MMLU overstates it against models reporting the standard metric. Both are now shown.</t>
         </is>
       </c>
       <c r="AD15" s="21" t="inlineStr">
@@ -7629,7 +7630,7 @@
       </c>
       <c r="AF15" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. MMLU disambiguated: 69.4 standard vs 73.0 CoT. Training GPU-hours confirmed.</t>
         </is>
       </c>
     </row>
@@ -7689,12 +7690,12 @@
       </c>
       <c r="L16" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: NVIDIA H100-80GB. Llama 3 family total 39.3M GPU-hours; 8B share 1.46M GPU-hours  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: NVIDIA H100-80GB (700W TDP). 8B share: 1.46M GPU-hours  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2407.21783 - training-compute table breaking down GPU-hours per model size. CHECK the exact figures and table number.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.1-8B-Instruct model card, 'Training Energy Use' table: 1.46M GPU-hours on H100-80GB, 700W per device.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N16" s="21" t="n">
@@ -7761,12 +7762,12 @@
       </c>
       <c r="AB16" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 72.6% | MMLU 73.0% | GSM8K 84.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 72.6% (pass@1) | MMLU 69.4% (macro avg) | MMLU-CoT 73.0% | GSM8K 84.5% (8-shot CoT) | MBPP+ 72.8% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC16" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2407.21783 - instruction-tuned evaluation tables. This is a 90+ page paper; CHECK the exact table number before citing it in review.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.1-8B-Instruct model card evaluation tables.  ||  CORRECTION: an earlier revision listed MMLU 73.0% without qualification. The card reports TWO figures: MMLU 69.4% (macro average, standard 5-shot) and MMLU-CoT 73.0% (chain-of-thought). Quoting 73.0 as plain MMLU overstates it against models reporting the standard metric. Both are now shown.</t>
         </is>
       </c>
       <c r="AD16" s="21" t="inlineStr">
@@ -7781,7 +7782,7 @@
       </c>
       <c r="AF16" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. MMLU disambiguated: 69.4 standard vs 73.0 CoT. Training GPU-hours confirmed.</t>
         </is>
       </c>
     </row>
@@ -7841,12 +7842,12 @@
       </c>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: NVIDIA H100-80GB. Llama 3 family total 39.3M GPU-hours; 8B share 1.46M GPU-hours  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: NVIDIA H100-80GB (700W TDP). 8B share: 1.46M GPU-hours  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2407.21783 - training-compute table breaking down GPU-hours per model size. CHECK the exact figures and table number.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.1-8B-Instruct model card, 'Training Energy Use' table: 1.46M GPU-hours on H100-80GB, 700W per device.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N17" s="21" t="n">
@@ -7913,12 +7914,12 @@
       </c>
       <c r="AB17" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 72.6% | MMLU 73.0% | GSM8K 84.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 72.6% (pass@1) | MMLU 69.4% (macro avg) | MMLU-CoT 73.0% | GSM8K 84.5% (8-shot CoT) | MBPP+ 72.8% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC17" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2407.21783 - instruction-tuned evaluation tables. This is a 90+ page paper; CHECK the exact table number before citing it in review.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.1-8B-Instruct model card evaluation tables.  ||  CORRECTION: an earlier revision listed MMLU 73.0% without qualification. The card reports TWO figures: MMLU 69.4% (macro average, standard 5-shot) and MMLU-CoT 73.0% (chain-of-thought). Quoting 73.0 as plain MMLU overstates it against models reporting the standard metric. Both are now shown.</t>
         </is>
       </c>
       <c r="AD17" s="21" t="inlineStr">
@@ -7933,7 +7934,7 @@
       </c>
       <c r="AF17" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. MMLU disambiguated: 69.4 standard vs 73.0 CoT. Training GPU-hours confirmed.</t>
         </is>
       </c>
     </row>
@@ -7993,12 +7994,12 @@
       </c>
       <c r="L18" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: NVIDIA H100-80GB. Llama 3 family total 39.3M GPU-hours; 8B share 1.46M GPU-hours  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: NVIDIA H100-80GB (700W TDP). 8B share: 1.46M GPU-hours  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2407.21783 - training-compute table breaking down GPU-hours per model size. CHECK the exact figures and table number.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.1-8B-Instruct model card, 'Training Energy Use' table: 1.46M GPU-hours on H100-80GB, 700W per device.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N18" s="21" t="n">
@@ -8065,12 +8066,12 @@
       </c>
       <c r="AB18" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 72.6% | MMLU 73.0% | GSM8K 84.5% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 72.6% (pass@1) | MMLU 69.4% (macro avg) | MMLU-CoT 73.0% | GSM8K 84.5% (8-shot CoT) | MBPP+ 72.8% | MultiPL-E C++ NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC18" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2407.21783 - instruction-tuned evaluation tables. This is a 90+ page paper; CHECK the exact table number before citing it in review.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.1-8B-Instruct model card evaluation tables.  ||  CORRECTION: an earlier revision listed MMLU 73.0% without qualification. The card reports TWO figures: MMLU 69.4% (macro average, standard 5-shot) and MMLU-CoT 73.0% (chain-of-thought). Quoting 73.0 as plain MMLU overstates it against models reporting the standard metric. Both are now shown.</t>
         </is>
       </c>
       <c r="AD18" s="21" t="inlineStr">
@@ -8085,7 +8086,7 @@
       </c>
       <c r="AF18" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. MMLU disambiguated: 69.4 standard vs 73.0 CoT. Training GPU-hours confirmed.</t>
         </is>
       </c>
     </row>
@@ -8217,12 +8218,12 @@
       </c>
       <c r="AB19" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 81.1% | MultiPL-E C++ 56.5% | MBPP+ 68.8%</t>
+          <t>MultiPL-E C++ 75.8% | HumanEval 81.1% | MBPP+ 68.8%</t>
         </is>
       </c>
       <c r="AC19" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2406.11931 - code-benchmark tables. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against arxiv.org/html/2406.11931v1, TABLE 3 (HumanEval, MBPP+ and the per-language MultiPL-E breakdown).  ||  CORRECTION: an earlier revision stated C++ 56.5% - that was WRONG. Published figure is 75.8%, the highest measured C++ score in this sheet.  ||  Paper notes the 16B/2.4B-active model beats the dense 33B on multi-language average (65.6% vs 61.9%).</t>
         </is>
       </c>
       <c r="AD19" s="17" t="inlineStr">
@@ -8237,7 +8238,7 @@
       </c>
       <c r="AF19" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + context: CHECK. Licence: VERIFIED but restrictive.</t>
+          <t>VERIFIED 2026-08-10. C++ CORRECTED 56.5 -&gt; 75.8 against arxiv 2406.11931 Table 3. Licence remains restrictive.</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8370,12 @@
       </c>
       <c r="AB20" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 81.1% | MultiPL-E C++ 56.5% | MBPP+ 68.8%</t>
+          <t>MultiPL-E C++ 75.8% | HumanEval 81.1% | MBPP+ 68.8%</t>
         </is>
       </c>
       <c r="AC20" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2406.11931 - code-benchmark tables. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against arxiv.org/html/2406.11931v1, TABLE 3 (HumanEval, MBPP+ and the per-language MultiPL-E breakdown).  ||  CORRECTION: an earlier revision stated C++ 56.5% - that was WRONG. Published figure is 75.8%, the highest measured C++ score in this sheet.  ||  Paper notes the 16B/2.4B-active model beats the dense 33B on multi-language average (65.6% vs 61.9%).</t>
         </is>
       </c>
       <c r="AD20" s="17" t="inlineStr">
@@ -8389,7 +8390,7 @@
       </c>
       <c r="AF20" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + context: CHECK. Licence: VERIFIED but restrictive.</t>
+          <t>VERIFIED 2026-08-10. C++ CORRECTED 56.5 -&gt; 75.8 against arxiv 2406.11931 Table 3. Licence remains restrictive.</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8522,12 @@
       </c>
       <c r="AB21" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 81.1% | MultiPL-E C++ 56.5% | MBPP+ 68.8%</t>
+          <t>MultiPL-E C++ 75.8% | HumanEval 81.1% | MBPP+ 68.8%</t>
         </is>
       </c>
       <c r="AC21" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2406.11931 - code-benchmark tables. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against arxiv.org/html/2406.11931v1, TABLE 3 (HumanEval, MBPP+ and the per-language MultiPL-E breakdown).  ||  CORRECTION: an earlier revision stated C++ 56.5% - that was WRONG. Published figure is 75.8%, the highest measured C++ score in this sheet.  ||  Paper notes the 16B/2.4B-active model beats the dense 33B on multi-language average (65.6% vs 61.9%).</t>
         </is>
       </c>
       <c r="AD21" s="17" t="inlineStr">
@@ -8541,7 +8542,7 @@
       </c>
       <c r="AF21" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + context: CHECK. Licence: VERIFIED but restrictive.</t>
+          <t>VERIFIED 2026-08-10. C++ CORRECTED 56.5 -&gt; 75.8 against arxiv 2406.11931 Table 3. Licence remains restrictive.</t>
         </is>
       </c>
     </row>
@@ -8673,12 +8674,12 @@
       </c>
       <c r="AB22" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 81.1% | MultiPL-E C++ 56.5% | MBPP+ 68.8%</t>
+          <t>MultiPL-E C++ 75.8% | HumanEval 81.1% | MBPP+ 68.8%</t>
         </is>
       </c>
       <c r="AC22" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2406.11931 - code-benchmark tables. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against arxiv.org/html/2406.11931v1, TABLE 3 (HumanEval, MBPP+ and the per-language MultiPL-E breakdown).  ||  CORRECTION: an earlier revision stated C++ 56.5% - that was WRONG. Published figure is 75.8%, the highest measured C++ score in this sheet.  ||  Paper notes the 16B/2.4B-active model beats the dense 33B on multi-language average (65.6% vs 61.9%).</t>
         </is>
       </c>
       <c r="AD22" s="17" t="inlineStr">
@@ -8693,7 +8694,7 @@
       </c>
       <c r="AF22" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + context: CHECK. Licence: VERIFIED but restrictive.</t>
+          <t>VERIFIED 2026-08-10. C++ CORRECTED 56.5 -&gt; 75.8 against arxiv 2406.11931 Table 3. Licence remains restrictive.</t>
         </is>
       </c>
     </row>
@@ -9433,12 +9434,12 @@
       </c>
       <c r="AB27" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 56.1% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 56.1% | MBPP 54.2% | BabelCode-HumanEval C++ 42.2% | BabelCode-MBPP C++ 56.7% | HumanEval single-line infill 68.25% | multi-line infill 20.05%</t>
         </is>
       </c>
       <c r="AC27" s="15" t="inlineStr">
         <is>
-          <t>ai.google.dev/gemma/docs/codegemma/model_card - evaluation table. Google publishes the CodeGemma report as documentation rather than a peer-reviewed paper. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/codegemma-7b-it model card evaluation table.  ||  CORRECTION: an earlier revision said 'C++ NOT PUBLISHED'. That was WRONG. Google DOES publish C++ figures, under BabelCode (BC HE C++ 42.2, BC MBPP C++ 56.7) rather than MultiPL-E - which is why it was missed. BabelCode and MultiPL-E are different harnesses and the scores are NOT directly comparable; flag this if a reviewer compares 42.2 against Qwen's 75.6.  ||  Multi-line infill 20.05% vs single-line 68.25% is a large gap worth noting for retry-patching use.</t>
         </is>
       </c>
       <c r="AD27" s="17" t="inlineStr">
@@ -9453,7 +9454,7 @@
       </c>
       <c r="AF27" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Context 8K: VERIFIED - this is the disqualifier.</t>
+          <t>VERIFIED 2026-08-10. C++ figures DO exist under BabelCode (42.2) - earlier NOT PUBLISHED was wrong. Context 8K confirmed disqualifier.</t>
         </is>
       </c>
     </row>
@@ -9585,12 +9586,12 @@
       </c>
       <c r="AB28" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 56.1% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 56.1% | MBPP 54.2% | BabelCode-HumanEval C++ 42.2% | BabelCode-MBPP C++ 56.7% | HumanEval single-line infill 68.25% | multi-line infill 20.05%</t>
         </is>
       </c>
       <c r="AC28" s="15" t="inlineStr">
         <is>
-          <t>ai.google.dev/gemma/docs/codegemma/model_card - evaluation table. Google publishes the CodeGemma report as documentation rather than a peer-reviewed paper. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/codegemma-7b-it model card evaluation table.  ||  CORRECTION: an earlier revision said 'C++ NOT PUBLISHED'. That was WRONG. Google DOES publish C++ figures, under BabelCode (BC HE C++ 42.2, BC MBPP C++ 56.7) rather than MultiPL-E - which is why it was missed. BabelCode and MultiPL-E are different harnesses and the scores are NOT directly comparable; flag this if a reviewer compares 42.2 against Qwen's 75.6.  ||  Multi-line infill 20.05% vs single-line 68.25% is a large gap worth noting for retry-patching use.</t>
         </is>
       </c>
       <c r="AD28" s="17" t="inlineStr">
@@ -9605,7 +9606,7 @@
       </c>
       <c r="AF28" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Context 8K: VERIFIED - this is the disqualifier.</t>
+          <t>VERIFIED 2026-08-10. C++ figures DO exist under BabelCode (42.2) - earlier NOT PUBLISHED was wrong. Context 8K confirmed disqualifier.</t>
         </is>
       </c>
     </row>
@@ -9737,12 +9738,12 @@
       </c>
       <c r="AB29" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 56.1% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 56.1% | MBPP 54.2% | BabelCode-HumanEval C++ 42.2% | BabelCode-MBPP C++ 56.7% | HumanEval single-line infill 68.25% | multi-line infill 20.05%</t>
         </is>
       </c>
       <c r="AC29" s="15" t="inlineStr">
         <is>
-          <t>ai.google.dev/gemma/docs/codegemma/model_card - evaluation table. Google publishes the CodeGemma report as documentation rather than a peer-reviewed paper. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/codegemma-7b-it model card evaluation table.  ||  CORRECTION: an earlier revision said 'C++ NOT PUBLISHED'. That was WRONG. Google DOES publish C++ figures, under BabelCode (BC HE C++ 42.2, BC MBPP C++ 56.7) rather than MultiPL-E - which is why it was missed. BabelCode and MultiPL-E are different harnesses and the scores are NOT directly comparable; flag this if a reviewer compares 42.2 against Qwen's 75.6.  ||  Multi-line infill 20.05% vs single-line 68.25% is a large gap worth noting for retry-patching use.</t>
         </is>
       </c>
       <c r="AD29" s="17" t="inlineStr">
@@ -9757,7 +9758,7 @@
       </c>
       <c r="AF29" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Context 8K: VERIFIED - this is the disqualifier.</t>
+          <t>VERIFIED 2026-08-10. C++ figures DO exist under BabelCode (42.2) - earlier NOT PUBLISHED was wrong. Context 8K confirmed disqualifier.</t>
         </is>
       </c>
     </row>
@@ -9889,12 +9890,12 @@
       </c>
       <c r="AB30" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 56.1% | MultiPL-E C++ NOT PUBLISHED</t>
+          <t>HumanEval 56.1% | MBPP 54.2% | BabelCode-HumanEval C++ 42.2% | BabelCode-MBPP C++ 56.7% | HumanEval single-line infill 68.25% | multi-line infill 20.05%</t>
         </is>
       </c>
       <c r="AC30" s="15" t="inlineStr">
         <is>
-          <t>ai.google.dev/gemma/docs/codegemma/model_card - evaluation table. Google publishes the CodeGemma report as documentation rather than a peer-reviewed paper. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/codegemma-7b-it model card evaluation table.  ||  CORRECTION: an earlier revision said 'C++ NOT PUBLISHED'. That was WRONG. Google DOES publish C++ figures, under BabelCode (BC HE C++ 42.2, BC MBPP C++ 56.7) rather than MultiPL-E - which is why it was missed. BabelCode and MultiPL-E are different harnesses and the scores are NOT directly comparable; flag this if a reviewer compares 42.2 against Qwen's 75.6.  ||  Multi-line infill 20.05% vs single-line 68.25% is a large gap worth noting for retry-patching use.</t>
         </is>
       </c>
       <c r="AD30" s="17" t="inlineStr">
@@ -9909,7 +9910,7 @@
       </c>
       <c r="AF30" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Context 8K: VERIFIED - this is the disqualifier.</t>
+          <t>VERIFIED 2026-08-10. C++ figures DO exist under BabelCode (42.2) - earlier NOT PUBLISHED was wrong. Context 8K confirmed disqualifier.</t>
         </is>
       </c>
     </row>
@@ -9969,12 +9970,12 @@
       </c>
       <c r="L31" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 512 x NVIDIA H100-80GB, 10 days (Phi-3-mini figure)  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 512 x NVIDIA H100-80GB, 10 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M31" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2404.14219 - training section. NOTE this figure is for Phi-3-mini; the 3.5 refresh may differ. CHECK.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-mini-instruct model card, 'Training' section: 512 H100-80G GPUs for 10 days.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N31" s="21" t="n">
@@ -10046,7 +10047,7 @@
       </c>
       <c r="AC31" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/microsoft/Phi-3.5-mini-instruct - model card evaluation tables. The 3.5 refresh is documented on the card rather than in a separate paper. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-mini-instruct model card: HumanEval 62.8 (0-shot), MMLU 69 (5-shot), GSM8K 86.2 (8-shot CoT). The 3.5 refresh is documented on the card rather than in a separate paper, so the card is the primary source.</t>
         </is>
       </c>
       <c r="AD31" s="21" t="inlineStr">
@@ -10061,7 +10062,7 @@
       </c>
       <c r="AF31" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. All benchmarks and training HW confirmed against the model card.</t>
         </is>
       </c>
     </row>
@@ -10121,12 +10122,12 @@
       </c>
       <c r="L32" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 512 x NVIDIA H100-80GB, 10 days (Phi-3-mini figure)  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 512 x NVIDIA H100-80GB, 10 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2404.14219 - training section. NOTE this figure is for Phi-3-mini; the 3.5 refresh may differ. CHECK.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-mini-instruct model card, 'Training' section: 512 H100-80G GPUs for 10 days.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N32" s="21" t="n">
@@ -10198,7 +10199,7 @@
       </c>
       <c r="AC32" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/microsoft/Phi-3.5-mini-instruct - model card evaluation tables. The 3.5 refresh is documented on the card rather than in a separate paper. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-mini-instruct model card: HumanEval 62.8 (0-shot), MMLU 69 (5-shot), GSM8K 86.2 (8-shot CoT). The 3.5 refresh is documented on the card rather than in a separate paper, so the card is the primary source.</t>
         </is>
       </c>
       <c r="AD32" s="21" t="inlineStr">
@@ -10213,7 +10214,7 @@
       </c>
       <c r="AF32" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. All benchmarks and training HW confirmed against the model card.</t>
         </is>
       </c>
     </row>
@@ -10273,12 +10274,12 @@
       </c>
       <c r="L33" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 512 x NVIDIA H100-80GB, 10 days (Phi-3-mini figure)  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 512 x NVIDIA H100-80GB, 10 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M33" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2404.14219 - training section. NOTE this figure is for Phi-3-mini; the 3.5 refresh may differ. CHECK.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-mini-instruct model card, 'Training' section: 512 H100-80G GPUs for 10 days.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N33" s="21" t="n">
@@ -10350,7 +10351,7 @@
       </c>
       <c r="AC33" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/microsoft/Phi-3.5-mini-instruct - model card evaluation tables. The 3.5 refresh is documented on the card rather than in a separate paper. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-mini-instruct model card: HumanEval 62.8 (0-shot), MMLU 69 (5-shot), GSM8K 86.2 (8-shot CoT). The 3.5 refresh is documented on the card rather than in a separate paper, so the card is the primary source.</t>
         </is>
       </c>
       <c r="AD33" s="21" t="inlineStr">
@@ -10365,7 +10366,7 @@
       </c>
       <c r="AF33" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. All benchmarks and training HW confirmed against the model card.</t>
         </is>
       </c>
     </row>
@@ -10425,12 +10426,12 @@
       </c>
       <c r="L34" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 512 x NVIDIA H100-80GB, 10 days (Phi-3-mini figure)  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 512 x NVIDIA H100-80GB, 10 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2404.14219 - training section. NOTE this figure is for Phi-3-mini; the 3.5 refresh may differ. CHECK.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-mini-instruct model card, 'Training' section: 512 H100-80G GPUs for 10 days.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N34" s="21" t="n">
@@ -10502,7 +10503,7 @@
       </c>
       <c r="AC34" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/microsoft/Phi-3.5-mini-instruct - model card evaluation tables. The 3.5 refresh is documented on the card rather than in a separate paper. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-mini-instruct model card: HumanEval 62.8 (0-shot), MMLU 69 (5-shot), GSM8K 86.2 (8-shot CoT). The 3.5 refresh is documented on the card rather than in a separate paper, so the card is the primary source.</t>
         </is>
       </c>
       <c r="AD34" s="21" t="inlineStr">
@@ -10517,7 +10518,7 @@
       </c>
       <c r="AF34" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence/params/context: VERIFIED.</t>
+          <t>VERIFIED 2026-08-10. All benchmarks and training HW confirmed against the model card.</t>
         </is>
       </c>
     </row>
@@ -10544,12 +10545,12 @@
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>No country restriction in the licence text. TWO conditions apply: (a) Acceptable Use Policy prohibits certain applications, (b) if the product exceeds 700M monthly active users a separate licence must be requested from Meta. ADDITIONAL RESTRICTION: the Llama 3.2 licence excludes use by individuals or companies domiciled in the EU for the multimodal models. VERIFY whether this clause affects the text-only 3B before shipping in Europe. Origin: United States (Meta).</t>
+          <t>No country restriction in the licence text. TWO conditions apply: (a) Acceptable Use Policy prohibits certain applications, (b) if the product exceeds 700M monthly active users a separate licence must be requested from Meta. EU CLAUSE DOES NOT APPLY TO THIS MODEL. The Llama 3.2 EU territorial exclusion is scoped to MULTIMODAL models only; this is a text-only model and is unaffected. Origin: United States (Meta).</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  EU restriction: Llama 3.2 licence Acceptable Use / territory clause. THIS IS A REAL AND UNUSUAL CLAUSE - have legal read it directly, do not rely on this summary.</t>
+          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.2-3B-Instruct: the EU restriction is expressly limited to multimodal models. This text-only 3B is NOT restricted.  ||  CORRECTION: an earlier revision of this sheet flagged an EU concern on this model. That was over-cautious and is withdrawn.</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
@@ -10649,12 +10650,12 @@
       </c>
       <c r="AB35" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 57.8% | MMLU 63.4% | GSM8K 77.7%</t>
+          <t>MMLU 63.4% (macro avg) | GSM8K 77.7% (8-shot CoT) | HumanEval NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC35" s="15" t="inlineStr">
         <is>
-          <t>ai.meta.com/blog/llama-3-2-connect-2024-edge-mobile-devices/ and the HuggingFace model card evaluation table. No arXiv paper for 3.2. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.2-3B-Instruct model card.  ||  CORRECTION: an earlier revision listed HumanEval 57.8%. Meta does NOT publish a HumanEval figure for the 3B on the model card. That number has been REMOVED as unsourced. Do not reinstate it without a primary citation.  ||  Consequence: this model's code ability is UNMEASURED. It is an edge-deployment candidate on size grounds only.</t>
         </is>
       </c>
       <c r="AD35" s="17" t="inlineStr">
@@ -10667,9 +10668,9 @@
           <t>ExecuTorch: pytorch.org/executorch - Meta's own on-device runtime, Llama 3.2 is the reference example.  ||  llama.cpp: aarch64 NEON path documented in docs/build.md.  ||  MLC-LLM: llm.mlc.ai model library.</t>
         </is>
       </c>
-      <c r="AF35" s="24" t="inlineStr">
-        <is>
-          <t>EU licence clause: MUST BE VERIFIED BY LEGAL. Benchmarks: CHECK.</t>
+      <c r="AF35" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10. EU clause does NOT apply (text-only). HumanEval 57.8 REMOVED as unsourced - code ability unmeasured.</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10697,12 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>No country restriction in the licence text. TWO conditions apply: (a) Acceptable Use Policy prohibits certain applications, (b) if the product exceeds 700M monthly active users a separate licence must be requested from Meta. ADDITIONAL RESTRICTION: the Llama 3.2 licence excludes use by individuals or companies domiciled in the EU for the multimodal models. VERIFY whether this clause affects the text-only 3B before shipping in Europe. Origin: United States (Meta).</t>
+          <t>No country restriction in the licence text. TWO conditions apply: (a) Acceptable Use Policy prohibits certain applications, (b) if the product exceeds 700M monthly active users a separate licence must be requested from Meta. EU CLAUSE DOES NOT APPLY TO THIS MODEL. The Llama 3.2 EU territorial exclusion is scoped to MULTIMODAL models only; this is a text-only model and is unaffected. Origin: United States (Meta).</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  EU restriction: Llama 3.2 licence Acceptable Use / territory clause. THIS IS A REAL AND UNUSUAL CLAUSE - have legal read it directly, do not rely on this summary.</t>
+          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.2-3B-Instruct: the EU restriction is expressly limited to multimodal models. This text-only 3B is NOT restricted.  ||  CORRECTION: an earlier revision of this sheet flagged an EU concern on this model. That was over-cautious and is withdrawn.</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
@@ -10801,12 +10802,12 @@
       </c>
       <c r="AB36" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 57.8% | MMLU 63.4% | GSM8K 77.7%</t>
+          <t>MMLU 63.4% (macro avg) | GSM8K 77.7% (8-shot CoT) | HumanEval NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC36" s="15" t="inlineStr">
         <is>
-          <t>ai.meta.com/blog/llama-3-2-connect-2024-edge-mobile-devices/ and the HuggingFace model card evaluation table. No arXiv paper for 3.2. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.2-3B-Instruct model card.  ||  CORRECTION: an earlier revision listed HumanEval 57.8%. Meta does NOT publish a HumanEval figure for the 3B on the model card. That number has been REMOVED as unsourced. Do not reinstate it without a primary citation.  ||  Consequence: this model's code ability is UNMEASURED. It is an edge-deployment candidate on size grounds only.</t>
         </is>
       </c>
       <c r="AD36" s="17" t="inlineStr">
@@ -10819,9 +10820,9 @@
           <t>ExecuTorch: pytorch.org/executorch - Meta's own on-device runtime, Llama 3.2 is the reference example.  ||  llama.cpp: aarch64 NEON path documented in docs/build.md.  ||  MLC-LLM: llm.mlc.ai model library.</t>
         </is>
       </c>
-      <c r="AF36" s="24" t="inlineStr">
-        <is>
-          <t>EU licence clause: MUST BE VERIFIED BY LEGAL. Benchmarks: CHECK.</t>
+      <c r="AF36" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10. EU clause does NOT apply (text-only). HumanEval 57.8 REMOVED as unsourced - code ability unmeasured.</t>
         </is>
       </c>
     </row>
@@ -10848,12 +10849,12 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>No country restriction in the licence text. TWO conditions apply: (a) Acceptable Use Policy prohibits certain applications, (b) if the product exceeds 700M monthly active users a separate licence must be requested from Meta. ADDITIONAL RESTRICTION: the Llama 3.2 licence excludes use by individuals or companies domiciled in the EU for the multimodal models. VERIFY whether this clause affects the text-only 3B before shipping in Europe. Origin: United States (Meta).</t>
+          <t>No country restriction in the licence text. TWO conditions apply: (a) Acceptable Use Policy prohibits certain applications, (b) if the product exceeds 700M monthly active users a separate licence must be requested from Meta. EU CLAUSE DOES NOT APPLY TO THIS MODEL. The Llama 3.2 EU territorial exclusion is scoped to MULTIMODAL models only; this is a text-only model and is unaffected. Origin: United States (Meta).</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  EU restriction: Llama 3.2 licence Acceptable Use / territory clause. THIS IS A REAL AND UNUSUAL CLAUSE - have legal read it directly, do not rely on this summary.</t>
+          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.2-3B-Instruct: the EU restriction is expressly limited to multimodal models. This text-only 3B is NOT restricted.  ||  CORRECTION: an earlier revision of this sheet flagged an EU concern on this model. That was over-cautious and is withdrawn.</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
@@ -10953,12 +10954,12 @@
       </c>
       <c r="AB37" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 57.8% | MMLU 63.4% | GSM8K 77.7%</t>
+          <t>MMLU 63.4% (macro avg) | GSM8K 77.7% (8-shot CoT) | HumanEval NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC37" s="15" t="inlineStr">
         <is>
-          <t>ai.meta.com/blog/llama-3-2-connect-2024-edge-mobile-devices/ and the HuggingFace model card evaluation table. No arXiv paper for 3.2. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.2-3B-Instruct model card.  ||  CORRECTION: an earlier revision listed HumanEval 57.8%. Meta does NOT publish a HumanEval figure for the 3B on the model card. That number has been REMOVED as unsourced. Do not reinstate it without a primary citation.  ||  Consequence: this model's code ability is UNMEASURED. It is an edge-deployment candidate on size grounds only.</t>
         </is>
       </c>
       <c r="AD37" s="17" t="inlineStr">
@@ -10971,9 +10972,9 @@
           <t>ExecuTorch: pytorch.org/executorch - Meta's own on-device runtime, Llama 3.2 is the reference example.  ||  llama.cpp: aarch64 NEON path documented in docs/build.md.  ||  MLC-LLM: llm.mlc.ai model library.</t>
         </is>
       </c>
-      <c r="AF37" s="24" t="inlineStr">
-        <is>
-          <t>EU licence clause: MUST BE VERIFIED BY LEGAL. Benchmarks: CHECK.</t>
+      <c r="AF37" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10. EU clause does NOT apply (text-only). HumanEval 57.8 REMOVED as unsourced - code ability unmeasured.</t>
         </is>
       </c>
     </row>
@@ -11000,12 +11001,12 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>No country restriction in the licence text. TWO conditions apply: (a) Acceptable Use Policy prohibits certain applications, (b) if the product exceeds 700M monthly active users a separate licence must be requested from Meta. ADDITIONAL RESTRICTION: the Llama 3.2 licence excludes use by individuals or companies domiciled in the EU for the multimodal models. VERIFY whether this clause affects the text-only 3B before shipping in Europe. Origin: United States (Meta).</t>
+          <t>No country restriction in the licence text. TWO conditions apply: (a) Acceptable Use Policy prohibits certain applications, (b) if the product exceeds 700M monthly active users a separate licence must be requested from Meta. EU CLAUSE DOES NOT APPLY TO THIS MODEL. The Llama 3.2 EU territorial exclusion is scoped to MULTIMODAL models only; this is a text-only model and is unaffected. Origin: United States (Meta).</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  EU restriction: Llama 3.2 licence Acceptable Use / territory clause. THIS IS A REAL AND UNUSUAL CLAUSE - have legal read it directly, do not rely on this summary.</t>
+          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.2-3B-Instruct: the EU restriction is expressly limited to multimodal models. This text-only 3B is NOT restricted.  ||  CORRECTION: an earlier revision of this sheet flagged an EU concern on this model. That was over-cautious and is withdrawn.</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -11105,12 +11106,12 @@
       </c>
       <c r="AB38" s="17" t="inlineStr">
         <is>
-          <t>HumanEval 57.8% | MMLU 63.4% | GSM8K 77.7%</t>
+          <t>MMLU 63.4% (macro avg) | GSM8K 77.7% (8-shot CoT) | HumanEval NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC38" s="15" t="inlineStr">
         <is>
-          <t>ai.meta.com/blog/llama-3-2-connect-2024-edge-mobile-devices/ and the HuggingFace model card evaluation table. No arXiv paper for 3.2. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/meta-llama/Llama-3.2-3B-Instruct model card.  ||  CORRECTION: an earlier revision listed HumanEval 57.8%. Meta does NOT publish a HumanEval figure for the 3B on the model card. That number has been REMOVED as unsourced. Do not reinstate it without a primary citation.  ||  Consequence: this model's code ability is UNMEASURED. It is an edge-deployment candidate on size grounds only.</t>
         </is>
       </c>
       <c r="AD38" s="17" t="inlineStr">
@@ -11123,9 +11124,9 @@
           <t>ExecuTorch: pytorch.org/executorch - Meta's own on-device runtime, Llama 3.2 is the reference example.  ||  llama.cpp: aarch64 NEON path documented in docs/build.md.  ||  MLC-LLM: llm.mlc.ai model library.</t>
         </is>
       </c>
-      <c r="AF38" s="24" t="inlineStr">
-        <is>
-          <t>EU licence clause: MUST BE VERIFIED BY LEGAL. Benchmarks: CHECK.</t>
+      <c r="AF38" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10. EU clause does NOT apply (text-only). HumanEval 57.8 REMOVED as unsourced - code ability unmeasured.</t>
         </is>
       </c>
     </row>
@@ -14197,7 +14198,7 @@
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  EU multimodal exclusion: stated in the Llama 3.2 licence / Acceptable Use Policy. THIS IS THE SINGLE MOST IMPORTANT LEGAL LINE IN THIS SHEET - have counsel read the licence text directly.</t>
+          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  VERIFIED 2026-08-10, EXACT LICENCE WORDING: 'With respect to any multimodal models included in Llama 3.2, the rights granted under Section 1(a) of the Llama 3.2 Community License Agreement are not being granted to you if you are an individual domiciled in, or a company with a principal place of business in, the European Union.'  ||  CRITICAL EXCEPTION, also verbatim: 'This restriction does not apply to end users of a product or service that incorporates any such multimodal models.'  ||  PRACTICAL READING for ipoefgfefs: if the developing entity's principal place of business is outside the EU, the model may be used and the resulting product MAY be supplied to EU end users. If the developing entity is EU-domiciled, it is blocked. This turns on where ipo's contracting entity sits - a question for counsel, not for this sheet.</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
@@ -14317,7 +14318,7 @@
       </c>
       <c r="AF59" s="24" t="inlineStr">
         <is>
-          <t>EU MULTIMODAL EXCLUSION - MUST BE VERIFIED BY LEGAL BEFORE ANY EU DEPLOYMENT.</t>
+          <t>EU MULTIMODAL EXCLUSION VERIFIED VERBATIM 2026-08-10. Blocks EU-DOMICILED DEVELOPERS, not EU end users. Turns on where ipo contracts from - LEGAL DECISION.</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14350,7 @@
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  EU multimodal exclusion: stated in the Llama 3.2 licence / Acceptable Use Policy. THIS IS THE SINGLE MOST IMPORTANT LEGAL LINE IN THIS SHEET - have counsel read the licence text directly.</t>
+          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  VERIFIED 2026-08-10, EXACT LICENCE WORDING: 'With respect to any multimodal models included in Llama 3.2, the rights granted under Section 1(a) of the Llama 3.2 Community License Agreement are not being granted to you if you are an individual domiciled in, or a company with a principal place of business in, the European Union.'  ||  CRITICAL EXCEPTION, also verbatim: 'This restriction does not apply to end users of a product or service that incorporates any such multimodal models.'  ||  PRACTICAL READING for ipoefgfefs: if the developing entity's principal place of business is outside the EU, the model may be used and the resulting product MAY be supplied to EU end users. If the developing entity is EU-domiciled, it is blocked. This turns on where ipo's contracting entity sits - a question for counsel, not for this sheet.</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -14469,7 +14470,7 @@
       </c>
       <c r="AF60" s="24" t="inlineStr">
         <is>
-          <t>EU MULTIMODAL EXCLUSION - MUST BE VERIFIED BY LEGAL BEFORE ANY EU DEPLOYMENT.</t>
+          <t>EU MULTIMODAL EXCLUSION VERIFIED VERBATIM 2026-08-10. Blocks EU-DOMICILED DEVELOPERS, not EU end users. Turns on where ipo contracts from - LEGAL DECISION.</t>
         </is>
       </c>
     </row>
@@ -14501,7 +14502,7 @@
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  EU multimodal exclusion: stated in the Llama 3.2 licence / Acceptable Use Policy. THIS IS THE SINGLE MOST IMPORTANT LEGAL LINE IN THIS SHEET - have counsel read the licence text directly.</t>
+          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  VERIFIED 2026-08-10, EXACT LICENCE WORDING: 'With respect to any multimodal models included in Llama 3.2, the rights granted under Section 1(a) of the Llama 3.2 Community License Agreement are not being granted to you if you are an individual domiciled in, or a company with a principal place of business in, the European Union.'  ||  CRITICAL EXCEPTION, also verbatim: 'This restriction does not apply to end users of a product or service that incorporates any such multimodal models.'  ||  PRACTICAL READING for ipoefgfefs: if the developing entity's principal place of business is outside the EU, the model may be used and the resulting product MAY be supplied to EU end users. If the developing entity is EU-domiciled, it is blocked. This turns on where ipo's contracting entity sits - a question for counsel, not for this sheet.</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
@@ -14621,7 +14622,7 @@
       </c>
       <c r="AF61" s="24" t="inlineStr">
         <is>
-          <t>EU MULTIMODAL EXCLUSION - MUST BE VERIFIED BY LEGAL BEFORE ANY EU DEPLOYMENT.</t>
+          <t>EU MULTIMODAL EXCLUSION VERIFIED VERBATIM 2026-08-10. Blocks EU-DOMICILED DEVELOPERS, not EU end users. Turns on where ipo contracts from - LEGAL DECISION.</t>
         </is>
       </c>
     </row>
@@ -14653,7 +14654,7 @@
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  EU multimodal exclusion: stated in the Llama 3.2 licence / Acceptable Use Policy. THIS IS THE SINGLE MOST IMPORTANT LEGAL LINE IN THIS SHEET - have counsel read the licence text directly.</t>
+          <t>llama.com/llama3_3/license - Section 2 'Additional Commercial Terms' (700M MAU clause) and the linked Acceptable Use Policy at llama.com/llama3/use-policy. VERIFY the MAU threshold against the specific 3.1/3.2 licence version you ship under.  ||  VERIFIED 2026-08-10, EXACT LICENCE WORDING: 'With respect to any multimodal models included in Llama 3.2, the rights granted under Section 1(a) of the Llama 3.2 Community License Agreement are not being granted to you if you are an individual domiciled in, or a company with a principal place of business in, the European Union.'  ||  CRITICAL EXCEPTION, also verbatim: 'This restriction does not apply to end users of a product or service that incorporates any such multimodal models.'  ||  PRACTICAL READING for ipoefgfefs: if the developing entity's principal place of business is outside the EU, the model may be used and the resulting product MAY be supplied to EU end users. If the developing entity is EU-domiciled, it is blocked. This turns on where ipo's contracting entity sits - a question for counsel, not for this sheet.</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
@@ -14773,7 +14774,7 @@
       </c>
       <c r="AF62" s="24" t="inlineStr">
         <is>
-          <t>EU MULTIMODAL EXCLUSION - MUST BE VERIFIED BY LEGAL BEFORE ANY EU DEPLOYMENT.</t>
+          <t>EU MULTIMODAL EXCLUSION VERIFIED VERBATIM 2026-08-10. Blocks EU-DOMICILED DEVELOPERS, not EU end users. Turns on where ipo contracts from - LEGAL DECISION.</t>
         </is>
       </c>
     </row>
@@ -17544,246 +17545,531 @@
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="25" t="inlineStr">
-        <is>
-          <t>PRIMARY SOURCE INDEX</t>
+      <c r="A135" s="27" t="inlineStr">
+        <is>
+          <t>CORRECTIONS LOG - VERIFICATION PASS 2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="27" t="inlineStr">
-        <is>
-          <t>PAPER / DOCUMENT                                     COVERS                         LOCATION</t>
+      <c r="A136" s="26" t="inlineStr">
+        <is>
+          <t>Nine models were checked directly against their primary sources. SIX material errors were found in the</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="26" t="inlineStr">
         <is>
-          <t>Qwen2.5-Coder Technical Report                       Qwen2.5-Coder 7B               arxiv.org/abs/2409.12186</t>
+          <t>previous revision of this sheet and are corrected above. They are logged here rather than quietly fixed,</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="26" t="inlineStr">
         <is>
-          <t>Phi-4 Technical Report                               Phi-4 14B                      arxiv.org/abs/2412.08905</t>
+          <t>because two of them change the ranking.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="26" t="inlineStr">
-        <is>
-          <t>Phi-3 Technical Report                               Phi-3.5-mini, Phi-3.5-Vision   arxiv.org/abs/2404.14219</t>
-        </is>
-      </c>
+      <c r="A139" s="26" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="26" t="inlineStr">
         <is>
-          <t>The Llama 3 Herd of Models                           Llama 3.1 8B                   arxiv.org/abs/2407.21783</t>
+          <t xml:space="preserve">  1. Granite 3.3 8B HumanEval:  67.1%  -&gt;  89.73%     [source: IBM model card, Evaluation Results table]</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="26" t="inlineStr">
         <is>
-          <t>StarCoder 2 and The Stack v2                         StarCoder2 15B                 arxiv.org/abs/2402.19173</t>
+          <t xml:space="preserve">     IMPACT: HIGH. Granite now has the HIGHEST HumanEval in this sheet, above Qwen2.5-Coder's 88.4%.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-Coder-V2                                    DeepSeek-Coder-V2-Lite         arxiv.org/abs/2406.11931</t>
+          <t xml:space="preserve">     It is US-origin, Apache 2.0, has FIM and 128K context. It was ranked 3rd on a wrong number.</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="26" t="inlineStr">
-        <is>
-          <t>DeepSeek-R1                                          DeepSeek-R1-Distill-Qwen-14B   arxiv.org/abs/2501.12948</t>
-        </is>
-      </c>
+      <c r="A143" s="26" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="26" t="inlineStr">
         <is>
-          <t>Mistral 7B                                           Mistral 7B Instruct v0.3       arxiv.org/abs/2310.06825</t>
+          <t xml:space="preserve">  2. Qwen2.5-Coder 7B MultiPL-E C++:  63.4%  -&gt;  75.6%   [source: arxiv 2409.12186 Table 17]</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="26" t="inlineStr">
         <is>
-          <t>Gemma 3 Technical Report                             Gemma 3 4B                     arxiv.org/abs/2503.19786</t>
+          <t xml:space="preserve">     IMPACT: MEDIUM. Understated. Strengthens the existing rank-1 case rather than changing it.</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="26" t="inlineStr">
-        <is>
-          <t>Qwen2-VL                                             Qwen2-VL 7B                    arxiv.org/abs/2409.12191</t>
-        </is>
-      </c>
+      <c r="A146" s="26" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="26" t="inlineStr">
         <is>
-          <t>PaliGemma                                            PaliGemma 3B                   arxiv.org/abs/2407.07726</t>
+          <t xml:space="preserve">  3. DeepSeek-Coder-V2-Lite MultiPL-E C++:  56.5%  -&gt;  75.8%   [source: arxiv 2406.11931 Table 3]</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="26" t="inlineStr">
         <is>
-          <t>Improved Baselines with Visual Instruction Tuning    LLaVA-1.5 / 1.6                arxiv.org/abs/2310.03744</t>
+          <t xml:space="preserve">     IMPACT: HIGH. This is now the highest MEASURED C++ score in the sheet, marginally above Qwen.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="26" t="inlineStr">
         <is>
-          <t>HumanEval / Evaluating LLMs Trained on Code          HumanEval benchmark definition arxiv.org/abs/2107.03374</t>
+          <t xml:space="preserve">     Offset by a restrictive custom licence and immature MoE tooling in llama.cpp.</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="26" t="inlineStr">
-        <is>
-          <t>MultiPL-E                                            MultiPL-E C++ benchmark definition arxiv.org/abs/2208.08227</t>
-        </is>
-      </c>
+      <c r="A150" s="26" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="26" t="inlineStr">
         <is>
-          <t>MMLU / Measuring Massive Multitask Understanding     MMLU benchmark definition      arxiv.org/abs/2009.03300</t>
+          <t xml:space="preserve">  4. CodeGemma 7B C++:  'NOT PUBLISHED'  -&gt;  BabelCode-HumanEval C++ 42.2%, BabelCode-MBPP C++ 56.7%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="26" t="inlineStr">
         <is>
-          <t>MMMU                                                 MMMU benchmark definition      arxiv.org/abs/2311.16502</t>
+          <t xml:space="preserve">     [source: Google model card]. IMPACT: LOW - the model is already eliminated by its 8K context.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="26" t="inlineStr">
         <is>
-          <t>DocVQA                                               DocVQA benchmark definition    arxiv.org/abs/2007.00398</t>
+          <t xml:space="preserve">     Root cause: Google reports C++ under BabelCode, not MultiPL-E, so a MultiPL-E search missed it.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="26" t="inlineStr">
         <is>
-          <t>LoRA                                                 Fine-tuning method             arxiv.org/abs/2106.09685</t>
+          <t xml:space="preserve">     NOTE: BabelCode and MultiPL-E are different harnesses. 42.2 is NOT comparable to Qwen's 75.6.</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="26" t="inlineStr">
-        <is>
-          <t>QLoRA                                                Fine-tuning method             arxiv.org/abs/2305.14314</t>
-        </is>
-      </c>
+      <c r="A155" s="26" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="26" t="inlineStr">
         <is>
-          <t>vLLM / PagedAttention                                Inference engine               arxiv.org/abs/2309.06180</t>
+          <t xml:space="preserve">  5. Phi-4 GSM8K 91.5%:  REMOVED as unsourced.   [Microsoft publishes MGSM 80.6%, not GSM8K]</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="26" t="inlineStr">
         <is>
-          <t>SGLang / RadixAttention                              Inference engine               arxiv.org/abs/2312.07104</t>
+          <t xml:space="preserve">     IMPACT: LOW. Phi-4's case rests on HumanEval 82.6 and MMLU 84.8, both confirmed.</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="26" t="inlineStr">
-        <is>
-          <t>llama.cpp - supported backends and build docs        ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
-        </is>
-      </c>
+      <c r="A158" s="26" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="26" t="inlineStr">
         <is>
-          <t>llama.cpp k-quants PR #1684                          ALL quantization accuracy deltas github.com/ggml-org/llama.cpp/pull/1684</t>
+          <t xml:space="preserve">  6. Llama 3.2 3B HumanEval 57.8%:  REMOVED as unsourced.   [Meta publishes no HumanEval for the 3B]</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA Ada GPU Architecture Whitepaper               RTX 4090 memory bandwidth (1008 GB/s) nvidia.com - Ada whitepaper</t>
+          <t xml:space="preserve">     IMPACT: MEDIUM. The edge candidate's code ability is UNMEASURED. It qualifies on size, not skill.</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="26" t="inlineStr">
-        <is>
-          <t>Apache License 2.0                                   Licence text                   apache.org/licenses/LICENSE-2.0</t>
-        </is>
-      </c>
+      <c r="A161" s="26" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="26" t="inlineStr">
         <is>
-          <t>Llama 3.x Community Licence                          Licence text incl. EU multimodal clause llama.com/llama3_3/license</t>
+          <t>TWO LICENCE FINDINGS, both narrower than previously stated:</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="26" t="inlineStr">
-        <is>
-          <t>Gemma Terms of Use                                   Licence text                   ai.google.dev/gemma/terms</t>
-        </is>
-      </c>
+      <c r="A163" s="26" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="26" t="inlineStr">
         <is>
-          <t>BigCode OpenRAIL-M v1                                Licence text incl. flow-down duty bigcode-project.org/docs/pages/model-license</t>
+          <t xml:space="preserve">  7. Llama 3.2 EU exclusion applies to MULTIMODAL models ONLY. The text-only 3B is unaffected -</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek Model Licence                               Licence text incl. use restrictions github.com/deepseek-ai/DeepSeek-LLM</t>
+          <t xml:space="preserve">     the previous flag on it is WITHDRAWN as over-cautious.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="26" t="inlineStr">
         <is>
-          <t>NDAA Section 889 / FAR 52.204-25                     Component-origin procurement rule acquisition.gov/far/52.204-25</t>
+          <t xml:space="preserve">  8. For the 11B Vision, the exclusion binds EU-DOMICILED DEVELOPERS, and expressly does NOT bind</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="26" t="inlineStr">
         <is>
-          <t>EvalPlus Leaderboard                                 Mistral 7B HumanEval (no paper exists) evalplus.github.io/leaderboard.html</t>
+          <t xml:space="preserve">     end users of a product incorporating the model. A non-EU entity may build with it and supply</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="26" t="inlineStr">
         <is>
+          <t xml:space="preserve">     EU customers. Exact licence wording is quoted in that model's Countries - SOURCE cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="26" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="26" t="inlineStr">
+        <is>
+          <t>CONFIRMED CORRECT, no change: Phi-4 (HumanEval 82.6, MMLU 84.8, MATH 80.4, 1920xH100 for 21 days),</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="26" t="inlineStr">
+        <is>
+          <t>Phi-3.5-mini (62.8 / 69 / 86.2, 512xH100 for 10 days), Llama 3.1 8B (HumanEval 72.6, GSM8K 84.5,</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="26" t="inlineStr">
+        <is>
+          <t>1.46M GPU-hours), Granite MMLU 65.54 and GSM8K 80.89, Qwen HumanEval 88.4 and MBPP 83.5,</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek HumanEval 81.1 and MBPP+ 68.8, Llama 3.2 3B MMLU 63.4 and GSM8K 77.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="26" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="26" t="inlineStr">
+        <is>
+          <t>ONE DISAMBIGUATION: Llama 3.1 8B MMLU is 69.4% standard 5-shot; the 73.0% previously quoted is the</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="26" t="inlineStr">
+        <is>
+          <t>chain-of-thought variant. Both are now shown so it is not compared unfairly against standard-metric models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="26" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="26" t="inlineStr">
+        <is>
+          <t>STILL UNVERIFIED - the remaining CHECK cells:</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  StarCoder2 15B (paper HTML would not yield the MultiPL-E table - needs the PDF read manually),</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mistral 7B, Gemma 3 4B, DeepSeek-R1-Distill-14B, and all seven vision models except where noted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  These are lower-stakes: none of them is in the shortlist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="25" t="inlineStr">
+        <is>
+          <t>PRIMARY SOURCE INDEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="28" t="inlineStr">
+        <is>
+          <t>PAPER / DOCUMENT                                     COVERS                         LOCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2.5-Coder Technical Report                       Qwen2.5-Coder 7B               arxiv.org/abs/2409.12186</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="26" t="inlineStr">
+        <is>
+          <t>Phi-4 Technical Report                               Phi-4 14B                      arxiv.org/abs/2412.08905</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="26" t="inlineStr">
+        <is>
+          <t>Phi-3 Technical Report                               Phi-3.5-mini, Phi-3.5-Vision   arxiv.org/abs/2404.14219</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="26" t="inlineStr">
+        <is>
+          <t>The Llama 3 Herd of Models                           Llama 3.1 8B                   arxiv.org/abs/2407.21783</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="26" t="inlineStr">
+        <is>
+          <t>StarCoder 2 and The Stack v2                         StarCoder2 15B                 arxiv.org/abs/2402.19173</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-Coder-V2                                    DeepSeek-Coder-V2-Lite         arxiv.org/abs/2406.11931</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-R1                                          DeepSeek-R1-Distill-Qwen-14B   arxiv.org/abs/2501.12948</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="26" t="inlineStr">
+        <is>
+          <t>Mistral 7B                                           Mistral 7B Instruct v0.3       arxiv.org/abs/2310.06825</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="26" t="inlineStr">
+        <is>
+          <t>Gemma 3 Technical Report                             Gemma 3 4B                     arxiv.org/abs/2503.19786</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2-VL                                             Qwen2-VL 7B                    arxiv.org/abs/2409.12191</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="26" t="inlineStr">
+        <is>
+          <t>PaliGemma                                            PaliGemma 3B                   arxiv.org/abs/2407.07726</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="26" t="inlineStr">
+        <is>
+          <t>Improved Baselines with Visual Instruction Tuning    LLaVA-1.5 / 1.6                arxiv.org/abs/2310.03744</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="26" t="inlineStr">
+        <is>
+          <t>HumanEval / Evaluating LLMs Trained on Code          HumanEval benchmark definition arxiv.org/abs/2107.03374</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="26" t="inlineStr">
+        <is>
+          <t>MultiPL-E                                            MultiPL-E C++ benchmark definition arxiv.org/abs/2208.08227</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="26" t="inlineStr">
+        <is>
+          <t>MMLU / Measuring Massive Multitask Understanding     MMLU benchmark definition      arxiv.org/abs/2009.03300</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="26" t="inlineStr">
+        <is>
+          <t>MMMU                                                 MMMU benchmark definition      arxiv.org/abs/2311.16502</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="26" t="inlineStr">
+        <is>
+          <t>DocVQA                                               DocVQA benchmark definition    arxiv.org/abs/2007.00398</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="26" t="inlineStr">
+        <is>
+          <t>LoRA                                                 Fine-tuning method             arxiv.org/abs/2106.09685</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="26" t="inlineStr">
+        <is>
+          <t>QLoRA                                                Fine-tuning method             arxiv.org/abs/2305.14314</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="26" t="inlineStr">
+        <is>
+          <t>vLLM / PagedAttention                                Inference engine               arxiv.org/abs/2309.06180</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="26" t="inlineStr">
+        <is>
+          <t>SGLang / RadixAttention                              Inference engine               arxiv.org/abs/2312.07104</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp - supported backends and build docs        ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp k-quants PR #1684                          ALL quantization accuracy deltas github.com/ggml-org/llama.cpp/pull/1684</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="26" t="inlineStr">
+        <is>
+          <t>NVIDIA Ada GPU Architecture Whitepaper               RTX 4090 memory bandwidth (1008 GB/s) nvidia.com - Ada whitepaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="26" t="inlineStr">
+        <is>
+          <t>Apache License 2.0                                   Licence text                   apache.org/licenses/LICENSE-2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="26" t="inlineStr">
+        <is>
+          <t>Llama 3.x Community Licence                          Licence text incl. EU multimodal clause llama.com/llama3_3/license</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="26" t="inlineStr">
+        <is>
+          <t>Gemma Terms of Use                                   Licence text                   ai.google.dev/gemma/terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="26" t="inlineStr">
+        <is>
+          <t>BigCode OpenRAIL-M v1                                Licence text incl. flow-down duty bigcode-project.org/docs/pages/model-license</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek Model Licence                               Licence text incl. use restrictions github.com/deepseek-ai/DeepSeek-LLM</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="26" t="inlineStr">
+        <is>
+          <t>NDAA Section 889 / FAR 52.204-25                     Component-origin procurement rule acquisition.gov/far/52.204-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="26" t="inlineStr">
+        <is>
+          <t>EvalPlus Leaderboard                                 Mistral 7B HumanEval (no paper exists) evalplus.github.io/leaderboard.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="26" t="inlineStr">
+        <is>
           <t>OpenCompass Multimodal Leaderboard                   InternVL2 (partly leaderboard-sourced) rank.opencompass.org.cn/leaderboard-multimodal</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:AF78"/>
-  <mergeCells count="89">
+  <mergeCells count="136">
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="A80:AF80"/>
     <mergeCell ref="A81:AF81"/>
@@ -17873,6 +18159,53 @@
     <mergeCell ref="A166:AF166"/>
     <mergeCell ref="A167:AF167"/>
     <mergeCell ref="A168:AF168"/>
+    <mergeCell ref="A169:AF169"/>
+    <mergeCell ref="A170:AF170"/>
+    <mergeCell ref="A171:AF171"/>
+    <mergeCell ref="A172:AF172"/>
+    <mergeCell ref="A173:AF173"/>
+    <mergeCell ref="A174:AF174"/>
+    <mergeCell ref="A175:AF175"/>
+    <mergeCell ref="A176:AF176"/>
+    <mergeCell ref="A177:AF177"/>
+    <mergeCell ref="A178:AF178"/>
+    <mergeCell ref="A179:AF179"/>
+    <mergeCell ref="A180:AF180"/>
+    <mergeCell ref="A181:AF181"/>
+    <mergeCell ref="A183:AF183"/>
+    <mergeCell ref="A184:AF184"/>
+    <mergeCell ref="A185:AF185"/>
+    <mergeCell ref="A186:AF186"/>
+    <mergeCell ref="A187:AF187"/>
+    <mergeCell ref="A188:AF188"/>
+    <mergeCell ref="A189:AF189"/>
+    <mergeCell ref="A190:AF190"/>
+    <mergeCell ref="A191:AF191"/>
+    <mergeCell ref="A192:AF192"/>
+    <mergeCell ref="A193:AF193"/>
+    <mergeCell ref="A194:AF194"/>
+    <mergeCell ref="A195:AF195"/>
+    <mergeCell ref="A196:AF196"/>
+    <mergeCell ref="A197:AF197"/>
+    <mergeCell ref="A198:AF198"/>
+    <mergeCell ref="A199:AF199"/>
+    <mergeCell ref="A200:AF200"/>
+    <mergeCell ref="A201:AF201"/>
+    <mergeCell ref="A202:AF202"/>
+    <mergeCell ref="A203:AF203"/>
+    <mergeCell ref="A204:AF204"/>
+    <mergeCell ref="A205:AF205"/>
+    <mergeCell ref="A206:AF206"/>
+    <mergeCell ref="A207:AF207"/>
+    <mergeCell ref="A208:AF208"/>
+    <mergeCell ref="A209:AF209"/>
+    <mergeCell ref="A210:AF210"/>
+    <mergeCell ref="A211:AF211"/>
+    <mergeCell ref="A212:AF212"/>
+    <mergeCell ref="A213:AF213"/>
+    <mergeCell ref="A214:AF214"/>
+    <mergeCell ref="A215:AF215"/>
+    <mergeCell ref="A216:AF216"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipoefgfefs_SLM_Matrix.xlsx
+++ b/ipoefgfefs_SLM_Matrix.xlsx
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -252,6 +252,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -631,8 +632,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="42" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
@@ -693,12 +694,12 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>tok/s CPU</t>
+          <t>tok/s CPU (est.)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>tok/s GPU</t>
+          <t>tok/s GPU (est.)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -761,7 +762,7 @@
         <v>11.2</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>164.1</v>
+        <v>138.3</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
@@ -823,7 +824,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>135.7</v>
+        <v>114.4</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
@@ -885,7 +886,7 @@
         <v>5.9</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>87.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
@@ -947,7 +948,7 @@
         <v>3.2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>46.4</v>
+        <v>39.1</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -1009,7 +1010,7 @@
         <v>5.9</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>86</v>
+        <v>72.5</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1071,7 +1072,7 @@
         <v>4.8</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>69.90000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -1133,7 +1134,7 @@
         <v>3.1</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>45.2</v>
+        <v>38.1</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1195,7 +1196,7 @@
         <v>1.6</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>24</v>
+        <v>20.2</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -1257,7 +1258,7 @@
         <v>10.7</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>156.8</v>
+        <v>132.2</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
@@ -1319,7 +1320,7 @@
         <v>8.6</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>126</v>
+        <v>106.2</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
@@ -1381,7 +1382,7 @@
         <v>5.6</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>82</v>
+        <v>69.2</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
@@ -1443,7 +1444,7 @@
         <v>3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>43.6</v>
+        <v>36.7</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
@@ -1505,7 +1506,7 @@
         <v>10.7</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>156.8</v>
+        <v>132.2</v>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
@@ -1567,7 +1568,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>128.3</v>
+        <v>108.1</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -1629,7 +1630,7 @@
         <v>5.6</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -1691,7 +1692,7 @@
         <v>3</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>44.1</v>
+        <v>37.2</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -1753,7 +1754,7 @@
         <v>5.5</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>80.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
@@ -1815,7 +1816,7 @@
         <v>4.4</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>65.3</v>
+        <v>55.1</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
@@ -1877,7 +1878,7 @@
         <v>2.9</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>42.5</v>
+        <v>35.8</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
@@ -1939,7 +1940,7 @@
         <v>1.5</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>22.5</v>
+        <v>18.9</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
@@ -2001,7 +2002,7 @@
         <v>5.3</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>78.40000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -2010,7 +2011,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 46.4% | MultiPL-E C++ 41.4%</t>
+          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
@@ -2063,7 +2064,7 @@
         <v>4.4</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>64.09999999999999</v>
+        <v>54.1</v>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
@@ -2072,7 +2073,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 46.4% | MultiPL-E C++ 41.4%</t>
+          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
@@ -2125,7 +2126,7 @@
         <v>2.8</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>41.5</v>
+        <v>35</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -2134,7 +2135,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 46.4% | MultiPL-E C++ 41.4%</t>
+          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
@@ -2187,7 +2188,7 @@
         <v>1.5</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>22</v>
+        <v>18.6</v>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
@@ -2196,7 +2197,7 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 46.4% | MultiPL-E C++ 41.4%</t>
+          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
@@ -2249,7 +2250,7 @@
         <v>10</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>147</v>
+        <v>123.9</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
@@ -2311,7 +2312,7 @@
         <v>8.1</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>119.6</v>
+        <v>100.8</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
@@ -2373,7 +2374,7 @@
         <v>5.3</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>78.40000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
@@ -2435,7 +2436,7 @@
         <v>2.8</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>41.5</v>
+        <v>35</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
@@ -2497,7 +2498,7 @@
         <v>22.9</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>336</v>
+        <v>283.2</v>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
@@ -2559,7 +2560,7 @@
         <v>18.5</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>271.4</v>
+        <v>228.7</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -2621,7 +2622,7 @@
         <v>12</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>176.4</v>
+        <v>148.7</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -2683,7 +2684,7 @@
         <v>6.3</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>92.8</v>
+        <v>78.3</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -2745,7 +2746,7 @@
         <v>26.7</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>392</v>
+        <v>330.4</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
@@ -2807,7 +2808,7 @@
         <v>21.8</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>320.7</v>
+        <v>270.3</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
@@ -2869,7 +2870,7 @@
         <v>14.1</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>207.5</v>
+        <v>174.9</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
@@ -2931,7 +2932,7 @@
         <v>7.5</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>110.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
@@ -2993,7 +2994,7 @@
         <v>12</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>176.4</v>
+        <v>148.7</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -3055,7 +3056,7 @@
         <v>9.6</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>141.1</v>
+        <v>118.9</v>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
@@ -3117,7 +3118,7 @@
         <v>6.3</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>92.8</v>
+        <v>78.3</v>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
@@ -3179,7 +3180,7 @@
         <v>3.3</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>49</v>
+        <v>41.3</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -3241,7 +3242,7 @@
         <v>5.8</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>85</v>
+        <v>71.7</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
@@ -3250,7 +3251,7 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>MATH-500 93.9% | AIME 2024 69.7% | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
+          <t>MATH-500 93.9% | AIME 2024 69.7% | GPQA Diamond 59.1% | LiveCodeBench 53.1% | Codeforces rating 1481 | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
@@ -3303,7 +3304,7 @@
         <v>4.7</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>69.2</v>
+        <v>58.3</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
@@ -3312,7 +3313,7 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>MATH-500 93.9% | AIME 2024 69.7% | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
+          <t>MATH-500 93.9% | AIME 2024 69.7% | GPQA Diamond 59.1% | LiveCodeBench 53.1% | Codeforces rating 1481 | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
@@ -3365,7 +3366,7 @@
         <v>3.1</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>44.9</v>
+        <v>37.9</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
@@ -3374,7 +3375,7 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>MATH-500 93.9% | AIME 2024 69.7% | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
+          <t>MATH-500 93.9% | AIME 2024 69.7% | GPQA Diamond 59.1% | LiveCodeBench 53.1% | Codeforces rating 1481 | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
@@ -3427,7 +3428,7 @@
         <v>1.6</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>23.8</v>
+        <v>20.1</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
@@ -3436,7 +3437,7 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>MATH-500 93.9% | AIME 2024 69.7% | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
+          <t>MATH-500 93.9% | AIME 2024 69.7% | GPQA Diamond 59.1% | LiveCodeBench 53.1% | Codeforces rating 1481 | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
@@ -3482,14 +3483,14 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>131,072</t>
+          <t>131,072 input / 8,192 output</t>
         </is>
       </c>
       <c r="J47" s="8" t="n">
         <v>20</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>294</v>
+        <v>247.8</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -3498,7 +3499,7 @@
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 36.0% | MMLU 59.6%</t>
+          <t>HumanEval 36.0% (0-shot) | MMLU 59.6% (5-shot) | MBPP 46.0% (3-shot) | MMMU 39.2% | GSM8K 38.4% (8-shot) | MATH 24.2% (4-shot)</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
@@ -3544,14 +3545,14 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>131,072</t>
+          <t>131,072 input / 8,192 output</t>
         </is>
       </c>
       <c r="J48" s="8" t="n">
         <v>16</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>235.2</v>
+        <v>198.2</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -3560,7 +3561,7 @@
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 36.0% | MMLU 59.6%</t>
+          <t>HumanEval 36.0% (0-shot) | MMLU 59.6% (5-shot) | MBPP 46.0% (3-shot) | MMMU 39.2% | GSM8K 38.4% (8-shot) | MATH 24.2% (4-shot)</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
@@ -3606,14 +3607,14 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>131,072</t>
+          <t>131,072 input / 8,192 output</t>
         </is>
       </c>
       <c r="J49" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>153.4</v>
+        <v>129.3</v>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
@@ -3622,7 +3623,7 @@
       </c>
       <c r="M49" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 36.0% | MMLU 59.6%</t>
+          <t>HumanEval 36.0% (0-shot) | MMLU 59.6% (5-shot) | MBPP 46.0% (3-shot) | MMMU 39.2% | GSM8K 38.4% (8-shot) | MATH 24.2% (4-shot)</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
@@ -3668,14 +3669,14 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>131,072</t>
+          <t>131,072 input / 8,192 output</t>
         </is>
       </c>
       <c r="J50" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>82</v>
+        <v>69.2</v>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
@@ -3684,7 +3685,7 @@
       </c>
       <c r="M50" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 36.0% | MMLU 59.6%</t>
+          <t>HumanEval 36.0% (0-shot) | MMLU 59.6% (5-shot) | MBPP 46.0% (3-shot) | MMMU 39.2% | GSM8K 38.4% (8-shot) | MATH 24.2% (4-shot)</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
@@ -3737,7 +3738,7 @@
         <v>10.4</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>153.4</v>
+        <v>129.3</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
@@ -3746,7 +3747,7 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>MMMU 54.1% | DocVQA 94.5% | MathVista 58.2%</t>
+          <t>DocVQA 94.5% (test) | TextVQA 84.3% (val) | MathVista 58.2% (testmini) | MMMU 54.1% (val)</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
@@ -3799,7 +3800,7 @@
         <v>8.4</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>123.8</v>
+        <v>104.3</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
@@ -3808,7 +3809,7 @@
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>MMMU 54.1% | DocVQA 94.5% | MathVista 58.2%</t>
+          <t>DocVQA 94.5% (test) | TextVQA 84.3% (val) | MathVista 58.2% (testmini) | MMMU 54.1% (val)</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr">
@@ -3861,7 +3862,7 @@
         <v>5.5</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>80.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
@@ -3870,7 +3871,7 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>MMMU 54.1% | DocVQA 94.5% | MathVista 58.2%</t>
+          <t>DocVQA 94.5% (test) | TextVQA 84.3% (val) | MathVista 58.2% (testmini) | MMMU 54.1% (val)</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr">
@@ -3923,7 +3924,7 @@
         <v>2.9</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>42.5</v>
+        <v>35.8</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
@@ -3932,7 +3933,7 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>MMMU 54.1% | DocVQA 94.5% | MathVista 58.2%</t>
+          <t>DocVQA 94.5% (test) | TextVQA 84.3% (val) | MathVista 58.2% (testmini) | MMMU 54.1% (val)</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr">
@@ -3985,7 +3986,7 @@
         <v>20</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>294</v>
+        <v>247.8</v>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
@@ -4047,7 +4048,7 @@
         <v>16.6</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>243.3</v>
+        <v>205.1</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -4109,7 +4110,7 @@
         <v>10.7</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>156.8</v>
+        <v>132.2</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -4171,7 +4172,7 @@
         <v>5.7</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>84</v>
+        <v>70.8</v>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
@@ -4233,7 +4234,7 @@
         <v>8.1</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>119.6</v>
+        <v>100.8</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
@@ -4242,7 +4243,7 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>MMMU 50.7% | DocVQA 88.4% | ChartQA 83.4%</t>
+          <t>AI2 Diagram 91.1% | DocVQA 88.4% ANLS (test) | ChartQA 83.4% (test, CoT) | VQAv2 75.2% (test) | MMMU 50.7% (0-shot, CoT)</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr">
@@ -4295,7 +4296,7 @@
         <v>6.6</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>96.7</v>
+        <v>81.5</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
@@ -4304,7 +4305,7 @@
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>MMMU 50.7% | DocVQA 88.4% | ChartQA 83.4%</t>
+          <t>AI2 Diagram 91.1% | DocVQA 88.4% ANLS (test) | ChartQA 83.4% (test, CoT) | VQAv2 75.2% (test) | MMMU 50.7% (0-shot, CoT)</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr">
@@ -4357,7 +4358,7 @@
         <v>4.3</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>63</v>
+        <v>53.1</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
@@ -4366,7 +4367,7 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>MMMU 50.7% | DocVQA 88.4% | ChartQA 83.4%</t>
+          <t>AI2 Diagram 91.1% | DocVQA 88.4% ANLS (test) | ChartQA 83.4% (test, CoT) | VQAv2 75.2% (test) | MMMU 50.7% (0-shot, CoT)</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr">
@@ -4419,7 +4420,7 @@
         <v>2.3</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>33.3</v>
+        <v>28.1</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
@@ -4428,7 +4429,7 @@
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>MMMU 50.7% | DocVQA 88.4% | ChartQA 83.4%</t>
+          <t>AI2 Diagram 91.1% | DocVQA 88.4% ANLS (test) | ChartQA 83.4% (test, CoT) | VQAv2 75.2% (test) | MMMU 50.7% (0-shot, CoT)</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr">
@@ -4481,7 +4482,7 @@
         <v>10.7</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>156.8</v>
+        <v>132.2</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -4490,7 +4491,7 @@
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
-          <t>MMBench 81.7% | MMMU 51.2% | DocVQA 91.6%</t>
+          <t>MMBench-EN 81.7% | DocVQA 91.6% | MMMU 51.8%</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr">
@@ -4543,7 +4544,7 @@
         <v>8.6</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>126</v>
+        <v>106.2</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -4552,7 +4553,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>MMBench 81.7% | MMMU 51.2% | DocVQA 91.6%</t>
+          <t>MMBench-EN 81.7% | DocVQA 91.6% | MMMU 51.8%</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr">
@@ -4605,7 +4606,7 @@
         <v>5.6</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>82</v>
+        <v>69.2</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -4614,7 +4615,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>MMBench 81.7% | MMMU 51.2% | DocVQA 91.6%</t>
+          <t>MMBench-EN 81.7% | DocVQA 91.6% | MMMU 51.8%</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
@@ -4667,7 +4668,7 @@
         <v>3</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>43.6</v>
+        <v>36.7</v>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
@@ -4676,7 +4677,7 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>MMBench 81.7% | MMMU 51.2% | DocVQA 91.6%</t>
+          <t>MMBench-EN 81.7% | DocVQA 91.6% | MMMU 51.8%</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
@@ -4693,7 +4694,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Apache 2.0 (code) - CHECK base weights  (FULL)</t>
+          <t>Llama 2 Community License  (FULL)</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -4729,7 +4730,7 @@
         <v>6.4</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>94.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
@@ -4755,7 +4756,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Apache 2.0 (code) - CHECK base weights  (FULL)</t>
+          <t>Llama 2 Community License  (FULL)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -4791,7 +4792,7 @@
         <v>5.2</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>76.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
@@ -4817,7 +4818,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Apache 2.0 (code) - CHECK base weights  (FULL)</t>
+          <t>Llama 2 Community License  (FULL)</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -4853,7 +4854,7 @@
         <v>3.4</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>49.7</v>
+        <v>41.9</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
@@ -4879,7 +4880,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Apache 2.0 (code) - CHECK base weights  (FULL)</t>
+          <t>Llama 2 Community License  (FULL)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -4915,7 +4916,7 @@
         <v>1.8</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>26.3</v>
+        <v>22.2</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
@@ -4970,14 +4971,14 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>8,192</t>
+          <t>512 tokens (input + output)</t>
         </is>
       </c>
       <c r="J71" s="8" t="n">
         <v>30</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>441</v>
+        <v>371.7</v>
       </c>
       <c r="L71" s="8" t="inlineStr">
         <is>
@@ -4986,7 +4987,7 @@
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
-          <t>COCO CIDEr 141.9 | VQAv2 85.6% | TextVQA 73.2%</t>
+          <t>VQAv2 85.64% | DocVQA 78.02% ANLS | TextVQA 73.15% | POPE 89.37% | MMVP 45.33% (ALL FINE-TUNED, NOT ZERO-SHOT)</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
@@ -5032,14 +5033,14 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>8,192</t>
+          <t>512 tokens (input + output)</t>
         </is>
       </c>
       <c r="J72" s="8" t="n">
         <v>24</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>352.8</v>
+        <v>297.4</v>
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
@@ -5048,7 +5049,7 @@
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>COCO CIDEr 141.9 | VQAv2 85.6% | TextVQA 73.2%</t>
+          <t>VQAv2 85.64% | DocVQA 78.02% ANLS | TextVQA 73.15% | POPE 89.37% | MMVP 45.33% (ALL FINE-TUNED, NOT ZERO-SHOT)</t>
         </is>
       </c>
       <c r="N72" s="8" t="inlineStr">
@@ -5094,14 +5095,14 @@
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>8,192</t>
+          <t>512 tokens (input + output)</t>
         </is>
       </c>
       <c r="J73" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>227.6</v>
+        <v>191.8</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -5110,7 +5111,7 @@
       </c>
       <c r="M73" s="8" t="inlineStr">
         <is>
-          <t>COCO CIDEr 141.9 | VQAv2 85.6% | TextVQA 73.2%</t>
+          <t>VQAv2 85.64% | DocVQA 78.02% ANLS | TextVQA 73.15% | POPE 89.37% | MMVP 45.33% (ALL FINE-TUNED, NOT ZERO-SHOT)</t>
         </is>
       </c>
       <c r="N73" s="8" t="inlineStr">
@@ -5156,14 +5157,14 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>8,192</t>
+          <t>512 tokens (input + output)</t>
         </is>
       </c>
       <c r="J74" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>121.7</v>
+        <v>102.5</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -5172,7 +5173,7 @@
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>COCO CIDEr 141.9 | VQAv2 85.6% | TextVQA 73.2%</t>
+          <t>VQAv2 85.64% | DocVQA 78.02% ANLS | TextVQA 73.15% | POPE 89.37% | MMVP 45.33% (ALL FINE-TUNED, NOT ZERO-SHOT)</t>
         </is>
       </c>
       <c r="N74" s="8" t="inlineStr">
@@ -5194,7 +5195,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>1.86B dense (SigLIP vision + Phi-1.5-derived language)</t>
+          <t>2B dense (SigLIP vision + Phi-1.5-derived language)</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -5225,7 +5226,7 @@
         <v>43.6</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>641.5</v>
+        <v>540.7</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
@@ -5234,7 +5235,7 @@
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>VQAv2 79.4% | TextVQA 60.2% | DocVQA 61.9%</t>
+          <t>DocVQA 79.3% | TextVQA 76.3% | ChartQA 77.5% (82.2% with PoT) | CountBenchQA 86.4% | OCRBench 61.2% | COCO object detection 51.2% | ScreenSpot F1@0.5 80.4%</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
@@ -5256,7 +5257,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>1.86B dense (SigLIP vision + Phi-1.5-derived language)</t>
+          <t>2B dense (SigLIP vision + Phi-1.5-derived language)</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -5265,7 +5266,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
@@ -5273,10 +5274,10 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
@@ -5284,10 +5285,10 @@
         </is>
       </c>
       <c r="J76" s="5" t="n">
-        <v>36.9</v>
+        <v>34.3</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>542.8</v>
+        <v>424.8</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
@@ -5296,7 +5297,7 @@
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>VQAv2 79.4% | TextVQA 60.2% | DocVQA 61.9%</t>
+          <t>DocVQA 79.3% | TextVQA 76.3% | ChartQA 77.5% (82.2% with PoT) | CountBenchQA 86.4% | OCRBench 61.2% | COCO object detection 51.2% | ScreenSpot F1@0.5 80.4%</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr">
@@ -5318,7 +5319,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>1.86B dense (SigLIP vision + Phi-1.5-derived language)</t>
+          <t>2B dense (SigLIP vision + Phi-1.5-derived language)</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -5327,7 +5328,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -5335,10 +5336,10 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
@@ -5346,10 +5347,10 @@
         </is>
       </c>
       <c r="J77" s="5" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>352.8</v>
+        <v>283.2</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
@@ -5358,7 +5359,7 @@
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>VQAv2 79.4% | TextVQA 60.2% | DocVQA 61.9%</t>
+          <t>DocVQA 79.3% | TextVQA 76.3% | ChartQA 77.5% (82.2% with PoT) | CountBenchQA 86.4% | OCRBench 61.2% | COCO object detection 51.2% | ScreenSpot F1@0.5 80.4%</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
@@ -5380,7 +5381,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>1.86B dense (SigLIP vision + Phi-1.5-derived language)</t>
+          <t>2B dense (SigLIP vision + Phi-1.5-derived language)</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -5389,7 +5390,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
@@ -5397,10 +5398,10 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
@@ -5408,10 +5409,10 @@
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>185.7</v>
+        <v>148.7</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
@@ -5420,7 +5421,7 @@
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>VQAv2 79.4% | TextVQA 60.2% | DocVQA 61.9%</t>
+          <t>DocVQA 79.3% | TextVQA 76.3% | ChartQA 77.5% (82.2% with PoT) | CountBenchQA 86.4% | OCRBench 61.2% | COCO object detection 51.2% | ScreenSpot F1@0.5 80.4%</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr">
@@ -5452,7 +5453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF216"/>
+  <dimension ref="A1:AF330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5474,10 +5475,10 @@
     <col width="50" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="54" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="48" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="23" max="23"/>
     <col width="34" customWidth="1" min="24" max="24"/>
     <col width="50" customWidth="1" min="25" max="25"/>
     <col width="40" customWidth="1" min="26" max="26"/>
@@ -5594,7 +5595,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>tok/s CPU</t>
+          <t>tok/s CPU (est.)</t>
         </is>
       </c>
       <c r="U2" s="12" t="inlineStr">
@@ -5604,7 +5605,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>tok/s GPU</t>
+          <t>tok/s GPU (est.)</t>
         </is>
       </c>
       <c r="W2" s="12" t="inlineStr">
@@ -5753,15 +5754,15 @@
       </c>
       <c r="U3" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V3" s="17" t="n">
-        <v>164.1</v>
+        <v>138.3</v>
       </c>
       <c r="W3" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X3" s="17" t="inlineStr">
@@ -5905,15 +5906,15 @@
       </c>
       <c r="U4" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V4" s="17" t="n">
-        <v>135.7</v>
+        <v>114.4</v>
       </c>
       <c r="W4" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X4" s="17" t="inlineStr">
@@ -6057,15 +6058,15 @@
       </c>
       <c r="U5" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V5" s="17" t="n">
-        <v>87.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="W5" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X5" s="17" t="inlineStr">
@@ -6209,15 +6210,15 @@
       </c>
       <c r="U6" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V6" s="17" t="n">
-        <v>46.4</v>
+        <v>39.1</v>
       </c>
       <c r="W6" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X6" s="17" t="inlineStr">
@@ -6361,15 +6362,15 @@
       </c>
       <c r="U7" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V7" s="21" t="n">
-        <v>86</v>
+        <v>72.5</v>
       </c>
       <c r="W7" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X7" s="21" t="inlineStr">
@@ -6513,15 +6514,15 @@
       </c>
       <c r="U8" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V8" s="21" t="n">
-        <v>69.90000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="W8" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X8" s="21" t="inlineStr">
@@ -6665,15 +6666,15 @@
       </c>
       <c r="U9" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V9" s="21" t="n">
-        <v>45.2</v>
+        <v>38.1</v>
       </c>
       <c r="W9" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X9" s="21" t="inlineStr">
@@ -6817,15 +6818,15 @@
       </c>
       <c r="U10" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V10" s="21" t="n">
-        <v>24</v>
+        <v>20.2</v>
       </c>
       <c r="W10" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X10" s="21" t="inlineStr">
@@ -6969,15 +6970,15 @@
       </c>
       <c r="U11" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V11" s="17" t="n">
-        <v>156.8</v>
+        <v>132.2</v>
       </c>
       <c r="W11" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X11" s="17" t="inlineStr">
@@ -7121,15 +7122,15 @@
       </c>
       <c r="U12" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V12" s="17" t="n">
-        <v>126</v>
+        <v>106.2</v>
       </c>
       <c r="W12" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X12" s="17" t="inlineStr">
@@ -7273,15 +7274,15 @@
       </c>
       <c r="U13" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V13" s="17" t="n">
-        <v>82</v>
+        <v>69.2</v>
       </c>
       <c r="W13" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X13" s="17" t="inlineStr">
@@ -7425,15 +7426,15 @@
       </c>
       <c r="U14" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V14" s="17" t="n">
-        <v>43.6</v>
+        <v>36.7</v>
       </c>
       <c r="W14" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X14" s="17" t="inlineStr">
@@ -7577,15 +7578,15 @@
       </c>
       <c r="U15" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V15" s="21" t="n">
-        <v>156.8</v>
+        <v>132.2</v>
       </c>
       <c r="W15" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X15" s="21" t="inlineStr">
@@ -7729,15 +7730,15 @@
       </c>
       <c r="U16" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V16" s="21" t="n">
-        <v>128.3</v>
+        <v>108.1</v>
       </c>
       <c r="W16" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X16" s="21" t="inlineStr">
@@ -7881,15 +7882,15 @@
       </c>
       <c r="U17" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V17" s="21" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="W17" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X17" s="21" t="inlineStr">
@@ -8033,15 +8034,15 @@
       </c>
       <c r="U18" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V18" s="21" t="n">
-        <v>44.1</v>
+        <v>37.2</v>
       </c>
       <c r="W18" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X18" s="21" t="inlineStr">
@@ -8185,15 +8186,15 @@
       </c>
       <c r="U19" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V19" s="17" t="n">
-        <v>80.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="W19" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X19" s="17" t="inlineStr">
@@ -8337,15 +8338,15 @@
       </c>
       <c r="U20" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V20" s="17" t="n">
-        <v>65.3</v>
+        <v>55.1</v>
       </c>
       <c r="W20" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X20" s="17" t="inlineStr">
@@ -8489,15 +8490,15 @@
       </c>
       <c r="U21" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V21" s="17" t="n">
-        <v>42.5</v>
+        <v>35.8</v>
       </c>
       <c r="W21" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X21" s="17" t="inlineStr">
@@ -8641,15 +8642,15 @@
       </c>
       <c r="U22" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V22" s="17" t="n">
-        <v>22.5</v>
+        <v>18.9</v>
       </c>
       <c r="W22" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X22" s="17" t="inlineStr">
@@ -8754,12 +8755,12 @@
       </c>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1024 x NVIDIA A100-80GB  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1024 x NVIDIA H100, 4+ trillion tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2402.19173 - training-infrastructure section. CHECK exact GPU count.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card: 1024 x H100, 4+ trillion training tokens.  ||  CORRECTION: an earlier revision said A100-80GB. That was WRONG - StarCoder2 was trained on H100s.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N23" s="21" t="n">
@@ -8793,15 +8794,15 @@
       </c>
       <c r="U23" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V23" s="21" t="n">
-        <v>78.40000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="W23" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X23" s="21" t="inlineStr">
@@ -8826,12 +8827,12 @@
       </c>
       <c r="AB23" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 46.4% | MultiPL-E C++ 41.4%</t>
+          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
         </is>
       </c>
       <c r="AC23" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2402.19173 - evaluation tables. MultiPL-E is reported per-language in this paper, which is unusual and useful. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card.  ||  CORRECTION: HumanEval is 46.3%, not 46.4% as previously stated.  ||  STILL UNVERIFIED: the MultiPL-E C++ 41.4% figure is NOT on the model card and could not be extracted from the arXiv HTML - it needs a manual read of the 2402.19173 PDF, Section 7.1.2 (MultiPL-E). Treat 41.4 as unconfirmed.  ||  RepoBench 74.08% is repository-level edit similarity - the most relevant published number here for retry-patching behaviour.</t>
         </is>
       </c>
       <c r="AD23" s="21" t="inlineStr">
@@ -8846,7 +8847,7 @@
       </c>
       <c r="AF23" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence: VERIFIED - note the flow-down obligation.</t>
+          <t>MOSTLY VERIFIED 2026-08-10. HumanEval corrected to 46.3, training HW corrected to H100. MultiPL-E C++ 41.4 REMAINS UNVERIFIED - needs manual PDF read.</t>
         </is>
       </c>
     </row>
@@ -8906,12 +8907,12 @@
       </c>
       <c r="L24" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1024 x NVIDIA A100-80GB  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1024 x NVIDIA H100, 4+ trillion tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2402.19173 - training-infrastructure section. CHECK exact GPU count.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card: 1024 x H100, 4+ trillion training tokens.  ||  CORRECTION: an earlier revision said A100-80GB. That was WRONG - StarCoder2 was trained on H100s.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N24" s="21" t="n">
@@ -8945,15 +8946,15 @@
       </c>
       <c r="U24" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V24" s="21" t="n">
-        <v>64.09999999999999</v>
+        <v>54.1</v>
       </c>
       <c r="W24" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X24" s="21" t="inlineStr">
@@ -8978,12 +8979,12 @@
       </c>
       <c r="AB24" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 46.4% | MultiPL-E C++ 41.4%</t>
+          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
         </is>
       </c>
       <c r="AC24" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2402.19173 - evaluation tables. MultiPL-E is reported per-language in this paper, which is unusual and useful. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card.  ||  CORRECTION: HumanEval is 46.3%, not 46.4% as previously stated.  ||  STILL UNVERIFIED: the MultiPL-E C++ 41.4% figure is NOT on the model card and could not be extracted from the arXiv HTML - it needs a manual read of the 2402.19173 PDF, Section 7.1.2 (MultiPL-E). Treat 41.4 as unconfirmed.  ||  RepoBench 74.08% is repository-level edit similarity - the most relevant published number here for retry-patching behaviour.</t>
         </is>
       </c>
       <c r="AD24" s="21" t="inlineStr">
@@ -8998,7 +8999,7 @@
       </c>
       <c r="AF24" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence: VERIFIED - note the flow-down obligation.</t>
+          <t>MOSTLY VERIFIED 2026-08-10. HumanEval corrected to 46.3, training HW corrected to H100. MultiPL-E C++ 41.4 REMAINS UNVERIFIED - needs manual PDF read.</t>
         </is>
       </c>
     </row>
@@ -9058,12 +9059,12 @@
       </c>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1024 x NVIDIA A100-80GB  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1024 x NVIDIA H100, 4+ trillion tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2402.19173 - training-infrastructure section. CHECK exact GPU count.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card: 1024 x H100, 4+ trillion training tokens.  ||  CORRECTION: an earlier revision said A100-80GB. That was WRONG - StarCoder2 was trained on H100s.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N25" s="21" t="n">
@@ -9097,15 +9098,15 @@
       </c>
       <c r="U25" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V25" s="21" t="n">
-        <v>41.5</v>
+        <v>35</v>
       </c>
       <c r="W25" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X25" s="21" t="inlineStr">
@@ -9130,12 +9131,12 @@
       </c>
       <c r="AB25" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 46.4% | MultiPL-E C++ 41.4%</t>
+          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
         </is>
       </c>
       <c r="AC25" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2402.19173 - evaluation tables. MultiPL-E is reported per-language in this paper, which is unusual and useful. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card.  ||  CORRECTION: HumanEval is 46.3%, not 46.4% as previously stated.  ||  STILL UNVERIFIED: the MultiPL-E C++ 41.4% figure is NOT on the model card and could not be extracted from the arXiv HTML - it needs a manual read of the 2402.19173 PDF, Section 7.1.2 (MultiPL-E). Treat 41.4 as unconfirmed.  ||  RepoBench 74.08% is repository-level edit similarity - the most relevant published number here for retry-patching behaviour.</t>
         </is>
       </c>
       <c r="AD25" s="21" t="inlineStr">
@@ -9150,7 +9151,7 @@
       </c>
       <c r="AF25" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence: VERIFIED - note the flow-down obligation.</t>
+          <t>MOSTLY VERIFIED 2026-08-10. HumanEval corrected to 46.3, training HW corrected to H100. MultiPL-E C++ 41.4 REMAINS UNVERIFIED - needs manual PDF read.</t>
         </is>
       </c>
     </row>
@@ -9210,12 +9211,12 @@
       </c>
       <c r="L26" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1024 x NVIDIA A100-80GB  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1024 x NVIDIA H100, 4+ trillion tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2402.19173 - training-infrastructure section. CHECK exact GPU count.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card: 1024 x H100, 4+ trillion training tokens.  ||  CORRECTION: an earlier revision said A100-80GB. That was WRONG - StarCoder2 was trained on H100s.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N26" s="21" t="n">
@@ -9249,15 +9250,15 @@
       </c>
       <c r="U26" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V26" s="21" t="n">
-        <v>22</v>
+        <v>18.6</v>
       </c>
       <c r="W26" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X26" s="21" t="inlineStr">
@@ -9282,12 +9283,12 @@
       </c>
       <c r="AB26" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 46.4% | MultiPL-E C++ 41.4%</t>
+          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
         </is>
       </c>
       <c r="AC26" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2402.19173 - evaluation tables. MultiPL-E is reported per-language in this paper, which is unusual and useful. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card.  ||  CORRECTION: HumanEval is 46.3%, not 46.4% as previously stated.  ||  STILL UNVERIFIED: the MultiPL-E C++ 41.4% figure is NOT on the model card and could not be extracted from the arXiv HTML - it needs a manual read of the 2402.19173 PDF, Section 7.1.2 (MultiPL-E). Treat 41.4 as unconfirmed.  ||  RepoBench 74.08% is repository-level edit similarity - the most relevant published number here for retry-patching behaviour.</t>
         </is>
       </c>
       <c r="AD26" s="21" t="inlineStr">
@@ -9302,7 +9303,7 @@
       </c>
       <c r="AF26" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence: VERIFIED - note the flow-down obligation.</t>
+          <t>MOSTLY VERIFIED 2026-08-10. HumanEval corrected to 46.3, training HW corrected to H100. MultiPL-E C++ 41.4 REMAINS UNVERIFIED - needs manual PDF read.</t>
         </is>
       </c>
     </row>
@@ -9401,15 +9402,15 @@
       </c>
       <c r="U27" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V27" s="17" t="n">
-        <v>147</v>
+        <v>123.9</v>
       </c>
       <c r="W27" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X27" s="17" t="inlineStr">
@@ -9553,15 +9554,15 @@
       </c>
       <c r="U28" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V28" s="17" t="n">
-        <v>119.6</v>
+        <v>100.8</v>
       </c>
       <c r="W28" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X28" s="17" t="inlineStr">
@@ -9705,15 +9706,15 @@
       </c>
       <c r="U29" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V29" s="17" t="n">
-        <v>78.40000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="W29" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X29" s="17" t="inlineStr">
@@ -9857,15 +9858,15 @@
       </c>
       <c r="U30" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V30" s="17" t="n">
-        <v>41.5</v>
+        <v>35</v>
       </c>
       <c r="W30" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X30" s="17" t="inlineStr">
@@ -10009,15 +10010,15 @@
       </c>
       <c r="U31" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V31" s="21" t="n">
-        <v>336</v>
+        <v>283.2</v>
       </c>
       <c r="W31" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X31" s="21" t="inlineStr">
@@ -10161,15 +10162,15 @@
       </c>
       <c r="U32" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V32" s="21" t="n">
-        <v>271.4</v>
+        <v>228.7</v>
       </c>
       <c r="W32" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X32" s="21" t="inlineStr">
@@ -10313,15 +10314,15 @@
       </c>
       <c r="U33" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V33" s="21" t="n">
-        <v>176.4</v>
+        <v>148.7</v>
       </c>
       <c r="W33" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X33" s="21" t="inlineStr">
@@ -10465,15 +10466,15 @@
       </c>
       <c r="U34" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V34" s="21" t="n">
-        <v>92.8</v>
+        <v>78.3</v>
       </c>
       <c r="W34" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X34" s="21" t="inlineStr">
@@ -10617,15 +10618,15 @@
       </c>
       <c r="U35" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V35" s="17" t="n">
-        <v>392</v>
+        <v>330.4</v>
       </c>
       <c r="W35" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X35" s="17" t="inlineStr">
@@ -10769,15 +10770,15 @@
       </c>
       <c r="U36" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V36" s="17" t="n">
-        <v>320.7</v>
+        <v>270.3</v>
       </c>
       <c r="W36" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X36" s="17" t="inlineStr">
@@ -10921,15 +10922,15 @@
       </c>
       <c r="U37" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V37" s="17" t="n">
-        <v>207.5</v>
+        <v>174.9</v>
       </c>
       <c r="W37" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X37" s="17" t="inlineStr">
@@ -11073,15 +11074,15 @@
       </c>
       <c r="U38" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V38" s="17" t="n">
-        <v>110.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W38" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X38" s="17" t="inlineStr">
@@ -11225,15 +11226,15 @@
       </c>
       <c r="U39" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V39" s="21" t="n">
-        <v>176.4</v>
+        <v>148.7</v>
       </c>
       <c r="W39" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X39" s="21" t="inlineStr">
@@ -11263,7 +11264,7 @@
       </c>
       <c r="AC39" s="15" t="inlineStr">
         <is>
-          <t>MMLU: arxiv 2310.06825 results table.  ||  HumanEval: THE PAPER DOES NOT REPORT IT. Value taken from evalplus.github.io/leaderboard.html - a third-party leaderboard, weaker evidence than a paper. Flag this explicitly in review.</t>
+          <t>VERIFIED 2026-08-10: huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores AT ALL. The card covers installation, usage and function calling only.  ||  MMLU 62.5% comes from arxiv 2310.06825 (the v0.1 paper), NOT from the v0.3 card - be careful, these are different model versions.  ||  HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard. NO PRIMARY SOURCE EXISTS. This is the weakest-evidenced model in the sheet.</t>
         </is>
       </c>
       <c r="AD39" s="21" t="inlineStr">
@@ -11278,7 +11279,7 @@
       </c>
       <c r="AF39" s="18" t="inlineStr">
         <is>
-          <t>HumanEval is leaderboard-sourced, NOT from the paper. Everything else: VERIFIED/CHECK.</t>
+          <t>VERIFIED 2026-08-10: the v0.3 model card publishes NO benchmarks whatsoever. MMLU is from the v0.1 paper, HumanEval from a leaderboard. WEAKEST EVIDENCE IN SHEET.</t>
         </is>
       </c>
     </row>
@@ -11377,15 +11378,15 @@
       </c>
       <c r="U40" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V40" s="21" t="n">
-        <v>141.1</v>
+        <v>118.9</v>
       </c>
       <c r="W40" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X40" s="21" t="inlineStr">
@@ -11415,7 +11416,7 @@
       </c>
       <c r="AC40" s="15" t="inlineStr">
         <is>
-          <t>MMLU: arxiv 2310.06825 results table.  ||  HumanEval: THE PAPER DOES NOT REPORT IT. Value taken from evalplus.github.io/leaderboard.html - a third-party leaderboard, weaker evidence than a paper. Flag this explicitly in review.</t>
+          <t>VERIFIED 2026-08-10: huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores AT ALL. The card covers installation, usage and function calling only.  ||  MMLU 62.5% comes from arxiv 2310.06825 (the v0.1 paper), NOT from the v0.3 card - be careful, these are different model versions.  ||  HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard. NO PRIMARY SOURCE EXISTS. This is the weakest-evidenced model in the sheet.</t>
         </is>
       </c>
       <c r="AD40" s="21" t="inlineStr">
@@ -11430,7 +11431,7 @@
       </c>
       <c r="AF40" s="18" t="inlineStr">
         <is>
-          <t>HumanEval is leaderboard-sourced, NOT from the paper. Everything else: VERIFIED/CHECK.</t>
+          <t>VERIFIED 2026-08-10: the v0.3 model card publishes NO benchmarks whatsoever. MMLU is from the v0.1 paper, HumanEval from a leaderboard. WEAKEST EVIDENCE IN SHEET.</t>
         </is>
       </c>
     </row>
@@ -11529,15 +11530,15 @@
       </c>
       <c r="U41" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V41" s="21" t="n">
-        <v>92.8</v>
+        <v>78.3</v>
       </c>
       <c r="W41" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X41" s="21" t="inlineStr">
@@ -11567,7 +11568,7 @@
       </c>
       <c r="AC41" s="15" t="inlineStr">
         <is>
-          <t>MMLU: arxiv 2310.06825 results table.  ||  HumanEval: THE PAPER DOES NOT REPORT IT. Value taken from evalplus.github.io/leaderboard.html - a third-party leaderboard, weaker evidence than a paper. Flag this explicitly in review.</t>
+          <t>VERIFIED 2026-08-10: huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores AT ALL. The card covers installation, usage and function calling only.  ||  MMLU 62.5% comes from arxiv 2310.06825 (the v0.1 paper), NOT from the v0.3 card - be careful, these are different model versions.  ||  HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard. NO PRIMARY SOURCE EXISTS. This is the weakest-evidenced model in the sheet.</t>
         </is>
       </c>
       <c r="AD41" s="21" t="inlineStr">
@@ -11582,7 +11583,7 @@
       </c>
       <c r="AF41" s="18" t="inlineStr">
         <is>
-          <t>HumanEval is leaderboard-sourced, NOT from the paper. Everything else: VERIFIED/CHECK.</t>
+          <t>VERIFIED 2026-08-10: the v0.3 model card publishes NO benchmarks whatsoever. MMLU is from the v0.1 paper, HumanEval from a leaderboard. WEAKEST EVIDENCE IN SHEET.</t>
         </is>
       </c>
     </row>
@@ -11681,15 +11682,15 @@
       </c>
       <c r="U42" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V42" s="21" t="n">
-        <v>49</v>
+        <v>41.3</v>
       </c>
       <c r="W42" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X42" s="21" t="inlineStr">
@@ -11719,7 +11720,7 @@
       </c>
       <c r="AC42" s="15" t="inlineStr">
         <is>
-          <t>MMLU: arxiv 2310.06825 results table.  ||  HumanEval: THE PAPER DOES NOT REPORT IT. Value taken from evalplus.github.io/leaderboard.html - a third-party leaderboard, weaker evidence than a paper. Flag this explicitly in review.</t>
+          <t>VERIFIED 2026-08-10: huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores AT ALL. The card covers installation, usage and function calling only.  ||  MMLU 62.5% comes from arxiv 2310.06825 (the v0.1 paper), NOT from the v0.3 card - be careful, these are different model versions.  ||  HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard. NO PRIMARY SOURCE EXISTS. This is the weakest-evidenced model in the sheet.</t>
         </is>
       </c>
       <c r="AD42" s="21" t="inlineStr">
@@ -11734,7 +11735,7 @@
       </c>
       <c r="AF42" s="18" t="inlineStr">
         <is>
-          <t>HumanEval is leaderboard-sourced, NOT from the paper. Everything else: VERIFIED/CHECK.</t>
+          <t>VERIFIED 2026-08-10: the v0.3 model card publishes NO benchmarks whatsoever. MMLU is from the v0.1 paper, HumanEval from a leaderboard. WEAKEST EVIDENCE IN SHEET.</t>
         </is>
       </c>
     </row>
@@ -11833,15 +11834,15 @@
       </c>
       <c r="U43" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V43" s="17" t="n">
-        <v>85</v>
+        <v>71.7</v>
       </c>
       <c r="W43" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X43" s="17" t="inlineStr">
@@ -11866,12 +11867,12 @@
       </c>
       <c r="AB43" s="17" t="inlineStr">
         <is>
-          <t>MATH-500 93.9% | AIME 2024 69.7% | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
+          <t>MATH-500 93.9% | AIME 2024 69.7% | GPQA Diamond 59.1% | LiveCodeBench 53.1% | Codeforces rating 1481 | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC43" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2501.12948 - distilled-model comparison table. CHECK exact table number.  ||  NOTE: no code benchmark is published for this distill, so its C++ ability is UNKNOWN. Do not assume it inherits Qwen2.5-Coder ability - the base is Qwen2.5 general, not Coder.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/deepseek-ai/DeepSeek-R1-Distill-Qwen-14B model card.  ||  CORRECTION: an earlier revision said no code benchmark was published and its code ability was UNKNOWN. That was WRONG - the card publishes LiveCodeBench 53.1% and a Codeforces rating of 1481.  ||  CAVEAT THAT STILL STANDS: HumanEval and MultiPL-E C++ are NOT published, and the base is Qwen2.5 general, NOT Qwen2.5-Coder. Do not assume it inherits coder-tuned C++ ability.</t>
         </is>
       </c>
       <c r="AD43" s="17" t="inlineStr">
@@ -11886,7 +11887,7 @@
       </c>
       <c r="AF43" s="24" t="inlineStr">
         <is>
-          <t>Code ability UNKNOWN - no code benchmark published. Benchmarks: CHECK.</t>
+          <t>VERIFIED 2026-08-10. Code ability IS measured (LiveCodeBench 53.1) - earlier UNKNOWN was wrong. HumanEval/C++ still unpublished.</t>
         </is>
       </c>
     </row>
@@ -11985,15 +11986,15 @@
       </c>
       <c r="U44" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V44" s="17" t="n">
-        <v>69.2</v>
+        <v>58.3</v>
       </c>
       <c r="W44" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X44" s="17" t="inlineStr">
@@ -12018,12 +12019,12 @@
       </c>
       <c r="AB44" s="17" t="inlineStr">
         <is>
-          <t>MATH-500 93.9% | AIME 2024 69.7% | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
+          <t>MATH-500 93.9% | AIME 2024 69.7% | GPQA Diamond 59.1% | LiveCodeBench 53.1% | Codeforces rating 1481 | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC44" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2501.12948 - distilled-model comparison table. CHECK exact table number.  ||  NOTE: no code benchmark is published for this distill, so its C++ ability is UNKNOWN. Do not assume it inherits Qwen2.5-Coder ability - the base is Qwen2.5 general, not Coder.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/deepseek-ai/DeepSeek-R1-Distill-Qwen-14B model card.  ||  CORRECTION: an earlier revision said no code benchmark was published and its code ability was UNKNOWN. That was WRONG - the card publishes LiveCodeBench 53.1% and a Codeforces rating of 1481.  ||  CAVEAT THAT STILL STANDS: HumanEval and MultiPL-E C++ are NOT published, and the base is Qwen2.5 general, NOT Qwen2.5-Coder. Do not assume it inherits coder-tuned C++ ability.</t>
         </is>
       </c>
       <c r="AD44" s="17" t="inlineStr">
@@ -12038,7 +12039,7 @@
       </c>
       <c r="AF44" s="24" t="inlineStr">
         <is>
-          <t>Code ability UNKNOWN - no code benchmark published. Benchmarks: CHECK.</t>
+          <t>VERIFIED 2026-08-10. Code ability IS measured (LiveCodeBench 53.1) - earlier UNKNOWN was wrong. HumanEval/C++ still unpublished.</t>
         </is>
       </c>
     </row>
@@ -12137,15 +12138,15 @@
       </c>
       <c r="U45" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V45" s="17" t="n">
-        <v>44.9</v>
+        <v>37.9</v>
       </c>
       <c r="W45" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X45" s="17" t="inlineStr">
@@ -12170,12 +12171,12 @@
       </c>
       <c r="AB45" s="17" t="inlineStr">
         <is>
-          <t>MATH-500 93.9% | AIME 2024 69.7% | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
+          <t>MATH-500 93.9% | AIME 2024 69.7% | GPQA Diamond 59.1% | LiveCodeBench 53.1% | Codeforces rating 1481 | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC45" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2501.12948 - distilled-model comparison table. CHECK exact table number.  ||  NOTE: no code benchmark is published for this distill, so its C++ ability is UNKNOWN. Do not assume it inherits Qwen2.5-Coder ability - the base is Qwen2.5 general, not Coder.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/deepseek-ai/DeepSeek-R1-Distill-Qwen-14B model card.  ||  CORRECTION: an earlier revision said no code benchmark was published and its code ability was UNKNOWN. That was WRONG - the card publishes LiveCodeBench 53.1% and a Codeforces rating of 1481.  ||  CAVEAT THAT STILL STANDS: HumanEval and MultiPL-E C++ are NOT published, and the base is Qwen2.5 general, NOT Qwen2.5-Coder. Do not assume it inherits coder-tuned C++ ability.</t>
         </is>
       </c>
       <c r="AD45" s="17" t="inlineStr">
@@ -12190,7 +12191,7 @@
       </c>
       <c r="AF45" s="24" t="inlineStr">
         <is>
-          <t>Code ability UNKNOWN - no code benchmark published. Benchmarks: CHECK.</t>
+          <t>VERIFIED 2026-08-10. Code ability IS measured (LiveCodeBench 53.1) - earlier UNKNOWN was wrong. HumanEval/C++ still unpublished.</t>
         </is>
       </c>
     </row>
@@ -12289,15 +12290,15 @@
       </c>
       <c r="U46" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V46" s="17" t="n">
-        <v>23.8</v>
+        <v>20.1</v>
       </c>
       <c r="W46" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X46" s="17" t="inlineStr">
@@ -12322,12 +12323,12 @@
       </c>
       <c r="AB46" s="17" t="inlineStr">
         <is>
-          <t>MATH-500 93.9% | AIME 2024 69.7% | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
+          <t>MATH-500 93.9% | AIME 2024 69.7% | GPQA Diamond 59.1% | LiveCodeBench 53.1% | Codeforces rating 1481 | HumanEval NOT PUBLISHED | MMLU NOT PUBLISHED</t>
         </is>
       </c>
       <c r="AC46" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2501.12948 - distilled-model comparison table. CHECK exact table number.  ||  NOTE: no code benchmark is published for this distill, so its C++ ability is UNKNOWN. Do not assume it inherits Qwen2.5-Coder ability - the base is Qwen2.5 general, not Coder.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/deepseek-ai/DeepSeek-R1-Distill-Qwen-14B model card.  ||  CORRECTION: an earlier revision said no code benchmark was published and its code ability was UNKNOWN. That was WRONG - the card publishes LiveCodeBench 53.1% and a Codeforces rating of 1481.  ||  CAVEAT THAT STILL STANDS: HumanEval and MultiPL-E C++ are NOT published, and the base is Qwen2.5 general, NOT Qwen2.5-Coder. Do not assume it inherits coder-tuned C++ ability.</t>
         </is>
       </c>
       <c r="AD46" s="17" t="inlineStr">
@@ -12342,7 +12343,7 @@
       </c>
       <c r="AF46" s="24" t="inlineStr">
         <is>
-          <t>Code ability UNKNOWN - no code benchmark published. Benchmarks: CHECK.</t>
+          <t>VERIFIED 2026-08-10. Code ability IS measured (LiveCodeBench 53.1) - earlier UNKNOWN was wrong. HumanEval/C++ still unpublished.</t>
         </is>
       </c>
     </row>
@@ -12402,12 +12403,12 @@
       </c>
       <c r="L47" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: Google TPUv5p  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: Google TPUv4p, TPUv5p and TPUv5e  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2503.19786 - training-infrastructure section. CHECK.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it model card: TPUv4p, TPUv5p and TPUv5e.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N47" s="21" t="n">
@@ -12428,12 +12429,12 @@
       </c>
       <c r="R47" s="21" t="inlineStr">
         <is>
-          <t>131,072</t>
+          <t>131,072 input / 8,192 output</t>
         </is>
       </c>
       <c r="S47" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/google/gemma-3-4b-it - model card states 128K for the 4B and above; config.json max_position_embeddings = 131072.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it: 128K token INPUT context but an 8,192 token OUTPUT limit. The output cap is a separate constraint from the context window and is not a problem for ipoefgfefs (generated blocks are ~80 lines), but note it before assuming 128K end to end.</t>
         </is>
       </c>
       <c r="T47" s="21" t="n">
@@ -12441,15 +12442,15 @@
       </c>
       <c r="U47" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V47" s="21" t="n">
-        <v>294</v>
+        <v>247.8</v>
       </c>
       <c r="W47" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X47" s="21" t="inlineStr">
@@ -12474,12 +12475,12 @@
       </c>
       <c r="AB47" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 36.0% | MMLU 59.6%</t>
+          <t>HumanEval 36.0% (0-shot) | MMLU 59.6% (5-shot) | MBPP 46.0% (3-shot) | MMMU 39.2% | GSM8K 38.4% (8-shot) | MATH 24.2% (4-shot)</t>
         </is>
       </c>
       <c r="AC47" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2503.19786 - evaluation tables. CHECK exact table number.  ||  NOTE the low HumanEval: multimodal capability at 4B comes at a real cost to code ability.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it model card evaluation table.  ||  NOTE the low code and math scores: multimodal capability at 4B costs real ground on code ability. HumanEval 36.0 and GSM8K 38.4 are the weakest in this sheet among instruct models.</t>
         </is>
       </c>
       <c r="AD47" s="21" t="inlineStr">
@@ -12494,7 +12495,7 @@
       </c>
       <c r="AF47" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence: VERIFIED - Terms of Use, not open source.</t>
+          <t>VERIFIED 2026-08-10. All benchmarks, training TPUs and the 8K output cap confirmed against the model card.</t>
         </is>
       </c>
     </row>
@@ -12554,12 +12555,12 @@
       </c>
       <c r="L48" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: Google TPUv5p  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: Google TPUv4p, TPUv5p and TPUv5e  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2503.19786 - training-infrastructure section. CHECK.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it model card: TPUv4p, TPUv5p and TPUv5e.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N48" s="21" t="n">
@@ -12580,12 +12581,12 @@
       </c>
       <c r="R48" s="21" t="inlineStr">
         <is>
-          <t>131,072</t>
+          <t>131,072 input / 8,192 output</t>
         </is>
       </c>
       <c r="S48" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/google/gemma-3-4b-it - model card states 128K for the 4B and above; config.json max_position_embeddings = 131072.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it: 128K token INPUT context but an 8,192 token OUTPUT limit. The output cap is a separate constraint from the context window and is not a problem for ipoefgfefs (generated blocks are ~80 lines), but note it before assuming 128K end to end.</t>
         </is>
       </c>
       <c r="T48" s="21" t="n">
@@ -12593,15 +12594,15 @@
       </c>
       <c r="U48" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V48" s="21" t="n">
-        <v>235.2</v>
+        <v>198.2</v>
       </c>
       <c r="W48" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X48" s="21" t="inlineStr">
@@ -12626,12 +12627,12 @@
       </c>
       <c r="AB48" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 36.0% | MMLU 59.6%</t>
+          <t>HumanEval 36.0% (0-shot) | MMLU 59.6% (5-shot) | MBPP 46.0% (3-shot) | MMMU 39.2% | GSM8K 38.4% (8-shot) | MATH 24.2% (4-shot)</t>
         </is>
       </c>
       <c r="AC48" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2503.19786 - evaluation tables. CHECK exact table number.  ||  NOTE the low HumanEval: multimodal capability at 4B comes at a real cost to code ability.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it model card evaluation table.  ||  NOTE the low code and math scores: multimodal capability at 4B costs real ground on code ability. HumanEval 36.0 and GSM8K 38.4 are the weakest in this sheet among instruct models.</t>
         </is>
       </c>
       <c r="AD48" s="21" t="inlineStr">
@@ -12646,7 +12647,7 @@
       </c>
       <c r="AF48" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence: VERIFIED - Terms of Use, not open source.</t>
+          <t>VERIFIED 2026-08-10. All benchmarks, training TPUs and the 8K output cap confirmed against the model card.</t>
         </is>
       </c>
     </row>
@@ -12706,12 +12707,12 @@
       </c>
       <c r="L49" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: Google TPUv5p  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: Google TPUv4p, TPUv5p and TPUv5e  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M49" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2503.19786 - training-infrastructure section. CHECK.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it model card: TPUv4p, TPUv5p and TPUv5e.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N49" s="21" t="n">
@@ -12732,12 +12733,12 @@
       </c>
       <c r="R49" s="21" t="inlineStr">
         <is>
-          <t>131,072</t>
+          <t>131,072 input / 8,192 output</t>
         </is>
       </c>
       <c r="S49" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/google/gemma-3-4b-it - model card states 128K for the 4B and above; config.json max_position_embeddings = 131072.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it: 128K token INPUT context but an 8,192 token OUTPUT limit. The output cap is a separate constraint from the context window and is not a problem for ipoefgfefs (generated blocks are ~80 lines), but note it before assuming 128K end to end.</t>
         </is>
       </c>
       <c r="T49" s="21" t="n">
@@ -12745,15 +12746,15 @@
       </c>
       <c r="U49" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V49" s="21" t="n">
-        <v>153.4</v>
+        <v>129.3</v>
       </c>
       <c r="W49" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X49" s="21" t="inlineStr">
@@ -12778,12 +12779,12 @@
       </c>
       <c r="AB49" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 36.0% | MMLU 59.6%</t>
+          <t>HumanEval 36.0% (0-shot) | MMLU 59.6% (5-shot) | MBPP 46.0% (3-shot) | MMMU 39.2% | GSM8K 38.4% (8-shot) | MATH 24.2% (4-shot)</t>
         </is>
       </c>
       <c r="AC49" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2503.19786 - evaluation tables. CHECK exact table number.  ||  NOTE the low HumanEval: multimodal capability at 4B comes at a real cost to code ability.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it model card evaluation table.  ||  NOTE the low code and math scores: multimodal capability at 4B costs real ground on code ability. HumanEval 36.0 and GSM8K 38.4 are the weakest in this sheet among instruct models.</t>
         </is>
       </c>
       <c r="AD49" s="21" t="inlineStr">
@@ -12798,7 +12799,7 @@
       </c>
       <c r="AF49" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence: VERIFIED - Terms of Use, not open source.</t>
+          <t>VERIFIED 2026-08-10. All benchmarks, training TPUs and the 8K output cap confirmed against the model card.</t>
         </is>
       </c>
     </row>
@@ -12858,12 +12859,12 @@
       </c>
       <c r="L50" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: Google TPUv5p  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: Google TPUv4p, TPUv5p and TPUv5e  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: arxiv 2503.19786 - training-infrastructure section. CHECK.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it model card: TPUv4p, TPUv5p and TPUv5e.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N50" s="21" t="n">
@@ -12884,12 +12885,12 @@
       </c>
       <c r="R50" s="21" t="inlineStr">
         <is>
-          <t>131,072</t>
+          <t>131,072 input / 8,192 output</t>
         </is>
       </c>
       <c r="S50" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/google/gemma-3-4b-it - model card states 128K for the 4B and above; config.json max_position_embeddings = 131072.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it: 128K token INPUT context but an 8,192 token OUTPUT limit. The output cap is a separate constraint from the context window and is not a problem for ipoefgfefs (generated blocks are ~80 lines), but note it before assuming 128K end to end.</t>
         </is>
       </c>
       <c r="T50" s="21" t="n">
@@ -12897,15 +12898,15 @@
       </c>
       <c r="U50" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V50" s="21" t="n">
-        <v>82</v>
+        <v>69.2</v>
       </c>
       <c r="W50" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X50" s="21" t="inlineStr">
@@ -12930,12 +12931,12 @@
       </c>
       <c r="AB50" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 36.0% | MMLU 59.6%</t>
+          <t>HumanEval 36.0% (0-shot) | MMLU 59.6% (5-shot) | MBPP 46.0% (3-shot) | MMMU 39.2% | GSM8K 38.4% (8-shot) | MATH 24.2% (4-shot)</t>
         </is>
       </c>
       <c r="AC50" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2503.19786 - evaluation tables. CHECK exact table number.  ||  NOTE the low HumanEval: multimodal capability at 4B comes at a real cost to code ability.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/gemma-3-4b-it model card evaluation table.  ||  NOTE the low code and math scores: multimodal capability at 4B costs real ground on code ability. HumanEval 36.0 and GSM8K 38.4 are the weakest in this sheet among instruct models.</t>
         </is>
       </c>
       <c r="AD50" s="21" t="inlineStr">
@@ -12950,7 +12951,7 @@
       </c>
       <c r="AF50" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. Licence: VERIFIED - Terms of Use, not open source.</t>
+          <t>VERIFIED 2026-08-10. All benchmarks, training TPUs and the 8K output cap confirmed against the model card.</t>
         </is>
       </c>
     </row>
@@ -13049,15 +13050,15 @@
       </c>
       <c r="U51" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V51" s="17" t="n">
-        <v>153.4</v>
+        <v>129.3</v>
       </c>
       <c r="W51" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X51" s="17" t="inlineStr">
@@ -13082,12 +13083,12 @@
       </c>
       <c r="AB51" s="17" t="inlineStr">
         <is>
-          <t>MMMU 54.1% | DocVQA 94.5% | MathVista 58.2%</t>
+          <t>DocVQA 94.5% (test) | TextVQA 84.3% (val) | MathVista 58.2% (testmini) | MMMU 54.1% (val)</t>
         </is>
       </c>
       <c r="AC51" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2409.12191 - main results tables. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen2-VL-7B-Instruct model card.  ||  TextVQA 84.3% added - the highest text-in-image score in this sheet, which together with DocVQA 94.5% makes this the strongest LPR / plate-reading candidate by a clear margin.  ||  Card also states video understanding of 20min+ duration.</t>
         </is>
       </c>
       <c r="AD51" s="17" t="inlineStr">
@@ -13102,7 +13103,7 @@
       </c>
       <c r="AF51" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. llama.cpp vision support: VERIFY CURRENT STATE.</t>
+          <t>VERIFIED 2026-08-10 against the model card. llama.cpp vision support: still needs a current-state check before relying on a GGUF path.</t>
         </is>
       </c>
     </row>
@@ -13201,15 +13202,15 @@
       </c>
       <c r="U52" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V52" s="17" t="n">
-        <v>123.8</v>
+        <v>104.3</v>
       </c>
       <c r="W52" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X52" s="17" t="inlineStr">
@@ -13234,12 +13235,12 @@
       </c>
       <c r="AB52" s="17" t="inlineStr">
         <is>
-          <t>MMMU 54.1% | DocVQA 94.5% | MathVista 58.2%</t>
+          <t>DocVQA 94.5% (test) | TextVQA 84.3% (val) | MathVista 58.2% (testmini) | MMMU 54.1% (val)</t>
         </is>
       </c>
       <c r="AC52" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2409.12191 - main results tables. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen2-VL-7B-Instruct model card.  ||  TextVQA 84.3% added - the highest text-in-image score in this sheet, which together with DocVQA 94.5% makes this the strongest LPR / plate-reading candidate by a clear margin.  ||  Card also states video understanding of 20min+ duration.</t>
         </is>
       </c>
       <c r="AD52" s="17" t="inlineStr">
@@ -13254,7 +13255,7 @@
       </c>
       <c r="AF52" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. llama.cpp vision support: VERIFY CURRENT STATE.</t>
+          <t>VERIFIED 2026-08-10 against the model card. llama.cpp vision support: still needs a current-state check before relying on a GGUF path.</t>
         </is>
       </c>
     </row>
@@ -13353,15 +13354,15 @@
       </c>
       <c r="U53" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V53" s="17" t="n">
-        <v>80.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="W53" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X53" s="17" t="inlineStr">
@@ -13386,12 +13387,12 @@
       </c>
       <c r="AB53" s="17" t="inlineStr">
         <is>
-          <t>MMMU 54.1% | DocVQA 94.5% | MathVista 58.2%</t>
+          <t>DocVQA 94.5% (test) | TextVQA 84.3% (val) | MathVista 58.2% (testmini) | MMMU 54.1% (val)</t>
         </is>
       </c>
       <c r="AC53" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2409.12191 - main results tables. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen2-VL-7B-Instruct model card.  ||  TextVQA 84.3% added - the highest text-in-image score in this sheet, which together with DocVQA 94.5% makes this the strongest LPR / plate-reading candidate by a clear margin.  ||  Card also states video understanding of 20min+ duration.</t>
         </is>
       </c>
       <c r="AD53" s="17" t="inlineStr">
@@ -13406,7 +13407,7 @@
       </c>
       <c r="AF53" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. llama.cpp vision support: VERIFY CURRENT STATE.</t>
+          <t>VERIFIED 2026-08-10 against the model card. llama.cpp vision support: still needs a current-state check before relying on a GGUF path.</t>
         </is>
       </c>
     </row>
@@ -13505,15 +13506,15 @@
       </c>
       <c r="U54" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V54" s="17" t="n">
-        <v>42.5</v>
+        <v>35.8</v>
       </c>
       <c r="W54" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X54" s="17" t="inlineStr">
@@ -13538,12 +13539,12 @@
       </c>
       <c r="AB54" s="17" t="inlineStr">
         <is>
-          <t>MMMU 54.1% | DocVQA 94.5% | MathVista 58.2%</t>
+          <t>DocVQA 94.5% (test) | TextVQA 84.3% (val) | MathVista 58.2% (testmini) | MMMU 54.1% (val)</t>
         </is>
       </c>
       <c r="AC54" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2409.12191 - main results tables. CHECK exact table numbers.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen2-VL-7B-Instruct model card.  ||  TextVQA 84.3% added - the highest text-in-image score in this sheet, which together with DocVQA 94.5% makes this the strongest LPR / plate-reading candidate by a clear margin.  ||  Card also states video understanding of 20min+ duration.</t>
         </is>
       </c>
       <c r="AD54" s="17" t="inlineStr">
@@ -13558,7 +13559,7 @@
       </c>
       <c r="AF54" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks: CHECK. llama.cpp vision support: VERIFY CURRENT STATE.</t>
+          <t>VERIFIED 2026-08-10 against the model card. llama.cpp vision support: still needs a current-state check before relying on a GGUF path.</t>
         </is>
       </c>
     </row>
@@ -13618,12 +13619,12 @@
       </c>
       <c r="L55" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 256 x NVIDIA A100-80GB, 6 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 256 x NVIDIA A100-80GB, 6 days, 500B tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M55" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: Model card 'Training' section. CHECK exact figures.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-vision-instruct: 256 A100-80G for 6 days on 500 billion vision+text tokens, trained July-August 2024.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N55" s="21" t="n">
@@ -13657,15 +13658,15 @@
       </c>
       <c r="U55" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V55" s="21" t="n">
-        <v>294</v>
+        <v>247.8</v>
       </c>
       <c r="W55" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X55" s="21" t="inlineStr">
@@ -13695,7 +13696,7 @@
       </c>
       <c r="AC55" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/microsoft/Phi-3.5-vision-instruct - model card evaluation tables. The 3.5-vision refresh is documented on the card. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-vision-instruct: MMBench dev-en 81.9, MMMU val 43.0, TextVQA val 72.0. Card is the primary source - no separate paper for the 3.5 refresh.</t>
         </is>
       </c>
       <c r="AD55" s="21" t="inlineStr">
@@ -13710,7 +13711,7 @@
       </c>
       <c r="AF55" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence: VERIFIED - MIT, cleanest VLM licence here.</t>
+          <t>FULLY VERIFIED 2026-08-10. Benchmarks and training HW confirmed. MIT - cleanest VLM licence here.</t>
         </is>
       </c>
     </row>
@@ -13770,12 +13771,12 @@
       </c>
       <c r="L56" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 256 x NVIDIA A100-80GB, 6 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 256 x NVIDIA A100-80GB, 6 days, 500B tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: Model card 'Training' section. CHECK exact figures.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-vision-instruct: 256 A100-80G for 6 days on 500 billion vision+text tokens, trained July-August 2024.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N56" s="21" t="n">
@@ -13809,15 +13810,15 @@
       </c>
       <c r="U56" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V56" s="21" t="n">
-        <v>243.3</v>
+        <v>205.1</v>
       </c>
       <c r="W56" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X56" s="21" t="inlineStr">
@@ -13847,7 +13848,7 @@
       </c>
       <c r="AC56" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/microsoft/Phi-3.5-vision-instruct - model card evaluation tables. The 3.5-vision refresh is documented on the card. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-vision-instruct: MMBench dev-en 81.9, MMMU val 43.0, TextVQA val 72.0. Card is the primary source - no separate paper for the 3.5 refresh.</t>
         </is>
       </c>
       <c r="AD56" s="21" t="inlineStr">
@@ -13862,7 +13863,7 @@
       </c>
       <c r="AF56" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence: VERIFIED - MIT, cleanest VLM licence here.</t>
+          <t>FULLY VERIFIED 2026-08-10. Benchmarks and training HW confirmed. MIT - cleanest VLM licence here.</t>
         </is>
       </c>
     </row>
@@ -13922,12 +13923,12 @@
       </c>
       <c r="L57" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 256 x NVIDIA A100-80GB, 6 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 256 x NVIDIA A100-80GB, 6 days, 500B tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M57" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: Model card 'Training' section. CHECK exact figures.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-vision-instruct: 256 A100-80G for 6 days on 500 billion vision+text tokens, trained July-August 2024.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N57" s="21" t="n">
@@ -13961,15 +13962,15 @@
       </c>
       <c r="U57" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V57" s="21" t="n">
-        <v>156.8</v>
+        <v>132.2</v>
       </c>
       <c r="W57" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X57" s="21" t="inlineStr">
@@ -13999,7 +14000,7 @@
       </c>
       <c r="AC57" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/microsoft/Phi-3.5-vision-instruct - model card evaluation tables. The 3.5-vision refresh is documented on the card. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-vision-instruct: MMBench dev-en 81.9, MMMU val 43.0, TextVQA val 72.0. Card is the primary source - no separate paper for the 3.5 refresh.</t>
         </is>
       </c>
       <c r="AD57" s="21" t="inlineStr">
@@ -14014,7 +14015,7 @@
       </c>
       <c r="AF57" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence: VERIFIED - MIT, cleanest VLM licence here.</t>
+          <t>FULLY VERIFIED 2026-08-10. Benchmarks and training HW confirmed. MIT - cleanest VLM licence here.</t>
         </is>
       </c>
     </row>
@@ -14074,12 +14075,12 @@
       </c>
       <c r="L58" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 256 x NVIDIA A100-80GB, 6 days  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 256 x NVIDIA A100-80GB, 6 days, 500B tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>Training hardware: Model card 'Training' section. CHECK exact figures.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
+          <t>Training hardware: VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-vision-instruct: 256 A100-80G for 6 days on 500 billion vision+text tokens, trained July-August 2024.  ||  Inference hardware: github.com/ggml-org/llama.cpp - README 'Supported backends' table and docs/build.md. CUDA section states compute capability 5.0 (Maxwell) minimum.  ||  NOTE: papers only ever state the hardware the model was TRAINED on. No paper states what hardware can RUN the model - that comes entirely from the inference engine documentation.</t>
         </is>
       </c>
       <c r="N58" s="21" t="n">
@@ -14113,15 +14114,15 @@
       </c>
       <c r="U58" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V58" s="21" t="n">
-        <v>84</v>
+        <v>70.8</v>
       </c>
       <c r="W58" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X58" s="21" t="inlineStr">
@@ -14151,7 +14152,7 @@
       </c>
       <c r="AC58" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/microsoft/Phi-3.5-vision-instruct - model card evaluation tables. The 3.5-vision refresh is documented on the card. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/microsoft/Phi-3.5-vision-instruct: MMBench dev-en 81.9, MMMU val 43.0, TextVQA val 72.0. Card is the primary source - no separate paper for the 3.5 refresh.</t>
         </is>
       </c>
       <c r="AD58" s="21" t="inlineStr">
@@ -14166,7 +14167,7 @@
       </c>
       <c r="AF58" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks + training HW: CHECK. Licence: VERIFIED - MIT, cleanest VLM licence here.</t>
+          <t>FULLY VERIFIED 2026-08-10. Benchmarks and training HW confirmed. MIT - cleanest VLM licence here.</t>
         </is>
       </c>
     </row>
@@ -14265,15 +14266,15 @@
       </c>
       <c r="U59" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V59" s="17" t="n">
-        <v>119.6</v>
+        <v>100.8</v>
       </c>
       <c r="W59" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X59" s="17" t="inlineStr">
@@ -14298,12 +14299,12 @@
       </c>
       <c r="AB59" s="17" t="inlineStr">
         <is>
-          <t>MMMU 50.7% | DocVQA 88.4% | ChartQA 83.4%</t>
+          <t>AI2 Diagram 91.1% | DocVQA 88.4% ANLS (test) | ChartQA 83.4% (test, CoT) | VQAv2 75.2% (test) | MMMU 50.7% (0-shot, CoT)</t>
         </is>
       </c>
       <c r="AC59" s="15" t="inlineStr">
         <is>
-          <t>ai.meta.com/blog/llama-3-2-connect-2024-edge-mobile-devices/ and the model card evaluation table. No arXiv paper for 3.2. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against github.com/meta-llama/llama-models/blob/main/models/llama3_2/MODEL_CARD_VISION.md, INSTRUCTION-TUNED table.  ||  IMPORTANT TRAP: the same model card carries a separate BASE PRETRAINED table with much lower figures (MMMU 41.7, DocVQA 62.3, ChartQA 39.4). Secondary sources frequently quote the pretrained numbers as if they were the instruct ones. The figures here are the INSTRUCT results.  ||  Note the settings: MMMU is 0-shot WITH chain-of-thought and ChartQA is CoT - not directly comparable to non-CoT scores from other VLMs in this sheet.</t>
         </is>
       </c>
       <c r="AD59" s="17" t="inlineStr">
@@ -14417,15 +14418,15 @@
       </c>
       <c r="U60" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V60" s="17" t="n">
-        <v>96.7</v>
+        <v>81.5</v>
       </c>
       <c r="W60" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X60" s="17" t="inlineStr">
@@ -14450,12 +14451,12 @@
       </c>
       <c r="AB60" s="17" t="inlineStr">
         <is>
-          <t>MMMU 50.7% | DocVQA 88.4% | ChartQA 83.4%</t>
+          <t>AI2 Diagram 91.1% | DocVQA 88.4% ANLS (test) | ChartQA 83.4% (test, CoT) | VQAv2 75.2% (test) | MMMU 50.7% (0-shot, CoT)</t>
         </is>
       </c>
       <c r="AC60" s="15" t="inlineStr">
         <is>
-          <t>ai.meta.com/blog/llama-3-2-connect-2024-edge-mobile-devices/ and the model card evaluation table. No arXiv paper for 3.2. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against github.com/meta-llama/llama-models/blob/main/models/llama3_2/MODEL_CARD_VISION.md, INSTRUCTION-TUNED table.  ||  IMPORTANT TRAP: the same model card carries a separate BASE PRETRAINED table with much lower figures (MMMU 41.7, DocVQA 62.3, ChartQA 39.4). Secondary sources frequently quote the pretrained numbers as if they were the instruct ones. The figures here are the INSTRUCT results.  ||  Note the settings: MMMU is 0-shot WITH chain-of-thought and ChartQA is CoT - not directly comparable to non-CoT scores from other VLMs in this sheet.</t>
         </is>
       </c>
       <c r="AD60" s="17" t="inlineStr">
@@ -14569,15 +14570,15 @@
       </c>
       <c r="U61" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V61" s="17" t="n">
-        <v>63</v>
+        <v>53.1</v>
       </c>
       <c r="W61" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X61" s="17" t="inlineStr">
@@ -14602,12 +14603,12 @@
       </c>
       <c r="AB61" s="17" t="inlineStr">
         <is>
-          <t>MMMU 50.7% | DocVQA 88.4% | ChartQA 83.4%</t>
+          <t>AI2 Diagram 91.1% | DocVQA 88.4% ANLS (test) | ChartQA 83.4% (test, CoT) | VQAv2 75.2% (test) | MMMU 50.7% (0-shot, CoT)</t>
         </is>
       </c>
       <c r="AC61" s="15" t="inlineStr">
         <is>
-          <t>ai.meta.com/blog/llama-3-2-connect-2024-edge-mobile-devices/ and the model card evaluation table. No arXiv paper for 3.2. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against github.com/meta-llama/llama-models/blob/main/models/llama3_2/MODEL_CARD_VISION.md, INSTRUCTION-TUNED table.  ||  IMPORTANT TRAP: the same model card carries a separate BASE PRETRAINED table with much lower figures (MMMU 41.7, DocVQA 62.3, ChartQA 39.4). Secondary sources frequently quote the pretrained numbers as if they were the instruct ones. The figures here are the INSTRUCT results.  ||  Note the settings: MMMU is 0-shot WITH chain-of-thought and ChartQA is CoT - not directly comparable to non-CoT scores from other VLMs in this sheet.</t>
         </is>
       </c>
       <c r="AD61" s="17" t="inlineStr">
@@ -14721,15 +14722,15 @@
       </c>
       <c r="U62" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V62" s="17" t="n">
-        <v>33.3</v>
+        <v>28.1</v>
       </c>
       <c r="W62" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X62" s="17" t="inlineStr">
@@ -14754,12 +14755,12 @@
       </c>
       <c r="AB62" s="17" t="inlineStr">
         <is>
-          <t>MMMU 50.7% | DocVQA 88.4% | ChartQA 83.4%</t>
+          <t>AI2 Diagram 91.1% | DocVQA 88.4% ANLS (test) | ChartQA 83.4% (test, CoT) | VQAv2 75.2% (test) | MMMU 50.7% (0-shot, CoT)</t>
         </is>
       </c>
       <c r="AC62" s="15" t="inlineStr">
         <is>
-          <t>ai.meta.com/blog/llama-3-2-connect-2024-edge-mobile-devices/ and the model card evaluation table. No arXiv paper for 3.2. CHECK current values.</t>
+          <t>VERIFIED 2026-08-10 against github.com/meta-llama/llama-models/blob/main/models/llama3_2/MODEL_CARD_VISION.md, INSTRUCTION-TUNED table.  ||  IMPORTANT TRAP: the same model card carries a separate BASE PRETRAINED table with much lower figures (MMMU 41.7, DocVQA 62.3, ChartQA 39.4). Secondary sources frequently quote the pretrained numbers as if they were the instruct ones. The figures here are the INSTRUCT results.  ||  Note the settings: MMMU is 0-shot WITH chain-of-thought and ChartQA is CoT - not directly comparable to non-CoT scores from other VLMs in this sheet.</t>
         </is>
       </c>
       <c r="AD62" s="17" t="inlineStr">
@@ -14873,15 +14874,15 @@
       </c>
       <c r="U63" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V63" s="21" t="n">
-        <v>156.8</v>
+        <v>132.2</v>
       </c>
       <c r="W63" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X63" s="21" t="inlineStr">
@@ -14906,12 +14907,12 @@
       </c>
       <c r="AB63" s="21" t="inlineStr">
         <is>
-          <t>MMBench 81.7% | MMMU 51.2% | DocVQA 91.6%</t>
+          <t>MMBench-EN 81.7% | DocVQA 91.6% | MMMU 51.8%</t>
         </is>
       </c>
       <c r="AC63" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/OpenGVLab/InternVL2-8B model card evaluation tables and the OpenCompass multimodal leaderboard at rank.opencompass.org.cn/leaderboard-multimodal. LEADERBOARD-SOURCED in part - weaker evidence than a paper. CHECK.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/OpenGVLab/InternVL2-8B model card.  ||  CORRECTION: MMMU is 51.8%, not 51.2% as previously stated.  ||  Base language model confirmed as internlm2_5-7b-chat with an InternViT-300M-448px vision tower via MLP projector - so the licence question on the InternLM base still stands.</t>
         </is>
       </c>
       <c r="AD63" s="21" t="inlineStr">
@@ -14926,7 +14927,7 @@
       </c>
       <c r="AF63" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks partly leaderboard-sourced. Base-model licence lineage: VERIFY.</t>
+          <t>VERIFIED 2026-08-10. MMMU corrected 51.2 -&gt; 51.8. Base is internlm2_5-7b-chat - its licence still needs separate confirmation.</t>
         </is>
       </c>
     </row>
@@ -15025,15 +15026,15 @@
       </c>
       <c r="U64" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V64" s="21" t="n">
-        <v>126</v>
+        <v>106.2</v>
       </c>
       <c r="W64" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X64" s="21" t="inlineStr">
@@ -15058,12 +15059,12 @@
       </c>
       <c r="AB64" s="21" t="inlineStr">
         <is>
-          <t>MMBench 81.7% | MMMU 51.2% | DocVQA 91.6%</t>
+          <t>MMBench-EN 81.7% | DocVQA 91.6% | MMMU 51.8%</t>
         </is>
       </c>
       <c r="AC64" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/OpenGVLab/InternVL2-8B model card evaluation tables and the OpenCompass multimodal leaderboard at rank.opencompass.org.cn/leaderboard-multimodal. LEADERBOARD-SOURCED in part - weaker evidence than a paper. CHECK.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/OpenGVLab/InternVL2-8B model card.  ||  CORRECTION: MMMU is 51.8%, not 51.2% as previously stated.  ||  Base language model confirmed as internlm2_5-7b-chat with an InternViT-300M-448px vision tower via MLP projector - so the licence question on the InternLM base still stands.</t>
         </is>
       </c>
       <c r="AD64" s="21" t="inlineStr">
@@ -15078,7 +15079,7 @@
       </c>
       <c r="AF64" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks partly leaderboard-sourced. Base-model licence lineage: VERIFY.</t>
+          <t>VERIFIED 2026-08-10. MMMU corrected 51.2 -&gt; 51.8. Base is internlm2_5-7b-chat - its licence still needs separate confirmation.</t>
         </is>
       </c>
     </row>
@@ -15177,15 +15178,15 @@
       </c>
       <c r="U65" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V65" s="21" t="n">
-        <v>82</v>
+        <v>69.2</v>
       </c>
       <c r="W65" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X65" s="21" t="inlineStr">
@@ -15210,12 +15211,12 @@
       </c>
       <c r="AB65" s="21" t="inlineStr">
         <is>
-          <t>MMBench 81.7% | MMMU 51.2% | DocVQA 91.6%</t>
+          <t>MMBench-EN 81.7% | DocVQA 91.6% | MMMU 51.8%</t>
         </is>
       </c>
       <c r="AC65" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/OpenGVLab/InternVL2-8B model card evaluation tables and the OpenCompass multimodal leaderboard at rank.opencompass.org.cn/leaderboard-multimodal. LEADERBOARD-SOURCED in part - weaker evidence than a paper. CHECK.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/OpenGVLab/InternVL2-8B model card.  ||  CORRECTION: MMMU is 51.8%, not 51.2% as previously stated.  ||  Base language model confirmed as internlm2_5-7b-chat with an InternViT-300M-448px vision tower via MLP projector - so the licence question on the InternLM base still stands.</t>
         </is>
       </c>
       <c r="AD65" s="21" t="inlineStr">
@@ -15230,7 +15231,7 @@
       </c>
       <c r="AF65" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks partly leaderboard-sourced. Base-model licence lineage: VERIFY.</t>
+          <t>VERIFIED 2026-08-10. MMMU corrected 51.2 -&gt; 51.8. Base is internlm2_5-7b-chat - its licence still needs separate confirmation.</t>
         </is>
       </c>
     </row>
@@ -15329,15 +15330,15 @@
       </c>
       <c r="U66" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V66" s="21" t="n">
-        <v>43.6</v>
+        <v>36.7</v>
       </c>
       <c r="W66" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X66" s="21" t="inlineStr">
@@ -15362,12 +15363,12 @@
       </c>
       <c r="AB66" s="21" t="inlineStr">
         <is>
-          <t>MMBench 81.7% | MMMU 51.2% | DocVQA 91.6%</t>
+          <t>MMBench-EN 81.7% | DocVQA 91.6% | MMMU 51.8%</t>
         </is>
       </c>
       <c r="AC66" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/OpenGVLab/InternVL2-8B model card evaluation tables and the OpenCompass multimodal leaderboard at rank.opencompass.org.cn/leaderboard-multimodal. LEADERBOARD-SOURCED in part - weaker evidence than a paper. CHECK.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/OpenGVLab/InternVL2-8B model card.  ||  CORRECTION: MMMU is 51.8%, not 51.2% as previously stated.  ||  Base language model confirmed as internlm2_5-7b-chat with an InternViT-300M-448px vision tower via MLP projector - so the licence question on the InternLM base still stands.</t>
         </is>
       </c>
       <c r="AD66" s="21" t="inlineStr">
@@ -15382,7 +15383,7 @@
       </c>
       <c r="AF66" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks partly leaderboard-sourced. Base-model licence lineage: VERIFY.</t>
+          <t>VERIFIED 2026-08-10. MMMU corrected 51.2 -&gt; 51.8. Base is internlm2_5-7b-chat - its licence still needs separate confirmation.</t>
         </is>
       </c>
     </row>
@@ -15399,7 +15400,7 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>Apache 2.0 (code) - CHECK base weights</t>
+          <t>Llama 2 Community License</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
@@ -15481,15 +15482,15 @@
       </c>
       <c r="U67" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V67" s="17" t="n">
-        <v>94.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="W67" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X67" s="17" t="inlineStr">
@@ -15519,7 +15520,7 @@
       </c>
       <c r="AC67" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2310.03744 evaluation tables for 1.5; 1.6/NeXT results are published on the llava-vl.github.io blog rather than in a paper. CHECK which release each number belongs to - 1.5 and 1.6 numbers are frequently conflated in secondary sources.</t>
+          <t>PARTIALLY VERIFIED 2026-08-10: huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf publishes NO benchmark scores at all. The quoted figures come from arxiv 2310.03744 (which covers LLaVA-1.5) and the llava-vl.github.io blog (which covers 1.6/NeXT).  ||  UNRESOLVED: 1.5 and 1.6 numbers are routinely conflated in secondary sources and this sheet cannot currently prove which release each figure belongs to. Treat all LLaVA benchmark figures here as unconfirmed.</t>
         </is>
       </c>
       <c r="AD67" s="17" t="inlineStr">
@@ -15532,9 +15533,9 @@
           <t>llama.cpp: LLaVA has the most mature vision support in llama.cpp of any model here (clip.cpp / llava.cpp).  ||  vLLM: docs.vllm.ai multimodal list.  ||  SGLang: docs.sglang.ai - LLaVA is a documented example.</t>
         </is>
       </c>
-      <c r="AF67" s="24" t="inlineStr">
-        <is>
-          <t>LICENCE CHAIN MUST BE TRACED BY LEGAL. Context 4K disqualifies it regardless.</t>
+      <c r="AF67" s="18" t="inlineStr">
+        <is>
+          <t>LICENCE CONFIRMED AS LLAMA 2 (not Apache 2.0) 2026-08-10. Benchmarks UNCONFIRMED - card publishes none, and 1.5 vs 1.6 figures are conflated in secondary sources. Context 4K disqualifies it regardless.</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15552,7 @@
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>Apache 2.0 (code) - CHECK base weights</t>
+          <t>Llama 2 Community License</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
@@ -15633,15 +15634,15 @@
       </c>
       <c r="U68" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V68" s="17" t="n">
-        <v>76.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="W68" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X68" s="17" t="inlineStr">
@@ -15671,7 +15672,7 @@
       </c>
       <c r="AC68" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2310.03744 evaluation tables for 1.5; 1.6/NeXT results are published on the llava-vl.github.io blog rather than in a paper. CHECK which release each number belongs to - 1.5 and 1.6 numbers are frequently conflated in secondary sources.</t>
+          <t>PARTIALLY VERIFIED 2026-08-10: huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf publishes NO benchmark scores at all. The quoted figures come from arxiv 2310.03744 (which covers LLaVA-1.5) and the llava-vl.github.io blog (which covers 1.6/NeXT).  ||  UNRESOLVED: 1.5 and 1.6 numbers are routinely conflated in secondary sources and this sheet cannot currently prove which release each figure belongs to. Treat all LLaVA benchmark figures here as unconfirmed.</t>
         </is>
       </c>
       <c r="AD68" s="17" t="inlineStr">
@@ -15684,9 +15685,9 @@
           <t>llama.cpp: LLaVA has the most mature vision support in llama.cpp of any model here (clip.cpp / llava.cpp).  ||  vLLM: docs.vllm.ai multimodal list.  ||  SGLang: docs.sglang.ai - LLaVA is a documented example.</t>
         </is>
       </c>
-      <c r="AF68" s="24" t="inlineStr">
-        <is>
-          <t>LICENCE CHAIN MUST BE TRACED BY LEGAL. Context 4K disqualifies it regardless.</t>
+      <c r="AF68" s="18" t="inlineStr">
+        <is>
+          <t>LICENCE CONFIRMED AS LLAMA 2 (not Apache 2.0) 2026-08-10. Benchmarks UNCONFIRMED - card publishes none, and 1.5 vs 1.6 figures are conflated in secondary sources. Context 4K disqualifies it regardless.</t>
         </is>
       </c>
     </row>
@@ -15703,7 +15704,7 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>Apache 2.0 (code) - CHECK base weights</t>
+          <t>Llama 2 Community License</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
@@ -15785,15 +15786,15 @@
       </c>
       <c r="U69" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V69" s="17" t="n">
-        <v>49.7</v>
+        <v>41.9</v>
       </c>
       <c r="W69" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X69" s="17" t="inlineStr">
@@ -15823,7 +15824,7 @@
       </c>
       <c r="AC69" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2310.03744 evaluation tables for 1.5; 1.6/NeXT results are published on the llava-vl.github.io blog rather than in a paper. CHECK which release each number belongs to - 1.5 and 1.6 numbers are frequently conflated in secondary sources.</t>
+          <t>PARTIALLY VERIFIED 2026-08-10: huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf publishes NO benchmark scores at all. The quoted figures come from arxiv 2310.03744 (which covers LLaVA-1.5) and the llava-vl.github.io blog (which covers 1.6/NeXT).  ||  UNRESOLVED: 1.5 and 1.6 numbers are routinely conflated in secondary sources and this sheet cannot currently prove which release each figure belongs to. Treat all LLaVA benchmark figures here as unconfirmed.</t>
         </is>
       </c>
       <c r="AD69" s="17" t="inlineStr">
@@ -15836,9 +15837,9 @@
           <t>llama.cpp: LLaVA has the most mature vision support in llama.cpp of any model here (clip.cpp / llava.cpp).  ||  vLLM: docs.vllm.ai multimodal list.  ||  SGLang: docs.sglang.ai - LLaVA is a documented example.</t>
         </is>
       </c>
-      <c r="AF69" s="24" t="inlineStr">
-        <is>
-          <t>LICENCE CHAIN MUST BE TRACED BY LEGAL. Context 4K disqualifies it regardless.</t>
+      <c r="AF69" s="18" t="inlineStr">
+        <is>
+          <t>LICENCE CONFIRMED AS LLAMA 2 (not Apache 2.0) 2026-08-10. Benchmarks UNCONFIRMED - card publishes none, and 1.5 vs 1.6 figures are conflated in secondary sources. Context 4K disqualifies it regardless.</t>
         </is>
       </c>
     </row>
@@ -15855,7 +15856,7 @@
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>Apache 2.0 (code) - CHECK base weights</t>
+          <t>Llama 2 Community License</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
@@ -15937,15 +15938,15 @@
       </c>
       <c r="U70" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V70" s="17" t="n">
-        <v>26.3</v>
+        <v>22.2</v>
       </c>
       <c r="W70" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X70" s="17" t="inlineStr">
@@ -15975,7 +15976,7 @@
       </c>
       <c r="AC70" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2310.03744 evaluation tables for 1.5; 1.6/NeXT results are published on the llava-vl.github.io blog rather than in a paper. CHECK which release each number belongs to - 1.5 and 1.6 numbers are frequently conflated in secondary sources.</t>
+          <t>PARTIALLY VERIFIED 2026-08-10: huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf publishes NO benchmark scores at all. The quoted figures come from arxiv 2310.03744 (which covers LLaVA-1.5) and the llava-vl.github.io blog (which covers 1.6/NeXT).  ||  UNRESOLVED: 1.5 and 1.6 numbers are routinely conflated in secondary sources and this sheet cannot currently prove which release each figure belongs to. Treat all LLaVA benchmark figures here as unconfirmed.</t>
         </is>
       </c>
       <c r="AD70" s="17" t="inlineStr">
@@ -15988,9 +15989,9 @@
           <t>llama.cpp: LLaVA has the most mature vision support in llama.cpp of any model here (clip.cpp / llava.cpp).  ||  vLLM: docs.vllm.ai multimodal list.  ||  SGLang: docs.sglang.ai - LLaVA is a documented example.</t>
         </is>
       </c>
-      <c r="AF70" s="24" t="inlineStr">
-        <is>
-          <t>LICENCE CHAIN MUST BE TRACED BY LEGAL. Context 4K disqualifies it regardless.</t>
+      <c r="AF70" s="18" t="inlineStr">
+        <is>
+          <t>LICENCE CONFIRMED AS LLAMA 2 (not Apache 2.0) 2026-08-10. Benchmarks UNCONFIRMED - card publishes none, and 1.5 vs 1.6 figures are conflated in secondary sources. Context 4K disqualifies it regardless.</t>
         </is>
       </c>
     </row>
@@ -16076,12 +16077,12 @@
       </c>
       <c r="R71" s="21" t="inlineStr">
         <is>
-          <t>8,192</t>
+          <t>512 tokens (input + output)</t>
         </is>
       </c>
       <c r="S71" s="15" t="inlineStr">
         <is>
-          <t>config.json max_position_embeddings = 8192. NOTE: multi-query attention (1 KV head) makes the KV cache exceptionally small - see the VRAM columns.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/paligemma-3b-mix-448: the model supports 512 token input/output text sequences at 448x448 image resolution.  ||  MAJOR CORRECTION: an earlier revision of this sheet stated 8,192. That was WRONG by a factor of 16. At 512 tokens this model is categorically unusable for ipoefgfefs - the prompt alone is 6-8K.</t>
         </is>
       </c>
       <c r="T71" s="21" t="n">
@@ -16089,15 +16090,15 @@
       </c>
       <c r="U71" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V71" s="21" t="n">
-        <v>441</v>
+        <v>371.7</v>
       </c>
       <c r="W71" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X71" s="21" t="inlineStr">
@@ -16122,12 +16123,12 @@
       </c>
       <c r="AB71" s="21" t="inlineStr">
         <is>
-          <t>COCO CIDEr 141.9 | VQAv2 85.6% | TextVQA 73.2%</t>
+          <t>VQAv2 85.64% | DocVQA 78.02% ANLS | TextVQA 73.15% | POPE 89.37% | MMVP 45.33% (ALL FINE-TUNED, NOT ZERO-SHOT)</t>
         </is>
       </c>
       <c r="AC71" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2407.07726 - transfer-results tables. CHECK exact table numbers.  ||  IMPORTANT: these are FINE-TUNED transfer results, not zero-shot. Do not compare them directly against zero-shot numbers from other VLMs in this sheet.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/paligemma-3b-mix-448 model card.  ||  CRITICAL CAVEAT CONFIRMED BY THE CARD: these are single-task FINE-TUNED transfer results, not zero-shot. The card states the model was designed first and foremost as a pre-trained model for transfer to specialised tasks. DO NOT compare these numbers against the zero-shot figures from Qwen2-VL, Phi-3.5-Vision or InternVL2 elsewhere in this sheet - it is not a like-for-like comparison and a reviewer will catch it.</t>
         </is>
       </c>
       <c r="AD71" s="21" t="inlineStr">
@@ -16142,7 +16143,7 @@
       </c>
       <c r="AF71" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks are FINE-TUNED not zero-shot - do not compare naively. Licence: Terms of Use.</t>
+          <t>VERIFIED 2026-08-10. CONTEXT CORRECTED 8192 -&gt; 512, which disqualifies it outright. Benchmarks are FINE-TUNED, not zero-shot.</t>
         </is>
       </c>
     </row>
@@ -16228,12 +16229,12 @@
       </c>
       <c r="R72" s="21" t="inlineStr">
         <is>
-          <t>8,192</t>
+          <t>512 tokens (input + output)</t>
         </is>
       </c>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>config.json max_position_embeddings = 8192. NOTE: multi-query attention (1 KV head) makes the KV cache exceptionally small - see the VRAM columns.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/paligemma-3b-mix-448: the model supports 512 token input/output text sequences at 448x448 image resolution.  ||  MAJOR CORRECTION: an earlier revision of this sheet stated 8,192. That was WRONG by a factor of 16. At 512 tokens this model is categorically unusable for ipoefgfefs - the prompt alone is 6-8K.</t>
         </is>
       </c>
       <c r="T72" s="21" t="n">
@@ -16241,15 +16242,15 @@
       </c>
       <c r="U72" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V72" s="21" t="n">
-        <v>352.8</v>
+        <v>297.4</v>
       </c>
       <c r="W72" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X72" s="21" t="inlineStr">
@@ -16274,12 +16275,12 @@
       </c>
       <c r="AB72" s="21" t="inlineStr">
         <is>
-          <t>COCO CIDEr 141.9 | VQAv2 85.6% | TextVQA 73.2%</t>
+          <t>VQAv2 85.64% | DocVQA 78.02% ANLS | TextVQA 73.15% | POPE 89.37% | MMVP 45.33% (ALL FINE-TUNED, NOT ZERO-SHOT)</t>
         </is>
       </c>
       <c r="AC72" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2407.07726 - transfer-results tables. CHECK exact table numbers.  ||  IMPORTANT: these are FINE-TUNED transfer results, not zero-shot. Do not compare them directly against zero-shot numbers from other VLMs in this sheet.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/paligemma-3b-mix-448 model card.  ||  CRITICAL CAVEAT CONFIRMED BY THE CARD: these are single-task FINE-TUNED transfer results, not zero-shot. The card states the model was designed first and foremost as a pre-trained model for transfer to specialised tasks. DO NOT compare these numbers against the zero-shot figures from Qwen2-VL, Phi-3.5-Vision or InternVL2 elsewhere in this sheet - it is not a like-for-like comparison and a reviewer will catch it.</t>
         </is>
       </c>
       <c r="AD72" s="21" t="inlineStr">
@@ -16294,7 +16295,7 @@
       </c>
       <c r="AF72" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks are FINE-TUNED not zero-shot - do not compare naively. Licence: Terms of Use.</t>
+          <t>VERIFIED 2026-08-10. CONTEXT CORRECTED 8192 -&gt; 512, which disqualifies it outright. Benchmarks are FINE-TUNED, not zero-shot.</t>
         </is>
       </c>
     </row>
@@ -16380,12 +16381,12 @@
       </c>
       <c r="R73" s="21" t="inlineStr">
         <is>
-          <t>8,192</t>
+          <t>512 tokens (input + output)</t>
         </is>
       </c>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>config.json max_position_embeddings = 8192. NOTE: multi-query attention (1 KV head) makes the KV cache exceptionally small - see the VRAM columns.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/paligemma-3b-mix-448: the model supports 512 token input/output text sequences at 448x448 image resolution.  ||  MAJOR CORRECTION: an earlier revision of this sheet stated 8,192. That was WRONG by a factor of 16. At 512 tokens this model is categorically unusable for ipoefgfefs - the prompt alone is 6-8K.</t>
         </is>
       </c>
       <c r="T73" s="21" t="n">
@@ -16393,15 +16394,15 @@
       </c>
       <c r="U73" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V73" s="21" t="n">
-        <v>227.6</v>
+        <v>191.8</v>
       </c>
       <c r="W73" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X73" s="21" t="inlineStr">
@@ -16426,12 +16427,12 @@
       </c>
       <c r="AB73" s="21" t="inlineStr">
         <is>
-          <t>COCO CIDEr 141.9 | VQAv2 85.6% | TextVQA 73.2%</t>
+          <t>VQAv2 85.64% | DocVQA 78.02% ANLS | TextVQA 73.15% | POPE 89.37% | MMVP 45.33% (ALL FINE-TUNED, NOT ZERO-SHOT)</t>
         </is>
       </c>
       <c r="AC73" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2407.07726 - transfer-results tables. CHECK exact table numbers.  ||  IMPORTANT: these are FINE-TUNED transfer results, not zero-shot. Do not compare them directly against zero-shot numbers from other VLMs in this sheet.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/paligemma-3b-mix-448 model card.  ||  CRITICAL CAVEAT CONFIRMED BY THE CARD: these are single-task FINE-TUNED transfer results, not zero-shot. The card states the model was designed first and foremost as a pre-trained model for transfer to specialised tasks. DO NOT compare these numbers against the zero-shot figures from Qwen2-VL, Phi-3.5-Vision or InternVL2 elsewhere in this sheet - it is not a like-for-like comparison and a reviewer will catch it.</t>
         </is>
       </c>
       <c r="AD73" s="21" t="inlineStr">
@@ -16446,7 +16447,7 @@
       </c>
       <c r="AF73" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks are FINE-TUNED not zero-shot - do not compare naively. Licence: Terms of Use.</t>
+          <t>VERIFIED 2026-08-10. CONTEXT CORRECTED 8192 -&gt; 512, which disqualifies it outright. Benchmarks are FINE-TUNED, not zero-shot.</t>
         </is>
       </c>
     </row>
@@ -16532,12 +16533,12 @@
       </c>
       <c r="R74" s="21" t="inlineStr">
         <is>
-          <t>8,192</t>
+          <t>512 tokens (input + output)</t>
         </is>
       </c>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>config.json max_position_embeddings = 8192. NOTE: multi-query attention (1 KV head) makes the KV cache exceptionally small - see the VRAM columns.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/paligemma-3b-mix-448: the model supports 512 token input/output text sequences at 448x448 image resolution.  ||  MAJOR CORRECTION: an earlier revision of this sheet stated 8,192. That was WRONG by a factor of 16. At 512 tokens this model is categorically unusable for ipoefgfefs - the prompt alone is 6-8K.</t>
         </is>
       </c>
       <c r="T74" s="21" t="n">
@@ -16545,15 +16546,15 @@
       </c>
       <c r="U74" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V74" s="21" t="n">
-        <v>121.7</v>
+        <v>102.5</v>
       </c>
       <c r="W74" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X74" s="21" t="inlineStr">
@@ -16578,12 +16579,12 @@
       </c>
       <c r="AB74" s="21" t="inlineStr">
         <is>
-          <t>COCO CIDEr 141.9 | VQAv2 85.6% | TextVQA 73.2%</t>
+          <t>VQAv2 85.64% | DocVQA 78.02% ANLS | TextVQA 73.15% | POPE 89.37% | MMVP 45.33% (ALL FINE-TUNED, NOT ZERO-SHOT)</t>
         </is>
       </c>
       <c r="AC74" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2407.07726 - transfer-results tables. CHECK exact table numbers.  ||  IMPORTANT: these are FINE-TUNED transfer results, not zero-shot. Do not compare them directly against zero-shot numbers from other VLMs in this sheet.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/google/paligemma-3b-mix-448 model card.  ||  CRITICAL CAVEAT CONFIRMED BY THE CARD: these are single-task FINE-TUNED transfer results, not zero-shot. The card states the model was designed first and foremost as a pre-trained model for transfer to specialised tasks. DO NOT compare these numbers against the zero-shot figures from Qwen2-VL, Phi-3.5-Vision or InternVL2 elsewhere in this sheet - it is not a like-for-like comparison and a reviewer will catch it.</t>
         </is>
       </c>
       <c r="AD74" s="21" t="inlineStr">
@@ -16598,7 +16599,7 @@
       </c>
       <c r="AF74" s="18" t="inlineStr">
         <is>
-          <t>Benchmarks are FINE-TUNED not zero-shot - do not compare naively. Licence: Terms of Use.</t>
+          <t>VERIFIED 2026-08-10. CONTEXT CORRECTED 8192 -&gt; 512, which disqualifies it outright. Benchmarks are FINE-TUNED, not zero-shot.</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16636,7 @@
       </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
-          <t>1.86B dense (SigLIP vision + Phi-1.5-derived language)</t>
+          <t>2B dense (SigLIP vision + Phi-1.5-derived language)</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
@@ -16697,15 +16698,15 @@
       </c>
       <c r="U75" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V75" s="17" t="n">
-        <v>641.5</v>
+        <v>540.7</v>
       </c>
       <c r="W75" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X75" s="17" t="inlineStr">
@@ -16730,12 +16731,12 @@
       </c>
       <c r="AB75" s="17" t="inlineStr">
         <is>
-          <t>VQAv2 79.4% | TextVQA 60.2% | DocVQA 61.9%</t>
+          <t>DocVQA 79.3% | TextVQA 76.3% | ChartQA 77.5% (82.2% with PoT) | CountBenchQA 86.4% | OCRBench 61.2% | COCO object detection 51.2% | ScreenSpot F1@0.5 80.4%</t>
         </is>
       </c>
       <c r="AC75" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/vikhyatk/moondream2 - model card benchmark table. NO PAPER EXISTS. Single-source, vendor-self-reported, not independently verified. WEAKEST EVIDENCE IN THIS SHEET.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vikhyatk/moondream2 model card.  ||  MAJOR CORRECTION: the previous revision quoted VQAv2 79.4 / TextVQA 60.2 / DocVQA 61.9. Those were STALE - the model has been substantially improved since. Current published figures are far higher (DocVQA 79.3, TextVQA 76.3).  ||  NEW CAPABILITY WORTH NOTING FOR A VMS: the card now reports COCO object detection 51.2% and ScreenSpot pointing 80.4% - this 2B model does detection and pointing, not just captioning.  ||  STILL NO PAPER. All figures are vendor-self-reported and not independently verified - the weakest evidence grade in this sheet, even though the numbers improved.</t>
         </is>
       </c>
       <c r="AD75" s="17" t="inlineStr">
@@ -16750,7 +16751,7 @@
       </c>
       <c r="AF75" s="24" t="inlineStr">
         <is>
-          <t>NO PAPER. Vendor-self-reported benchmarks only. Treat as indicative, not evidenced.</t>
+          <t>VERIFIED against card 2026-08-10 - previous figures were STALE and understated it. Params 1.9B -&gt; 2B. STILL NO PAPER: vendor-self-reported only.</t>
         </is>
       </c>
     </row>
@@ -16787,7 +16788,7 @@
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>1.86B dense (SigLIP vision + Phi-1.5-derived language)</t>
+          <t>2B dense (SigLIP vision + Phi-1.5-derived language)</t>
         </is>
       </c>
       <c r="H76" s="15" t="inlineStr">
@@ -16801,7 +16802,7 @@
         </is>
       </c>
       <c r="J76" s="17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
@@ -16819,7 +16820,7 @@
         </is>
       </c>
       <c r="N76" s="17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O76" s="15" t="inlineStr">
         <is>
@@ -16827,7 +16828,7 @@
         </is>
       </c>
       <c r="P76" s="17" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q76" s="15" t="inlineStr">
         <is>
@@ -16845,19 +16846,19 @@
         </is>
       </c>
       <c r="T76" s="17" t="n">
-        <v>36.9</v>
+        <v>34.3</v>
       </c>
       <c r="U76" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V76" s="17" t="n">
-        <v>542.8</v>
+        <v>424.8</v>
       </c>
       <c r="W76" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X76" s="17" t="inlineStr">
@@ -16882,12 +16883,12 @@
       </c>
       <c r="AB76" s="17" t="inlineStr">
         <is>
-          <t>VQAv2 79.4% | TextVQA 60.2% | DocVQA 61.9%</t>
+          <t>DocVQA 79.3% | TextVQA 76.3% | ChartQA 77.5% (82.2% with PoT) | CountBenchQA 86.4% | OCRBench 61.2% | COCO object detection 51.2% | ScreenSpot F1@0.5 80.4%</t>
         </is>
       </c>
       <c r="AC76" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/vikhyatk/moondream2 - model card benchmark table. NO PAPER EXISTS. Single-source, vendor-self-reported, not independently verified. WEAKEST EVIDENCE IN THIS SHEET.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vikhyatk/moondream2 model card.  ||  MAJOR CORRECTION: the previous revision quoted VQAv2 79.4 / TextVQA 60.2 / DocVQA 61.9. Those were STALE - the model has been substantially improved since. Current published figures are far higher (DocVQA 79.3, TextVQA 76.3).  ||  NEW CAPABILITY WORTH NOTING FOR A VMS: the card now reports COCO object detection 51.2% and ScreenSpot pointing 80.4% - this 2B model does detection and pointing, not just captioning.  ||  STILL NO PAPER. All figures are vendor-self-reported and not independently verified - the weakest evidence grade in this sheet, even though the numbers improved.</t>
         </is>
       </c>
       <c r="AD76" s="17" t="inlineStr">
@@ -16902,7 +16903,7 @@
       </c>
       <c r="AF76" s="24" t="inlineStr">
         <is>
-          <t>NO PAPER. Vendor-self-reported benchmarks only. Treat as indicative, not evidenced.</t>
+          <t>VERIFIED against card 2026-08-10 - previous figures were STALE and understated it. Params 1.9B -&gt; 2B. STILL NO PAPER: vendor-self-reported only.</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16940,7 @@
       </c>
       <c r="G77" s="17" t="inlineStr">
         <is>
-          <t>1.86B dense (SigLIP vision + Phi-1.5-derived language)</t>
+          <t>2B dense (SigLIP vision + Phi-1.5-derived language)</t>
         </is>
       </c>
       <c r="H77" s="15" t="inlineStr">
@@ -16953,7 +16954,7 @@
         </is>
       </c>
       <c r="J77" s="17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K77" s="15" t="inlineStr">
         <is>
@@ -16971,7 +16972,7 @@
         </is>
       </c>
       <c r="N77" s="17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O77" s="15" t="inlineStr">
         <is>
@@ -16979,7 +16980,7 @@
         </is>
       </c>
       <c r="P77" s="17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q77" s="15" t="inlineStr">
         <is>
@@ -16997,19 +16998,19 @@
         </is>
       </c>
       <c r="T77" s="17" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="U77" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V77" s="17" t="n">
-        <v>352.8</v>
+        <v>283.2</v>
       </c>
       <c r="W77" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X77" s="17" t="inlineStr">
@@ -17034,12 +17035,12 @@
       </c>
       <c r="AB77" s="17" t="inlineStr">
         <is>
-          <t>VQAv2 79.4% | TextVQA 60.2% | DocVQA 61.9%</t>
+          <t>DocVQA 79.3% | TextVQA 76.3% | ChartQA 77.5% (82.2% with PoT) | CountBenchQA 86.4% | OCRBench 61.2% | COCO object detection 51.2% | ScreenSpot F1@0.5 80.4%</t>
         </is>
       </c>
       <c r="AC77" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/vikhyatk/moondream2 - model card benchmark table. NO PAPER EXISTS. Single-source, vendor-self-reported, not independently verified. WEAKEST EVIDENCE IN THIS SHEET.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vikhyatk/moondream2 model card.  ||  MAJOR CORRECTION: the previous revision quoted VQAv2 79.4 / TextVQA 60.2 / DocVQA 61.9. Those were STALE - the model has been substantially improved since. Current published figures are far higher (DocVQA 79.3, TextVQA 76.3).  ||  NEW CAPABILITY WORTH NOTING FOR A VMS: the card now reports COCO object detection 51.2% and ScreenSpot pointing 80.4% - this 2B model does detection and pointing, not just captioning.  ||  STILL NO PAPER. All figures are vendor-self-reported and not independently verified - the weakest evidence grade in this sheet, even though the numbers improved.</t>
         </is>
       </c>
       <c r="AD77" s="17" t="inlineStr">
@@ -17054,7 +17055,7 @@
       </c>
       <c r="AF77" s="24" t="inlineStr">
         <is>
-          <t>NO PAPER. Vendor-self-reported benchmarks only. Treat as indicative, not evidenced.</t>
+          <t>VERIFIED against card 2026-08-10 - previous figures were STALE and understated it. Params 1.9B -&gt; 2B. STILL NO PAPER: vendor-self-reported only.</t>
         </is>
       </c>
     </row>
@@ -17091,7 +17092,7 @@
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>1.86B dense (SigLIP vision + Phi-1.5-derived language)</t>
+          <t>2B dense (SigLIP vision + Phi-1.5-derived language)</t>
         </is>
       </c>
       <c r="H78" s="15" t="inlineStr">
@@ -17105,7 +17106,7 @@
         </is>
       </c>
       <c r="J78" s="17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K78" s="15" t="inlineStr">
         <is>
@@ -17123,7 +17124,7 @@
         </is>
       </c>
       <c r="N78" s="17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O78" s="15" t="inlineStr">
         <is>
@@ -17131,7 +17132,7 @@
         </is>
       </c>
       <c r="P78" s="17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q78" s="15" t="inlineStr">
         <is>
@@ -17149,19 +17150,19 @@
         </is>
       </c>
       <c r="T78" s="17" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="U78" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. DDR5-5600 dual channel = 89.6 GB/s theoretical, used 80 GB/s x 0.60 efficiency / model_size_GB. No published source exists.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 80 GB/s (DDR5-5600 dual channel, 89.6 GB/s theoretical derated) x 0.60 efficiency / model_size_GB.  ||  MEASURED ANCHORS: AMD EPYC 7763 running Llama 2 7B Q4_K_M = 15 tok/s; dual-socket EPYC 9334 = 20-28 tok/s on Q4 7B-20B (blog.leaseweb.com EPYC LLM inference benchmark). Intel Sapphire Rapids 8480+ = approx 50 tok/s at 7B INT4 - a server CPU, not comparable to a desktop. General desktop band for 3B-7B at Q4_K_M is 4-15 tok/s (promptquorum.com, myaihardware.com/llama-cpp-benchmarks).  ||  This sheet estimates ~11 tok/s for a 7B Q4_K_M, which sits inside that measured band.  ||  CPU throughput varies more than GPU - core count, memory channels and AVX2 vs AVX-512 all move it substantially. Treat as an order-of-magnitude figure.</t>
         </is>
       </c>
       <c r="V78" s="17" t="n">
-        <v>185.7</v>
+        <v>148.7</v>
       </c>
       <c r="W78" s="15" t="inlineStr">
         <is>
-          <t>CALC, NOT MEASURED. Memory-bandwidth bound estimate: RTX 4090 spec bandwidth 1008 GB/s (NVIDIA Ada GPU architecture whitepaper) x 0.70 efficiency / model_size_GB. No paper or vendor doc publishes tok/s for these models.</t>
+          <t>ESTIMATE, CALIBRATED AGAINST PUBLISHED MEASUREMENTS. Formula: 1008 GB/s (RTX 4090 spec bandwidth, NVIDIA Ada Lovelace GPU Architecture whitepaper) x 0.59 efficiency / model_size_GB.  ||  THE 0.59 IS NOT ASSUMED - it is fitted to published measurements: mustafa.net/llm-tokens-per-second-benchmarks reports RTX 4090 + llama.cpp build 3520 + Q4_K_M + 2048 ctx + single batch = 135 tok/s at 7B, 78 tok/s at 13B, 42 tok/s at 34B. Independent cross-check: Llama 3.1 8B Q4_K_M on RTX 4090 measured at 95-110 tok/s via Ollama and 104 tok/s via llama.cpp at 16K context (markaicode.com, smeltcore.com).  ||  NO MODEL PAPER OR VENDOR DOC PUBLISHES tok/s - community benchmarks are the only source that exists for this metric, for any model in this sheet.  ||  WHY MEASURED IS LOWER THAN NAIVE BANDWIDTH MATH: attention is not purely bandwidth bound, kernel launch overhead and sampling cost real time, and throughput falls as the KV cache grows. Expect the longer 6-8K ipoefgfefs prompt to run BELOW these figures, which are 2K-context numbers.</t>
         </is>
       </c>
       <c r="X78" s="17" t="inlineStr">
@@ -17186,12 +17187,12 @@
       </c>
       <c r="AB78" s="17" t="inlineStr">
         <is>
-          <t>VQAv2 79.4% | TextVQA 60.2% | DocVQA 61.9%</t>
+          <t>DocVQA 79.3% | TextVQA 76.3% | ChartQA 77.5% (82.2% with PoT) | CountBenchQA 86.4% | OCRBench 61.2% | COCO object detection 51.2% | ScreenSpot F1@0.5 80.4%</t>
         </is>
       </c>
       <c r="AC78" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/vikhyatk/moondream2 - model card benchmark table. NO PAPER EXISTS. Single-source, vendor-self-reported, not independently verified. WEAKEST EVIDENCE IN THIS SHEET.</t>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vikhyatk/moondream2 model card.  ||  MAJOR CORRECTION: the previous revision quoted VQAv2 79.4 / TextVQA 60.2 / DocVQA 61.9. Those were STALE - the model has been substantially improved since. Current published figures are far higher (DocVQA 79.3, TextVQA 76.3).  ||  NEW CAPABILITY WORTH NOTING FOR A VMS: the card now reports COCO object detection 51.2% and ScreenSpot pointing 80.4% - this 2B model does detection and pointing, not just captioning.  ||  STILL NO PAPER. All figures are vendor-self-reported and not independently verified - the weakest evidence grade in this sheet, even though the numbers improved.</t>
         </is>
       </c>
       <c r="AD78" s="17" t="inlineStr">
@@ -17206,7 +17207,7 @@
       </c>
       <c r="AF78" s="24" t="inlineStr">
         <is>
-          <t>NO PAPER. Vendor-self-reported benchmarks only. Treat as indicative, not evidenced.</t>
+          <t>VERIFIED against card 2026-08-10 - previous figures were STALE and understated it. Params 1.9B -&gt; 2B. STILL NO PAPER: vendor-self-reported only.</t>
         </is>
       </c>
     </row>
@@ -17547,69 +17548,65 @@
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="27" t="inlineStr">
         <is>
-          <t>CORRECTIONS LOG - VERIFICATION PASS 2026-08-10</t>
+          <t>TOKEN RATE - PUBLISHED MEASUREMENTS BEHIND THE ESTIMATES</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="26" t="inlineStr">
         <is>
-          <t>Nine models were checked directly against their primary sources. SIX material errors were found in the</t>
+          <t>READ THIS BEFORE ANYONE CHALLENGES THE tok/s COLUMNS.</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="26" t="inlineStr">
-        <is>
-          <t>previous revision of this sheet and are corrected above. They are logged here rather than quietly fixed,</t>
-        </is>
-      </c>
+      <c r="A137" s="26" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="26" t="inlineStr">
         <is>
-          <t>because two of them change the ranking.</t>
+          <t>No model paper and no vendor model card publishes tokens/sec - not for a single model in this sheet.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="26" t="inlineStr"/>
+      <c r="A139" s="26" t="inlineStr">
+        <is>
+          <t>The metric depends on the inference engine, quantization, context length, batch size and hardware, none</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Granite 3.3 8B HumanEval:  67.1%  -&gt;  89.73%     [source: IBM model card, Evaluation Results table]</t>
+          <t>of which a model paper controls. Community benchmarks are the only published source that exists.</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     IMPACT: HIGH. Granite now has the HIGHEST HumanEval in this sheet, above Qwen2.5-Coder's 88.4%.</t>
-        </is>
-      </c>
+      <c r="A141" s="26" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     It is US-origin, Apache 2.0, has FIM and 128K context. It was ranked 3rd on a wrong number.</t>
+          <t>The tok/s columns are therefore ESTIMATES, and the efficiency factor in the formula is FITTED to the</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="26" t="inlineStr"/>
+      <c r="A143" s="26" t="inlineStr">
+        <is>
+          <t>measurements below rather than assumed. The measurements themselves are cited so they can be checked.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Qwen2.5-Coder 7B MultiPL-E C++:  63.4%  -&gt;  75.6%   [source: arxiv 2409.12186 Table 17]</t>
-        </is>
-      </c>
+      <c r="A144" s="26" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     IMPACT: MEDIUM. Understated. Strengthens the existing rank-1 case rather than changing it.</t>
+          <t>GPU - RTX 4090 24GB, llama.cpp build 3520, Q4_K_M, 2048 context, single batch (not server-batched):</t>
         </is>
       </c>
     </row>
@@ -17619,165 +17616,165 @@
     <row r="147">
       <c r="A147" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. DeepSeek-Coder-V2-Lite MultiPL-E C++:  56.5%  -&gt;  75.8%   [source: arxiv 2406.11931 Table 3]</t>
+          <t xml:space="preserve">    model size        measured tok/s      this sheet's estimate</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     IMPACT: HIGH. This is now the highest MEASURED C++ score in the sheet, marginally above Qwen.</t>
+          <t xml:space="preserve">    7B                135                 ~131 at 4.3 GB</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Offset by a restrictive custom licence and immature MoE tooling in llama.cpp.</t>
+          <t xml:space="preserve">    13B                78                 ~ 76 at 7.3 GB</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="26" t="inlineStr"/>
+      <c r="A150" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    34B                42                 (out of SLM range)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. CodeGemma 7B C++:  'NOT PUBLISHED'  -&gt;  BabelCode-HumanEval C++ 42.2%, BabelCode-MBPP C++ 56.7%</t>
+          <t xml:space="preserve">    70B (Q2_K)         18                 (out of SLM range)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     [source: Google model card]. IMPACT: LOW - the model is already eliminated by its 8K context.</t>
+          <t xml:space="preserve">    [source: mustafa.net/llm-tokens-per-second-benchmarks]</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Root cause: Google reports C++ under BabelCode, not MultiPL-E, so a MultiPL-E search missed it.</t>
-        </is>
-      </c>
+      <c r="A153" s="26" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     NOTE: BabelCode and MultiPL-E are different harnesses. 42.2 is NOT comparable to Qwen's 75.6.</t>
+          <t xml:space="preserve">  Independent cross-check on the exact model in this sheet:</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="26" t="inlineStr"/>
+      <c r="A155" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Llama 3.1 8B Q4_K_M, RTX 4090:  95-110 tok/s via Ollama;  104 tok/s via llama.cpp at 16K context</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Phi-4 GSM8K 91.5%:  REMOVED as unsourced.   [Microsoft publishes MGSM 80.6%, not GSM8K]</t>
+          <t xml:space="preserve">    [sources: markaicode.com Ollama vs llama.cpp benchmark; smeltcore.com]</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     IMPACT: LOW. Phi-4's case rests on HumanEval 82.6 and MMLU 84.8, both confirmed.</t>
-        </is>
-      </c>
+      <c r="A157" s="26" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="26" t="inlineStr"/>
+      <c r="A158" s="26" t="inlineStr">
+        <is>
+          <t>GPU - other cards, same conditions, useful if the ipoefgfefs server is not a 4090:</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6. Llama 3.2 3B HumanEval 57.8%:  REMOVED as unsourced.   [Meta publishes no HumanEval for the 3B]</t>
-        </is>
-      </c>
+      <c r="A159" s="26" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     IMPACT: MEDIUM. The edge candidate's code ability is UNMEASURED. It qualifies on size, not skill.</t>
+          <t xml:space="preserve">    RTX 3090 24GB      7B  95 tok/s    13B  55 tok/s    34B  28 tok/s</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="26" t="inlineStr"/>
+      <c r="A161" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RTX 4070S 12GB     7B  75 tok/s    13B  40 tok/s    34B  out of memory</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="26" t="inlineStr">
         <is>
-          <t>TWO LICENCE FINDINGS, both narrower than previously stated:</t>
+          <t xml:space="preserve">    RTX 3060 12GB      7B  45 tok/s    13B  22 tok/s    34B  out of memory</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="26" t="inlineStr"/>
+      <c r="A163" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [source: mustafa.net/llm-tokens-per-second-benchmarks]</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7. Llama 3.2 EU exclusion applies to MULTIMODAL models ONLY. The text-only 3B is unaffected -</t>
-        </is>
-      </c>
+      <c r="A164" s="26" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the previous flag on it is WITHDRAWN as over-cautious.</t>
+          <t>CPU - measured anchors:</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8. For the 11B Vision, the exclusion binds EU-DOMICILED DEVELOPERS, and expressly does NOT bind</t>
-        </is>
-      </c>
+      <c r="A166" s="26" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     end users of a product incorporating the model. A non-EU entity may build with it and supply</t>
+          <t xml:space="preserve">    AMD EPYC 7763            Llama 2 7B Q4_K_M      15 tok/s</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     EU customers. Exact licence wording is quoted in that model's Countries - SOURCE cell.</t>
+          <t xml:space="preserve">    Dual-socket EPYC 9334    Q4 7B-20B              20-28 tok/s</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="26" t="inlineStr"/>
+      <c r="A169" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Intel Sapphire Rapids 8480+  7B INT4            ~50 tok/s   (server CPU, not a desktop comparison)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="26" t="inlineStr">
         <is>
-          <t>CONFIRMED CORRECT, no change: Phi-4 (HumanEval 82.6, MMLU 84.8, MATH 80.4, 1920xH100 for 21 days),</t>
+          <t xml:space="preserve">    General desktop band     3B-7B Q4_K_M           4-15 tok/s</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="26" t="inlineStr">
         <is>
-          <t>Phi-3.5-mini (62.8 / 69 / 86.2, 512xH100 for 10 days), Llama 3.1 8B (HumanEval 72.6, GSM8K 84.5,</t>
+          <t xml:space="preserve">    [sources: blog.leaseweb.com EPYC LLM inference benchmark; promptquorum.com; myaihardware.com]</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="26" t="inlineStr">
-        <is>
-          <t>1.46M GPU-hours), Granite MMLU 65.54 and GSM8K 80.89, Qwen HumanEval 88.4 and MBPP 83.5,</t>
-        </is>
-      </c>
+      <c r="A172" s="26" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek HumanEval 81.1 and MBPP+ 68.8, Llama 3.2 3B MMLU 63.4 and GSM8K 77.7.</t>
+          <t xml:space="preserve">    This sheet estimates ~11 tok/s for a 7B Q4_K_M, inside the measured desktop band.</t>
         </is>
       </c>
     </row>
@@ -17787,281 +17784,952 @@
     <row r="175">
       <c r="A175" s="26" t="inlineStr">
         <is>
-          <t>ONE DISAMBIGUATION: Llama 3.1 8B MMLU is 69.4% standard 5-shot; the 73.0% previously quoted is the</t>
+          <t>THREE CAVEATS THAT APPLY TO EVERY tok/s FIGURE HERE:</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="26" t="inlineStr">
-        <is>
-          <t>chain-of-thought variant. Both are now shown so it is not compared unfairly against standard-metric models.</t>
-        </is>
-      </c>
+      <c r="A176" s="26" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="26" t="inlineStr"/>
+      <c r="A177" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. These are 2048-CONTEXT numbers. The ipoefgfefs prompt is 6-8K. Throughput falls as the KV cache</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="26" t="inlineStr">
         <is>
-          <t>STILL UNVERIFIED - the remaining CHECK cells:</t>
+          <t xml:space="preserve">     grows, so expect REAL rates BELOW the table above. The 16K-context cross-check (104 vs 135 tok/s)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  StarCoder2 15B (paper HTML would not yield the MultiPL-E table - needs the PDF read manually),</t>
+          <t xml:space="preserve">     shows roughly a 20-25% drop, which is the right order to plan against.</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mistral 7B, Gemma 3 4B, DeepSeek-R1-Distill-14B, and all seven vision models except where noted.</t>
-        </is>
-      </c>
+      <c r="A180" s="26" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  These are lower-stakes: none of them is in the shortlist.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="20" customHeight="1">
-      <c r="A183" s="25" t="inlineStr">
-        <is>
-          <t>PRIMARY SOURCE INDEX</t>
+          <t xml:space="preserve">  2. SINGLE REQUEST, NOT CONCURRENT. Under 4 simultaneous users on a 24GB card, published figures drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     to around 18 tok/s per user [source: localllm.in/blog/llamacpp-vram-requirements-for-local-llms].</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     If the workflow builder serves multiple engineers at once, size against that, not against 135.</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="28" t="inlineStr">
-        <is>
-          <t>PAPER / DOCUMENT                                     COVERS                         LOCATION</t>
-        </is>
-      </c>
+      <c r="A184" s="26" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="26" t="inlineStr">
         <is>
-          <t>Qwen2.5-Coder Technical Report                       Qwen2.5-Coder 7B               arxiv.org/abs/2409.12186</t>
+          <t xml:space="preserve">  3. ENGINE MATTERS AS MUCH AS HARDWARE. These are llama.cpp figures. vLLM and SGLang trade single-</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="26" t="inlineStr">
         <is>
-          <t>Phi-4 Technical Report                               Phi-4 14B                      arxiv.org/abs/2412.08905</t>
+          <t xml:space="preserve">     request latency for far higher aggregate throughput under concurrency, so these numbers do not</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="26" t="inlineStr">
         <is>
-          <t>Phi-3 Technical Report                               Phi-3.5-mini, Phi-3.5-Vision   arxiv.org/abs/2404.14219</t>
+          <t xml:space="preserve">     transfer across engines.</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="26" t="inlineStr">
-        <is>
-          <t>The Llama 3 Herd of Models                           Llama 3.1 8B                   arxiv.org/abs/2407.21783</t>
-        </is>
-      </c>
+      <c r="A188" s="26" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="26" t="inlineStr">
         <is>
-          <t>StarCoder 2 and The Stack v2                         StarCoder2 15B                 arxiv.org/abs/2402.19173</t>
+          <t>BOTTOM LINE FOR REVIEW: use tok/s to RANK the models against each other, which is what it is reliable</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-Coder-V2                                    DeepSeek-Coder-V2-Lite         arxiv.org/abs/2406.11931</t>
+          <t>for. Do not quote it as a performance commitment. The only number that settles real throughput on the</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-R1                                          DeepSeek-R1-Distill-Qwen-14B   arxiv.org/abs/2501.12948</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="26" t="inlineStr">
-        <is>
-          <t>Mistral 7B                                           Mistral 7B Instruct v0.3       arxiv.org/abs/2310.06825</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="26" t="inlineStr">
-        <is>
-          <t>Gemma 3 Technical Report                             Gemma 3 4B                     arxiv.org/abs/2503.19786</t>
+          <t>ipoefgfefs workload is a measurement on ipo's own hardware at the real 6-8K prompt length.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="28" t="inlineStr">
+        <is>
+          <t>CORRECTIONS LOG - VERIFICATION PASS 2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="26" t="inlineStr">
         <is>
-          <t>Qwen2-VL                                             Qwen2-VL 7B                    arxiv.org/abs/2409.12191</t>
+          <t>Nine models were checked directly against their primary sources. SIX material errors were found in the</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="26" t="inlineStr">
         <is>
-          <t>PaliGemma                                            PaliGemma 3B                   arxiv.org/abs/2407.07726</t>
+          <t>previous revision of this sheet and are corrected above. They are logged here rather than quietly fixed,</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="26" t="inlineStr">
         <is>
-          <t>Improved Baselines with Visual Instruction Tuning    LLaVA-1.5 / 1.6                arxiv.org/abs/2310.03744</t>
+          <t>because two of them change the ranking.</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="26" t="inlineStr">
-        <is>
-          <t>HumanEval / Evaluating LLMs Trained on Code          HumanEval benchmark definition arxiv.org/abs/2107.03374</t>
-        </is>
-      </c>
+      <c r="A197" s="26" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="26" t="inlineStr">
         <is>
-          <t>MultiPL-E                                            MultiPL-E C++ benchmark definition arxiv.org/abs/2208.08227</t>
+          <t xml:space="preserve">  1. Granite 3.3 8B HumanEval:  67.1%  -&gt;  89.73%     [source: IBM model card, Evaluation Results table]</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="26" t="inlineStr">
         <is>
-          <t>MMLU / Measuring Massive Multitask Understanding     MMLU benchmark definition      arxiv.org/abs/2009.03300</t>
+          <t xml:space="preserve">     IMPACT: HIGH. Granite now has the HIGHEST HumanEval in this sheet, above Qwen2.5-Coder's 88.4%.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="26" t="inlineStr">
         <is>
-          <t>MMMU                                                 MMMU benchmark definition      arxiv.org/abs/2311.16502</t>
+          <t xml:space="preserve">     It is US-origin, Apache 2.0, has FIM and 128K context. It was ranked 3rd on a wrong number.</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="26" t="inlineStr">
-        <is>
-          <t>DocVQA                                               DocVQA benchmark definition    arxiv.org/abs/2007.00398</t>
-        </is>
-      </c>
+      <c r="A201" s="26" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="26" t="inlineStr">
         <is>
-          <t>LoRA                                                 Fine-tuning method             arxiv.org/abs/2106.09685</t>
+          <t xml:space="preserve">  2. Qwen2.5-Coder 7B MultiPL-E C++:  63.4%  -&gt;  75.6%   [source: arxiv 2409.12186 Table 17]</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="26" t="inlineStr">
         <is>
-          <t>QLoRA                                                Fine-tuning method             arxiv.org/abs/2305.14314</t>
+          <t xml:space="preserve">     IMPACT: MEDIUM. Understated. Strengthens the existing rank-1 case rather than changing it.</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="26" t="inlineStr">
-        <is>
-          <t>vLLM / PagedAttention                                Inference engine               arxiv.org/abs/2309.06180</t>
-        </is>
-      </c>
+      <c r="A204" s="26" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="26" t="inlineStr">
         <is>
-          <t>SGLang / RadixAttention                              Inference engine               arxiv.org/abs/2312.07104</t>
+          <t xml:space="preserve">  3. DeepSeek-Coder-V2-Lite MultiPL-E C++:  56.5%  -&gt;  75.8%   [source: arxiv 2406.11931 Table 3]</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="26" t="inlineStr">
         <is>
-          <t>llama.cpp - supported backends and build docs        ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
+          <t xml:space="preserve">     IMPACT: HIGH. This is now the highest MEASURED C++ score in the sheet, marginally above Qwen.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="26" t="inlineStr">
         <is>
-          <t>llama.cpp k-quants PR #1684                          ALL quantization accuracy deltas github.com/ggml-org/llama.cpp/pull/1684</t>
+          <t xml:space="preserve">     Offset by a restrictive custom licence and immature MoE tooling in llama.cpp.</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="26" t="inlineStr">
-        <is>
-          <t>NVIDIA Ada GPU Architecture Whitepaper               RTX 4090 memory bandwidth (1008 GB/s) nvidia.com - Ada whitepaper</t>
-        </is>
-      </c>
+      <c r="A208" s="26" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="26" t="inlineStr">
         <is>
-          <t>Apache License 2.0                                   Licence text                   apache.org/licenses/LICENSE-2.0</t>
+          <t xml:space="preserve">  4. CodeGemma 7B C++:  'NOT PUBLISHED'  -&gt;  BabelCode-HumanEval C++ 42.2%, BabelCode-MBPP C++ 56.7%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="26" t="inlineStr">
         <is>
-          <t>Llama 3.x Community Licence                          Licence text incl. EU multimodal clause llama.com/llama3_3/license</t>
+          <t xml:space="preserve">     [source: Google model card]. IMPACT: LOW - the model is already eliminated by its 8K context.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="26" t="inlineStr">
         <is>
-          <t>Gemma Terms of Use                                   Licence text                   ai.google.dev/gemma/terms</t>
+          <t xml:space="preserve">     Root cause: Google reports C++ under BabelCode, not MultiPL-E, so a MultiPL-E search missed it.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="26" t="inlineStr">
         <is>
-          <t>BigCode OpenRAIL-M v1                                Licence text incl. flow-down duty bigcode-project.org/docs/pages/model-license</t>
+          <t xml:space="preserve">     NOTE: BabelCode and MultiPL-E are different harnesses. 42.2 is NOT comparable to Qwen's 75.6.</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="26" t="inlineStr">
-        <is>
-          <t>DeepSeek Model Licence                               Licence text incl. use restrictions github.com/deepseek-ai/DeepSeek-LLM</t>
-        </is>
-      </c>
+      <c r="A213" s="26" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="26" t="inlineStr">
         <is>
-          <t>NDAA Section 889 / FAR 52.204-25                     Component-origin procurement rule acquisition.gov/far/52.204-25</t>
+          <t xml:space="preserve">  5. Phi-4 GSM8K 91.5%:  REMOVED as unsourced.   [Microsoft publishes MGSM 80.6%, not GSM8K]</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="26" t="inlineStr">
         <is>
+          <t xml:space="preserve">     IMPACT: LOW. Phi-4's case rests on HumanEval 82.6 and MMLU 84.8, both confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="26" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Llama 3.2 3B HumanEval 57.8%:  REMOVED as unsourced.   [Meta publishes no HumanEval for the 3B]</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     IMPACT: MEDIUM. The edge candidate's code ability is UNMEASURED. It qualifies on size, not skill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="26" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="26" t="inlineStr">
+        <is>
+          <t>TWO LICENCE FINDINGS, both narrower than previously stated:</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="26" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Llama 3.2 EU exclusion applies to MULTIMODAL models ONLY. The text-only 3B is unaffected -</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     the previous flag on it is WITHDRAWN as over-cautious.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. For the 11B Vision, the exclusion binds EU-DOMICILED DEVELOPERS, and expressly does NOT bind</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     end users of a product incorporating the model. A non-EU entity may build with it and supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     EU customers. Exact licence wording is quoted in that model's Countries - SOURCE cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="26" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="26" t="inlineStr">
+        <is>
+          <t>CONFIRMED CORRECT, no change: Phi-4 (HumanEval 82.6, MMLU 84.8, MATH 80.4, 1920xH100 for 21 days),</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="26" t="inlineStr">
+        <is>
+          <t>Phi-3.5-mini (62.8 / 69 / 86.2, 512xH100 for 10 days), Llama 3.1 8B (HumanEval 72.6, GSM8K 84.5,</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="26" t="inlineStr">
+        <is>
+          <t>1.46M GPU-hours), Granite MMLU 65.54 and GSM8K 80.89, Qwen HumanEval 88.4 and MBPP 83.5,</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek HumanEval 81.1 and MBPP+ 68.8, Llama 3.2 3B MMLU 63.4 and GSM8K 77.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="26" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="26" t="inlineStr">
+        <is>
+          <t>ONE DISAMBIGUATION: Llama 3.1 8B MMLU is 69.4% standard 5-shot; the 73.0% previously quoted is the</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="26" t="inlineStr">
+        <is>
+          <t>chain-of-thought variant. Both are now shown so it is not compared unfairly against standard-metric models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="26" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="26" t="inlineStr">
+        <is>
+          <t>STILL UNVERIFIED - the remaining CHECK cells:</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  StarCoder2 15B (paper HTML would not yield the MultiPL-E table - needs the PDF read manually),</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mistral 7B, Gemma 3 4B, DeepSeek-R1-Distill-14B, and all seven vision models except where noted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  These are lower-stakes: none of them is in the shortlist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="26" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="26" t="inlineStr">
+        <is>
+          <t>PASS 2 - REMAINING 11 MODELS CHECKED, 2026-08-10. Eight further corrections:</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="26" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  PaliGemma 3B context:  8,192  -&gt;  512 tokens     [source: Google model card]</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      IMPACT: HIGH. Wrong by a factor of 16. At 512 tokens it cannot hold the ipoefgfefs prompt</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      at all. Categorically disqualified, not merely marginal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="26" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10. Moondream2 benchmarks were STALE and UNDERSTATED the model:</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      DocVQA 61.9 -&gt; 79.3, TextVQA 60.2 -&gt; 76.3. Params 1.9B -&gt; 2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      It now also reports COCO object detection 51.2% and ScreenSpot pointing 80.4% - a 2B model</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      doing detection and pointing is directly interesting for a VMS. Still no paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="26" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11. StarCoder2 training hardware:  1024 x A100-80GB  -&gt;  1024 x H100.  HumanEval 46.4 -&gt; 46.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="26" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  12. DeepSeek-R1-Distill-14B code ability: previously recorded UNKNOWN. WRONG - the card gives</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      LiveCodeBench 53.1% and Codeforces 1481. HumanEval and C++ remain unpublished, and the base</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      is Qwen2.5 general (NOT Coder), so that caveat still stands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="26" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  13. InternVL2 8B MMMU:  51.2  -&gt;  51.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="26" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  14. LLaVA-1.6 13B licence: 'Apache 2.0, check base' -&gt; LLAMA 2 COMMUNITY LICENSE, stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      directly on the HuggingFace card. The licence-chain warning was right; the label was not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Benchmarks remain UNCONFIRMED - the card publishes none and 1.5 vs 1.6 figures are conflated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="26" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  15. Gemma 3 4B: context is 128K INPUT but 8,192 OUTPUT. Added MBPP 46.0, MMMU 39.2, GSM8K 38.4,</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      MATH 24.2. Training hardware is TPUv4p/v5p/v5e, not TPUv5p alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="26" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  16. Qwen2-VL: added TextVQA 84.3% - highest text-in-image score in this sheet. With DocVQA 94.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      it is the clear LPR / plate-reading candidate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="26" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="26" t="inlineStr">
+        <is>
+          <t>TWO EVALUATION-SETTING TRAPS, both of the kind a reviewer will probe:</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="26" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a) Llama 3.2 11B Vision - the model card carries TWO tables. BASE PRETRAINED shows MMMU 41.7,</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     DocVQA 62.3, ChartQA 39.4. INSTRUCTION-TUNED shows MMMU 50.7, DocVQA 88.4, ChartQA 83.4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Secondary sources quote the pretrained figures as if they were the instruct ones. This sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     uses the INSTRUCT table, which is correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="26" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  b) PaliGemma figures are single-task FINE-TUNED transfer results, confirmed by the card, NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     zero-shot. They must not be compared against zero-shot numbers from Qwen2-VL, Phi-3.5-Vision</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     or InternVL2 elsewhere in this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="26" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="26" t="inlineStr">
+        <is>
+          <t>CONFIRMED CORRECT IN PASS 2: Phi-3.5-Vision (81.9 / 43.0 / 72.0, 256xA100 for 6 days, 500B tokens),</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="26" t="inlineStr">
+        <is>
+          <t>Gemma 3 4B HumanEval 36.0 and MMLU 59.6, Qwen2-VL MMMU 54.1 / DocVQA 94.5 / MathVista 58.2,</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="26" t="inlineStr">
+        <is>
+          <t>R1-Distill MATH-500 93.9 and AIME 69.7, InternVL2 MMBench 81.7 and DocVQA 91.6, Llama 3.2 11B</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="26" t="inlineStr">
+        <is>
+          <t>Vision MMMU 50.7 / DocVQA 88.4 / ChartQA 83.4, StarCoder2 context 16,384.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="26" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="26" t="inlineStr">
+        <is>
+          <t>WHAT REMAINS UNVERIFIED AFTER BOTH PASSES - the honest residue:</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="26" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - StarCoder2 MultiPL-E C++ 41.4%: not on the model card, and the arXiv HTML would not yield the</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    table. Needs a manual read of the 2402.19173 PDF, Section 7.1.2. Marked UNVERIFIED in the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Mistral 7B: the v0.3 card publishes NO benchmarks at all. MMLU 62.5% is from the v0.1 paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (a DIFFERENT model version); HumanEval 36.5% is leaderboard-only. Weakest evidence in the sheet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    though the model is not a contender so the stakes are low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - LLaVA-1.6: all benchmark figures unconfirmed, per correction 14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="26" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Every other cell across all 19 models has now been checked against a primary source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="20" customHeight="1">
+      <c r="A297" s="25" t="inlineStr">
+        <is>
+          <t>PRIMARY SOURCE INDEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="29" t="inlineStr">
+        <is>
+          <t>PAPER / DOCUMENT                                     COVERS                         LOCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2.5-Coder Technical Report                       Qwen2.5-Coder 7B               arxiv.org/abs/2409.12186</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="26" t="inlineStr">
+        <is>
+          <t>Phi-4 Technical Report                               Phi-4 14B                      arxiv.org/abs/2412.08905</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="26" t="inlineStr">
+        <is>
+          <t>Phi-3 Technical Report                               Phi-3.5-mini, Phi-3.5-Vision   arxiv.org/abs/2404.14219</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="26" t="inlineStr">
+        <is>
+          <t>The Llama 3 Herd of Models                           Llama 3.1 8B                   arxiv.org/abs/2407.21783</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="26" t="inlineStr">
+        <is>
+          <t>StarCoder 2 and The Stack v2                         StarCoder2 15B                 arxiv.org/abs/2402.19173</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-Coder-V2                                    DeepSeek-Coder-V2-Lite         arxiv.org/abs/2406.11931</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-R1                                          DeepSeek-R1-Distill-Qwen-14B   arxiv.org/abs/2501.12948</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="26" t="inlineStr">
+        <is>
+          <t>Mistral 7B                                           Mistral 7B Instruct v0.3       arxiv.org/abs/2310.06825</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="26" t="inlineStr">
+        <is>
+          <t>Gemma 3 Technical Report                             Gemma 3 4B                     arxiv.org/abs/2503.19786</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2-VL                                             Qwen2-VL 7B                    arxiv.org/abs/2409.12191</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="26" t="inlineStr">
+        <is>
+          <t>PaliGemma                                            PaliGemma 3B                   arxiv.org/abs/2407.07726</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="26" t="inlineStr">
+        <is>
+          <t>Improved Baselines with Visual Instruction Tuning    LLaVA-1.5 / 1.6                arxiv.org/abs/2310.03744</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="26" t="inlineStr">
+        <is>
+          <t>HumanEval / Evaluating LLMs Trained on Code          HumanEval benchmark definition arxiv.org/abs/2107.03374</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="26" t="inlineStr">
+        <is>
+          <t>MultiPL-E                                            MultiPL-E C++ benchmark definition arxiv.org/abs/2208.08227</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="26" t="inlineStr">
+        <is>
+          <t>MMLU / Measuring Massive Multitask Understanding     MMLU benchmark definition      arxiv.org/abs/2009.03300</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="26" t="inlineStr">
+        <is>
+          <t>MMMU                                                 MMMU benchmark definition      arxiv.org/abs/2311.16502</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="26" t="inlineStr">
+        <is>
+          <t>DocVQA                                               DocVQA benchmark definition    arxiv.org/abs/2007.00398</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="26" t="inlineStr">
+        <is>
+          <t>LoRA                                                 Fine-tuning method             arxiv.org/abs/2106.09685</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="26" t="inlineStr">
+        <is>
+          <t>QLoRA                                                Fine-tuning method             arxiv.org/abs/2305.14314</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="26" t="inlineStr">
+        <is>
+          <t>vLLM / PagedAttention                                Inference engine               arxiv.org/abs/2309.06180</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="26" t="inlineStr">
+        <is>
+          <t>SGLang / RadixAttention                              Inference engine               arxiv.org/abs/2312.07104</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp - supported backends and build docs        ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp k-quants PR #1684                          ALL quantization accuracy deltas github.com/ggml-org/llama.cpp/pull/1684</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="26" t="inlineStr">
+        <is>
+          <t>NVIDIA Ada GPU Architecture Whitepaper               RTX 4090 memory bandwidth (1008 GB/s) nvidia.com - Ada whitepaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="26" t="inlineStr">
+        <is>
+          <t>Apache License 2.0                                   Licence text                   apache.org/licenses/LICENSE-2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="26" t="inlineStr">
+        <is>
+          <t>Llama 3.x Community Licence                          Licence text incl. EU multimodal clause llama.com/llama3_3/license</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="26" t="inlineStr">
+        <is>
+          <t>Gemma Terms of Use                                   Licence text                   ai.google.dev/gemma/terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="26" t="inlineStr">
+        <is>
+          <t>BigCode OpenRAIL-M v1                                Licence text incl. flow-down duty bigcode-project.org/docs/pages/model-license</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek Model Licence                               Licence text incl. use restrictions github.com/deepseek-ai/DeepSeek-LLM</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="26" t="inlineStr">
+        <is>
+          <t>NDAA Section 889 / FAR 52.204-25                     Component-origin procurement rule acquisition.gov/far/52.204-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="26" t="inlineStr">
+        <is>
           <t>EvalPlus Leaderboard                                 Mistral 7B HumanEval (no paper exists) evalplus.github.io/leaderboard.html</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="26" t="inlineStr">
+    <row r="330">
+      <c r="A330" s="26" t="inlineStr">
         <is>
           <t>OpenCompass Multimodal Leaderboard                   InternVL2 (partly leaderboard-sourced) rank.opencompass.org.cn/leaderboard-multimodal</t>
         </is>
@@ -18069,7 +18737,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:AF78"/>
-  <mergeCells count="136">
+  <mergeCells count="249">
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="A80:AF80"/>
     <mergeCell ref="A81:AF81"/>
@@ -18172,6 +18840,7 @@
     <mergeCell ref="A179:AF179"/>
     <mergeCell ref="A180:AF180"/>
     <mergeCell ref="A181:AF181"/>
+    <mergeCell ref="A182:AF182"/>
     <mergeCell ref="A183:AF183"/>
     <mergeCell ref="A184:AF184"/>
     <mergeCell ref="A185:AF185"/>
@@ -18181,7 +18850,6 @@
     <mergeCell ref="A189:AF189"/>
     <mergeCell ref="A190:AF190"/>
     <mergeCell ref="A191:AF191"/>
-    <mergeCell ref="A192:AF192"/>
     <mergeCell ref="A193:AF193"/>
     <mergeCell ref="A194:AF194"/>
     <mergeCell ref="A195:AF195"/>
@@ -18206,6 +18874,119 @@
     <mergeCell ref="A214:AF214"/>
     <mergeCell ref="A215:AF215"/>
     <mergeCell ref="A216:AF216"/>
+    <mergeCell ref="A217:AF217"/>
+    <mergeCell ref="A218:AF218"/>
+    <mergeCell ref="A219:AF219"/>
+    <mergeCell ref="A220:AF220"/>
+    <mergeCell ref="A221:AF221"/>
+    <mergeCell ref="A222:AF222"/>
+    <mergeCell ref="A223:AF223"/>
+    <mergeCell ref="A224:AF224"/>
+    <mergeCell ref="A225:AF225"/>
+    <mergeCell ref="A226:AF226"/>
+    <mergeCell ref="A227:AF227"/>
+    <mergeCell ref="A228:AF228"/>
+    <mergeCell ref="A229:AF229"/>
+    <mergeCell ref="A230:AF230"/>
+    <mergeCell ref="A231:AF231"/>
+    <mergeCell ref="A232:AF232"/>
+    <mergeCell ref="A233:AF233"/>
+    <mergeCell ref="A234:AF234"/>
+    <mergeCell ref="A235:AF235"/>
+    <mergeCell ref="A236:AF236"/>
+    <mergeCell ref="A237:AF237"/>
+    <mergeCell ref="A238:AF238"/>
+    <mergeCell ref="A239:AF239"/>
+    <mergeCell ref="A240:AF240"/>
+    <mergeCell ref="A241:AF241"/>
+    <mergeCell ref="A242:AF242"/>
+    <mergeCell ref="A243:AF243"/>
+    <mergeCell ref="A244:AF244"/>
+    <mergeCell ref="A245:AF245"/>
+    <mergeCell ref="A246:AF246"/>
+    <mergeCell ref="A247:AF247"/>
+    <mergeCell ref="A248:AF248"/>
+    <mergeCell ref="A249:AF249"/>
+    <mergeCell ref="A250:AF250"/>
+    <mergeCell ref="A251:AF251"/>
+    <mergeCell ref="A252:AF252"/>
+    <mergeCell ref="A253:AF253"/>
+    <mergeCell ref="A254:AF254"/>
+    <mergeCell ref="A255:AF255"/>
+    <mergeCell ref="A256:AF256"/>
+    <mergeCell ref="A257:AF257"/>
+    <mergeCell ref="A258:AF258"/>
+    <mergeCell ref="A259:AF259"/>
+    <mergeCell ref="A260:AF260"/>
+    <mergeCell ref="A261:AF261"/>
+    <mergeCell ref="A262:AF262"/>
+    <mergeCell ref="A263:AF263"/>
+    <mergeCell ref="A264:AF264"/>
+    <mergeCell ref="A265:AF265"/>
+    <mergeCell ref="A266:AF266"/>
+    <mergeCell ref="A267:AF267"/>
+    <mergeCell ref="A268:AF268"/>
+    <mergeCell ref="A269:AF269"/>
+    <mergeCell ref="A270:AF270"/>
+    <mergeCell ref="A271:AF271"/>
+    <mergeCell ref="A272:AF272"/>
+    <mergeCell ref="A273:AF273"/>
+    <mergeCell ref="A274:AF274"/>
+    <mergeCell ref="A275:AF275"/>
+    <mergeCell ref="A276:AF276"/>
+    <mergeCell ref="A277:AF277"/>
+    <mergeCell ref="A278:AF278"/>
+    <mergeCell ref="A279:AF279"/>
+    <mergeCell ref="A280:AF280"/>
+    <mergeCell ref="A281:AF281"/>
+    <mergeCell ref="A282:AF282"/>
+    <mergeCell ref="A283:AF283"/>
+    <mergeCell ref="A284:AF284"/>
+    <mergeCell ref="A285:AF285"/>
+    <mergeCell ref="A286:AF286"/>
+    <mergeCell ref="A287:AF287"/>
+    <mergeCell ref="A288:AF288"/>
+    <mergeCell ref="A289:AF289"/>
+    <mergeCell ref="A290:AF290"/>
+    <mergeCell ref="A291:AF291"/>
+    <mergeCell ref="A292:AF292"/>
+    <mergeCell ref="A293:AF293"/>
+    <mergeCell ref="A294:AF294"/>
+    <mergeCell ref="A295:AF295"/>
+    <mergeCell ref="A297:AF297"/>
+    <mergeCell ref="A298:AF298"/>
+    <mergeCell ref="A299:AF299"/>
+    <mergeCell ref="A300:AF300"/>
+    <mergeCell ref="A301:AF301"/>
+    <mergeCell ref="A302:AF302"/>
+    <mergeCell ref="A303:AF303"/>
+    <mergeCell ref="A304:AF304"/>
+    <mergeCell ref="A305:AF305"/>
+    <mergeCell ref="A306:AF306"/>
+    <mergeCell ref="A307:AF307"/>
+    <mergeCell ref="A308:AF308"/>
+    <mergeCell ref="A309:AF309"/>
+    <mergeCell ref="A310:AF310"/>
+    <mergeCell ref="A311:AF311"/>
+    <mergeCell ref="A312:AF312"/>
+    <mergeCell ref="A313:AF313"/>
+    <mergeCell ref="A314:AF314"/>
+    <mergeCell ref="A315:AF315"/>
+    <mergeCell ref="A316:AF316"/>
+    <mergeCell ref="A317:AF317"/>
+    <mergeCell ref="A318:AF318"/>
+    <mergeCell ref="A319:AF319"/>
+    <mergeCell ref="A320:AF320"/>
+    <mergeCell ref="A321:AF321"/>
+    <mergeCell ref="A322:AF322"/>
+    <mergeCell ref="A323:AF323"/>
+    <mergeCell ref="A324:AF324"/>
+    <mergeCell ref="A325:AF325"/>
+    <mergeCell ref="A326:AF326"/>
+    <mergeCell ref="A327:AF327"/>
+    <mergeCell ref="A328:AF328"/>
+    <mergeCell ref="A329:AF329"/>
+    <mergeCell ref="A330:AF330"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipoefgfefs_SLM_Matrix.xlsx
+++ b/ipoefgfefs_SLM_Matrix.xlsx
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
+          <t>MultiPL-E C++ 41.4% | HumanEval 46.3% | HumanEval+ 37.8% | MBPP 66.2% | MBPP+ 53.1% | CanItEdit descriptive 43.08% / lazy 38.45% | RepoBench-v1.1 ES 74.08% | CRUXEval-I 48.1% / O 47.1% | GSM8K-PAL 65.1% | FIM Python 48.4% (SEE SOURCE - BUGGED)</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
+          <t>MultiPL-E C++ 41.4% | HumanEval 46.3% | HumanEval+ 37.8% | MBPP 66.2% | MBPP+ 53.1% | CanItEdit descriptive 43.08% / lazy 38.45% | RepoBench-v1.1 ES 74.08% | CRUXEval-I 48.1% / O 47.1% | GSM8K-PAL 65.1% | FIM Python 48.4% (SEE SOURCE - BUGGED)</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
+          <t>MultiPL-E C++ 41.4% | HumanEval 46.3% | HumanEval+ 37.8% | MBPP 66.2% | MBPP+ 53.1% | CanItEdit descriptive 43.08% / lazy 38.45% | RepoBench-v1.1 ES 74.08% | CRUXEval-I 48.1% / O 47.1% | GSM8K-PAL 65.1% | FIM Python 48.4% (SEE SOURCE - BUGGED)</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
+          <t>MultiPL-E C++ 41.4% | HumanEval 46.3% | HumanEval+ 37.8% | MBPP 66.2% | MBPP+ 53.1% | CanItEdit descriptive 43.08% / lazy 38.45% | RepoBench-v1.1 ES 74.08% | CRUXEval-I 48.1% / O 47.1% | GSM8K-PAL 65.1% | FIM Python 48.4% (SEE SOURCE - BUGGED)</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>MMLU 62.5% | HumanEval 36.5% (leaderboard only, NOT in the paper)</t>
+          <t>NO PRIMARY BENCHMARKS EXIST FOR v0.3. MMLU 62.5% is a v0.1 figure; HumanEval 36.5% is leaderboard-only. SEE SOURCE.</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>MMLU 62.5% | HumanEval 36.5% (leaderboard only, NOT in the paper)</t>
+          <t>NO PRIMARY BENCHMARKS EXIST FOR v0.3. MMLU 62.5% is a v0.1 figure; HumanEval 36.5% is leaderboard-only. SEE SOURCE.</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>MMLU 62.5% | HumanEval 36.5% (leaderboard only, NOT in the paper)</t>
+          <t>NO PRIMARY BENCHMARKS EXIST FOR v0.3. MMLU 62.5% is a v0.1 figure; HumanEval 36.5% is leaderboard-only. SEE SOURCE.</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>MMLU 62.5% | HumanEval 36.5% (leaderboard only, NOT in the paper)</t>
+          <t>NO PRIMARY BENCHMARKS EXIST FOR v0.3. MMLU 62.5% is a v0.1 figure; HumanEval 36.5% is leaderboard-only. SEE SOURCE.</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>MMBench 70.0% | TextVQA 67.1% | MMMU 35.9%</t>
+          <t>VQAv2 82.8% | ScienceQA 73.6% | TextVQA 67.1% | GQA 65.4% | VisWiz 60.5% | MMMU val 36.2%</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>MMBench 70.0% | TextVQA 67.1% | MMMU 35.9%</t>
+          <t>VQAv2 82.8% | ScienceQA 73.6% | TextVQA 67.1% | GQA 65.4% | VisWiz 60.5% | MMMU val 36.2%</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>MMBench 70.0% | TextVQA 67.1% | MMMU 35.9%</t>
+          <t>VQAv2 82.8% | ScienceQA 73.6% | TextVQA 67.1% | GQA 65.4% | VisWiz 60.5% | MMMU val 36.2%</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>MMBench 70.0% | TextVQA 67.1% | MMMU 35.9%</t>
+          <t>VQAv2 82.8% | ScienceQA 73.6% | TextVQA 67.1% | GQA 65.4% | VisWiz 60.5% | MMMU val 36.2%</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr">
@@ -5453,7 +5453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF330"/>
+  <dimension ref="A1:AF375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/bigcode/starcoder2-15b - config.json. NOTE the marketing name understates the actual parameter count; this sits at the top of the SLM range.</t>
+          <t>VERIFIED 2026-08-10 from arxiv 2402.19173 PDF TABLE 6 (Model architecture details): hidden_dim 6144, n_heads 48, n_kv_heads 4 (GQA), n_layers 40, vocab 49152, RoPE. head_dim = 6144/48 = 128, which is the geometry used for the KV-cache calculation in this sheet. NOTE the marketing name understates the actual parameter count; this sits at the top of the SLM range.</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1024 x NVIDIA H100, 4+ trillion tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1024 x NVIDIA H100; 4.1T tokens, 1M iterations, batch 4.1M (15B)  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="S23" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/bigcode/starcoder2-15b - config.json max_position_embeddings = 16384; sliding-window attention of 4096 also configured. CHECK the interaction between the two.</t>
+          <t>VERIFIED 2026-08-10 from arxiv 2402.19173 PDF Section 6.3 and TABLE 8: base models trained at sequence length 4,096, then long-context pre-trained on 200B further tokens at 16,384 context with a 4,096 sliding window and FlashAttention-2. Model card confirms 16,384. The 4,096 sliding window is the practical attention span - relevant when reasoning about a 6-8K prompt.</t>
         </is>
       </c>
       <c r="T23" s="21" t="n">
@@ -8817,22 +8817,22 @@
       </c>
       <c r="Z23" s="21" t="inlineStr">
         <is>
-          <t>Code completion across 600+ programming languages; repository-level context</t>
+          <t>Repository-level code completion; code editing (CanItEdit). FIM supported but MEASURABLY BROKEN (see source)</t>
         </is>
       </c>
       <c r="AA23" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2402.19173 - The Stack v2 covers 600+ languages; paper describes repo-level training context.</t>
+          <t>VERIFIED 2026-08-10 by direct read of the arxiv 2402.19173 PDF.  ||  Repo-level completion: TABLE 17 (RepoBench v1.1) and Section 7.6. Code editing: TABLE 13 (CanItEdit).  ||  TWO PAPER-DOCUMENTED WEAKNESSES THAT MATTER FOR ipoefgfefs AND ARE NOT VISIBLE IN ANY HEADLINE SCORE:  ||  (1) FIM IS BROKEN. TABLE 16 caption, verbatim: 'Due to an implementation bug, FIM was incorrect for most of the training of StarCoder2-15B.' Section 7.5 text: 'StarCoder2-15B underperforms on FIM.' Measured FIM is Python 48.4 / Java 60.5 / JS 54.7 against StarCoderBase-15B at 62 / 73 / 74. Listing FIM as a STRENGTH of this model would be wrong - it is a regression.  ||  (2) C++ SPECIFICALLY IS WEAK. Section 7.2.1, paraphrased from the paper: StarCoder2-15B underperforms on C++ because roughly ONE THIRD of the C++ it generates is incomplete - the paper's example is an unexpected break immediately after the beginning of a for loop. That is exactly the failure mode a 5-gate cross-compile pipeline would hit on every run.</t>
         </is>
       </c>
       <c r="AB23" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
+          <t>MultiPL-E C++ 41.4% | HumanEval 46.3% | HumanEval+ 37.8% | MBPP 66.2% | MBPP+ 53.1% | CanItEdit descriptive 43.08% / lazy 38.45% | RepoBench-v1.1 ES 74.08% | CRUXEval-I 48.1% / O 47.1% | GSM8K-PAL 65.1% | FIM Python 48.4% (SEE SOURCE - BUGGED)</t>
         </is>
       </c>
       <c r="AC23" s="15" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card.  ||  CORRECTION: HumanEval is 46.3%, not 46.4% as previously stated.  ||  STILL UNVERIFIED: the MultiPL-E C++ 41.4% figure is NOT on the model card and could not be extracted from the arXiv HTML - it needs a manual read of the 2402.19173 PDF, Section 7.1.2 (MultiPL-E). Treat 41.4 as unconfirmed.  ||  RepoBench 74.08% is repository-level edit similarity - the most relevant published number here for retry-patching behaviour.</t>
+          <t>FULLY VERIFIED 2026-08-10 by direct read of the arxiv 2402.19173 PDF.  ||  MultiPL-E C++ 41.4% = TABLE 10 (Pass@1 on MultiPL-E, 50 samples per problem, temperature 0.2, top-p 0.95). For context in the same table: CodeLlama-13B C++ 37.4, DeepSeekCoder-33B C++ 51.2, StarCoder2-7B C++ 33.6.  ||  HumanEval 46.3 / HumanEval+ 37.8 / MBPP 66.2 / MBPP+ 53.1 = TABLE 9 (greedy decoding, EvalPlus framework).  ||  CanItEdit code-EDITING 43.08 descriptive / 38.45 lazy = TABLE 13 - the most relevant published benchmark in this sheet for a compile-retry loop, since it measures editing existing code rather than writing it fresh.  ||  RepoBench-v1.1 Python edit-similarity 74.08 = TABLE 17.  ||  CRUXEval-I 48.1 / CRUXEval-O 47.1 = TABLE 15.  ||  GSM8K-PAL 65.1 = TABLE 14.  ||  FIM Python 48.4 / Java 60.5 / JavaScript 54.7 = TABLE 16. CRITICAL: these FIM scores are LOWER than StarCoder2-15B's own predecessor StarCoderBase-15B (62 / 73 / 74) and far below CodeLlama-13B (74.5 / 80 / 85). The Table 16 caption states verbatim: 'Due to an implementation bug, FIM was incorrect for most of the training of StarCoder2-15B.' Full detail in the Secondary Purpose - SOURCE cell.</t>
         </is>
       </c>
       <c r="AD23" s="21" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AF23" s="18" t="inlineStr">
         <is>
-          <t>MOSTLY VERIFIED 2026-08-10. HumanEval corrected to 46.3, training HW corrected to H100. MultiPL-E C++ 41.4 REMAINS UNVERIFIED - needs manual PDF read.</t>
+          <t>FULLY VERIFIED 2026-08-10 by direct PDF read; every figure cited to a table number. C++ 41.4 CONFIRMED (Table 10). NEW FINDINGS: FIM is BUGGED (Table 16 caption) and C++ output is 1/3 incomplete (Sec 7.2.1). Both argue against this model for ipoefgfefs.</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/bigcode/starcoder2-15b - config.json. NOTE the marketing name understates the actual parameter count; this sits at the top of the SLM range.</t>
+          <t>VERIFIED 2026-08-10 from arxiv 2402.19173 PDF TABLE 6 (Model architecture details): hidden_dim 6144, n_heads 48, n_kv_heads 4 (GQA), n_layers 40, vocab 49152, RoPE. head_dim = 6144/48 = 128, which is the geometry used for the KV-cache calculation in this sheet. NOTE the marketing name understates the actual parameter count; this sits at the top of the SLM range.</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="L24" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1024 x NVIDIA H100, 4+ trillion tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1024 x NVIDIA H100; 4.1T tokens, 1M iterations, batch 4.1M (15B)  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="S24" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/bigcode/starcoder2-15b - config.json max_position_embeddings = 16384; sliding-window attention of 4096 also configured. CHECK the interaction between the two.</t>
+          <t>VERIFIED 2026-08-10 from arxiv 2402.19173 PDF Section 6.3 and TABLE 8: base models trained at sequence length 4,096, then long-context pre-trained on 200B further tokens at 16,384 context with a 4,096 sliding window and FlashAttention-2. Model card confirms 16,384. The 4,096 sliding window is the practical attention span - relevant when reasoning about a 6-8K prompt.</t>
         </is>
       </c>
       <c r="T24" s="21" t="n">
@@ -8969,22 +8969,22 @@
       </c>
       <c r="Z24" s="21" t="inlineStr">
         <is>
-          <t>Code completion across 600+ programming languages; repository-level context</t>
+          <t>Repository-level code completion; code editing (CanItEdit). FIM supported but MEASURABLY BROKEN (see source)</t>
         </is>
       </c>
       <c r="AA24" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2402.19173 - The Stack v2 covers 600+ languages; paper describes repo-level training context.</t>
+          <t>VERIFIED 2026-08-10 by direct read of the arxiv 2402.19173 PDF.  ||  Repo-level completion: TABLE 17 (RepoBench v1.1) and Section 7.6. Code editing: TABLE 13 (CanItEdit).  ||  TWO PAPER-DOCUMENTED WEAKNESSES THAT MATTER FOR ipoefgfefs AND ARE NOT VISIBLE IN ANY HEADLINE SCORE:  ||  (1) FIM IS BROKEN. TABLE 16 caption, verbatim: 'Due to an implementation bug, FIM was incorrect for most of the training of StarCoder2-15B.' Section 7.5 text: 'StarCoder2-15B underperforms on FIM.' Measured FIM is Python 48.4 / Java 60.5 / JS 54.7 against StarCoderBase-15B at 62 / 73 / 74. Listing FIM as a STRENGTH of this model would be wrong - it is a regression.  ||  (2) C++ SPECIFICALLY IS WEAK. Section 7.2.1, paraphrased from the paper: StarCoder2-15B underperforms on C++ because roughly ONE THIRD of the C++ it generates is incomplete - the paper's example is an unexpected break immediately after the beginning of a for loop. That is exactly the failure mode a 5-gate cross-compile pipeline would hit on every run.</t>
         </is>
       </c>
       <c r="AB24" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
+          <t>MultiPL-E C++ 41.4% | HumanEval 46.3% | HumanEval+ 37.8% | MBPP 66.2% | MBPP+ 53.1% | CanItEdit descriptive 43.08% / lazy 38.45% | RepoBench-v1.1 ES 74.08% | CRUXEval-I 48.1% / O 47.1% | GSM8K-PAL 65.1% | FIM Python 48.4% (SEE SOURCE - BUGGED)</t>
         </is>
       </c>
       <c r="AC24" s="15" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card.  ||  CORRECTION: HumanEval is 46.3%, not 46.4% as previously stated.  ||  STILL UNVERIFIED: the MultiPL-E C++ 41.4% figure is NOT on the model card and could not be extracted from the arXiv HTML - it needs a manual read of the 2402.19173 PDF, Section 7.1.2 (MultiPL-E). Treat 41.4 as unconfirmed.  ||  RepoBench 74.08% is repository-level edit similarity - the most relevant published number here for retry-patching behaviour.</t>
+          <t>FULLY VERIFIED 2026-08-10 by direct read of the arxiv 2402.19173 PDF.  ||  MultiPL-E C++ 41.4% = TABLE 10 (Pass@1 on MultiPL-E, 50 samples per problem, temperature 0.2, top-p 0.95). For context in the same table: CodeLlama-13B C++ 37.4, DeepSeekCoder-33B C++ 51.2, StarCoder2-7B C++ 33.6.  ||  HumanEval 46.3 / HumanEval+ 37.8 / MBPP 66.2 / MBPP+ 53.1 = TABLE 9 (greedy decoding, EvalPlus framework).  ||  CanItEdit code-EDITING 43.08 descriptive / 38.45 lazy = TABLE 13 - the most relevant published benchmark in this sheet for a compile-retry loop, since it measures editing existing code rather than writing it fresh.  ||  RepoBench-v1.1 Python edit-similarity 74.08 = TABLE 17.  ||  CRUXEval-I 48.1 / CRUXEval-O 47.1 = TABLE 15.  ||  GSM8K-PAL 65.1 = TABLE 14.  ||  FIM Python 48.4 / Java 60.5 / JavaScript 54.7 = TABLE 16. CRITICAL: these FIM scores are LOWER than StarCoder2-15B's own predecessor StarCoderBase-15B (62 / 73 / 74) and far below CodeLlama-13B (74.5 / 80 / 85). The Table 16 caption states verbatim: 'Due to an implementation bug, FIM was incorrect for most of the training of StarCoder2-15B.' Full detail in the Secondary Purpose - SOURCE cell.</t>
         </is>
       </c>
       <c r="AD24" s="21" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="AF24" s="18" t="inlineStr">
         <is>
-          <t>MOSTLY VERIFIED 2026-08-10. HumanEval corrected to 46.3, training HW corrected to H100. MultiPL-E C++ 41.4 REMAINS UNVERIFIED - needs manual PDF read.</t>
+          <t>FULLY VERIFIED 2026-08-10 by direct PDF read; every figure cited to a table number. C++ 41.4 CONFIRMED (Table 10). NEW FINDINGS: FIM is BUGGED (Table 16 caption) and C++ output is 1/3 incomplete (Sec 7.2.1). Both argue against this model for ipoefgfefs.</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/bigcode/starcoder2-15b - config.json. NOTE the marketing name understates the actual parameter count; this sits at the top of the SLM range.</t>
+          <t>VERIFIED 2026-08-10 from arxiv 2402.19173 PDF TABLE 6 (Model architecture details): hidden_dim 6144, n_heads 48, n_kv_heads 4 (GQA), n_layers 40, vocab 49152, RoPE. head_dim = 6144/48 = 128, which is the geometry used for the KV-cache calculation in this sheet. NOTE the marketing name understates the actual parameter count; this sits at the top of the SLM range.</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1024 x NVIDIA H100, 4+ trillion tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1024 x NVIDIA H100; 4.1T tokens, 1M iterations, batch 4.1M (15B)  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="S25" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/bigcode/starcoder2-15b - config.json max_position_embeddings = 16384; sliding-window attention of 4096 also configured. CHECK the interaction between the two.</t>
+          <t>VERIFIED 2026-08-10 from arxiv 2402.19173 PDF Section 6.3 and TABLE 8: base models trained at sequence length 4,096, then long-context pre-trained on 200B further tokens at 16,384 context with a 4,096 sliding window and FlashAttention-2. Model card confirms 16,384. The 4,096 sliding window is the practical attention span - relevant when reasoning about a 6-8K prompt.</t>
         </is>
       </c>
       <c r="T25" s="21" t="n">
@@ -9121,22 +9121,22 @@
       </c>
       <c r="Z25" s="21" t="inlineStr">
         <is>
-          <t>Code completion across 600+ programming languages; repository-level context</t>
+          <t>Repository-level code completion; code editing (CanItEdit). FIM supported but MEASURABLY BROKEN (see source)</t>
         </is>
       </c>
       <c r="AA25" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2402.19173 - The Stack v2 covers 600+ languages; paper describes repo-level training context.</t>
+          <t>VERIFIED 2026-08-10 by direct read of the arxiv 2402.19173 PDF.  ||  Repo-level completion: TABLE 17 (RepoBench v1.1) and Section 7.6. Code editing: TABLE 13 (CanItEdit).  ||  TWO PAPER-DOCUMENTED WEAKNESSES THAT MATTER FOR ipoefgfefs AND ARE NOT VISIBLE IN ANY HEADLINE SCORE:  ||  (1) FIM IS BROKEN. TABLE 16 caption, verbatim: 'Due to an implementation bug, FIM was incorrect for most of the training of StarCoder2-15B.' Section 7.5 text: 'StarCoder2-15B underperforms on FIM.' Measured FIM is Python 48.4 / Java 60.5 / JS 54.7 against StarCoderBase-15B at 62 / 73 / 74. Listing FIM as a STRENGTH of this model would be wrong - it is a regression.  ||  (2) C++ SPECIFICALLY IS WEAK. Section 7.2.1, paraphrased from the paper: StarCoder2-15B underperforms on C++ because roughly ONE THIRD of the C++ it generates is incomplete - the paper's example is an unexpected break immediately after the beginning of a for loop. That is exactly the failure mode a 5-gate cross-compile pipeline would hit on every run.</t>
         </is>
       </c>
       <c r="AB25" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
+          <t>MultiPL-E C++ 41.4% | HumanEval 46.3% | HumanEval+ 37.8% | MBPP 66.2% | MBPP+ 53.1% | CanItEdit descriptive 43.08% / lazy 38.45% | RepoBench-v1.1 ES 74.08% | CRUXEval-I 48.1% / O 47.1% | GSM8K-PAL 65.1% | FIM Python 48.4% (SEE SOURCE - BUGGED)</t>
         </is>
       </c>
       <c r="AC25" s="15" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card.  ||  CORRECTION: HumanEval is 46.3%, not 46.4% as previously stated.  ||  STILL UNVERIFIED: the MultiPL-E C++ 41.4% figure is NOT on the model card and could not be extracted from the arXiv HTML - it needs a manual read of the 2402.19173 PDF, Section 7.1.2 (MultiPL-E). Treat 41.4 as unconfirmed.  ||  RepoBench 74.08% is repository-level edit similarity - the most relevant published number here for retry-patching behaviour.</t>
+          <t>FULLY VERIFIED 2026-08-10 by direct read of the arxiv 2402.19173 PDF.  ||  MultiPL-E C++ 41.4% = TABLE 10 (Pass@1 on MultiPL-E, 50 samples per problem, temperature 0.2, top-p 0.95). For context in the same table: CodeLlama-13B C++ 37.4, DeepSeekCoder-33B C++ 51.2, StarCoder2-7B C++ 33.6.  ||  HumanEval 46.3 / HumanEval+ 37.8 / MBPP 66.2 / MBPP+ 53.1 = TABLE 9 (greedy decoding, EvalPlus framework).  ||  CanItEdit code-EDITING 43.08 descriptive / 38.45 lazy = TABLE 13 - the most relevant published benchmark in this sheet for a compile-retry loop, since it measures editing existing code rather than writing it fresh.  ||  RepoBench-v1.1 Python edit-similarity 74.08 = TABLE 17.  ||  CRUXEval-I 48.1 / CRUXEval-O 47.1 = TABLE 15.  ||  GSM8K-PAL 65.1 = TABLE 14.  ||  FIM Python 48.4 / Java 60.5 / JavaScript 54.7 = TABLE 16. CRITICAL: these FIM scores are LOWER than StarCoder2-15B's own predecessor StarCoderBase-15B (62 / 73 / 74) and far below CodeLlama-13B (74.5 / 80 / 85). The Table 16 caption states verbatim: 'Due to an implementation bug, FIM was incorrect for most of the training of StarCoder2-15B.' Full detail in the Secondary Purpose - SOURCE cell.</t>
         </is>
       </c>
       <c r="AD25" s="21" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="AF25" s="18" t="inlineStr">
         <is>
-          <t>MOSTLY VERIFIED 2026-08-10. HumanEval corrected to 46.3, training HW corrected to H100. MultiPL-E C++ 41.4 REMAINS UNVERIFIED - needs manual PDF read.</t>
+          <t>FULLY VERIFIED 2026-08-10 by direct PDF read; every figure cited to a table number. C++ 41.4 CONFIRMED (Table 10). NEW FINDINGS: FIM is BUGGED (Table 16 caption) and C++ output is 1/3 incomplete (Sec 7.2.1). Both argue against this model for ipoefgfefs.</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/bigcode/starcoder2-15b - config.json. NOTE the marketing name understates the actual parameter count; this sits at the top of the SLM range.</t>
+          <t>VERIFIED 2026-08-10 from arxiv 2402.19173 PDF TABLE 6 (Model architecture details): hidden_dim 6144, n_heads 48, n_kv_heads 4 (GQA), n_layers 40, vocab 49152, RoPE. head_dim = 6144/48 = 128, which is the geometry used for the KV-cache calculation in this sheet. NOTE the marketing name understates the actual parameter count; this sits at the top of the SLM range.</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="L26" s="21" t="inlineStr">
         <is>
-          <t>TRAINING: 1024 x NVIDIA H100, 4+ trillion tokens  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
+          <t>TRAINING: 1024 x NVIDIA H100; 4.1T tokens, 1M iterations, batch 4.1M (15B)  ||  INFERENCE (what ipoefgfefs actually runs on) - llama.cpp: NVIDIA CUDA compute capability 5.0+ (Maxwell: GTX 750 Ti, GTX 900 series and newer); AMD ROCm RDNA2+ (RX 6000 series); Apple Metal (M1 and later); Vulkan; SYCL/oneAPI (Intel); CPU x86-64 AVX2/AVX-512 and aarch64 NEON.</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="S26" s="15" t="inlineStr">
         <is>
-          <t>huggingface.co/bigcode/starcoder2-15b - config.json max_position_embeddings = 16384; sliding-window attention of 4096 also configured. CHECK the interaction between the two.</t>
+          <t>VERIFIED 2026-08-10 from arxiv 2402.19173 PDF Section 6.3 and TABLE 8: base models trained at sequence length 4,096, then long-context pre-trained on 200B further tokens at 16,384 context with a 4,096 sliding window and FlashAttention-2. Model card confirms 16,384. The 4,096 sliding window is the practical attention span - relevant when reasoning about a 6-8K prompt.</t>
         </is>
       </c>
       <c r="T26" s="21" t="n">
@@ -9273,22 +9273,22 @@
       </c>
       <c r="Z26" s="21" t="inlineStr">
         <is>
-          <t>Code completion across 600+ programming languages; repository-level context</t>
+          <t>Repository-level code completion; code editing (CanItEdit). FIM supported but MEASURABLY BROKEN (see source)</t>
         </is>
       </c>
       <c r="AA26" s="15" t="inlineStr">
         <is>
-          <t>arxiv 2402.19173 - The Stack v2 covers 600+ languages; paper describes repo-level training context.</t>
+          <t>VERIFIED 2026-08-10 by direct read of the arxiv 2402.19173 PDF.  ||  Repo-level completion: TABLE 17 (RepoBench v1.1) and Section 7.6. Code editing: TABLE 13 (CanItEdit).  ||  TWO PAPER-DOCUMENTED WEAKNESSES THAT MATTER FOR ipoefgfefs AND ARE NOT VISIBLE IN ANY HEADLINE SCORE:  ||  (1) FIM IS BROKEN. TABLE 16 caption, verbatim: 'Due to an implementation bug, FIM was incorrect for most of the training of StarCoder2-15B.' Section 7.5 text: 'StarCoder2-15B underperforms on FIM.' Measured FIM is Python 48.4 / Java 60.5 / JS 54.7 against StarCoderBase-15B at 62 / 73 / 74. Listing FIM as a STRENGTH of this model would be wrong - it is a regression.  ||  (2) C++ SPECIFICALLY IS WEAK. Section 7.2.1, paraphrased from the paper: StarCoder2-15B underperforms on C++ because roughly ONE THIRD of the C++ it generates is incomplete - the paper's example is an unexpected break immediately after the beginning of a for loop. That is exactly the failure mode a 5-gate cross-compile pipeline would hit on every run.</t>
         </is>
       </c>
       <c r="AB26" s="21" t="inlineStr">
         <is>
-          <t>HumanEval 46.3% | HumanEval+ 37.8% | CruxEval-I 48.1% | DS-1000 33.8% | GSM8K-PAL 65.1% | RepoBench-v1.1 74.08% | MultiPL-E C++ 41.4% (UNVERIFIED)</t>
+          <t>MultiPL-E C++ 41.4% | HumanEval 46.3% | HumanEval+ 37.8% | MBPP 66.2% | MBPP+ 53.1% | CanItEdit descriptive 43.08% / lazy 38.45% | RepoBench-v1.1 ES 74.08% | CRUXEval-I 48.1% / O 47.1% | GSM8K-PAL 65.1% | FIM Python 48.4% (SEE SOURCE - BUGGED)</t>
         </is>
       </c>
       <c r="AC26" s="15" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-08-10 against huggingface.co/bigcode/starcoder2-15b model card.  ||  CORRECTION: HumanEval is 46.3%, not 46.4% as previously stated.  ||  STILL UNVERIFIED: the MultiPL-E C++ 41.4% figure is NOT on the model card and could not be extracted from the arXiv HTML - it needs a manual read of the 2402.19173 PDF, Section 7.1.2 (MultiPL-E). Treat 41.4 as unconfirmed.  ||  RepoBench 74.08% is repository-level edit similarity - the most relevant published number here for retry-patching behaviour.</t>
+          <t>FULLY VERIFIED 2026-08-10 by direct read of the arxiv 2402.19173 PDF.  ||  MultiPL-E C++ 41.4% = TABLE 10 (Pass@1 on MultiPL-E, 50 samples per problem, temperature 0.2, top-p 0.95). For context in the same table: CodeLlama-13B C++ 37.4, DeepSeekCoder-33B C++ 51.2, StarCoder2-7B C++ 33.6.  ||  HumanEval 46.3 / HumanEval+ 37.8 / MBPP 66.2 / MBPP+ 53.1 = TABLE 9 (greedy decoding, EvalPlus framework).  ||  CanItEdit code-EDITING 43.08 descriptive / 38.45 lazy = TABLE 13 - the most relevant published benchmark in this sheet for a compile-retry loop, since it measures editing existing code rather than writing it fresh.  ||  RepoBench-v1.1 Python edit-similarity 74.08 = TABLE 17.  ||  CRUXEval-I 48.1 / CRUXEval-O 47.1 = TABLE 15.  ||  GSM8K-PAL 65.1 = TABLE 14.  ||  FIM Python 48.4 / Java 60.5 / JavaScript 54.7 = TABLE 16. CRITICAL: these FIM scores are LOWER than StarCoder2-15B's own predecessor StarCoderBase-15B (62 / 73 / 74) and far below CodeLlama-13B (74.5 / 80 / 85). The Table 16 caption states verbatim: 'Due to an implementation bug, FIM was incorrect for most of the training of StarCoder2-15B.' Full detail in the Secondary Purpose - SOURCE cell.</t>
         </is>
       </c>
       <c r="AD26" s="21" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AF26" s="18" t="inlineStr">
         <is>
-          <t>MOSTLY VERIFIED 2026-08-10. HumanEval corrected to 46.3, training HW corrected to H100. MultiPL-E C++ 41.4 REMAINS UNVERIFIED - needs manual PDF read.</t>
+          <t>FULLY VERIFIED 2026-08-10 by direct PDF read; every figure cited to a table number. C++ 41.4 CONFIRMED (Table 10). NEW FINDINGS: FIM is BUGGED (Table 16 caption) and C++ output is 1/3 incomplete (Sec 7.2.1). Both argue against this model for ipoefgfefs.</t>
         </is>
       </c>
     </row>
@@ -11259,12 +11259,12 @@
       </c>
       <c r="AB39" s="21" t="inlineStr">
         <is>
-          <t>MMLU 62.5% | HumanEval 36.5% (leaderboard only, NOT in the paper)</t>
+          <t>NO PRIMARY BENCHMARKS EXIST FOR v0.3. MMLU 62.5% is a v0.1 figure; HumanEval 36.5% is leaderboard-only. SEE SOURCE.</t>
         </is>
       </c>
       <c r="AC39" s="15" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-08-10: huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores AT ALL. The card covers installation, usage and function calling only.  ||  MMLU 62.5% comes from arxiv 2310.06825 (the v0.1 paper), NOT from the v0.3 card - be careful, these are different model versions.  ||  HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard. NO PRIMARY SOURCE EXISTS. This is the weakest-evidenced model in the sheet.</t>
+          <t>VERIFIED 2026-08-10, AND THE FINDING IS THAT NO SOLID REFERENCE EXISTS.  ||  (1) huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores at all - the card covers installation, usage and function calling only.  ||  (2) MMLU 62.5% comes from arxiv 2310.06825, which is the v0.1 BASE model paper. It is a DIFFERENT MODEL VERSION and should not be presented as a v0.3 Instruct figure. Secondary sources put v0.3 nearer 59.9-60.0%, but those are not primary either.  ||  (3) HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard whose table is JavaScript-rendered and could not be captured for citation.  ||  CONCLUSION: this is the only model in the sheet with NO citable primary benchmark. It is retained for completeness but must not be ranked on these numbers. It is not a contender for the C++ role in any case.</t>
         </is>
       </c>
       <c r="AD39" s="21" t="inlineStr">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="AB40" s="21" t="inlineStr">
         <is>
-          <t>MMLU 62.5% | HumanEval 36.5% (leaderboard only, NOT in the paper)</t>
+          <t>NO PRIMARY BENCHMARKS EXIST FOR v0.3. MMLU 62.5% is a v0.1 figure; HumanEval 36.5% is leaderboard-only. SEE SOURCE.</t>
         </is>
       </c>
       <c r="AC40" s="15" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-08-10: huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores AT ALL. The card covers installation, usage and function calling only.  ||  MMLU 62.5% comes from arxiv 2310.06825 (the v0.1 paper), NOT from the v0.3 card - be careful, these are different model versions.  ||  HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard. NO PRIMARY SOURCE EXISTS. This is the weakest-evidenced model in the sheet.</t>
+          <t>VERIFIED 2026-08-10, AND THE FINDING IS THAT NO SOLID REFERENCE EXISTS.  ||  (1) huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores at all - the card covers installation, usage and function calling only.  ||  (2) MMLU 62.5% comes from arxiv 2310.06825, which is the v0.1 BASE model paper. It is a DIFFERENT MODEL VERSION and should not be presented as a v0.3 Instruct figure. Secondary sources put v0.3 nearer 59.9-60.0%, but those are not primary either.  ||  (3) HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard whose table is JavaScript-rendered and could not be captured for citation.  ||  CONCLUSION: this is the only model in the sheet with NO citable primary benchmark. It is retained for completeness but must not be ranked on these numbers. It is not a contender for the C++ role in any case.</t>
         </is>
       </c>
       <c r="AD40" s="21" t="inlineStr">
@@ -11563,12 +11563,12 @@
       </c>
       <c r="AB41" s="21" t="inlineStr">
         <is>
-          <t>MMLU 62.5% | HumanEval 36.5% (leaderboard only, NOT in the paper)</t>
+          <t>NO PRIMARY BENCHMARKS EXIST FOR v0.3. MMLU 62.5% is a v0.1 figure; HumanEval 36.5% is leaderboard-only. SEE SOURCE.</t>
         </is>
       </c>
       <c r="AC41" s="15" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-08-10: huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores AT ALL. The card covers installation, usage and function calling only.  ||  MMLU 62.5% comes from arxiv 2310.06825 (the v0.1 paper), NOT from the v0.3 card - be careful, these are different model versions.  ||  HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard. NO PRIMARY SOURCE EXISTS. This is the weakest-evidenced model in the sheet.</t>
+          <t>VERIFIED 2026-08-10, AND THE FINDING IS THAT NO SOLID REFERENCE EXISTS.  ||  (1) huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores at all - the card covers installation, usage and function calling only.  ||  (2) MMLU 62.5% comes from arxiv 2310.06825, which is the v0.1 BASE model paper. It is a DIFFERENT MODEL VERSION and should not be presented as a v0.3 Instruct figure. Secondary sources put v0.3 nearer 59.9-60.0%, but those are not primary either.  ||  (3) HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard whose table is JavaScript-rendered and could not be captured for citation.  ||  CONCLUSION: this is the only model in the sheet with NO citable primary benchmark. It is retained for completeness but must not be ranked on these numbers. It is not a contender for the C++ role in any case.</t>
         </is>
       </c>
       <c r="AD41" s="21" t="inlineStr">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="AB42" s="21" t="inlineStr">
         <is>
-          <t>MMLU 62.5% | HumanEval 36.5% (leaderboard only, NOT in the paper)</t>
+          <t>NO PRIMARY BENCHMARKS EXIST FOR v0.3. MMLU 62.5% is a v0.1 figure; HumanEval 36.5% is leaderboard-only. SEE SOURCE.</t>
         </is>
       </c>
       <c r="AC42" s="15" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-08-10: huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores AT ALL. The card covers installation, usage and function calling only.  ||  MMLU 62.5% comes from arxiv 2310.06825 (the v0.1 paper), NOT from the v0.3 card - be careful, these are different model versions.  ||  HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard. NO PRIMARY SOURCE EXISTS. This is the weakest-evidenced model in the sheet.</t>
+          <t>VERIFIED 2026-08-10, AND THE FINDING IS THAT NO SOLID REFERENCE EXISTS.  ||  (1) huggingface.co/mistralai/Mistral-7B-Instruct-v0.3 publishes NO benchmark scores at all - the card covers installation, usage and function calling only.  ||  (2) MMLU 62.5% comes from arxiv 2310.06825, which is the v0.1 BASE model paper. It is a DIFFERENT MODEL VERSION and should not be presented as a v0.3 Instruct figure. Secondary sources put v0.3 nearer 59.9-60.0%, but those are not primary either.  ||  (3) HumanEval 36.5% is from evalplus.github.io/leaderboard.html, a third-party leaderboard whose table is JavaScript-rendered and could not be captured for citation.  ||  CONCLUSION: this is the only model in the sheet with NO citable primary benchmark. It is retained for completeness but must not be ranked on these numbers. It is not a contender for the C++ role in any case.</t>
         </is>
       </c>
       <c r="AD42" s="21" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="AB67" s="17" t="inlineStr">
         <is>
-          <t>MMBench 70.0% | TextVQA 67.1% | MMMU 35.9%</t>
+          <t>VQAv2 82.8% | ScienceQA 73.6% | TextVQA 67.1% | GQA 65.4% | VisWiz 60.5% | MMMU val 36.2%</t>
         </is>
       </c>
       <c r="AC67" s="15" t="inlineStr">
         <is>
-          <t>PARTIALLY VERIFIED 2026-08-10: huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf publishes NO benchmark scores at all. The quoted figures come from arxiv 2310.03744 (which covers LLaVA-1.5) and the llava-vl.github.io blog (which covers 1.6/NeXT).  ||  UNRESOLVED: 1.5 and 1.6 numbers are routinely conflated in secondary sources and this sheet cannot currently prove which release each figure belongs to. Treat all LLaVA benchmark figures here as unconfirmed.</t>
+          <t>VERIFIED 2026-08-10 against llava-vl.github.io/blog/2024-01-30-llava-next/ - the official LLaVA-NeXT release blog. Figures are for LLaVA-NeXT-Vicuna-13B at 672x672 resolution.  ||  CORRECTION: MMMU is 36.2% (val), not 35.9% as previously stated - 35.9 is the LLaVA-1.5 figure from arxiv 2310.03744. This is exactly the 1.5-vs-1.6 conflation the previous revision warned about, and this sheet had fallen into it.  ||  MMBench 70.0% has been REMOVED - it does not appear in the NeXT blog tables for the 13B and could not be sourced.  ||  DocVQA is NOT published for this variant.  ||  NOTE: the HuggingFace card llava-hf/llava-v1.6-vicuna-13b-hf publishes no benchmarks at all; the release blog is the primary source.</t>
         </is>
       </c>
       <c r="AD67" s="17" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="AF67" s="18" t="inlineStr">
         <is>
-          <t>LICENCE CONFIRMED AS LLAMA 2 (not Apache 2.0) 2026-08-10. Benchmarks UNCONFIRMED - card publishes none, and 1.5 vs 1.6 figures are conflated in secondary sources. Context 4K disqualifies it regardless.</t>
+          <t>VERIFIED 2026-08-10. Licence confirmed LLAMA 2. Benchmarks now sourced to the official LLaVA-NeXT blog; MMMU corrected 35.9 (a 1.5 figure) -&gt; 36.2, MMBench 70.0 removed as unsourceable. Context 4K disqualifies it regardless.</t>
         </is>
       </c>
     </row>
@@ -15667,12 +15667,12 @@
       </c>
       <c r="AB68" s="17" t="inlineStr">
         <is>
-          <t>MMBench 70.0% | TextVQA 67.1% | MMMU 35.9%</t>
+          <t>VQAv2 82.8% | ScienceQA 73.6% | TextVQA 67.1% | GQA 65.4% | VisWiz 60.5% | MMMU val 36.2%</t>
         </is>
       </c>
       <c r="AC68" s="15" t="inlineStr">
         <is>
-          <t>PARTIALLY VERIFIED 2026-08-10: huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf publishes NO benchmark scores at all. The quoted figures come from arxiv 2310.03744 (which covers LLaVA-1.5) and the llava-vl.github.io blog (which covers 1.6/NeXT).  ||  UNRESOLVED: 1.5 and 1.6 numbers are routinely conflated in secondary sources and this sheet cannot currently prove which release each figure belongs to. Treat all LLaVA benchmark figures here as unconfirmed.</t>
+          <t>VERIFIED 2026-08-10 against llava-vl.github.io/blog/2024-01-30-llava-next/ - the official LLaVA-NeXT release blog. Figures are for LLaVA-NeXT-Vicuna-13B at 672x672 resolution.  ||  CORRECTION: MMMU is 36.2% (val), not 35.9% as previously stated - 35.9 is the LLaVA-1.5 figure from arxiv 2310.03744. This is exactly the 1.5-vs-1.6 conflation the previous revision warned about, and this sheet had fallen into it.  ||  MMBench 70.0% has been REMOVED - it does not appear in the NeXT blog tables for the 13B and could not be sourced.  ||  DocVQA is NOT published for this variant.  ||  NOTE: the HuggingFace card llava-hf/llava-v1.6-vicuna-13b-hf publishes no benchmarks at all; the release blog is the primary source.</t>
         </is>
       </c>
       <c r="AD68" s="17" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="AF68" s="18" t="inlineStr">
         <is>
-          <t>LICENCE CONFIRMED AS LLAMA 2 (not Apache 2.0) 2026-08-10. Benchmarks UNCONFIRMED - card publishes none, and 1.5 vs 1.6 figures are conflated in secondary sources. Context 4K disqualifies it regardless.</t>
+          <t>VERIFIED 2026-08-10. Licence confirmed LLAMA 2. Benchmarks now sourced to the official LLaVA-NeXT blog; MMMU corrected 35.9 (a 1.5 figure) -&gt; 36.2, MMBench 70.0 removed as unsourceable. Context 4K disqualifies it regardless.</t>
         </is>
       </c>
     </row>
@@ -15819,12 +15819,12 @@
       </c>
       <c r="AB69" s="17" t="inlineStr">
         <is>
-          <t>MMBench 70.0% | TextVQA 67.1% | MMMU 35.9%</t>
+          <t>VQAv2 82.8% | ScienceQA 73.6% | TextVQA 67.1% | GQA 65.4% | VisWiz 60.5% | MMMU val 36.2%</t>
         </is>
       </c>
       <c r="AC69" s="15" t="inlineStr">
         <is>
-          <t>PARTIALLY VERIFIED 2026-08-10: huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf publishes NO benchmark scores at all. The quoted figures come from arxiv 2310.03744 (which covers LLaVA-1.5) and the llava-vl.github.io blog (which covers 1.6/NeXT).  ||  UNRESOLVED: 1.5 and 1.6 numbers are routinely conflated in secondary sources and this sheet cannot currently prove which release each figure belongs to. Treat all LLaVA benchmark figures here as unconfirmed.</t>
+          <t>VERIFIED 2026-08-10 against llava-vl.github.io/blog/2024-01-30-llava-next/ - the official LLaVA-NeXT release blog. Figures are for LLaVA-NeXT-Vicuna-13B at 672x672 resolution.  ||  CORRECTION: MMMU is 36.2% (val), not 35.9% as previously stated - 35.9 is the LLaVA-1.5 figure from arxiv 2310.03744. This is exactly the 1.5-vs-1.6 conflation the previous revision warned about, and this sheet had fallen into it.  ||  MMBench 70.0% has been REMOVED - it does not appear in the NeXT blog tables for the 13B and could not be sourced.  ||  DocVQA is NOT published for this variant.  ||  NOTE: the HuggingFace card llava-hf/llava-v1.6-vicuna-13b-hf publishes no benchmarks at all; the release blog is the primary source.</t>
         </is>
       </c>
       <c r="AD69" s="17" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="AF69" s="18" t="inlineStr">
         <is>
-          <t>LICENCE CONFIRMED AS LLAMA 2 (not Apache 2.0) 2026-08-10. Benchmarks UNCONFIRMED - card publishes none, and 1.5 vs 1.6 figures are conflated in secondary sources. Context 4K disqualifies it regardless.</t>
+          <t>VERIFIED 2026-08-10. Licence confirmed LLAMA 2. Benchmarks now sourced to the official LLaVA-NeXT blog; MMMU corrected 35.9 (a 1.5 figure) -&gt; 36.2, MMBench 70.0 removed as unsourceable. Context 4K disqualifies it regardless.</t>
         </is>
       </c>
     </row>
@@ -15971,12 +15971,12 @@
       </c>
       <c r="AB70" s="17" t="inlineStr">
         <is>
-          <t>MMBench 70.0% | TextVQA 67.1% | MMMU 35.9%</t>
+          <t>VQAv2 82.8% | ScienceQA 73.6% | TextVQA 67.1% | GQA 65.4% | VisWiz 60.5% | MMMU val 36.2%</t>
         </is>
       </c>
       <c r="AC70" s="15" t="inlineStr">
         <is>
-          <t>PARTIALLY VERIFIED 2026-08-10: huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf publishes NO benchmark scores at all. The quoted figures come from arxiv 2310.03744 (which covers LLaVA-1.5) and the llava-vl.github.io blog (which covers 1.6/NeXT).  ||  UNRESOLVED: 1.5 and 1.6 numbers are routinely conflated in secondary sources and this sheet cannot currently prove which release each figure belongs to. Treat all LLaVA benchmark figures here as unconfirmed.</t>
+          <t>VERIFIED 2026-08-10 against llava-vl.github.io/blog/2024-01-30-llava-next/ - the official LLaVA-NeXT release blog. Figures are for LLaVA-NeXT-Vicuna-13B at 672x672 resolution.  ||  CORRECTION: MMMU is 36.2% (val), not 35.9% as previously stated - 35.9 is the LLaVA-1.5 figure from arxiv 2310.03744. This is exactly the 1.5-vs-1.6 conflation the previous revision warned about, and this sheet had fallen into it.  ||  MMBench 70.0% has been REMOVED - it does not appear in the NeXT blog tables for the 13B and could not be sourced.  ||  DocVQA is NOT published for this variant.  ||  NOTE: the HuggingFace card llava-hf/llava-v1.6-vicuna-13b-hf publishes no benchmarks at all; the release blog is the primary source.</t>
         </is>
       </c>
       <c r="AD70" s="17" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="AF70" s="18" t="inlineStr">
         <is>
-          <t>LICENCE CONFIRMED AS LLAMA 2 (not Apache 2.0) 2026-08-10. Benchmarks UNCONFIRMED - card publishes none, and 1.5 vs 1.6 figures are conflated in secondary sources. Context 4K disqualifies it regardless.</t>
+          <t>VERIFIED 2026-08-10. Licence confirmed LLAMA 2. Benchmarks now sourced to the official LLaVA-NeXT blog; MMMU corrected 35.9 (a 1.5 figure) -&gt; 36.2, MMBench 70.0 removed as unsourceable. Context 4K disqualifies it regardless.</t>
         </is>
       </c>
     </row>
@@ -18497,247 +18497,538 @@
         </is>
       </c>
     </row>
-    <row r="297" ht="20" customHeight="1">
-      <c r="A297" s="25" t="inlineStr">
-        <is>
-          <t>PRIMARY SOURCE INDEX</t>
+    <row r="296">
+      <c r="A296" s="26" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="26" t="inlineStr">
+        <is>
+          <t>PASS 3 - THE THREE RESIDUAL CELLS, RESOLVED 2026-08-10 BY DIRECT PDF READ.</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="29" t="inlineStr">
-        <is>
-          <t>PAPER / DOCUMENT                                     COVERS                         LOCATION</t>
-        </is>
-      </c>
+      <c r="A298" s="26" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="26" t="inlineStr">
         <is>
-          <t>Qwen2.5-Coder Technical Report                       Qwen2.5-Coder 7B               arxiv.org/abs/2409.12186</t>
+          <t xml:space="preserve">  17. StarCoder2 MultiPL-E C++ 41.4%: NOW CONFIRMED. arxiv 2402.19173 TABLE 10, Pass@1 on MultiPL-E,</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="26" t="inlineStr">
         <is>
-          <t>Phi-4 Technical Report                               Phi-4 14B                      arxiv.org/abs/2412.08905</t>
+          <t xml:space="preserve">      50 samples per problem, temperature 0.2, top-p 0.95. The figure this sheet carried was correct;</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="26" t="inlineStr">
         <is>
-          <t>Phi-3 Technical Report                               Phi-3.5-mini, Phi-3.5-Vision   arxiv.org/abs/2404.14219</t>
+          <t xml:space="preserve">      it simply had no citation. It now cites the table. Same read also confirmed HumanEval 46.3 and</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="26" t="inlineStr">
         <is>
-          <t>The Llama 3 Herd of Models                           Llama 3.1 8B                   arxiv.org/abs/2407.21783</t>
+          <t xml:space="preserve">      added MBPP 66.2 / MBPP+ 53.1 (Table 9), CanItEdit 43.08/38.45 (Table 13), CRUXEval-I 48.1 and</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="26" t="inlineStr">
         <is>
-          <t>StarCoder 2 and The Stack v2                         StarCoder2 15B                 arxiv.org/abs/2402.19173</t>
+          <t xml:space="preserve">      CRUXEval-O 47.1 (Table 15), GSM8K-PAL 65.1 (Table 14), RepoBench ES 74.08 (Table 17), and the</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-Coder-V2                                    DeepSeek-Coder-V2-Lite         arxiv.org/abs/2406.11931</t>
+          <t xml:space="preserve">      full architecture from Table 6 (40 layers, 4 KV heads, hidden 6144 so head_dim 128) which is the</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-R1                                          DeepSeek-R1-Distill-Qwen-14B   arxiv.org/abs/2501.12948</t>
+          <t xml:space="preserve">      geometry this sheet uses for its KV-cache maths.</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="26" t="inlineStr">
-        <is>
-          <t>Mistral 7B                                           Mistral 7B Instruct v0.3       arxiv.org/abs/2310.06825</t>
-        </is>
-      </c>
+      <c r="A306" s="26" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="26" t="inlineStr">
         <is>
-          <t>Gemma 3 Technical Report                             Gemma 3 4B                     arxiv.org/abs/2503.19786</t>
+          <t xml:space="preserve">  18. TWO STARCODER2 WEAKNESSES FOUND IN THE PAPER THAT NO HEADLINE SCORE SHOWS. These were missed by</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="26" t="inlineStr">
         <is>
-          <t>Qwen2-VL                                             Qwen2-VL 7B                    arxiv.org/abs/2409.12191</t>
+          <t xml:space="preserve">      every earlier pass because they live in a table caption and a discussion paragraph, not in a</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="26" t="inlineStr">
         <is>
-          <t>PaliGemma                                            PaliGemma 3B                   arxiv.org/abs/2407.07726</t>
+          <t xml:space="preserve">      results row:</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="26" t="inlineStr">
         <is>
-          <t>Improved Baselines with Visual Instruction Tuning    LLaVA-1.5 / 1.6                arxiv.org/abs/2310.03744</t>
+          <t xml:space="preserve">        a) FIM IS BROKEN. Table 16 caption, verbatim: 'Due to an implementation bug, FIM was incorrect</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="26" t="inlineStr">
         <is>
-          <t>HumanEval / Evaluating LLMs Trained on Code          HumanEval benchmark definition arxiv.org/abs/2107.03374</t>
+          <t xml:space="preserve">           for most of the training of StarCoder2-15B.' Measured FIM is Python 48.4 / Java 60.5 /</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="26" t="inlineStr">
         <is>
-          <t>MultiPL-E                                            MultiPL-E C++ benchmark definition arxiv.org/abs/2208.08227</t>
+          <t xml:space="preserve">           JS 54.7 - WORSE than its own predecessor StarCoderBase-15B at 62 / 73 / 74. This sheet</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="26" t="inlineStr">
         <is>
-          <t>MMLU / Measuring Massive Multitask Understanding     MMLU benchmark definition      arxiv.org/abs/2009.03300</t>
+          <t xml:space="preserve">           previously listed 'FIM: YES (native)' as a STRENGTH. That was misleading and is corrected.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="26" t="inlineStr">
         <is>
-          <t>MMMU                                                 MMMU benchmark definition      arxiv.org/abs/2311.16502</t>
+          <t xml:space="preserve">        b) C++ OUTPUT IS ONE-THIRD INCOMPLETE. Section 7.2.1 reports that StarCoder2-15B underperforms</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="26" t="inlineStr">
         <is>
-          <t>DocVQA                                               DocVQA benchmark definition    arxiv.org/abs/2007.00398</t>
+          <t xml:space="preserve">           on C++ because about a third of generated C++ is incomplete - the paper's own example is an</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="26" t="inlineStr">
         <is>
-          <t>LoRA                                                 Fine-tuning method             arxiv.org/abs/2106.09685</t>
+          <t xml:space="preserve">           unexpected break straight after the start of a for loop. For a 5-gate cross-compile pipeline</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="26" t="inlineStr">
         <is>
-          <t>QLoRA                                                Fine-tuning method             arxiv.org/abs/2305.14314</t>
+          <t xml:space="preserve">           that is the worst possible failure mode.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="26" t="inlineStr">
         <is>
-          <t>vLLM / PagedAttention                                Inference engine               arxiv.org/abs/2309.06180</t>
+          <t xml:space="preserve">      TAKEN TOGETHER these remove StarCoder2 from serious consideration for ipoefgfefs, on the paper's</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="26" t="inlineStr">
         <is>
-          <t>SGLang / RadixAttention                              Inference engine               arxiv.org/abs/2312.07104</t>
+          <t xml:space="preserve">      own evidence rather than on a benchmark ranking.</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="26" t="inlineStr">
-        <is>
-          <t>llama.cpp - supported backends and build docs        ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
-        </is>
-      </c>
+      <c r="A320" s="26" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="26" t="inlineStr">
         <is>
-          <t>llama.cpp k-quants PR #1684                          ALL quantization accuracy deltas github.com/ggml-org/llama.cpp/pull/1684</t>
+          <t xml:space="preserve">  19. LLaVA-1.6 13B benchmarks: NOW SOURCED to llava-vl.github.io/blog/2024-01-30-llava-next (the</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA Ada GPU Architecture Whitepaper               RTX 4090 memory bandwidth (1008 GB/s) nvidia.com - Ada whitepaper</t>
+          <t xml:space="preserve">      official release blog, since the HuggingFace card publishes none). VQAv2 82.8, ScienceQA 73.6,</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="26" t="inlineStr">
         <is>
-          <t>Apache License 2.0                                   Licence text                   apache.org/licenses/LICENSE-2.0</t>
+          <t xml:space="preserve">      TextVQA 67.1, GQA 65.4, VisWiz 60.5, MMMU val 36.2, at 672x672 resolution.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="26" t="inlineStr">
         <is>
-          <t>Llama 3.x Community Licence                          Licence text incl. EU multimodal clause llama.com/llama3_3/license</t>
+          <t xml:space="preserve">      CORRECTION: MMMU 35.9 was a LLaVA-1.5 figure from arxiv 2310.03744 - the exact 1.5-vs-1.6</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="26" t="inlineStr">
         <is>
-          <t>Gemma Terms of Use                                   Licence text                   ai.google.dev/gemma/terms</t>
+          <t xml:space="preserve">      conflation the previous revision warned about, which this sheet had itself fallen into.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="26" t="inlineStr">
         <is>
-          <t>BigCode OpenRAIL-M v1                                Licence text incl. flow-down duty bigcode-project.org/docs/pages/model-license</t>
+          <t xml:space="preserve">      MMBench 70.0 has been REMOVED: it is not in the NeXT blog tables for the 13B and could not be</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek Model Licence                               Licence text incl. use restrictions github.com/deepseek-ai/DeepSeek-LLM</t>
+          <t xml:space="preserve">      sourced anywhere primary.</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="26" t="inlineStr">
-        <is>
-          <t>NDAA Section 889 / FAR 52.204-25                     Component-origin procurement rule acquisition.gov/far/52.204-25</t>
-        </is>
-      </c>
+      <c r="A328" s="26" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="26" t="inlineStr">
         <is>
-          <t>EvalPlus Leaderboard                                 Mistral 7B HumanEval (no paper exists) evalplus.github.io/leaderboard.html</t>
+          <t xml:space="preserve">  20. Mistral 7B Instruct v0.3: RESOLVED, and the resolution is that NO SOLID REFERENCE EXISTS.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="26" t="inlineStr">
         <is>
+          <t xml:space="preserve">      The v0.3 model card publishes no benchmarks at all. The MMLU 62.5% figure comes from arxiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2310.06825, which is the v0.1 BASE model paper - a different model version. Secondary sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      place v0.3 nearer 59.9-60.0% but are not primary. HumanEval 36.5% is from the EvalPlus</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      leaderboard, whose table is JavaScript-rendered and could not be captured for citation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      This is now the ONLY model in the sheet with no citable primary benchmark, and it is labelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      as such in its own cells. It is not a contender for the C++ role, so the stakes are low - but</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      it must not be ranked on those numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="26" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="26" t="inlineStr">
+        <is>
+          <t>STATUS AFTER THREE PASSES: every benchmark figure in this sheet is now traceable to a named primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="26" t="inlineStr">
+        <is>
+          <t>source, and where a table number exists it is cited. The single exception is Mistral 7B v0.3, where</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="26" t="inlineStr">
+        <is>
+          <t>the absence of a source IS the finding and is stated in the cell rather than papered over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="20" customHeight="1">
+      <c r="A342" s="25" t="inlineStr">
+        <is>
+          <t>PRIMARY SOURCE INDEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="29" t="inlineStr">
+        <is>
+          <t>PAPER / DOCUMENT                                     COVERS                         LOCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2.5-Coder Technical Report                       Qwen2.5-Coder 7B               arxiv.org/abs/2409.12186</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="26" t="inlineStr">
+        <is>
+          <t>Phi-4 Technical Report                               Phi-4 14B                      arxiv.org/abs/2412.08905</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="26" t="inlineStr">
+        <is>
+          <t>Phi-3 Technical Report                               Phi-3.5-mini, Phi-3.5-Vision   arxiv.org/abs/2404.14219</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="26" t="inlineStr">
+        <is>
+          <t>The Llama 3 Herd of Models                           Llama 3.1 8B                   arxiv.org/abs/2407.21783</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="26" t="inlineStr">
+        <is>
+          <t>StarCoder 2 and The Stack v2                         StarCoder2 15B                 arxiv.org/abs/2402.19173</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-Coder-V2                                    DeepSeek-Coder-V2-Lite         arxiv.org/abs/2406.11931</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-R1                                          DeepSeek-R1-Distill-Qwen-14B   arxiv.org/abs/2501.12948</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="26" t="inlineStr">
+        <is>
+          <t>Mistral 7B                                           Mistral 7B Instruct v0.3       arxiv.org/abs/2310.06825</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="26" t="inlineStr">
+        <is>
+          <t>Gemma 3 Technical Report                             Gemma 3 4B                     arxiv.org/abs/2503.19786</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2-VL                                             Qwen2-VL 7B                    arxiv.org/abs/2409.12191</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="26" t="inlineStr">
+        <is>
+          <t>PaliGemma                                            PaliGemma 3B                   arxiv.org/abs/2407.07726</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="26" t="inlineStr">
+        <is>
+          <t>Improved Baselines with Visual Instruction Tuning    LLaVA-1.5 / 1.6                arxiv.org/abs/2310.03744</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="26" t="inlineStr">
+        <is>
+          <t>HumanEval / Evaluating LLMs Trained on Code          HumanEval benchmark definition arxiv.org/abs/2107.03374</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="26" t="inlineStr">
+        <is>
+          <t>MultiPL-E                                            MultiPL-E C++ benchmark definition arxiv.org/abs/2208.08227</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="26" t="inlineStr">
+        <is>
+          <t>MMLU / Measuring Massive Multitask Understanding     MMLU benchmark definition      arxiv.org/abs/2009.03300</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="26" t="inlineStr">
+        <is>
+          <t>MMMU                                                 MMMU benchmark definition      arxiv.org/abs/2311.16502</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="26" t="inlineStr">
+        <is>
+          <t>DocVQA                                               DocVQA benchmark definition    arxiv.org/abs/2007.00398</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="26" t="inlineStr">
+        <is>
+          <t>LoRA                                                 Fine-tuning method             arxiv.org/abs/2106.09685</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="26" t="inlineStr">
+        <is>
+          <t>QLoRA                                                Fine-tuning method             arxiv.org/abs/2305.14314</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="26" t="inlineStr">
+        <is>
+          <t>vLLM / PagedAttention                                Inference engine               arxiv.org/abs/2309.06180</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="26" t="inlineStr">
+        <is>
+          <t>SGLang / RadixAttention                              Inference engine               arxiv.org/abs/2312.07104</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp - supported backends and build docs        ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp k-quants PR #1684                          ALL quantization accuracy deltas github.com/ggml-org/llama.cpp/pull/1684</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="26" t="inlineStr">
+        <is>
+          <t>NVIDIA Ada GPU Architecture Whitepaper               RTX 4090 memory bandwidth (1008 GB/s) nvidia.com - Ada whitepaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="26" t="inlineStr">
+        <is>
+          <t>Apache License 2.0                                   Licence text                   apache.org/licenses/LICENSE-2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="26" t="inlineStr">
+        <is>
+          <t>Llama 3.x Community Licence                          Licence text incl. EU multimodal clause llama.com/llama3_3/license</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="26" t="inlineStr">
+        <is>
+          <t>Gemma Terms of Use                                   Licence text                   ai.google.dev/gemma/terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="26" t="inlineStr">
+        <is>
+          <t>BigCode OpenRAIL-M v1                                Licence text incl. flow-down duty bigcode-project.org/docs/pages/model-license</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek Model Licence                               Licence text incl. use restrictions github.com/deepseek-ai/DeepSeek-LLM</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="26" t="inlineStr">
+        <is>
+          <t>NDAA Section 889 / FAR 52.204-25                     Component-origin procurement rule acquisition.gov/far/52.204-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="26" t="inlineStr">
+        <is>
+          <t>EvalPlus Leaderboard                                 Mistral 7B HumanEval (no paper exists) evalplus.github.io/leaderboard.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="26" t="inlineStr">
+        <is>
           <t>OpenCompass Multimodal Leaderboard                   InternVL2 (partly leaderboard-sourced) rank.opencompass.org.cn/leaderboard-multimodal</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:AF78"/>
-  <mergeCells count="249">
+  <mergeCells count="294">
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="A80:AF80"/>
     <mergeCell ref="A81:AF81"/>
@@ -18953,6 +19244,7 @@
     <mergeCell ref="A293:AF293"/>
     <mergeCell ref="A294:AF294"/>
     <mergeCell ref="A295:AF295"/>
+    <mergeCell ref="A296:AF296"/>
     <mergeCell ref="A297:AF297"/>
     <mergeCell ref="A298:AF298"/>
     <mergeCell ref="A299:AF299"/>
@@ -18987,6 +19279,50 @@
     <mergeCell ref="A328:AF328"/>
     <mergeCell ref="A329:AF329"/>
     <mergeCell ref="A330:AF330"/>
+    <mergeCell ref="A331:AF331"/>
+    <mergeCell ref="A332:AF332"/>
+    <mergeCell ref="A333:AF333"/>
+    <mergeCell ref="A334:AF334"/>
+    <mergeCell ref="A335:AF335"/>
+    <mergeCell ref="A336:AF336"/>
+    <mergeCell ref="A337:AF337"/>
+    <mergeCell ref="A338:AF338"/>
+    <mergeCell ref="A339:AF339"/>
+    <mergeCell ref="A340:AF340"/>
+    <mergeCell ref="A342:AF342"/>
+    <mergeCell ref="A343:AF343"/>
+    <mergeCell ref="A344:AF344"/>
+    <mergeCell ref="A345:AF345"/>
+    <mergeCell ref="A346:AF346"/>
+    <mergeCell ref="A347:AF347"/>
+    <mergeCell ref="A348:AF348"/>
+    <mergeCell ref="A349:AF349"/>
+    <mergeCell ref="A350:AF350"/>
+    <mergeCell ref="A351:AF351"/>
+    <mergeCell ref="A352:AF352"/>
+    <mergeCell ref="A353:AF353"/>
+    <mergeCell ref="A354:AF354"/>
+    <mergeCell ref="A355:AF355"/>
+    <mergeCell ref="A356:AF356"/>
+    <mergeCell ref="A357:AF357"/>
+    <mergeCell ref="A358:AF358"/>
+    <mergeCell ref="A359:AF359"/>
+    <mergeCell ref="A360:AF360"/>
+    <mergeCell ref="A361:AF361"/>
+    <mergeCell ref="A362:AF362"/>
+    <mergeCell ref="A363:AF363"/>
+    <mergeCell ref="A364:AF364"/>
+    <mergeCell ref="A365:AF365"/>
+    <mergeCell ref="A366:AF366"/>
+    <mergeCell ref="A367:AF367"/>
+    <mergeCell ref="A368:AF368"/>
+    <mergeCell ref="A369:AF369"/>
+    <mergeCell ref="A370:AF370"/>
+    <mergeCell ref="A371:AF371"/>
+    <mergeCell ref="A372:AF372"/>
+    <mergeCell ref="A373:AF373"/>
+    <mergeCell ref="A374:AF374"/>
+    <mergeCell ref="A375:AF375"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipoefgfefs_SLM_Matrix.xlsx
+++ b/ipoefgfefs_SLM_Matrix.xlsx
@@ -5453,7 +5453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF375"/>
+  <dimension ref="A1:AF427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -18798,237 +18798,573 @@
     <row r="343">
       <c r="A343" s="29" t="inlineStr">
         <is>
-          <t>PAPER / DOCUMENT                                     COVERS                         LOCATION</t>
+          <t>SOURCE                                                     WHAT IT BACKS                      LOCATION</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="26" t="inlineStr">
-        <is>
-          <t>Qwen2.5-Coder Technical Report                       Qwen2.5-Coder 7B               arxiv.org/abs/2409.12186</t>
-        </is>
-      </c>
+      <c r="A344" s="26" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="26" t="inlineStr">
-        <is>
-          <t>Phi-4 Technical Report                               Phi-4 14B                      arxiv.org/abs/2412.08905</t>
+      <c r="A345" s="29" t="inlineStr">
+        <is>
+          <t>--- PEER-REVIEWED PAPERS (evidence grade 1) ----------------------------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="26" t="inlineStr">
         <is>
-          <t>Phi-3 Technical Report                               Phi-3.5-mini, Phi-3.5-Vision   arxiv.org/abs/2404.14219</t>
+          <t>Qwen2.5-Coder Technical Report                             Qwen C++ 75.6 (Tbl 17), HumanEval/MBPP (Tbl 16) arxiv.org/abs/2409.12186</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="26" t="inlineStr">
         <is>
-          <t>The Llama 3 Herd of Models                           Llama 3.1 8B                   arxiv.org/abs/2407.21783</t>
+          <t>Phi-4 Technical Report                                     Phi-4 - paper backing the model card figures arxiv.org/abs/2412.08905</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="26" t="inlineStr">
         <is>
-          <t>StarCoder 2 and The Stack v2                         StarCoder2 15B                 arxiv.org/abs/2402.19173</t>
+          <t>Phi-3 Technical Report                                     Phi-3.5-mini and Phi-3.5-Vision lineage arxiv.org/abs/2404.14219</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-Coder-V2                                    DeepSeek-Coder-V2-Lite         arxiv.org/abs/2406.11931</t>
+          <t>The Llama 3 Herd of Models                                 Llama 3.1 8B architecture and training arxiv.org/abs/2407.21783</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-R1                                          DeepSeek-R1-Distill-Qwen-14B   arxiv.org/abs/2501.12948</t>
+          <t>StarCoder 2 and The Stack v2                               StarCoder2 - Tbl 6,9,10,13,14,15,16,17; Sec 7.2.1 arxiv.org/abs/2402.19173</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="26" t="inlineStr">
         <is>
-          <t>Mistral 7B                                           Mistral 7B Instruct v0.3       arxiv.org/abs/2310.06825</t>
+          <t>DeepSeek-Coder-V2                                          DeepSeek-Lite C++ 75.8, HumanEval, MBPP+ (Tbl 3) arxiv.org/abs/2406.11931</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="26" t="inlineStr">
         <is>
-          <t>Gemma 3 Technical Report                             Gemma 3 4B                     arxiv.org/abs/2503.19786</t>
+          <t>DeepSeek-R1                                                R1-Distill-14B distillation method and results arxiv.org/abs/2501.12948</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="26" t="inlineStr">
         <is>
-          <t>Qwen2-VL                                             Qwen2-VL 7B                    arxiv.org/abs/2409.12191</t>
+          <t>Mistral 7B                                                 MMLU 62.5 - NOTE: v0.1 BASE model, not v0.3 arxiv.org/abs/2310.06825</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="26" t="inlineStr">
         <is>
-          <t>PaliGemma                                            PaliGemma 3B                   arxiv.org/abs/2407.07726</t>
+          <t>Gemma 3 Technical Report                                   Gemma 3 4B architecture and training arxiv.org/abs/2503.19786</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="26" t="inlineStr">
         <is>
-          <t>Improved Baselines with Visual Instruction Tuning    LLaVA-1.5 / 1.6                arxiv.org/abs/2310.03744</t>
+          <t>Qwen2-VL                                                   Qwen2-VL 7B vision architecture    arxiv.org/abs/2409.12191</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="26" t="inlineStr">
         <is>
-          <t>HumanEval / Evaluating LLMs Trained on Code          HumanEval benchmark definition arxiv.org/abs/2107.03374</t>
+          <t>PaliGemma                                                  PaliGemma 3B - fine-tuned transfer results arxiv.org/abs/2407.07726</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="26" t="inlineStr">
         <is>
-          <t>MultiPL-E                                            MultiPL-E C++ benchmark definition arxiv.org/abs/2208.08227</t>
+          <t>Improved Baselines with Visual Instruction Tuning          LLaVA-1.5 baseline (NOT the 1.6 figures) arxiv.org/abs/2310.03744</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="26" t="inlineStr">
-        <is>
-          <t>MMLU / Measuring Massive Multitask Understanding     MMLU benchmark definition      arxiv.org/abs/2009.03300</t>
-        </is>
-      </c>
+      <c r="A358" s="26" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="26" t="inlineStr">
-        <is>
-          <t>MMMU                                                 MMMU benchmark definition      arxiv.org/abs/2311.16502</t>
+      <c r="A359" s="29" t="inlineStr">
+        <is>
+          <t>--- OFFICIAL MODEL CARDS (evidence grade 2 - PRIMARY where no paper exists) ------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="26" t="inlineStr">
         <is>
-          <t>DocVQA                                               DocVQA benchmark definition    arxiv.org/abs/2007.00398</t>
+          <t>IBM granite-3.3-8b-instruct card                           HumanEval 89.73, MMLU 65.54, GSM8K 80.89 huggingface.co/ibm-granite/granite-3.3-8b-instruct</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="26" t="inlineStr">
         <is>
-          <t>LoRA                                                 Fine-tuning method             arxiv.org/abs/2106.09685</t>
+          <t>Microsoft phi-4 card                                       HumanEval 82.6, MMLU 84.8, 1920xH100 21 days huggingface.co/microsoft/phi-4</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="26" t="inlineStr">
         <is>
-          <t>QLoRA                                                Fine-tuning method             arxiv.org/abs/2305.14314</t>
+          <t>Microsoft Phi-3.5-mini-instruct card                       62.8 / 69 / 86.2, 512xH100 10 days huggingface.co/microsoft/Phi-3.5-mini-instruct</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="26" t="inlineStr">
         <is>
-          <t>vLLM / PagedAttention                                Inference engine               arxiv.org/abs/2309.06180</t>
+          <t>Microsoft Phi-3.5-vision-instruct card                     MMBench 81.9, MMMU 43.0, 256xA100 6 days huggingface.co/microsoft/Phi-3.5-vision-instruct</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="26" t="inlineStr">
         <is>
-          <t>SGLang / RadixAttention                              Inference engine               arxiv.org/abs/2312.07104</t>
+          <t>Qwen2.5-Coder-7B-Instruct card                             7.61B params, 28 layers, 4 KV heads, 131072 ctx huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="26" t="inlineStr">
         <is>
-          <t>llama.cpp - supported backends and build docs        ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
+          <t>Qwen2-VL-7B-Instruct card                                  DocVQA 94.5, TextVQA 84.3, MMMU 54.1 huggingface.co/Qwen/Qwen2-VL-7B-Instruct</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="26" t="inlineStr">
         <is>
-          <t>llama.cpp k-quants PR #1684                          ALL quantization accuracy deltas github.com/ggml-org/llama.cpp/pull/1684</t>
+          <t>Meta Llama-3.1-8B-Instruct card                            HumanEval 72.6, MMLU 69.4 vs CoT 73.0, GPU-hours huggingface.co/meta-llama/Llama-3.1-8B-Instruct</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA Ada GPU Architecture Whitepaper               RTX 4090 memory bandwidth (1008 GB/s) nvidia.com - Ada whitepaper</t>
+          <t>Meta Llama-3.2-3B-Instruct card                            MMLU 63.4, GSM8K 77.7, EU clause scope huggingface.co/meta-llama/Llama-3.2-3B-Instruct</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="26" t="inlineStr">
         <is>
-          <t>Apache License 2.0                                   Licence text                   apache.org/licenses/LICENSE-2.0</t>
+          <t>Meta Llama 3.2 MODEL_CARD_VISION.md                        11B Vision INSTRUCT table (not pretrained) github.com/meta-llama/llama-models</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="26" t="inlineStr">
         <is>
-          <t>Llama 3.x Community Licence                          Licence text incl. EU multimodal clause llama.com/llama3_3/license</t>
+          <t>BigCode starcoder2-15b card                                1024xH100, 16384 ctx, HumanEval 46.3 huggingface.co/bigcode/starcoder2-15b</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="26" t="inlineStr">
         <is>
-          <t>Gemma Terms of Use                                   Licence text                   ai.google.dev/gemma/terms</t>
+          <t>Google codegemma-7b-it card                                HumanEval 56.1, BabelCode C++ 42.2, 8K ctx huggingface.co/google/codegemma-7b-it</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="26" t="inlineStr">
         <is>
-          <t>BigCode OpenRAIL-M v1                                Licence text incl. flow-down duty bigcode-project.org/docs/pages/model-license</t>
+          <t>Google gemma-3-4b-it card                                  HumanEval 36.0, MMLU 59.6, 128K in / 8K out huggingface.co/google/gemma-3-4b-it</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek Model Licence                               Licence text incl. use restrictions github.com/deepseek-ai/DeepSeek-LLM</t>
+          <t>Google paligemma-3b-mix-448 card                           512 token ctx, fine-tuned transfer scores huggingface.co/google/paligemma-3b-mix-448</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="26" t="inlineStr">
         <is>
-          <t>NDAA Section 889 / FAR 52.204-25                     Component-origin procurement rule acquisition.gov/far/52.204-25</t>
+          <t>DeepSeek-R1-Distill-Qwen-14B card                          MATH-500 93.9, LiveCodeBench 53.1, Codeforces 1481 huggingface.co/deepseek-ai/DeepSeek-R1-Distill-Qwen-14B</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="26" t="inlineStr">
         <is>
-          <t>EvalPlus Leaderboard                                 Mistral 7B HumanEval (no paper exists) evalplus.github.io/leaderboard.html</t>
+          <t>DeepSeek-Coder-V2-Lite-Instruct card                       MoE config, licence terms          huggingface.co/deepseek-ai/DeepSeek-Coder-V2-Lite-Instruct</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="26" t="inlineStr">
         <is>
-          <t>OpenCompass Multimodal Leaderboard                   InternVL2 (partly leaderboard-sourced) rank.opencompass.org.cn/leaderboard-multimodal</t>
+          <t>OpenGVLab InternVL2-8B card                                MMBench 81.7, MMMU 51.8, DocVQA 91.6, 8K ctx huggingface.co/OpenGVLab/InternVL2-8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="26" t="inlineStr">
+        <is>
+          <t>llava-hf llava-v1.6-vicuna-13b-hf card                     Licence = LLAMA 2 (publishes no benchmarks) huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="26" t="inlineStr">
+        <is>
+          <t>vikhyatk/moondream2 card                                   DocVQA 79.3, TextVQA 76.3, COCO detect 51.2 huggingface.co/vikhyatk/moondream2</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="26" t="inlineStr">
+        <is>
+          <t>mistralai Mistral-7B-Instruct-v0.3 card                    PUBLISHES NO BENCHMARKS - that is the finding huggingface.co/mistralai/Mistral-7B-Instruct-v0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="26" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="29" t="inlineStr">
+        <is>
+          <t>--- OFFICIAL BLOGS AND VENDOR DOCS (evidence grade 3) ----------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="26" t="inlineStr">
+        <is>
+          <t>LLaVA-NeXT release blog                                    LLaVA-1.6 13B: VQAv2 82.8, MMMU 36.2, TextVQA 67.1 llava-vl.github.io/blog/2024-01-30-llava-next</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2.5-Coder family blog                                  Qwen family overview (no per-model numbers) qwenlm.github.io/blog/qwen2.5-coder-family</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="26" t="inlineStr">
+        <is>
+          <t>Google CodeGemma docs                                      CodeGemma model documentation      ai.google.dev/gemma/docs/codegemma</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="26" t="inlineStr">
+        <is>
+          <t>InternVL project site                                      InternVL2 family documentation     internvl.github.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="26" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="29" t="inlineStr">
+        <is>
+          <t>--- TOKEN-RATE MEASUREMENTS (evidence grade 4 - the ONLY published source for tok/s) -------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="26" t="inlineStr">
+        <is>
+          <t>LLM tokens/sec benchmarks, llama.cpp b3520                 RTX4090 Q4_K_M: 7B 135, 13B 78, 34B 42 tok/s mustafa.net/llm-tokens-per-second-benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="26" t="inlineStr">
+        <is>
+          <t>Ollama vs llama.cpp benchmark                              Llama 3.1 8B Q4_K_M on 4090 = 95-110 tok/s markaicode.com/benchmarks/ollama-vs-llamacpp-benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="26" t="inlineStr">
+        <is>
+          <t>Qwen3-8B on RTX 4090 recipe                                llama.cpp 104 tok/s at 16K context cross-check smeltcore.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="26" t="inlineStr">
+        <is>
+          <t>AMD EPYC LLM inference benchmark                           CPU: EPYC 7763 7B Q4_K_M = 15 tok/s blog.leaseweb.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp VRAM requirements guide                          Concurrency: ~18 tok/s per user, 4 users, 24GB localllm.in/blog/llamacpp-vram-requirements-for-local-llms</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="26" t="inlineStr">
+        <is>
+          <t>myaihardware llama.cpp benchmarks                          CPU desktop band 4-15 tok/s at Q4_K_M myaihardware.com/llama-cpp-benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="26" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="29" t="inlineStr">
+        <is>
+          <t>--- BENCHMARK DEFINITIONS (what each metric actually measures) --------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="26" t="inlineStr">
+        <is>
+          <t>HumanEval / Evaluating LLMs Trained on Code                164 Python problems, pass@1        arxiv.org/abs/2107.03374</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="26" t="inlineStr">
+        <is>
+          <t>MultiPL-E                                                  HumanEval translated to 18 languages incl. C++ arxiv.org/abs/2208.08227</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="26" t="inlineStr">
+        <is>
+          <t>MBPP                                                       Mostly Basic Python Problems       arxiv.org/abs/2108.07732</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="26" t="inlineStr">
+        <is>
+          <t>EvalPlus (HumanEval+ / MBPP+)                              80x and 35x more tests than the originals arxiv.org/abs/2305.01210</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="26" t="inlineStr">
+        <is>
+          <t>CanItEdit                                                  Code EDITING - closest proxy to a retry loop arxiv.org/abs/2312.12450</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="26" t="inlineStr">
+        <is>
+          <t>CRUXEval                                                   Code reasoning, understanding and execution arxiv.org/abs/2401.03065</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="26" t="inlineStr">
+        <is>
+          <t>RepoBench                                                  Repository-level next-line completion arxiv.org/abs/2306.03091</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="26" t="inlineStr">
+        <is>
+          <t>MMLU                                                       57-subject multitask accuracy      arxiv.org/abs/2009.03300</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="26" t="inlineStr">
+        <is>
+          <t>GSM8K                                                      Grade-school math word problems    arxiv.org/abs/2110.14168</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="26" t="inlineStr">
+        <is>
+          <t>MATH                                                       Competition mathematics            arxiv.org/abs/2103.03874</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="26" t="inlineStr">
+        <is>
+          <t>MMMU                                                       College-level multimodal understanding arxiv.org/abs/2311.16502</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="26" t="inlineStr">
+        <is>
+          <t>DocVQA                                                     Document visual question answering arxiv.org/abs/2007.00398</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="26" t="inlineStr">
+        <is>
+          <t>TextVQA                                                    Reading text within images         arxiv.org/abs/1904.08920</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="26" t="inlineStr">
+        <is>
+          <t>LiveCodeBench                                              Contamination-free live coding problems arxiv.org/abs/2403.07974</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="26" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="29" t="inlineStr">
+        <is>
+          <t>--- ENGINEERING AND HARDWARE SOURCES ---------------------------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp - supported backends and build docs              ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp k-quants PR #1684                                ALL quantization accuracy deltas   github.com/ggml-org/llama.cpp/pull/1684</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="26" t="inlineStr">
+        <is>
+          <t>NVIDIA Ada GPU Architecture Whitepaper                     RTX 4090 bandwidth 1008 GB/s       nvidia.com - Ada whitepaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="26" t="inlineStr">
+        <is>
+          <t>vLLM / PagedAttention                                      Concurrency behaviour              arxiv.org/abs/2309.06180</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="26" t="inlineStr">
+        <is>
+          <t>SGLang / RadixAttention                                    Prefix caching for the shared 6-8K header arxiv.org/abs/2312.07104</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="26" t="inlineStr">
+        <is>
+          <t>LoRA                                                       Fine-tuning VRAM baseline          arxiv.org/abs/2106.09685</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="26" t="inlineStr">
+        <is>
+          <t>QLoRA                                                      4-bit fine-tuning VRAM             arxiv.org/abs/2305.14314</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="26" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="29" t="inlineStr">
+        <is>
+          <t>--- LICENCE AND COMPLIANCE TEXTS -------------------------------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="26" t="inlineStr">
+        <is>
+          <t>Apache License 2.0                                         Qwen, Granite, Mistral, Moondream, Qwen2-VL apache.org/licenses/LICENSE-2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="26" t="inlineStr">
+        <is>
+          <t>MIT License                                                Phi-4, Phi-3.5-mini, Phi-3.5-Vision, InternVL2, R1 opensource.org/license/mit</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="26" t="inlineStr">
+        <is>
+          <t>Llama 3.x Community Licence                                EU MULTIMODAL EXCLUSION - exact wording llama.com/llama3_3/license</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="26" t="inlineStr">
+        <is>
+          <t>Llama 2 Community Licence                                  LLaVA-1.6 effective licence via Vicuna ai.meta.com/llama/license</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="26" t="inlineStr">
+        <is>
+          <t>Gemma Terms of Use                                         CodeGemma, Gemma 3, PaliGemma      ai.google.dev/gemma/terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="26" t="inlineStr">
+        <is>
+          <t>BigCode OpenRAIL-M v1                                      StarCoder2 - flow-down duty on derivatives bigcode-project.org/docs/pages/model-license</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek Model Licence                                     Use restrictions attachment        github.com/deepseek-ai/DeepSeek-LLM</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="26" t="inlineStr">
+        <is>
+          <t>NDAA Section 889 / FAR 52.204-25                           Component-origin procurement rule  acquisition.gov/far/52.204-25</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:AF78"/>
-  <mergeCells count="294">
+  <mergeCells count="346">
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="A80:AF80"/>
     <mergeCell ref="A81:AF81"/>
@@ -19323,6 +19659,58 @@
     <mergeCell ref="A373:AF373"/>
     <mergeCell ref="A374:AF374"/>
     <mergeCell ref="A375:AF375"/>
+    <mergeCell ref="A376:AF376"/>
+    <mergeCell ref="A377:AF377"/>
+    <mergeCell ref="A378:AF378"/>
+    <mergeCell ref="A379:AF379"/>
+    <mergeCell ref="A380:AF380"/>
+    <mergeCell ref="A381:AF381"/>
+    <mergeCell ref="A382:AF382"/>
+    <mergeCell ref="A383:AF383"/>
+    <mergeCell ref="A384:AF384"/>
+    <mergeCell ref="A385:AF385"/>
+    <mergeCell ref="A386:AF386"/>
+    <mergeCell ref="A387:AF387"/>
+    <mergeCell ref="A388:AF388"/>
+    <mergeCell ref="A389:AF389"/>
+    <mergeCell ref="A390:AF390"/>
+    <mergeCell ref="A391:AF391"/>
+    <mergeCell ref="A392:AF392"/>
+    <mergeCell ref="A393:AF393"/>
+    <mergeCell ref="A394:AF394"/>
+    <mergeCell ref="A395:AF395"/>
+    <mergeCell ref="A396:AF396"/>
+    <mergeCell ref="A397:AF397"/>
+    <mergeCell ref="A398:AF398"/>
+    <mergeCell ref="A399:AF399"/>
+    <mergeCell ref="A400:AF400"/>
+    <mergeCell ref="A401:AF401"/>
+    <mergeCell ref="A402:AF402"/>
+    <mergeCell ref="A403:AF403"/>
+    <mergeCell ref="A404:AF404"/>
+    <mergeCell ref="A405:AF405"/>
+    <mergeCell ref="A406:AF406"/>
+    <mergeCell ref="A407:AF407"/>
+    <mergeCell ref="A408:AF408"/>
+    <mergeCell ref="A409:AF409"/>
+    <mergeCell ref="A410:AF410"/>
+    <mergeCell ref="A411:AF411"/>
+    <mergeCell ref="A412:AF412"/>
+    <mergeCell ref="A413:AF413"/>
+    <mergeCell ref="A414:AF414"/>
+    <mergeCell ref="A415:AF415"/>
+    <mergeCell ref="A416:AF416"/>
+    <mergeCell ref="A417:AF417"/>
+    <mergeCell ref="A418:AF418"/>
+    <mergeCell ref="A419:AF419"/>
+    <mergeCell ref="A420:AF420"/>
+    <mergeCell ref="A421:AF421"/>
+    <mergeCell ref="A422:AF422"/>
+    <mergeCell ref="A423:AF423"/>
+    <mergeCell ref="A424:AF424"/>
+    <mergeCell ref="A425:AF425"/>
+    <mergeCell ref="A426:AF426"/>
+    <mergeCell ref="A427:AF427"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipoefgfefs_SLM_Matrix.xlsx
+++ b/ipoefgfefs_SLM_Matrix.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$2:$N$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed'!$A$2:$AF$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$2:$N$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed'!$A$2:$AF$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5430,18 +5430,1074 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-8B</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>8B dense (base: Qwen3-VL-8B-Instruct)</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>32,000 tokens</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K79" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - unified text/image/video/document retrieval</t>
+        </is>
+      </c>
+      <c r="M79" s="8" t="inlineStr">
+        <is>
+          <t>MMEB-V2 Image 80.1 | VisDoc 83.3 | VIDEO 66.1 | MMTEB mean(task) 67.88 | Retrieval 69.41 | STS 75.41</t>
+        </is>
+      </c>
+      <c r="N79" s="8" t="inlineStr">
+        <is>
+          <t>transformers, vLLM (embedding mode), sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-8B</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>8B dense (base: Qwen3-VL-8B-Instruct)</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>32,000 tokens</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - unified text/image/video/document retrieval</t>
+        </is>
+      </c>
+      <c r="M80" s="8" t="inlineStr">
+        <is>
+          <t>MMEB-V2 Image 80.1 | VisDoc 83.3 | VIDEO 66.1 | MMTEB mean(task) 67.88 | Retrieval 69.41 | STS 75.41</t>
+        </is>
+      </c>
+      <c r="N80" s="8" t="inlineStr">
+        <is>
+          <t>transformers, vLLM (embedding mode), sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-2B</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>2B dense (base: Qwen3-VL-2B-Instruct)</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>32,000 tokens</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - unified retrieval at edge-viable size</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>MMEB-V2 Image 75.0 | VIDEO 61.9 | MMTEB mean(task) 63.87 | mean(type) 55.84</t>
+        </is>
+      </c>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>transformers, vLLM (embedding mode), sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-2B</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>2B dense (base: Qwen3-VL-2B-Instruct)</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>32,000 tokens</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - unified retrieval at edge-viable size</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>MMEB-V2 Image 75.0 | VIDEO 61.9 | MMTEB mean(task) 63.87 | mean(type) 55.84</t>
+        </is>
+      </c>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>transformers, vLLM (embedding mode), sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>GME-Qwen2-VL-7B-Instruct</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>8.29B dense (base: Qwen2-VL-7B)</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="J83" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K83" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L83" s="8" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - single-modal, cross-modal and fused-modal retrieval</t>
+        </is>
+      </c>
+      <c r="M83" s="8" t="inlineStr">
+        <is>
+          <t>UMRB 67.44 | MTEB-en 67.48 | MTEB-zh 71.36 | UMRB text-to-visual-doc 89.92</t>
+        </is>
+      </c>
+      <c r="N83" s="8" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>GME-Qwen2-VL-7B-Instruct</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>8.29B dense (base: Qwen2-VL-7B)</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - single-modal, cross-modal and fused-modal retrieval</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="inlineStr">
+        <is>
+          <t>UMRB 67.44 | MTEB-en 67.48 | MTEB-zh 71.36 | UMRB text-to-visual-doc 89.92</t>
+        </is>
+      </c>
+      <c r="N84" s="8" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>GME-Qwen2-VL-2B-Instruct</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>2.21B dense (base: Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - fused-modal retrieval, edge-viable size</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>UMRB 64.45 | MTEB-en 65.27 | MTEB-zh 66.92</t>
+        </is>
+      </c>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>GME-Qwen2-VL-2B-Instruct</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>2.21B dense (base: Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - fused-modal retrieval, edge-viable size</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>UMRB 64.45 | MTEB-en 65.27 | MTEB-zh 66.92</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>VLM2Vec-V2 (Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>2.2B dense (base: Qwen2-VL-2B-Instruct, LoRA fine-tuned)</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>5. Video to Embeddings - purpose-built for video, image and visual document in one space</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="inlineStr">
+        <is>
+          <t>MMEB-V2 overall 58.0 across 78 datasets | video retrieval 34.9 Hit@1</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="inlineStr">
+        <is>
+          <t>transformers (github.com/TIGER-AI-Lab/VLM2Vec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>VLM2Vec-V2 (Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>2.2B dense (base: Qwen2-VL-2B-Instruct, LoRA fine-tuned)</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K88" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L88" s="8" t="inlineStr">
+        <is>
+          <t>5. Video to Embeddings - purpose-built for video, image and visual document in one space</t>
+        </is>
+      </c>
+      <c r="M88" s="8" t="inlineStr">
+        <is>
+          <t>MMEB-V2 overall 58.0 across 78 datasets | video retrieval 34.9 Hit@1</t>
+        </is>
+      </c>
+      <c r="N88" s="8" t="inlineStr">
+        <is>
+          <t>transformers (github.com/TIGER-AI-Lab/VLM2Vec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>E5-V (LLaVA-NeXT-8B)</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>LICENCE UNCLEAR - see source  (COMMERCIAL)</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>8B dense (base: llama3-llava-next-8b)</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>8,192 tokens</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - universal multimodal embeddings</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>Embedding dimension 4096. NUMERIC BENCHMARKS NOT ON THE CARD - see source.</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>E5-V (LLaVA-NeXT-8B)</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>LICENCE UNCLEAR - see source  (COMMERCIAL)</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>8B dense (base: llama3-llava-next-8b)</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>8,192 tokens</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - universal multimodal embeddings</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>Embedding dimension 4096. NUMERIC BENCHMARKS NOT ON THE CARD - see source.</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>ColQwen2-v1.0 (Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0 (backbone) + MIT (adapters)  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>2.2B dense (base: Qwen2-VL-2B-Instruct)</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>Image patches, not a text window</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - MULTI-VECTOR (ColBERT late interaction), not a single vector</t>
+        </is>
+      </c>
+      <c r="M91" s="8" t="inlineStr">
+        <is>
+          <t>ViDoRe benchmark - SCORES NOT ON THE CARD, see source</t>
+        </is>
+      </c>
+      <c r="N91" s="8" t="inlineStr">
+        <is>
+          <t>colpali-engine, transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>ColQwen2-v1.0 (Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Apache 2.0 (backbone) + MIT (adapters)  (OPEN)</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>2.2B dense (base: Qwen2-VL-2B-Instruct)</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>Image patches, not a text window</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - MULTI-VECTOR (ColBERT late interaction), not a single vector</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="inlineStr">
+        <is>
+          <t>ViDoRe benchmark - SCORES NOT ON THE CARD, see source</t>
+        </is>
+      </c>
+      <c r="N92" s="8" t="inlineStr">
+        <is>
+          <t>colpali-engine, transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>ColPali-v1.2 (PaliGemma-3B)</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>MIT (adapters) + Gemma Terms (backbone)  (COMMERCIAL)</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>3B dense (base: google/paligemma-3b-pt-448)</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Image patches, not a text window</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - MULTI-VECTOR (ColBERT late interaction)</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>ViDoRe benchmark - SCORES NOT ON THE CARD, see source</t>
+        </is>
+      </c>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t>colpali-engine, transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>ColPali-v1.2 (PaliGemma-3B)</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>MIT (adapters) + Gemma Terms (backbone)  (COMMERCIAL)</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>3B dense (base: google/paligemma-3b-pt-448)</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>NOT llama.cpp. transformers / vLLM embedding mode. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Image patches, not a text window</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>NA - emits a vector</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - MULTI-VECTOR (ColBERT late interaction)</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>ViDoRe benchmark - SCORES NOT ON THE CARD, see source</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="inlineStr">
+        <is>
+          <t>colpali-engine, transformers</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>READ ME  -  CPU RAM = model file size x 1.15 (context buffers and allocator overhead).  VRAM = model weights + KV cache at an 8K context, which is the actual ipoefgfefs prompt size.  tok/s figures are CALCULATED from memory bandwidth, NOT measured on hardware - no vendor publishes them.  Every figure on this sheet has a full source citation in the matching column of the 'Detailed' sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N78"/>
+  <autoFilter ref="A2:N94"/>
   <mergeCells count="2">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A80:N80"/>
+    <mergeCell ref="A96:N96"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5453,7 +6509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF427"/>
+  <dimension ref="A1:AF530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -17211,289 +18267,2689 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="25" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-8B</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-8B - model card title</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-8B - model card licence field</t>
+        </is>
+      </c>
+      <c r="E79" s="21" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: China (Alibaba Cloud). Same origin/procurement question as Qwen2.5-Coder.</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2601.04720, Qwen team.</t>
+        </is>
+      </c>
+      <c r="G79" s="21" t="inlineStr">
+        <is>
+          <t>8B dense (base: Qwen3-VL-8B-Instruct)</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I79" s="21" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="J79" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="K79" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L79" s="21" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M79" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2601.04720 'Qwen3-VL-Embedding and Qwen3-VL-Reranker'. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N79" s="21" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O79" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P79" s="21" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q79" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R79" s="21" t="inlineStr">
+        <is>
+          <t>32,000 tokens</t>
+        </is>
+      </c>
+      <c r="S79" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen3-VL-Embedding-8B: max sequence length 32,000 tokens. Embedding dimension is customisable 64-4096 (Matryoshka), so you can trade index size against accuracy without retraining.</t>
+        </is>
+      </c>
+      <c r="T79" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U79" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V79" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W79" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X79" s="21" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - unified text/image/video/document retrieval</t>
+        </is>
+      </c>
+      <c r="Y79" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-8B: supports text, images, screenshots, videos and combined text+image / text+video inputs into one shared vector space.</t>
+        </is>
+      </c>
+      <c r="Z79" s="21" t="inlineStr">
+        <is>
+          <t>5. Video to Embeddings; visual document retrieval; cross-modal search</t>
+        </is>
+      </c>
+      <c r="AA79" s="15" t="inlineStr">
+        <is>
+          <t>Same model card - MMEB-V2 is reported separately for image, video and visual-document tracks, so video is a first-class supported modality rather than an afterthought.</t>
+        </is>
+      </c>
+      <c r="AB79" s="21" t="inlineStr">
+        <is>
+          <t>MMEB-V2 Image 80.1 | VisDoc 83.3 | VIDEO 66.1 | MMTEB mean(task) 67.88 | Retrieval 69.41 | STS 75.41</t>
+        </is>
+      </c>
+      <c r="AC79" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen3-VL-Embedding-8B model card benchmark tables.  ||  MMEB-V2 Video Overall 66.1 is the HIGHEST video embedding score found anywhere in this research - see the CATEGORY 4/5 note at the bottom of this sheet for the frame-count caveat that makes some competing numbers non-comparable.  ||  Benchmark definition: MMEB-V2 [arxiv 2507.04590], 78 tasks across image, video and visual document.</t>
+        </is>
+      </c>
+      <c r="AD79" s="21" t="inlineStr">
+        <is>
+          <t>transformers, vLLM (embedding mode), sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE79" s="15" t="inlineStr">
+        <is>
+          <t>vLLM: docs.vllm.ai/projects/ascend - Qwen3-VL-Embedding has a documented vLLM path.  ||  github.com/QwenLM/Qwen3-VL-Embedding is the reference implementation.  ||  NO GGUF EXISTS - this cannot go through your llama.cpp pipeline.</t>
+        </is>
+      </c>
+      <c r="AF79" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against the model card. NOTE: SLM-DERIVED, not a native SLM - emits vectors, not tokens. NO GGUF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-8B</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-8B - model card title</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-8B - model card licence field</t>
+        </is>
+      </c>
+      <c r="E80" s="21" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: China (Alibaba Cloud). Same origin/procurement question as Qwen2.5-Coder.</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2601.04720, Qwen team.</t>
+        </is>
+      </c>
+      <c r="G80" s="21" t="inlineStr">
+        <is>
+          <t>8B dense (base: Qwen3-VL-8B-Instruct)</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I80" s="21" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="J80" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L80" s="21" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2601.04720 'Qwen3-VL-Embedding and Qwen3-VL-Reranker'. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N80" s="21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O80" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P80" s="21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q80" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R80" s="21" t="inlineStr">
+        <is>
+          <t>32,000 tokens</t>
+        </is>
+      </c>
+      <c r="S80" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen3-VL-Embedding-8B: max sequence length 32,000 tokens. Embedding dimension is customisable 64-4096 (Matryoshka), so you can trade index size against accuracy without retraining.</t>
+        </is>
+      </c>
+      <c r="T80" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U80" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V80" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W80" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X80" s="21" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - unified text/image/video/document retrieval</t>
+        </is>
+      </c>
+      <c r="Y80" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-8B: supports text, images, screenshots, videos and combined text+image / text+video inputs into one shared vector space.</t>
+        </is>
+      </c>
+      <c r="Z80" s="21" t="inlineStr">
+        <is>
+          <t>5. Video to Embeddings; visual document retrieval; cross-modal search</t>
+        </is>
+      </c>
+      <c r="AA80" s="15" t="inlineStr">
+        <is>
+          <t>Same model card - MMEB-V2 is reported separately for image, video and visual-document tracks, so video is a first-class supported modality rather than an afterthought.</t>
+        </is>
+      </c>
+      <c r="AB80" s="21" t="inlineStr">
+        <is>
+          <t>MMEB-V2 Image 80.1 | VisDoc 83.3 | VIDEO 66.1 | MMTEB mean(task) 67.88 | Retrieval 69.41 | STS 75.41</t>
+        </is>
+      </c>
+      <c r="AC80" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen3-VL-Embedding-8B model card benchmark tables.  ||  MMEB-V2 Video Overall 66.1 is the HIGHEST video embedding score found anywhere in this research - see the CATEGORY 4/5 note at the bottom of this sheet for the frame-count caveat that makes some competing numbers non-comparable.  ||  Benchmark definition: MMEB-V2 [arxiv 2507.04590], 78 tasks across image, video and visual document.</t>
+        </is>
+      </c>
+      <c r="AD80" s="21" t="inlineStr">
+        <is>
+          <t>transformers, vLLM (embedding mode), sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE80" s="15" t="inlineStr">
+        <is>
+          <t>vLLM: docs.vllm.ai/projects/ascend - Qwen3-VL-Embedding has a documented vLLM path.  ||  github.com/QwenLM/Qwen3-VL-Embedding is the reference implementation.  ||  NO GGUF EXISTS - this cannot go through your llama.cpp pipeline.</t>
+        </is>
+      </c>
+      <c r="AF80" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against the model card. NOTE: SLM-DERIVED, not a native SLM - emits vectors, not tokens. NO GGUF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-2B</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-2B - model card title</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-2B - model card licence field</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: China (Alibaba Cloud).</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2601.04720, Qwen team.</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="inlineStr">
+        <is>
+          <t>2B dense (base: Qwen3-VL-2B-Instruct)</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="J81" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L81" s="17" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M81" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2601.04720. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N81" s="17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O81" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P81" s="17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q81" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R81" s="17" t="inlineStr">
+        <is>
+          <t>32,000 tokens</t>
+        </is>
+      </c>
+      <c r="S81" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen3-VL-Embedding-2B: 32,000 token max sequence. Embedding dimension customisable 64-2048 (Matryoshka).</t>
+        </is>
+      </c>
+      <c r="T81" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U81" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V81" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W81" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X81" s="17" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - unified retrieval at edge-viable size</t>
+        </is>
+      </c>
+      <c r="Y81" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-2B model card.</t>
+        </is>
+      </c>
+      <c r="Z81" s="17" t="inlineStr">
+        <is>
+          <t>5. Video to Embeddings; visual document retrieval</t>
+        </is>
+      </c>
+      <c r="AA81" s="15" t="inlineStr">
+        <is>
+          <t>Model card reports separate image and video MMEB-V2 tracks.</t>
+        </is>
+      </c>
+      <c r="AB81" s="17" t="inlineStr">
+        <is>
+          <t>MMEB-V2 Image 75.0 | VIDEO 61.9 | MMTEB mean(task) 63.87 | mean(type) 55.84</t>
+        </is>
+      </c>
+      <c r="AC81" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen3-VL-Embedding-2B model card. Image Overall 75.0 across 36 image datasets, Video Overall 61.9 across 18 video datasets.  ||  BEST SIZE/PERFORMANCE TRADE IN THIS CATEGORY: at 2B it gives up only 5.1 points of image and 4.2 points of video against the 8B, for a quarter of the memory.</t>
+        </is>
+      </c>
+      <c r="AD81" s="17" t="inlineStr">
+        <is>
+          <t>transformers, vLLM (embedding mode), sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE81" s="15" t="inlineStr">
+        <is>
+          <t>Same stack as the 8B - github.com/QwenLM/Qwen3-VL-Embedding. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF81" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against the model card. SLM-DERIVED. NO GGUF. Best size/accuracy trade for edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-2B</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-2B - model card title</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-2B - model card licence field</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: China (Alibaba Cloud).</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2601.04720, Qwen team.</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>2B dense (base: Qwen3-VL-2B-Instruct)</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="J82" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L82" s="17" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2601.04720. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N82" s="17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O82" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P82" s="17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q82" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R82" s="17" t="inlineStr">
+        <is>
+          <t>32,000 tokens</t>
+        </is>
+      </c>
+      <c r="S82" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen3-VL-Embedding-2B: 32,000 token max sequence. Embedding dimension customisable 64-2048 (Matryoshka).</t>
+        </is>
+      </c>
+      <c r="T82" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U82" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V82" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W82" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X82" s="17" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - unified retrieval at edge-viable size</t>
+        </is>
+      </c>
+      <c r="Y82" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Qwen/Qwen3-VL-Embedding-2B model card.</t>
+        </is>
+      </c>
+      <c r="Z82" s="17" t="inlineStr">
+        <is>
+          <t>5. Video to Embeddings; visual document retrieval</t>
+        </is>
+      </c>
+      <c r="AA82" s="15" t="inlineStr">
+        <is>
+          <t>Model card reports separate image and video MMEB-V2 tracks.</t>
+        </is>
+      </c>
+      <c r="AB82" s="17" t="inlineStr">
+        <is>
+          <t>MMEB-V2 Image 75.0 | VIDEO 61.9 | MMTEB mean(task) 63.87 | mean(type) 55.84</t>
+        </is>
+      </c>
+      <c r="AC82" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Qwen/Qwen3-VL-Embedding-2B model card. Image Overall 75.0 across 36 image datasets, Video Overall 61.9 across 18 video datasets.  ||  BEST SIZE/PERFORMANCE TRADE IN THIS CATEGORY: at 2B it gives up only 5.1 points of image and 4.2 points of video against the 8B, for a quarter of the memory.</t>
+        </is>
+      </c>
+      <c r="AD82" s="17" t="inlineStr">
+        <is>
+          <t>transformers, vLLM (embedding mode), sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE82" s="15" t="inlineStr">
+        <is>
+          <t>Same stack as the 8B - github.com/QwenLM/Qwen3-VL-Embedding. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF82" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against the model card. SLM-DERIVED. NO GGUF. Best size/accuracy trade for edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>GME-Qwen2-VL-7B-Instruct</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct - model card</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct - model card licence field</t>
+        </is>
+      </c>
+      <c r="E83" s="21" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: China (Alibaba NLP).</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2412.16855 'GME: General Multimodal Embedder', Alibaba.</t>
+        </is>
+      </c>
+      <c r="G83" s="21" t="inlineStr">
+        <is>
+          <t>8.29B dense (base: Qwen2-VL-7B)</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I83" s="21" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="J83" s="21" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="K83" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L83" s="21" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M83" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2412.16855. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N83" s="21" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="O83" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P83" s="21" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Q83" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R83" s="21" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="S83" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct: max sequence length 32,768, embedding dimension 3584 (fixed, not Matryoshka).</t>
+        </is>
+      </c>
+      <c r="T83" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U83" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V83" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W83" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X83" s="21" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - single-modal, cross-modal and fused-modal retrieval</t>
+        </is>
+      </c>
+      <c r="Y83" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct model card: supports text-only, image-only and fused text+image retrieval in one shared space.</t>
+        </is>
+      </c>
+      <c r="Z83" s="21" t="inlineStr">
+        <is>
+          <t>Visual document retrieval; text embeddings (it also scores on MTEB)</t>
+        </is>
+      </c>
+      <c r="AA83" s="15" t="inlineStr">
+        <is>
+          <t>Model card reports MTEB-en and MTEB-zh alongside UMRB, so it doubles as a text embedder - unusual and useful if you want ONE model for both header retrieval and image search.</t>
+        </is>
+      </c>
+      <c r="AB83" s="21" t="inlineStr">
+        <is>
+          <t>UMRB 67.44 | MTEB-en 67.48 | MTEB-zh 71.36 | UMRB text-to-visual-doc 89.92</t>
+        </is>
+      </c>
+      <c r="AC83" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct model card.  ||  UMRB = Universal Multimodal Retrieval Benchmark, introduced in the GME paper arxiv 2412.16855.  ||  CAUTION ON VIDEO: third-party evaluation reports GME at 38.6 Hit@1 on MMEB-V2 video, but GME was evaluated using a SINGLE MIDDLE FRAME while VLM2Vec-V2 and others use 8 uniformly sampled frames [source: arxiv 2507.04590 evaluation protocol]. GME is therefore NOT a genuine video embedder and is listed here under image only.</t>
+        </is>
+      </c>
+      <c r="AD83" s="21" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE83" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct usage section. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF83" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10. SLM-DERIVED. NO GGUF. NOT suitable for video despite third-party video scores - see benchmark source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="inlineStr">
+        <is>
+          <t>GME-Qwen2-VL-7B-Instruct</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct - model card</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct - model card licence field</t>
+        </is>
+      </c>
+      <c r="E84" s="21" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: China (Alibaba NLP).</t>
+        </is>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2412.16855 'GME: General Multimodal Embedder', Alibaba.</t>
+        </is>
+      </c>
+      <c r="G84" s="21" t="inlineStr">
+        <is>
+          <t>8.29B dense (base: Qwen2-VL-7B)</t>
+        </is>
+      </c>
+      <c r="H84" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I84" s="21" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="J84" s="21" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K84" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L84" s="21" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M84" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2412.16855. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N84" s="21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O84" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P84" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R84" s="21" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="S84" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct: max sequence length 32,768, embedding dimension 3584 (fixed, not Matryoshka).</t>
+        </is>
+      </c>
+      <c r="T84" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U84" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V84" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W84" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X84" s="21" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - single-modal, cross-modal and fused-modal retrieval</t>
+        </is>
+      </c>
+      <c r="Y84" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct model card: supports text-only, image-only and fused text+image retrieval in one shared space.</t>
+        </is>
+      </c>
+      <c r="Z84" s="21" t="inlineStr">
+        <is>
+          <t>Visual document retrieval; text embeddings (it also scores on MTEB)</t>
+        </is>
+      </c>
+      <c r="AA84" s="15" t="inlineStr">
+        <is>
+          <t>Model card reports MTEB-en and MTEB-zh alongside UMRB, so it doubles as a text embedder - unusual and useful if you want ONE model for both header retrieval and image search.</t>
+        </is>
+      </c>
+      <c r="AB84" s="21" t="inlineStr">
+        <is>
+          <t>UMRB 67.44 | MTEB-en 67.48 | MTEB-zh 71.36 | UMRB text-to-visual-doc 89.92</t>
+        </is>
+      </c>
+      <c r="AC84" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct model card.  ||  UMRB = Universal Multimodal Retrieval Benchmark, introduced in the GME paper arxiv 2412.16855.  ||  CAUTION ON VIDEO: third-party evaluation reports GME at 38.6 Hit@1 on MMEB-V2 video, but GME was evaluated using a SINGLE MIDDLE FRAME while VLM2Vec-V2 and others use 8 uniformly sampled frames [source: arxiv 2507.04590 evaluation protocol]. GME is therefore NOT a genuine video embedder and is listed here under image only.</t>
+        </is>
+      </c>
+      <c r="AD84" s="21" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE84" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct usage section. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF84" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10. SLM-DERIVED. NO GGUF. NOT suitable for video despite third-party video scores - see benchmark source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>GME-Qwen2-VL-2B-Instruct</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct - model card</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct - model card licence field</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: China (Alibaba NLP).</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2412.16855.</t>
+        </is>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>2.21B dense (base: Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="J85" s="17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K85" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L85" s="17" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M85" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2412.16855. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N85" s="17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O85" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P85" s="17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q85" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R85" s="17" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="S85" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct: 32,768 max sequence, embedding dimension 1536.</t>
+        </is>
+      </c>
+      <c r="T85" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U85" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V85" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W85" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X85" s="17" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - fused-modal retrieval, edge-viable size</t>
+        </is>
+      </c>
+      <c r="Y85" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct model card.</t>
+        </is>
+      </c>
+      <c r="Z85" s="17" t="inlineStr">
+        <is>
+          <t>Text embeddings (MTEB-scored); visual document retrieval</t>
+        </is>
+      </c>
+      <c r="AA85" s="15" t="inlineStr">
+        <is>
+          <t>Model card reports MTEB-en 65.27 and MTEB-zh 66.92.</t>
+        </is>
+      </c>
+      <c r="AB85" s="17" t="inlineStr">
+        <is>
+          <t>UMRB 64.45 | MTEB-en 65.27 | MTEB-zh 66.92</t>
+        </is>
+      </c>
+      <c r="AC85" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct model card. Embedding dim 1536.  ||  Loses 3.0 UMRB points against the 7B for roughly a quarter of the memory.</t>
+        </is>
+      </c>
+      <c r="AD85" s="17" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE85" s="15" t="inlineStr">
+        <is>
+          <t>Model card usage section. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF85" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10. SLM-DERIVED. NO GGUF. Image/text only, not video.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>GME-Qwen2-VL-2B-Instruct</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct - model card</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct - model card licence field</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: China (Alibaba NLP).</t>
+        </is>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2412.16855.</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>2.21B dense (base: Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="J86" s="17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K86" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L86" s="17" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M86" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2412.16855. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N86" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O86" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P86" s="17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q86" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R86" s="17" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="S86" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct: 32,768 max sequence, embedding dimension 1536.</t>
+        </is>
+      </c>
+      <c r="T86" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U86" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V86" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W86" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X86" s="17" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - fused-modal retrieval, edge-viable size</t>
+        </is>
+      </c>
+      <c r="Y86" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct model card.</t>
+        </is>
+      </c>
+      <c r="Z86" s="17" t="inlineStr">
+        <is>
+          <t>Text embeddings (MTEB-scored); visual document retrieval</t>
+        </is>
+      </c>
+      <c r="AA86" s="15" t="inlineStr">
+        <is>
+          <t>Model card reports MTEB-en 65.27 and MTEB-zh 66.92.</t>
+        </is>
+      </c>
+      <c r="AB86" s="17" t="inlineStr">
+        <is>
+          <t>UMRB 64.45 | MTEB-en 65.27 | MTEB-zh 66.92</t>
+        </is>
+      </c>
+      <c r="AC86" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct model card. Embedding dim 1536.  ||  Loses 3.0 UMRB points against the 7B for roughly a quarter of the memory.</t>
+        </is>
+      </c>
+      <c r="AD86" s="17" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE86" s="15" t="inlineStr">
+        <is>
+          <t>Model card usage section. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF86" s="18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10. SLM-DERIVED. NO GGUF. Image/text only, not video.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>VLM2Vec-V2 (Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>arxiv.org/abs/2507.04590 - 'VLM2Vec-V2: Advancing Multimodal Embedding for Videos, Images, and Visual Documents'</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/TIGER-Lab - VLM2Vec model family is released Apache 2.0. CHECK the specific V2 checkpoint card, which returned HTTP 401 at time of writing.</t>
+        </is>
+      </c>
+      <c r="E87" s="21" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: TIGER-AI-Lab (University of Waterloo, Canada) with Salesforce Research co-authors. Allied jurisdiction. Base model is Qwen2-VL (China) - the licence stack is Apache over Apache, but note the lineage.</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2507.04590 author list (Meng, Jiang, Liu, Su, Yang, Fu, Qin, Chen, Xu, Xiong, Zhou, Chen, Yavuz).  ||  Base model lineage: Qwen2-VL-2B-Instruct.</t>
+        </is>
+      </c>
+      <c r="G87" s="21" t="inlineStr">
+        <is>
+          <t>2.2B dense (base: Qwen2-VL-2B-Instruct, LoRA fine-tuned)</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I87" s="21" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="J87" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K87" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L87" s="21" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M87" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2507.04590 - method section. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N87" s="21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O87" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P87" s="21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q87" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R87" s="21" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="S87" s="15" t="inlineStr">
+        <is>
+          <t>Inherited from the Qwen2-VL-2B-Instruct base: 32,768 max sequence. CHECK against the V2 checkpoint config.json once the card is reachable.</t>
+        </is>
+      </c>
+      <c r="T87" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U87" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V87" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W87" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X87" s="21" t="inlineStr">
+        <is>
+          <t>5. Video to Embeddings - purpose-built for video, image and visual document in one space</t>
+        </is>
+      </c>
+      <c r="Y87" s="15" t="inlineStr">
+        <is>
+          <t>arxiv 2507.04590 title and abstract: explicitly motivated by existing embedders (VLM2Vec, E5-V, GME) being limited to natural images with poor video support.</t>
+        </is>
+      </c>
+      <c r="Z87" s="21" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings; visual document retrieval; temporal grounding</t>
+        </is>
+      </c>
+      <c r="AA87" s="15" t="inlineStr">
+        <is>
+          <t>MMEB-V2 adds five task types over MMEB: visual document retrieval, video retrieval, temporal grounding, video classification and video QA [arxiv 2507.04590].</t>
+        </is>
+      </c>
+      <c r="AB87" s="21" t="inlineStr">
+        <is>
+          <t>MMEB-V2 overall 58.0 across 78 datasets | video retrieval 34.9 Hit@1</t>
+        </is>
+      </c>
+      <c r="AC87" s="15" t="inlineStr">
+        <is>
+          <t>MMEB-V2 overall 58.0 VERIFIED 2026-08-10 from arxiv 2507.04590 and the project page tiger-ai-lab.github.io/VLM2Vec - reported as the top overall score across all 78 MMEB-V2 datasets at publication, beating GME, LamRA and the original VLM2Vec on the SAME Qwen2-VL backbone.  ||  Video retrieval 34.9 Hit@1 is third-party-reported; CHECK against the paper table directly before quoting it.  ||  NOTE: since publication Qwen3-VL-Embedding-8B has overtaken it at 66.1 MMEB-V2 video.</t>
+        </is>
+      </c>
+      <c r="AD87" s="21" t="inlineStr">
+        <is>
+          <t>transformers (github.com/TIGER-AI-Lab/VLM2Vec)</t>
+        </is>
+      </c>
+      <c r="AE87" s="15" t="inlineStr">
+        <is>
+          <t>github.com/TIGER-AI-Lab/VLM2Vec is the reference implementation. NO GGUF, NO vLLM path documented.</t>
+        </is>
+      </c>
+      <c r="AF87" s="18" t="inlineStr">
+        <is>
+          <t>PARTIALLY VERIFIED 2026-08-10. Paper and project page confirm MMEB-V2 58.0. The HuggingFace checkpoint card returned HTTP 401 so licence and config could not be read directly - CHECK before deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="19" t="inlineStr">
+        <is>
+          <t>VLM2Vec-V2 (Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>arxiv.org/abs/2507.04590 - 'VLM2Vec-V2: Advancing Multimodal Embedding for Videos, Images, and Visual Documents'</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/TIGER-Lab - VLM2Vec model family is released Apache 2.0. CHECK the specific V2 checkpoint card, which returned HTTP 401 at time of writing.</t>
+        </is>
+      </c>
+      <c r="E88" s="21" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: TIGER-AI-Lab (University of Waterloo, Canada) with Salesforce Research co-authors. Allied jurisdiction. Base model is Qwen2-VL (China) - the licence stack is Apache over Apache, but note the lineage.</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Origin: arxiv 2507.04590 author list (Meng, Jiang, Liu, Su, Yang, Fu, Qin, Chen, Xu, Xiong, Zhou, Chen, Yavuz).  ||  Base model lineage: Qwen2-VL-2B-Instruct.</t>
+        </is>
+      </c>
+      <c r="G88" s="21" t="inlineStr">
+        <is>
+          <t>2.2B dense (base: Qwen2-VL-2B-Instruct, LoRA fine-tuned)</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I88" s="21" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="J88" s="21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K88" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L88" s="21" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2507.04590 - method section. Hardware not disclosed. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N88" s="21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O88" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P88" s="21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q88" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R88" s="21" t="inlineStr">
+        <is>
+          <t>32,768 tokens</t>
+        </is>
+      </c>
+      <c r="S88" s="15" t="inlineStr">
+        <is>
+          <t>Inherited from the Qwen2-VL-2B-Instruct base: 32,768 max sequence. CHECK against the V2 checkpoint config.json once the card is reachable.</t>
+        </is>
+      </c>
+      <c r="T88" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U88" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V88" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W88" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X88" s="21" t="inlineStr">
+        <is>
+          <t>5. Video to Embeddings - purpose-built for video, image and visual document in one space</t>
+        </is>
+      </c>
+      <c r="Y88" s="15" t="inlineStr">
+        <is>
+          <t>arxiv 2507.04590 title and abstract: explicitly motivated by existing embedders (VLM2Vec, E5-V, GME) being limited to natural images with poor video support.</t>
+        </is>
+      </c>
+      <c r="Z88" s="21" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings; visual document retrieval; temporal grounding</t>
+        </is>
+      </c>
+      <c r="AA88" s="15" t="inlineStr">
+        <is>
+          <t>MMEB-V2 adds five task types over MMEB: visual document retrieval, video retrieval, temporal grounding, video classification and video QA [arxiv 2507.04590].</t>
+        </is>
+      </c>
+      <c r="AB88" s="21" t="inlineStr">
+        <is>
+          <t>MMEB-V2 overall 58.0 across 78 datasets | video retrieval 34.9 Hit@1</t>
+        </is>
+      </c>
+      <c r="AC88" s="15" t="inlineStr">
+        <is>
+          <t>MMEB-V2 overall 58.0 VERIFIED 2026-08-10 from arxiv 2507.04590 and the project page tiger-ai-lab.github.io/VLM2Vec - reported as the top overall score across all 78 MMEB-V2 datasets at publication, beating GME, LamRA and the original VLM2Vec on the SAME Qwen2-VL backbone.  ||  Video retrieval 34.9 Hit@1 is third-party-reported; CHECK against the paper table directly before quoting it.  ||  NOTE: since publication Qwen3-VL-Embedding-8B has overtaken it at 66.1 MMEB-V2 video.</t>
+        </is>
+      </c>
+      <c r="AD88" s="21" t="inlineStr">
+        <is>
+          <t>transformers (github.com/TIGER-AI-Lab/VLM2Vec)</t>
+        </is>
+      </c>
+      <c r="AE88" s="15" t="inlineStr">
+        <is>
+          <t>github.com/TIGER-AI-Lab/VLM2Vec is the reference implementation. NO GGUF, NO vLLM path documented.</t>
+        </is>
+      </c>
+      <c r="AF88" s="18" t="inlineStr">
+        <is>
+          <t>PARTIALLY VERIFIED 2026-08-10. Paper and project page confirm MMEB-V2 58.0. The HuggingFace checkpoint card returned HTTP 401 so licence and config could not be read directly - CHECK before deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>E5-V (LLaVA-NeXT-8B)</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/royokong/e5-v - model card</t>
+        </is>
+      </c>
+      <c r="C89" s="23" t="inlineStr">
+        <is>
+          <t>LICENCE UNCLEAR - see source</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/royokong/e5-v does NOT state a licence on the card. The base is lmms-lab/llama3-llava-next-8b, which derives from Llama 3 - so the Llama 3 Community Licence very likely flows through. DO NOT DEPLOY WITHOUT LEGAL CONFIRMING THE CHAIN.</t>
+        </is>
+      </c>
+      <c r="E89" s="17" t="inlineStr">
+        <is>
+          <t>Cannot be stated with confidence because the licence is not declared on the model card. The Llama 3 lineage means the Llama Community Licence terms probably apply, including the Acceptable Use Policy. LEGAL REVIEW REQUIRED BEFORE USE.</t>
+        </is>
+      </c>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/royokong/e5-v - no licence field present as at 2026-08-10.  ||  Base model: lmms-lab/llama3-llava-next-8b.  ||  Llama 3 licence: llama.com.  ||  This is the weakest licence position of any model in this sheet - weaker even than LLaVA-1.6, because there the licence is at least declared.</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>8B dense (base: llama3-llava-next-8b)</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="J89" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="K89" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L89" s="17" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M89" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2407.12580 'E5-V: Universal Embeddings with Multimodal Large Language Models'. The notable claim is that training on TEXT PAIRS ALONE transfers to multimodal embedding.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N89" s="17" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O89" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P89" s="17" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q89" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R89" s="17" t="inlineStr">
+        <is>
+          <t>8,192 tokens</t>
+        </is>
+      </c>
+      <c r="S89" s="15" t="inlineStr">
+        <is>
+          <t>Inherited from the Llama-3-8B base used by llama3-llava-next-8b. CHECK the checkpoint config.json - the card does not state it.</t>
+        </is>
+      </c>
+      <c r="T89" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U89" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V89" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W89" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X89" s="17" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - universal multimodal embeddings</t>
+        </is>
+      </c>
+      <c r="Y89" s="15" t="inlineStr">
+        <is>
+          <t>arxiv 2407.12580 abstract.</t>
+        </is>
+      </c>
+      <c r="Z89" s="17" t="inlineStr">
+        <is>
+          <t>Text embeddings; cross-modal retrieval</t>
+        </is>
+      </c>
+      <c r="AA89" s="15" t="inlineStr">
+        <is>
+          <t>The paper's core contribution is single-modality (text-only) training transferring to multimodal use, which cuts training cost substantially.</t>
+        </is>
+      </c>
+      <c r="AB89" s="17" t="inlineStr">
+        <is>
+          <t>Embedding dimension 4096. NUMERIC BENCHMARKS NOT ON THE CARD - see source.</t>
+        </is>
+      </c>
+      <c r="AC89" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10: huggingface.co/royokong/e5-v publishes NO numerical benchmark scores and NO licence. Embedding dimension 4096 and the 8B parameter count are confirmed from the card.  ||  Scores exist in arxiv 2407.12580 but were not read directly, so nothing is quoted here rather than quoting a number this sheet cannot cite to a table.  ||  Superseded in practice by Qwen3-VL-Embedding and GME, both of which publish scores and declare a licence.</t>
+        </is>
+      </c>
+      <c r="AD89" s="17" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE89" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/royokong/e5-v usage section. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF89" s="24" t="inlineStr">
+        <is>
+          <t>LICENCE NOT DECLARED ON THE CARD AND LLAMA 3 LINEAGE - LEGAL REVIEW REQUIRED. No benchmark figures published on the card. Listed for completeness; NOT recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>E5-V (LLaVA-NeXT-8B)</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/royokong/e5-v - model card</t>
+        </is>
+      </c>
+      <c r="C90" s="23" t="inlineStr">
+        <is>
+          <t>LICENCE UNCLEAR - see source</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/royokong/e5-v does NOT state a licence on the card. The base is lmms-lab/llama3-llava-next-8b, which derives from Llama 3 - so the Llama 3 Community Licence very likely flows through. DO NOT DEPLOY WITHOUT LEGAL CONFIRMING THE CHAIN.</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>Cannot be stated with confidence because the licence is not declared on the model card. The Llama 3 lineage means the Llama Community Licence terms probably apply, including the Acceptable Use Policy. LEGAL REVIEW REQUIRED BEFORE USE.</t>
+        </is>
+      </c>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/royokong/e5-v - no licence field present as at 2026-08-10.  ||  Base model: lmms-lab/llama3-llava-next-8b.  ||  Llama 3 licence: llama.com.  ||  This is the weakest licence position of any model in this sheet - weaker even than LLaVA-1.6, because there the licence is at least declared.</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>8B dense (base: llama3-llava-next-8b)</t>
+        </is>
+      </c>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="J90" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K90" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L90" s="17" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M90" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2407.12580 'E5-V: Universal Embeddings with Multimodal Large Language Models'. The notable claim is that training on TEXT PAIRS ALONE transfers to multimodal embedding.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N90" s="17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O90" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P90" s="17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q90" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R90" s="17" t="inlineStr">
+        <is>
+          <t>8,192 tokens</t>
+        </is>
+      </c>
+      <c r="S90" s="15" t="inlineStr">
+        <is>
+          <t>Inherited from the Llama-3-8B base used by llama3-llava-next-8b. CHECK the checkpoint config.json - the card does not state it.</t>
+        </is>
+      </c>
+      <c r="T90" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U90" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V90" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W90" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X90" s="17" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - universal multimodal embeddings</t>
+        </is>
+      </c>
+      <c r="Y90" s="15" t="inlineStr">
+        <is>
+          <t>arxiv 2407.12580 abstract.</t>
+        </is>
+      </c>
+      <c r="Z90" s="17" t="inlineStr">
+        <is>
+          <t>Text embeddings; cross-modal retrieval</t>
+        </is>
+      </c>
+      <c r="AA90" s="15" t="inlineStr">
+        <is>
+          <t>The paper's core contribution is single-modality (text-only) training transferring to multimodal use, which cuts training cost substantially.</t>
+        </is>
+      </c>
+      <c r="AB90" s="17" t="inlineStr">
+        <is>
+          <t>Embedding dimension 4096. NUMERIC BENCHMARKS NOT ON THE CARD - see source.</t>
+        </is>
+      </c>
+      <c r="AC90" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10: huggingface.co/royokong/e5-v publishes NO numerical benchmark scores and NO licence. Embedding dimension 4096 and the 8B parameter count are confirmed from the card.  ||  Scores exist in arxiv 2407.12580 but were not read directly, so nothing is quoted here rather than quoting a number this sheet cannot cite to a table.  ||  Superseded in practice by Qwen3-VL-Embedding and GME, both of which publish scores and declare a licence.</t>
+        </is>
+      </c>
+      <c r="AD90" s="17" t="inlineStr">
+        <is>
+          <t>transformers, sentence-transformers</t>
+        </is>
+      </c>
+      <c r="AE90" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/royokong/e5-v usage section. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF90" s="24" t="inlineStr">
+        <is>
+          <t>LICENCE NOT DECLARED ON THE CARD AND LLAMA 3 LINEAGE - LEGAL REVIEW REQUIRED. No benchmark figures published on the card. Listed for completeness; NOT recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>ColQwen2-v1.0 (Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/vidore/colqwen2-v1.0 - model card</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0 (backbone) + MIT (adapters)</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colqwen2-v1.0: the Qwen2-VL backbone is Apache 2.0 and the ColBERT adapters are MIT. Both permissive - this is the CLEANEST licence position of the ColBERT-style retrievers, and notably cleaner than ColPali whose backbone carries the Gemma Terms of Use.</t>
+        </is>
+      </c>
+      <c r="E91" s="21" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: ILLUIN Technology / CentraleSupelec (France) for the adapters; Qwen2-VL backbone is China-origin.</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Adapters: ColPali team, arxiv 2407.01449 (Faysse, Sibille, Wu, Omrani, Viaud, Hudelot, Colombo).  ||  Backbone: Qwen2-VL-2B-Instruct.</t>
+        </is>
+      </c>
+      <c r="G91" s="21" t="inlineStr">
+        <is>
+          <t>2.2B dense (base: Qwen2-VL-2B-Instruct)</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I91" s="21" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="J91" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K91" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L91" s="21" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M91" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2407.01449 'ColPali: Efficient Document Retrieval with Vision Language Models'. Hardware not disclosed on the card. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N91" s="21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O91" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P91" s="21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q91" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R91" s="21" t="inlineStr">
+        <is>
+          <t>Image patches, not a text window</t>
+        </is>
+      </c>
+      <c r="S91" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colqwen2-v1.0. NOTE: this model embeds PAGE IMAGES, so the meaningful limit is image resolution and patch count, not a token context window. It benefits from Qwen2-VL's dynamic resolution - no fixed page-size limit.</t>
+        </is>
+      </c>
+      <c r="T91" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U91" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V91" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W91" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X91" s="21" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - MULTI-VECTOR (ColBERT late interaction), not a single vector</t>
+        </is>
+      </c>
+      <c r="Y91" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colqwen2-v1.0: 'generates ColBERT-style multi-vector representations of text and images'.  ||  IMPORTANT ARCHITECTURAL DIFFERENCE: multi-vector means one embedding PER IMAGE PATCH, not one per image. Retrieval quality is much higher but the index is far larger and needs a store that supports late interaction (e.g. Vespa, Qdrant multivector). This is a real infrastructure commitment, not a drop-in.</t>
+        </is>
+      </c>
+      <c r="Z91" s="21" t="inlineStr">
+        <is>
+          <t>Screenshot and PDF page retrieval without OCR</t>
+        </is>
+      </c>
+      <c r="AA91" s="15" t="inlineStr">
+        <is>
+          <t>arxiv 2407.01449 - the central claim is retrieving from page IMAGES directly, skipping the OCR/layout/chunking pipeline entirely.</t>
+        </is>
+      </c>
+      <c r="AB91" s="21" t="inlineStr">
+        <is>
+          <t>ViDoRe benchmark - SCORES NOT ON THE CARD, see source</t>
+        </is>
+      </c>
+      <c r="AC91" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10: huggingface.co/vidore/colqwen2-v1.0 publishes NO numerical ViDoRe scores on the card, and arxiv.org/abs/2407.01449 abstract does not carry them either - they are in the paper body which was not read directly.  ||  Nothing is quoted here rather than quoting an uncited figure. The ViDoRe leaderboard at huggingface.co/spaces/vidore/vidore-leaderboard is the live source if a number is needed for review.</t>
+        </is>
+      </c>
+      <c r="AD91" s="21" t="inlineStr">
+        <is>
+          <t>colpali-engine, transformers</t>
+        </is>
+      </c>
+      <c r="AE91" s="15" t="inlineStr">
+        <is>
+          <t>github.com/illuin-tech/colpali is the reference implementation. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF91" s="18" t="inlineStr">
+        <is>
+          <t>LICENCE FULLY VERIFIED (Apache 2.0 + MIT) - cleanest of the ColBERT retrievers. BENCHMARK SCORES NOT CITED - not on the card, needs the paper body or the ViDoRe leaderboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>ColQwen2-v1.0 (Qwen2-VL-2B)</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/vidore/colqwen2-v1.0 - model card</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>Apache 2.0 (backbone) + MIT (adapters)</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colqwen2-v1.0: the Qwen2-VL backbone is Apache 2.0 and the ColBERT adapters are MIT. Both permissive - this is the CLEANEST licence position of the ColBERT-style retrievers, and notably cleaner than ColPali whose backbone carries the Gemma Terms of Use.</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="inlineStr">
+        <is>
+          <t>No country restriction. No field-of-use restriction. Patent grant included. Commercial use permitted. Origin: ILLUIN Technology / CentraleSupelec (France) for the adapters; Qwen2-VL backbone is China-origin.</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>apache.org/licenses/LICENSE-2.0 - Sections 2 (Copyright Licence) and 3 (Patent Licence). No geographic clause exists in the text.  ||  Adapters: ColPali team, arxiv 2407.01449 (Faysse, Sibille, Wu, Omrani, Viaud, Hudelot, Colombo).  ||  Backbone: Qwen2-VL-2B-Instruct.</t>
+        </is>
+      </c>
+      <c r="G92" s="21" t="inlineStr">
+        <is>
+          <t>2.2B dense (base: Qwen2-VL-2B-Instruct)</t>
+        </is>
+      </c>
+      <c r="H92" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I92" s="21" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="J92" s="21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K92" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L92" s="21" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M92" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2407.01449 'ColPali: Efficient Document Retrieval with Vision Language Models'. Hardware not disclosed on the card. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N92" s="21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O92" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P92" s="21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q92" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R92" s="21" t="inlineStr">
+        <is>
+          <t>Image patches, not a text window</t>
+        </is>
+      </c>
+      <c r="S92" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colqwen2-v1.0. NOTE: this model embeds PAGE IMAGES, so the meaningful limit is image resolution and patch count, not a token context window. It benefits from Qwen2-VL's dynamic resolution - no fixed page-size limit.</t>
+        </is>
+      </c>
+      <c r="T92" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U92" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V92" s="21" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W92" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X92" s="21" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - MULTI-VECTOR (ColBERT late interaction), not a single vector</t>
+        </is>
+      </c>
+      <c r="Y92" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colqwen2-v1.0: 'generates ColBERT-style multi-vector representations of text and images'.  ||  IMPORTANT ARCHITECTURAL DIFFERENCE: multi-vector means one embedding PER IMAGE PATCH, not one per image. Retrieval quality is much higher but the index is far larger and needs a store that supports late interaction (e.g. Vespa, Qdrant multivector). This is a real infrastructure commitment, not a drop-in.</t>
+        </is>
+      </c>
+      <c r="Z92" s="21" t="inlineStr">
+        <is>
+          <t>Screenshot and PDF page retrieval without OCR</t>
+        </is>
+      </c>
+      <c r="AA92" s="15" t="inlineStr">
+        <is>
+          <t>arxiv 2407.01449 - the central claim is retrieving from page IMAGES directly, skipping the OCR/layout/chunking pipeline entirely.</t>
+        </is>
+      </c>
+      <c r="AB92" s="21" t="inlineStr">
+        <is>
+          <t>ViDoRe benchmark - SCORES NOT ON THE CARD, see source</t>
+        </is>
+      </c>
+      <c r="AC92" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10: huggingface.co/vidore/colqwen2-v1.0 publishes NO numerical ViDoRe scores on the card, and arxiv.org/abs/2407.01449 abstract does not carry them either - they are in the paper body which was not read directly.  ||  Nothing is quoted here rather than quoting an uncited figure. The ViDoRe leaderboard at huggingface.co/spaces/vidore/vidore-leaderboard is the live source if a number is needed for review.</t>
+        </is>
+      </c>
+      <c r="AD92" s="21" t="inlineStr">
+        <is>
+          <t>colpali-engine, transformers</t>
+        </is>
+      </c>
+      <c r="AE92" s="15" t="inlineStr">
+        <is>
+          <t>github.com/illuin-tech/colpali is the reference implementation. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF92" s="18" t="inlineStr">
+        <is>
+          <t>LICENCE FULLY VERIFIED (Apache 2.0 + MIT) - cleanest of the ColBERT retrievers. BENCHMARK SCORES NOT CITED - not on the card, needs the paper body or the ViDoRe leaderboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>ColPali-v1.2 (PaliGemma-3B)</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/vidore/colpali-v1.2 - model card</t>
+        </is>
+      </c>
+      <c r="C93" s="23" t="inlineStr">
+        <is>
+          <t>MIT (adapters) + Gemma Terms (backbone)</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colpali-v1.2: 'the adapters use MIT license; the PaliGemma backbone operates under the gemma license'.  ||  THE EFFECTIVE LICENCE IS THE MORE RESTRICTIVE OF THE TWO, i.e. the Gemma Terms of Use, which is NOT an OSI open source licence.</t>
+        </is>
+      </c>
+      <c r="E93" s="17" t="inlineStr">
+        <is>
+          <t>No country restriction stated. Google retains the right to restrict use remotely. Prohibited Use Policy applies and Google may update it. Adapters are MIT and unrestricted, but the PaliGemma backbone carries the Gemma Terms including the Prohibited Use Policy. Prefer ColQwen2 (Apache 2.0 + MIT) unless there is a specific reason to use this one.</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>ai.google.dev/gemma/terms - Section 3.2 (Use Restrictions) and the Gemma Prohibited Use Policy at ai.google.dev/gemma/prohibited_use_policy. NOTE: this is a Terms-of-Use, NOT an OSI-approved open source licence. Legal review required before shipping.  ||  Adapter licence: huggingface.co/vidore/colpali-v1.2.  ||  Backbone: google/paligemma-3b-pt-448.</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>3B dense (base: google/paligemma-3b-pt-448)</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
+      <c r="J93" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K93" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L93" s="17" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M93" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2407.01449. Hardware not disclosed on the card. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N93" s="17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O93" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P93" s="17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q93" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R93" s="17" t="inlineStr">
+        <is>
+          <t>Image patches, not a text window</t>
+        </is>
+      </c>
+      <c r="S93" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colpali-v1.2: base is paligemma-3b-pt-448, so pages are processed at 448x448. NOTE the PaliGemma text window is only 512 tokens (see the PaliGemma row in this sheet) - irrelevant here since the model embeds images, but it is the reason this cannot be repurposed as a text model.</t>
+        </is>
+      </c>
+      <c r="T93" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U93" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V93" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W93" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X93" s="17" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - MULTI-VECTOR (ColBERT late interaction)</t>
+        </is>
+      </c>
+      <c r="Y93" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/vidore/colpali-v1.2: 'ColBERT-style multi-vector representations', built by refining SigLIP and PaliGemma-3B with a late-interaction strategy.</t>
+        </is>
+      </c>
+      <c r="Z93" s="17" t="inlineStr">
+        <is>
+          <t>PDF and screenshot retrieval without an OCR pipeline</t>
+        </is>
+      </c>
+      <c r="AA93" s="15" t="inlineStr">
+        <is>
+          <t>arxiv 2407.01449 abstract: 'largely outperforms modern document retrieval pipelines while being drastically simpler, faster and end-to-end trainable'.</t>
+        </is>
+      </c>
+      <c r="AB93" s="17" t="inlineStr">
+        <is>
+          <t>ViDoRe benchmark - SCORES NOT ON THE CARD, see source</t>
+        </is>
+      </c>
+      <c r="AC93" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10: neither huggingface.co/vidore/colpali-v1.2 nor the arxiv 2407.01449 abstract carries numerical ViDoRe scores; they are in the paper body, which was not read directly.  ||  A third-party comparison put ColPali at 71.0 on a visual document retrieval score, but that figure could not be traced to a primary table and is therefore NOT entered in the benchmark column.  ||  Live source if needed: huggingface.co/spaces/vidore/vidore-leaderboard.</t>
+        </is>
+      </c>
+      <c r="AD93" s="17" t="inlineStr">
+        <is>
+          <t>colpali-engine, transformers</t>
+        </is>
+      </c>
+      <c r="AE93" s="15" t="inlineStr">
+        <is>
+          <t>github.com/illuin-tech/colpali. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF93" s="18" t="inlineStr">
+        <is>
+          <t>LICENCE VERIFIED but EFFECTIVE LICENCE IS GEMMA TERMS via the backbone - prefer ColQwen2. BENCHMARK SCORES NOT CITED - not on the card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>ColPali-v1.2 (PaliGemma-3B)</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/vidore/colpali-v1.2 - model card</t>
+        </is>
+      </c>
+      <c r="C94" s="23" t="inlineStr">
+        <is>
+          <t>MIT (adapters) + Gemma Terms (backbone)</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colpali-v1.2: 'the adapters use MIT license; the PaliGemma backbone operates under the gemma license'.  ||  THE EFFECTIVE LICENCE IS THE MORE RESTRICTIVE OF THE TWO, i.e. the Gemma Terms of Use, which is NOT an OSI open source licence.</t>
+        </is>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>No country restriction stated. Google retains the right to restrict use remotely. Prohibited Use Policy applies and Google may update it. Adapters are MIT and unrestricted, but the PaliGemma backbone carries the Gemma Terms including the Prohibited Use Policy. Prefer ColQwen2 (Apache 2.0 + MIT) unless there is a specific reason to use this one.</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>ai.google.dev/gemma/terms - Section 3.2 (Use Restrictions) and the Gemma Prohibited Use Policy at ai.google.dev/gemma/prohibited_use_policy. NOTE: this is a Terms-of-Use, NOT an OSI-approved open source licence. Legal review required before shipping.  ||  Adapter licence: huggingface.co/vidore/colpali-v1.2.  ||  Backbone: google/paligemma-3b-pt-448.</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>3B dense (base: google/paligemma-3b-pt-448)</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="inlineStr">
+        <is>
+          <t>See Model Name - SOURCE; parameter count read from the model card.</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>INT8</t>
+        </is>
+      </c>
+      <c r="J94" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K94" s="15" t="inlineStr">
+        <is>
+          <t>CALC. FP16 = params_B x 2.0 GB, INT8 = params_B x 1.0 GB.  ||  NOTE: these are NOT llama.cpp GGUF quantizations. No official GGUF builds exist for these models - they are served through transformers or sentence-transformers at native precision. The Q4_K_M/Q5_K_M/Q8_0 rows used elsewhere in this sheet do not apply here.</t>
+        </is>
+      </c>
+      <c r="L94" s="17" t="inlineStr">
+        <is>
+          <t>NOT A llama.cpp MODEL. INFERENCE: PyTorch/transformers on NVIDIA CUDA (sm_70+ practical for bf16), AMD ROCm, or CPU. vLLM supports several of these in embedding mode. NO GGUF BUILDS EXIST - the llama.cpp hardware floor quoted elsewhere in this sheet does not apply.</t>
+        </is>
+      </c>
+      <c r="M94" s="15" t="inlineStr">
+        <is>
+          <t>TRAINING: arxiv 2407.01449. Hardware not disclosed on the card. CHECK.  ||  INFERENCE: Inference stack read from each model card usage section, 2026-08-10.  ||  THE KEY POINT FOR ipoefgfefs: none of these models has an official GGUF build, so none of them can be served through the existing llama.cpp pipeline. Adopting any of them means standing up a second serving path (transformers, or vLLM in embedding mode). That is an infrastructure decision, not just a model choice.</t>
+        </is>
+      </c>
+      <c r="N94" s="17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O94" s="15" t="inlineStr">
+        <is>
+          <t>CALC. file_size * 1.15. The 15% covers llama.cpp context buffers, KV cache and allocator overhead.</t>
+        </is>
+      </c>
+      <c r="P94" s="17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q94" s="15" t="inlineStr">
+        <is>
+          <t>CALC. weights x 1.20. Embedding models run a SINGLE forward pass with no autoregressive decode, so there is NO growing KV cache - the 20% covers activations and batch buffers. This is why these rows are far cheaper in VRAM than a generative model of the same size.</t>
+        </is>
+      </c>
+      <c r="R94" s="17" t="inlineStr">
+        <is>
+          <t>Image patches, not a text window</t>
+        </is>
+      </c>
+      <c r="S94" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10 against huggingface.co/vidore/colpali-v1.2: base is paligemma-3b-pt-448, so pages are processed at 448x448. NOTE the PaliGemma text window is only 512 tokens (see the PaliGemma row in this sheet) - irrelevant here since the model embeds images, but it is the reason this cannot be repurposed as a text model.</t>
+        </is>
+      </c>
+      <c r="T94" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="U94" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="V94" s="17" t="inlineStr">
+        <is>
+          <t>NA - emits a vector, not tokens</t>
+        </is>
+      </c>
+      <c r="W94" s="15" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE. This model does not generate tokens - it emits a single fixed-length embedding vector (or a multi-vector set) from one forward pass. Throughput is measured in images/sec or documents/sec, not tokens/sec, and depends almost entirely on batch size. Quoting a tok/s figure here would be meaningless.</t>
+        </is>
+      </c>
+      <c r="X94" s="17" t="inlineStr">
+        <is>
+          <t>4. Image to Embeddings - MULTI-VECTOR (ColBERT late interaction)</t>
+        </is>
+      </c>
+      <c r="Y94" s="15" t="inlineStr">
+        <is>
+          <t>huggingface.co/vidore/colpali-v1.2: 'ColBERT-style multi-vector representations', built by refining SigLIP and PaliGemma-3B with a late-interaction strategy.</t>
+        </is>
+      </c>
+      <c r="Z94" s="17" t="inlineStr">
+        <is>
+          <t>PDF and screenshot retrieval without an OCR pipeline</t>
+        </is>
+      </c>
+      <c r="AA94" s="15" t="inlineStr">
+        <is>
+          <t>arxiv 2407.01449 abstract: 'largely outperforms modern document retrieval pipelines while being drastically simpler, faster and end-to-end trainable'.</t>
+        </is>
+      </c>
+      <c r="AB94" s="17" t="inlineStr">
+        <is>
+          <t>ViDoRe benchmark - SCORES NOT ON THE CARD, see source</t>
+        </is>
+      </c>
+      <c r="AC94" s="15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-10: neither huggingface.co/vidore/colpali-v1.2 nor the arxiv 2407.01449 abstract carries numerical ViDoRe scores; they are in the paper body, which was not read directly.  ||  A third-party comparison put ColPali at 71.0 on a visual document retrieval score, but that figure could not be traced to a primary table and is therefore NOT entered in the benchmark column.  ||  Live source if needed: huggingface.co/spaces/vidore/vidore-leaderboard.</t>
+        </is>
+      </c>
+      <c r="AD94" s="17" t="inlineStr">
+        <is>
+          <t>colpali-engine, transformers</t>
+        </is>
+      </c>
+      <c r="AE94" s="15" t="inlineStr">
+        <is>
+          <t>github.com/illuin-tech/colpali. NO GGUF.</t>
+        </is>
+      </c>
+      <c r="AF94" s="18" t="inlineStr">
+        <is>
+          <t>LICENCE VERIFIED but EFFECTIVE LICENCE IS GEMMA TERMS via the backbone - prefer ColQwen2. BENCHMARK SCORES NOT CITED - not on the card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="25" t="inlineStr">
         <is>
           <t>SOURCING METHODOLOGY - READ BEFORE REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="26" t="inlineStr">
-        <is>
-          <t>EVIDENCE GRADE, strongest to weakest. Every SOURCE cell above resolves to one of these:</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="26" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. PEER-REVIEWED PAPER      arXiv ID given. Strongest evidence. Used for Phi-4, Llama 3.1, StarCoder2,</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                              Qwen2.5-Coder, DeepSeek-Coder-V2, Qwen2-VL, PaliGemma, LLaVA, Gemma 3, R1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. OFFICIAL MODEL CARD      HuggingFace card or vendor doc. This is the PRIMARY source where no paper</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                              exists - Granite 3.3, Phi-3.5-mini, Phi-3.5-Vision, Llama 3.2, CodeGemma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                              Not peer reviewed, but first-party and authoritative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. VENDOR BLOG              Official announcement. Used where the card and paper are both silent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. PUBLIC LEADERBOARD       NO PAPER EXISTS for the number. Third-party. Weakest published evidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                              Applies to: Mistral 7B HumanEval (EvalPlus), part of InternVL2 (OpenCompass).</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. CALCULATED HERE          Formula stated inline in the SOURCE cell. Nothing measured on hardware.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                              Applies to: model size, CPU RAM, VRAM, and ALL tok/s figures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="26" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="26" t="inlineStr">
-        <is>
-          <t>THREE THINGS A REVIEWER SHOULD CHALLENGE FIRST:</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="26" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  a) tok/s is CALCULATED, NOT MEASURED. Every tok/s figure is a memory-bandwidth-bound estimate:</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     bandwidth x efficiency / model_size_GB. No vendor publishes tok/s and none was benchmarked here.</t>
+          <t>EVIDENCE GRADE, strongest to weakest. Every SOURCE cell above resolves to one of these:</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Real throughput depends on batch size, prompt length, KV cache pressure and the engine used.</t>
-        </is>
-      </c>
+      <c r="A98" s="26" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Treat these as relative rankings between models, NOT as absolute performance commitments.</t>
+          <t xml:space="preserve">  1. PEER-REVIEWED PAPER      arXiv ID given. Strongest evidence. Used for Phi-4, Llama 3.1, StarCoder2,</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="26" t="inlineStr"/>
+      <c r="A100" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              Qwen2.5-Coder, DeepSeek-Coder-V2, Qwen2-VL, PaliGemma, LLaVA, Gemma 3, R1.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  b) HARDWARE SUPPORT SPLITS INTO TWO DIFFERENT THINGS. Papers state only the hardware a model was</t>
+          <t xml:space="preserve">  2. OFFICIAL MODEL CARD      HuggingFace card or vendor doc. This is the PRIMARY source where no paper</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     TRAINED on (H100, A100, TPU). No paper states what hardware can RUN the model. Inference</t>
+          <t xml:space="preserve">                              exists - Granite 3.3, Phi-3.5-mini, Phi-3.5-Vision, Llama 3.2, CodeGemma.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     compatibility comes entirely from llama.cpp's supported-backends documentation. Both are given</t>
+          <t xml:space="preserve">                              Not peer reviewed, but first-party and authoritative.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     separately in the Hardware Support column and must not be conflated.</t>
+          <t xml:space="preserve">  3. VENDOR BLOG              Official announcement. Used where the card and paper are both silent.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="26" t="inlineStr"/>
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. PUBLIC LEADERBOARD       NO PAPER EXISTS for the number. Third-party. Weakest published evidence.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  c) 'NOT PUBLISHED' IS A FINDING, NOT A GAP. MultiPL-E C++ - the benchmark closest to the ipoefgfefs</t>
+          <t xml:space="preserve">                              Applies to: Mistral 7B HumanEval (EvalPlus), part of InternVL2 (OpenCompass).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     workload - is published by only 3 of the 19 models here. Phi-4, Granite and CodeGemma never</t>
+          <t xml:space="preserve">  5. CALCULATED HERE          Formula stated inline in the SOURCE cell. Nothing measured on hardware.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     released a C++ number. Any C++ claim about them is inference from Python HumanEval, and should</t>
+          <t xml:space="preserve">                              Applies to: model size, CPU RAM, VRAM, and ALL tok/s figures.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     be challenged as such.</t>
-        </is>
-      </c>
+      <c r="A109" s="26" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="26" t="inlineStr"/>
+      <c r="A110" s="26" t="inlineStr">
+        <is>
+          <t>THREE THINGS A REVIEWER SHOULD CHALLENGE FIRST:</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="26" t="inlineStr">
-        <is>
-          <t>CELLS MARKED 'CHECK' IN THE VERIFICATION STATUS COLUMN:</t>
-        </is>
-      </c>
+      <c r="A111" s="26" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="26" t="inlineStr"/>
+      <c r="A112" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a) tok/s is CALCULATED, NOT MEASURED. Every tok/s figure is a memory-bandwidth-bound estimate:</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  These values are correct to the best of current knowledge, but the exact table or section citation</t>
+          <t xml:space="preserve">     bandwidth x efficiency / model_size_GB. No vendor publishes tok/s and none was benchmarked here.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  has NOT been re-read against the source document. Before this sheet goes to architecture review,</t>
+          <t xml:space="preserve">     Real throughput depends on batch size, prompt length, KV cache pressure and the engine used.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  open each cited paper and confirm the number and its table. This is flagged deliberately rather than</t>
+          <t xml:space="preserve">     Treat these as relative rankings between models, NOT as absolute performance commitments.</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  presenting an unverified citation as authoritative.</t>
-        </is>
-      </c>
+      <c r="A116" s="26" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="26" t="inlineStr"/>
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  b) HARDWARE SUPPORT SPLITS INTO TWO DIFFERENT THINGS. Papers state only the hardware a model was</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="26" t="inlineStr">
         <is>
-          <t>CELLS MARKED RED - HARD BLOCKERS REQUIRING LEGAL SIGN-OFF:</t>
+          <t xml:space="preserve">     TRAINED on (H100, A100, TPU). No paper states what hardware can RUN the model. Inference</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="26" t="inlineStr"/>
+      <c r="A119" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     compatibility comes entirely from llama.cpp's supported-backends documentation. Both are given</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Llama 3.2 11B Vision: the Llama 3.2 licence excludes EU-domiciled entities from using the</t>
+          <t xml:space="preserve">     separately in the Hardware Support column and must not be conflated.</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    MULTIMODAL models. If ipoefgfefs ships in Europe this is a blocker, not a caveat.</t>
-        </is>
-      </c>
+      <c r="A121" s="26" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - LLaVA-1.6 13B: licence chain is LLaVA (Apache 2.0) over Vicuna over Llama 2. The effective</t>
+          <t xml:space="preserve">  c) 'NOT PUBLISHED' IS A FINDING, NOT A GAP. MultiPL-E C++ - the benchmark closest to the ipoefgfefs</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    licence is the most restrictive link, not the top one.</t>
+          <t xml:space="preserve">     workload - is published by only 3 of the 19 models here. Phi-4, Granite and CodeGemma never</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - DeepSeek-Coder-V2-Lite: custom licence with an attached use-restriction policy, not Apache/MIT.</t>
+          <t xml:space="preserve">     released a C++ number. Any C++ claim about them is inference from Python HumanEval, and should</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Moondream2: no paper exists. All benchmarks are vendor-self-reported and unverified.</t>
+          <t xml:space="preserve">     be challenged as such.</t>
         </is>
       </c>
     </row>
@@ -17503,7 +20959,7 @@
     <row r="127">
       <c r="A127" s="26" t="inlineStr">
         <is>
-          <t>MODEL ORIGIN vs LICENCE - THESE ARE SEPARATE QUESTIONS:</t>
+          <t>CELLS MARKED 'CHECK' IN THE VERIFICATION STATUS COLUMN:</t>
         </is>
       </c>
     </row>
@@ -17513,90 +20969,93 @@
     <row r="129">
       <c r="A129" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Qwen2.5-Coder, Qwen2-VL, DeepSeek and InternVL2 are China-origin. Their LICENCES (Apache 2.0/MIT)</t>
+          <t xml:space="preserve">  These values are correct to the best of current knowledge, but the exact table or section citation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  impose no restriction whatsoever. Whether component ORIGIN matters is a procurement and policy</t>
+          <t xml:space="preserve">  has NOT been re-read against the source document. Before this sheet goes to architecture review,</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  question - see NDAA Section 889, acquisition.gov/far/52.204-25 - and is a decision for legal and</t>
+          <t xml:space="preserve">  open each cited paper and confirm the number and its table. This is flagged deliberately rather than</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  contracts, not a technical filter. Both facts are stated in the Countries OK column; neither is</t>
+          <t xml:space="preserve">  presenting an unverified citation as authoritative.</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  presented as overriding the other.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="27" t="inlineStr">
-        <is>
-          <t>TOKEN RATE - PUBLISHED MEASUREMENTS BEHIND THE ESTIMATES</t>
-        </is>
-      </c>
+      <c r="A133" s="26" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="26" t="inlineStr">
+        <is>
+          <t>CELLS MARKED RED - HARD BLOCKERS REQUIRING LEGAL SIGN-OFF:</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="26" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="26" t="inlineStr">
         <is>
-          <t>READ THIS BEFORE ANYONE CHALLENGES THE tok/s COLUMNS.</t>
+          <t xml:space="preserve">  - Llama 3.2 11B Vision: the Llama 3.2 licence excludes EU-domiciled entities from using the</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="26" t="inlineStr"/>
+      <c r="A137" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    MULTIMODAL models. If ipoefgfefs ships in Europe this is a blocker, not a caveat.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="26" t="inlineStr">
         <is>
-          <t>No model paper and no vendor model card publishes tokens/sec - not for a single model in this sheet.</t>
+          <t xml:space="preserve">  - LLaVA-1.6 13B: licence chain is LLaVA (Apache 2.0) over Vicuna over Llama 2. The effective</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="26" t="inlineStr">
         <is>
-          <t>The metric depends on the inference engine, quantization, context length, batch size and hardware, none</t>
+          <t xml:space="preserve">    licence is the most restrictive link, not the top one.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="26" t="inlineStr">
         <is>
-          <t>of which a model paper controls. Community benchmarks are the only published source that exists.</t>
+          <t xml:space="preserve">  - DeepSeek-Coder-V2-Lite: custom licence with an attached use-restriction policy, not Apache/MIT.</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="26" t="inlineStr"/>
+      <c r="A141" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Moondream2: no paper exists. All benchmarks are vendor-self-reported and unverified.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="26" t="inlineStr">
-        <is>
-          <t>The tok/s columns are therefore ESTIMATES, and the efficiency factor in the formula is FITTED to the</t>
-        </is>
-      </c>
+      <c r="A142" s="26" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="26" t="inlineStr">
         <is>
-          <t>measurements below rather than assumed. The measurements themselves are cited so they can be checked.</t>
+          <t>MODEL ORIGIN vs LICENCE - THESE ARE SEPARATE QUESTIONS:</t>
         </is>
       </c>
     </row>
@@ -17606,52 +21065,49 @@
     <row r="145">
       <c r="A145" s="26" t="inlineStr">
         <is>
-          <t>GPU - RTX 4090 24GB, llama.cpp build 3520, Q4_K_M, 2048 context, single batch (not server-batched):</t>
+          <t xml:space="preserve">  Qwen2.5-Coder, Qwen2-VL, DeepSeek and InternVL2 are China-origin. Their LICENCES (Apache 2.0/MIT)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="26" t="inlineStr"/>
+      <c r="A146" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  impose no restriction whatsoever. Whether component ORIGIN matters is a procurement and policy</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    model size        measured tok/s      this sheet's estimate</t>
+          <t xml:space="preserve">  question - see NDAA Section 889, acquisition.gov/far/52.204-25 - and is a decision for legal and</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7B                135                 ~131 at 4.3 GB</t>
+          <t xml:space="preserve">  contracts, not a technical filter. Both facts are stated in the Countries OK column; neither is</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    13B                78                 ~ 76 at 7.3 GB</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    34B                42                 (out of SLM range)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    70B (Q2_K)         18                 (out of SLM range)</t>
+          <t xml:space="preserve">  presented as overriding the other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="27" t="inlineStr">
+        <is>
+          <t>TOKEN RATE - PUBLISHED MEASUREMENTS BEHIND THE ESTIMATES</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    [source: mustafa.net/llm-tokens-per-second-benchmarks]</t>
+          <t>READ THIS BEFORE ANYONE CHALLENGES THE tok/s COLUMNS.</t>
         </is>
       </c>
     </row>
@@ -17661,21 +21117,21 @@
     <row r="154">
       <c r="A154" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Independent cross-check on the exact model in this sheet:</t>
+          <t>No model paper and no vendor model card publishes tokens/sec - not for a single model in this sheet.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Llama 3.1 8B Q4_K_M, RTX 4090:  95-110 tok/s via Ollama;  104 tok/s via llama.cpp at 16K context</t>
+          <t>The metric depends on the inference engine, quantization, context length, batch size and hardware, none</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    [sources: markaicode.com Ollama vs llama.cpp benchmark; smeltcore.com]</t>
+          <t>of which a model paper controls. Community benchmarks are the only published source that exists.</t>
         </is>
       </c>
     </row>
@@ -17685,130 +21141,134 @@
     <row r="158">
       <c r="A158" s="26" t="inlineStr">
         <is>
-          <t>GPU - other cards, same conditions, useful if the ipoefgfefs server is not a 4090:</t>
+          <t>The tok/s columns are therefore ESTIMATES, and the efficiency factor in the formula is FITTED to the</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="26" t="inlineStr"/>
+      <c r="A159" s="26" t="inlineStr">
+        <is>
+          <t>measurements below rather than assumed. The measurements themselves are cited so they can be checked.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RTX 3090 24GB      7B  95 tok/s    13B  55 tok/s    34B  28 tok/s</t>
-        </is>
-      </c>
+      <c r="A160" s="26" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    RTX 4070S 12GB     7B  75 tok/s    13B  40 tok/s    34B  out of memory</t>
+          <t>GPU - RTX 4090 24GB, llama.cpp build 3520, Q4_K_M, 2048 context, single batch (not server-batched):</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RTX 3060 12GB      7B  45 tok/s    13B  22 tok/s    34B  out of memory</t>
-        </is>
-      </c>
+      <c r="A162" s="26" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    [source: mustafa.net/llm-tokens-per-second-benchmarks]</t>
+          <t xml:space="preserve">    model size        measured tok/s      this sheet's estimate</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="26" t="inlineStr"/>
+      <c r="A164" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    7B                135                 ~131 at 4.3 GB</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="26" t="inlineStr">
         <is>
-          <t>CPU - measured anchors:</t>
+          <t xml:space="preserve">    13B                78                 ~ 76 at 7.3 GB</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="26" t="inlineStr"/>
+      <c r="A166" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    34B                42                 (out of SLM range)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AMD EPYC 7763            Llama 2 7B Q4_K_M      15 tok/s</t>
+          <t xml:space="preserve">    70B (Q2_K)         18                 (out of SLM range)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Dual-socket EPYC 9334    Q4 7B-20B              20-28 tok/s</t>
+          <t xml:space="preserve">    [source: mustafa.net/llm-tokens-per-second-benchmarks]</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Intel Sapphire Rapids 8480+  7B INT4            ~50 tok/s   (server CPU, not a desktop comparison)</t>
-        </is>
-      </c>
+      <c r="A169" s="26" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    General desktop band     3B-7B Q4_K_M           4-15 tok/s</t>
+          <t xml:space="preserve">  Independent cross-check on the exact model in this sheet:</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    [sources: blog.leaseweb.com EPYC LLM inference benchmark; promptquorum.com; myaihardware.com]</t>
+          <t xml:space="preserve">    Llama 3.1 8B Q4_K_M, RTX 4090:  95-110 tok/s via Ollama;  104 tok/s via llama.cpp at 16K context</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="26" t="inlineStr"/>
+      <c r="A172" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [sources: markaicode.com Ollama vs llama.cpp benchmark; smeltcore.com]</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    This sheet estimates ~11 tok/s for a 7B Q4_K_M, inside the measured desktop band.</t>
-        </is>
-      </c>
+      <c r="A173" s="26" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="26" t="inlineStr"/>
+      <c r="A174" s="26" t="inlineStr">
+        <is>
+          <t>GPU - other cards, same conditions, useful if the ipoefgfefs server is not a 4090:</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="26" t="inlineStr">
-        <is>
-          <t>THREE CAVEATS THAT APPLY TO EVERY tok/s FIGURE HERE:</t>
-        </is>
-      </c>
+      <c r="A175" s="26" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="26" t="inlineStr"/>
+      <c r="A176" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RTX 3090 24GB      7B  95 tok/s    13B  55 tok/s    34B  28 tok/s</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. These are 2048-CONTEXT numbers. The ipoefgfefs prompt is 6-8K. Throughput falls as the KV cache</t>
+          <t xml:space="preserve">    RTX 4070S 12GB     7B  75 tok/s    13B  40 tok/s    34B  out of memory</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     grows, so expect REAL rates BELOW the table above. The 16K-context cross-check (104 vs 135 tok/s)</t>
+          <t xml:space="preserve">    RTX 3060 12GB      7B  45 tok/s    13B  22 tok/s    34B  out of memory</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     shows roughly a 20-25% drop, which is the right order to plan against.</t>
+          <t xml:space="preserve">    [source: mustafa.net/llm-tokens-per-second-benchmarks]</t>
         </is>
       </c>
     </row>
@@ -17818,45 +21278,45 @@
     <row r="181">
       <c r="A181" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. SINGLE REQUEST, NOT CONCURRENT. Under 4 simultaneous users on a 24GB card, published figures drop</t>
+          <t>CPU - measured anchors:</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     to around 18 tok/s per user [source: localllm.in/blog/llamacpp-vram-requirements-for-local-llms].</t>
-        </is>
-      </c>
+      <c r="A182" s="26" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     If the workflow builder serves multiple engineers at once, size against that, not against 135.</t>
+          <t xml:space="preserve">    AMD EPYC 7763            Llama 2 7B Q4_K_M      15 tok/s</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="26" t="inlineStr"/>
+      <c r="A184" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Dual-socket EPYC 9334    Q4 7B-20B              20-28 tok/s</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. ENGINE MATTERS AS MUCH AS HARDWARE. These are llama.cpp figures. vLLM and SGLang trade single-</t>
+          <t xml:space="preserve">    Intel Sapphire Rapids 8480+  7B INT4            ~50 tok/s   (server CPU, not a desktop comparison)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     request latency for far higher aggregate throughput under concurrency, so these numbers do not</t>
+          <t xml:space="preserve">    General desktop band     3B-7B Q4_K_M           4-15 tok/s</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     transfer across engines.</t>
+          <t xml:space="preserve">    [sources: blog.leaseweb.com EPYC LLM inference benchmark; promptquorum.com; myaihardware.com]</t>
         </is>
       </c>
     </row>
@@ -17866,90 +21326,89 @@
     <row r="189">
       <c r="A189" s="26" t="inlineStr">
         <is>
-          <t>BOTTOM LINE FOR REVIEW: use tok/s to RANK the models against each other, which is what it is reliable</t>
+          <t xml:space="preserve">    This sheet estimates ~11 tok/s for a 7B Q4_K_M, inside the measured desktop band.</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="26" t="inlineStr">
-        <is>
-          <t>for. Do not quote it as a performance commitment. The only number that settles real throughput on the</t>
-        </is>
-      </c>
+      <c r="A190" s="26" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="26" t="inlineStr">
         <is>
-          <t>ipoefgfefs workload is a measurement on ipo's own hardware at the real 6-8K prompt length.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="20" customHeight="1">
-      <c r="A193" s="28" t="inlineStr">
-        <is>
-          <t>CORRECTIONS LOG - VERIFICATION PASS 2026-08-10</t>
+          <t>THREE CAVEATS THAT APPLY TO EVERY tok/s FIGURE HERE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="26" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. These are 2048-CONTEXT numbers. The ipoefgfefs prompt is 6-8K. Throughput falls as the KV cache</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="26" t="inlineStr">
         <is>
-          <t>Nine models were checked directly against their primary sources. SIX material errors were found in the</t>
+          <t xml:space="preserve">     grows, so expect REAL rates BELOW the table above. The 16K-context cross-check (104 vs 135 tok/s)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="26" t="inlineStr">
         <is>
-          <t>previous revision of this sheet and are corrected above. They are logged here rather than quietly fixed,</t>
+          <t xml:space="preserve">     shows roughly a 20-25% drop, which is the right order to plan against.</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="26" t="inlineStr">
-        <is>
-          <t>because two of them change the ranking.</t>
-        </is>
-      </c>
+      <c r="A196" s="26" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="26" t="inlineStr"/>
+      <c r="A197" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. SINGLE REQUEST, NOT CONCURRENT. Under 4 simultaneous users on a 24GB card, published figures drop</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Granite 3.3 8B HumanEval:  67.1%  -&gt;  89.73%     [source: IBM model card, Evaluation Results table]</t>
+          <t xml:space="preserve">     to around 18 tok/s per user [source: localllm.in/blog/llamacpp-vram-requirements-for-local-llms].</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     IMPACT: HIGH. Granite now has the HIGHEST HumanEval in this sheet, above Qwen2.5-Coder's 88.4%.</t>
+          <t xml:space="preserve">     If the workflow builder serves multiple engineers at once, size against that, not against 135.</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     It is US-origin, Apache 2.0, has FIM and 128K context. It was ranked 3rd on a wrong number.</t>
-        </is>
-      </c>
+      <c r="A200" s="26" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="26" t="inlineStr"/>
+      <c r="A201" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. ENGINE MATTERS AS MUCH AS HARDWARE. These are llama.cpp figures. vLLM and SGLang trade single-</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Qwen2.5-Coder 7B MultiPL-E C++:  63.4%  -&gt;  75.6%   [source: arxiv 2409.12186 Table 17]</t>
+          <t xml:space="preserve">     request latency for far higher aggregate throughput under concurrency, so these numbers do not</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     IMPACT: MEDIUM. Understated. Strengthens the existing rank-1 case rather than changing it.</t>
+          <t xml:space="preserve">     transfer across engines.</t>
         </is>
       </c>
     </row>
@@ -17959,165 +21418,162 @@
     <row r="205">
       <c r="A205" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. DeepSeek-Coder-V2-Lite MultiPL-E C++:  56.5%  -&gt;  75.8%   [source: arxiv 2406.11931 Table 3]</t>
+          <t>BOTTOM LINE FOR REVIEW: use tok/s to RANK the models against each other, which is what it is reliable</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     IMPACT: HIGH. This is now the highest MEASURED C++ score in the sheet, marginally above Qwen.</t>
+          <t>for. Do not quote it as a performance commitment. The only number that settles real throughput on the</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Offset by a restrictive custom licence and immature MoE tooling in llama.cpp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="26" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. CodeGemma 7B C++:  'NOT PUBLISHED'  -&gt;  BabelCode-HumanEval C++ 42.2%, BabelCode-MBPP C++ 56.7%</t>
+          <t>ipoefgfefs workload is a measurement on ipo's own hardware at the real 6-8K prompt length.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="27" t="inlineStr">
+        <is>
+          <t>CATEGORIES 4 AND 5 - IMAGE AND VIDEO EMBEDDINGS - READ BEFORE COMPARING THESE ROWS</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     [source: Google model card]. IMPACT: LOW - the model is already eliminated by its 8K context.</t>
+          <t>The last 8 models in this sheet cover the two categories the SLM-only filter had left empty.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Root cause: Google reports C++ under BabelCode, not MultiPL-E, so a MultiPL-E search missed it.</t>
+          <t>They need reading differently from everything above them. Four things matter.</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     NOTE: BabelCode and MultiPL-E are different harnesses. 42.2 is NOT comparable to Qwen's 75.6.</t>
-        </is>
-      </c>
+      <c r="A212" s="26" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="26" t="inlineStr"/>
+      <c r="A213" s="26" t="inlineStr">
+        <is>
+          <t>1. THEY ARE SLM-DERIVED, NOT NATIVE SLMs.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. Phi-4 GSM8K 91.5%:  REMOVED as unsourced.   [Microsoft publishes MGSM 80.6%, not GSM8K]</t>
-        </is>
-      </c>
+      <c r="A214" s="26" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     IMPACT: LOW. Phi-4's case rests on HumanEval 82.6 and MMLU 84.8, both confirmed.</t>
+          <t xml:space="preserve">   Each one is a VLM backbone - Qwen3-VL, Qwen2-VL, Phi-3.5-Vision, PaliGemma, LLaVA-NeXT - with the</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="26" t="inlineStr"/>
+      <c r="A216" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   generation head replaced by a pooled embedding head and retrained with contrastive loss. Same</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Llama 3.2 3B HumanEval 57.8%:  REMOVED as unsourced.   [Meta publishes no HumanEval for the 3B]</t>
+          <t xml:space="preserve">   architecture and parameter class as the models above, different output: a VECTOR, not tokens.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     IMPACT: MEDIUM. The edge candidate's code ability is UNMEASURED. It qualifies on size, not skill.</t>
+          <t xml:space="preserve">   Strictly they fail the 'generative language model' rule this sheet is built on. They are included</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="26" t="inlineStr"/>
+      <c r="A219" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   because they are the only SLM-class way to cover image and video embeddings at all, and because a</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="26" t="inlineStr">
         <is>
-          <t>TWO LICENCE FINDINGS, both narrower than previously stated:</t>
+          <t xml:space="preserve">   populated row with a caveat is more useful than an empty category. Every one is labelled</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="26" t="inlineStr"/>
+      <c r="A221" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SLM-DERIVED in its VERIFICATION STATUS cell so the distinction survives review.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7. Llama 3.2 EU exclusion applies to MULTIMODAL models ONLY. The text-only 3B is unaffected -</t>
-        </is>
-      </c>
+      <c r="A222" s="26" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     the previous flag on it is WITHDRAWN as over-cautious.</t>
+          <t>2. NONE OF THEM HAS A GGUF BUILD. THIS IS THE BIGGEST PRACTICAL CONSTRAINT.</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8. For the 11B Vision, the exclusion binds EU-DOMICILED DEVELOPERS, and expressly does NOT bind</t>
-        </is>
-      </c>
+      <c r="A224" s="26" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     end users of a product incorporating the model. A non-EU entity may build with it and supply</t>
+          <t xml:space="preserve">   The rest of this sheet assumes llama.cpp and GGUF quantization. These models are served through</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     EU customers. Exact licence wording is quoted in that model's Countries - SOURCE cell.</t>
+          <t xml:space="preserve">   transformers, or vLLM in embedding mode. That is why their rows show FP16 and INT8 instead of</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="26" t="inlineStr"/>
+      <c r="A227" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Q4_K_M / Q5_K_M / Q8_0 - the llama.cpp quantization spec simply does not apply to them.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="26" t="inlineStr">
         <is>
-          <t>CONFIRMED CORRECT, no change: Phi-4 (HumanEval 82.6, MMLU 84.8, MATH 80.4, 1920xH100 for 21 days),</t>
+          <t xml:space="preserve">   ADOPTING ANY OF THEM MEANS STANDING UP A SECOND SERVING PATH. That is an infrastructure decision</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="26" t="inlineStr">
         <is>
-          <t>Phi-3.5-mini (62.8 / 69 / 86.2, 512xH100 for 10 days), Llama 3.1 8B (HumanEval 72.6, GSM8K 84.5,</t>
+          <t xml:space="preserve">   for the ipoefgfefs SRV layer, not just a model choice, and it should be costed as one.</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="26" t="inlineStr">
-        <is>
-          <t>1.46M GPU-hours), Granite MMLU 65.54 and GSM8K 80.89, Qwen HumanEval 88.4 and MBPP 83.5,</t>
-        </is>
-      </c>
+      <c r="A230" s="26" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek HumanEval 81.1 and MBPP+ 68.8, Llama 3.2 3B MMLU 63.4 and GSM8K 77.7.</t>
+          <t>3. tok/s IS BLANK ON PURPOSE, AND VRAM IS LOWER THAN YOU MIGHT EXPECT.</t>
         </is>
       </c>
     </row>
@@ -18127,144 +21583,144 @@
     <row r="233">
       <c r="A233" s="26" t="inlineStr">
         <is>
-          <t>ONE DISAMBIGUATION: Llama 3.1 8B MMLU is 69.4% standard 5-shot; the 73.0% previously quoted is the</t>
+          <t xml:space="preserve">   These models do not decode autoregressively. One forward pass in, one vector out. There is no</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="26" t="inlineStr">
         <is>
-          <t>chain-of-thought variant. Both are now shown so it is not compared unfairly against standard-metric models.</t>
+          <t xml:space="preserve">   tokens-per-second figure to quote and no growing KV cache, which is why their VRAM is computed as</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="26" t="inlineStr"/>
+      <c r="A235" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   weights x 1.20 rather than weights + KV. Throughput for them is images/sec or documents/sec and</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="26" t="inlineStr">
         <is>
-          <t>STILL UNVERIFIED - the remaining CHECK cells:</t>
+          <t xml:space="preserve">   depends almost entirely on batch size. Any tok/s number for these models would be meaningless.</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  StarCoder2 15B (paper HTML would not yield the MultiPL-E table - needs the PDF read manually),</t>
-        </is>
-      </c>
+      <c r="A237" s="26" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Mistral 7B, Gemma 3 4B, DeepSeek-R1-Distill-14B, and all seven vision models except where noted.</t>
+          <t>4. THE VIDEO SCORES ARE NOT COMPARABLE TO EACH OTHER. THIS IS THE TRAP.</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  These are lower-stakes: none of them is in the shortlist.</t>
-        </is>
-      </c>
+      <c r="A239" s="26" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="26" t="inlineStr"/>
+      <c r="A240" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   MMEB-V2 video results are reported under DIFFERENT FRAME-SAMPLING PROTOCOLS depending on the model.</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="26" t="inlineStr">
         <is>
-          <t>PASS 2 - REMAINING 11 MODELS CHECKED, 2026-08-10. Eight further corrections:</t>
+          <t xml:space="preserve">   Per the VLM2Vec-V2 evaluation protocol [arxiv 2507.04590]: GME and LamRA were evaluated using a</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="26" t="inlineStr"/>
+      <c r="A242" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SINGLE MIDDLE FRAME, while VLM2Vec-V2 and the others use 8 UNIFORMLY SAMPLED FRAMES.</t>
+        </is>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  PaliGemma 3B context:  8,192  -&gt;  512 tokens     [source: Google model card]</t>
-        </is>
-      </c>
+      <c r="A243" s="26" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      IMPACT: HIGH. Wrong by a factor of 16. At 512 tokens it cannot hold the ipoefgfefs prompt</t>
+          <t xml:space="preserve">   A single-middle-frame score is an IMAGE result wearing a video label - it cannot capture motion,</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      at all. Categorically disqualified, not merely marginal.</t>
+          <t xml:space="preserve">   duration or event ordering, which is the entire point of video embedding for a VMS. So although</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="26" t="inlineStr"/>
+      <c r="A246" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   third-party tables show GME-7B at 38.6 Hit@1 on video, ABOVE VLM2Vec-V2's 34.9, that comparison is</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10. Moondream2 benchmarks were STALE and UNDERSTATED the model:</t>
+          <t xml:space="preserve">   invalid. GME is listed in this sheet under IMAGE ONLY for exactly this reason.</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      DocVQA 61.9 -&gt; 79.3, TextVQA 60.2 -&gt; 76.3. Params 1.9B -&gt; 2B.</t>
-        </is>
-      </c>
+      <c r="A248" s="26" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      It now also reports COCO object detection 51.2% and ScreenSpot pointing 80.4% - a 2B model</t>
+          <t xml:space="preserve">   If a reviewer points at a video leaderboard, this is the question to ask first: how many frames?</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      doing detection and pointing is directly interesting for a VMS. Still no paper.</t>
-        </is>
-      </c>
+      <c r="A250" s="26" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="26" t="inlineStr"/>
+      <c r="A251" s="26" t="inlineStr">
+        <is>
+          <t>WHAT THIS SHEET ACTUALLY RECOMMENDS FOR THESE TWO CATEGORIES:</t>
+        </is>
+      </c>
     </row>
     <row r="252">
-      <c r="A252" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  11. StarCoder2 training hardware:  1024 x A100-80GB  -&gt;  1024 x H100.  HumanEval 46.4 -&gt; 46.3.</t>
-        </is>
-      </c>
+      <c r="A252" s="26" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="26" t="inlineStr"/>
+      <c r="A253" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Category 4, image to embeddings   -&gt; Qwen3-VL-Embedding-2B</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  12. DeepSeek-R1-Distill-14B code ability: previously recorded UNKNOWN. WRONG - the card gives</t>
+          <t xml:space="preserve">     MMEB-V2 Image 75.0 at 2B and 4 GB in FP16. The 8B scores 80.1 but costs four times the memory</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      LiveCodeBench 53.1% and Codeforces 1481. HumanEval and C++ remain unpublished, and the base</t>
+          <t xml:space="preserve">     for 5.1 points. Apache 2.0, and Matryoshka dimensions (64-2048) let you shrink the index later</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      is Qwen2.5 general (NOT Coder), so that caveat still stands.</t>
+          <t xml:space="preserve">     without retraining - which matters if you are embedding every camera frame.</t>
         </is>
       </c>
     </row>
@@ -18274,65 +21730,73 @@
     <row r="258">
       <c r="A258" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13. InternVL2 8B MMMU:  51.2  -&gt;  51.8</t>
+          <t xml:space="preserve">   Category 5, video to embeddings   -&gt; Qwen3-VL-Embedding-8B, or the 2B if memory is tight</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="26" t="inlineStr"/>
+      <c r="A259" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     MMEB-V2 Video 66.1 (8B) and 61.9 (2B) are the highest genuine video figures found, both measured</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14. LLaVA-1.6 13B licence: 'Apache 2.0, check base' -&gt; LLAMA 2 COMMUNITY LICENSE, stated</t>
+          <t xml:space="preserve">     under the 8-frame protocol. VLM2Vec-V2 at 2.2B is the credible alternative and is purpose-built</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      directly on the HuggingFace card. The licence-chain warning was right; the label was not.</t>
+          <t xml:space="preserve">     for video, but at MMEB-V2 58.0 overall it has been overtaken since publication.</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Benchmarks remain UNCONFIRMED - the card publishes none and 1.5 vs 1.6 figures are conflated.</t>
-        </is>
-      </c>
+      <c r="A262" s="26" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="26" t="inlineStr"/>
+      <c r="A263" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   AVOID for these categories:</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  15. Gemma 3 4B: context is 128K INPUT but 8,192 OUTPUT. Added MBPP 46.0, MMMU 39.2, GSM8K 38.4,</t>
+          <t xml:space="preserve">     E5-V         - the model card declares NO LICENCE at all, and it inherits a Llama 3 lineage.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      MATH 24.2. Training hardware is TPUv4p/v5p/v5e, not TPUv5p alone.</t>
+          <t xml:space="preserve">                    Worst licence position in this entire sheet. Not worth the legal time.</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="26" t="inlineStr"/>
+      <c r="A266" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     ColPali      - effective licence is the Gemma Terms via the PaliGemma backbone. Use ColQwen2</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  16. Qwen2-VL: added TextVQA 84.3% - highest text-in-image score in this sheet. With DocVQA 94.5%</t>
+          <t xml:space="preserve">                    instead, which is Apache 2.0 backbone plus MIT adapters and scores comparably.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      it is the clear LPR / plate-reading candidate.</t>
+          <t xml:space="preserve">     GME for video - single-frame evaluation, see point 4.</t>
         </is>
       </c>
     </row>
@@ -18342,62 +21806,63 @@
     <row r="270">
       <c r="A270" s="26" t="inlineStr">
         <is>
-          <t>TWO EVALUATION-SETTING TRAPS, both of the kind a reviewer will probe:</t>
+          <t xml:space="preserve">   ONE ARCHITECTURAL WARNING ON ColPali AND ColQwen2: both emit MULTI-VECTOR (ColBERT late-interaction)</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="26" t="inlineStr"/>
+      <c r="A271" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   representations - one embedding per image patch, not one per image. Retrieval quality is markedly</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  a) Llama 3.2 11B Vision - the model card carries TWO tables. BASE PRETRAINED shows MMMU 41.7,</t>
+          <t xml:space="preserve">   better on documents, but the index is far larger and needs a vector store that supports late</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     DocVQA 62.3, ChartQA 39.4. INSTRUCTION-TUNED shows MMMU 50.7, DocVQA 88.4, ChartQA 83.4.</t>
+          <t xml:space="preserve">   interaction, such as Vespa or Qdrant multivector. They are not drop-in replacements for a</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Secondary sources quote the pretrained figures as if they were the instruct ones. This sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     uses the INSTRUCT table, which is correct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="26" t="inlineStr"/>
+          <t xml:space="preserve">   single-vector embedder and should not be compared to one on storage cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="20" customHeight="1">
+      <c r="A276" s="28" t="inlineStr">
+        <is>
+          <t>CORRECTIONS LOG - VERIFICATION PASS 2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  b) PaliGemma figures are single-task FINE-TUNED transfer results, confirmed by the card, NOT</t>
+          <t>Nine models were checked directly against their primary sources. SIX material errors were found in the</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     zero-shot. They must not be compared against zero-shot numbers from Qwen2-VL, Phi-3.5-Vision</t>
+          <t>previous revision of this sheet and are corrected above. They are logged here rather than quietly fixed,</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">     or InternVL2 elsewhere in this sheet.</t>
+          <t>because two of them change the ranking.</t>
         </is>
       </c>
     </row>
@@ -18407,38 +21872,38 @@
     <row r="281">
       <c r="A281" s="26" t="inlineStr">
         <is>
-          <t>CONFIRMED CORRECT IN PASS 2: Phi-3.5-Vision (81.9 / 43.0 / 72.0, 256xA100 for 6 days, 500B tokens),</t>
+          <t xml:space="preserve">  1. Granite 3.3 8B HumanEval:  67.1%  -&gt;  89.73%     [source: IBM model card, Evaluation Results table]</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="26" t="inlineStr">
         <is>
-          <t>Gemma 3 4B HumanEval 36.0 and MMLU 59.6, Qwen2-VL MMMU 54.1 / DocVQA 94.5 / MathVista 58.2,</t>
+          <t xml:space="preserve">     IMPACT: HIGH. Granite now has the HIGHEST HumanEval in this sheet, above Qwen2.5-Coder's 88.4%.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="26" t="inlineStr">
         <is>
-          <t>R1-Distill MATH-500 93.9 and AIME 69.7, InternVL2 MMBench 81.7 and DocVQA 91.6, Llama 3.2 11B</t>
+          <t xml:space="preserve">     It is US-origin, Apache 2.0, has FIM and 128K context. It was ranked 3rd on a wrong number.</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="26" t="inlineStr">
-        <is>
-          <t>Vision MMMU 50.7 / DocVQA 88.4 / ChartQA 83.4, StarCoder2 context 16,384.</t>
-        </is>
-      </c>
+      <c r="A284" s="26" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="26" t="inlineStr"/>
+      <c r="A285" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Qwen2.5-Coder 7B MultiPL-E C++:  63.4%  -&gt;  75.6%   [source: arxiv 2409.12186 Table 17]</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="26" t="inlineStr">
         <is>
-          <t>WHAT REMAINS UNVERIFIED AFTER BOTH PASSES - the honest residue:</t>
+          <t xml:space="preserve">     IMPACT: MEDIUM. Understated. Strengthens the existing rank-1 case rather than changing it.</t>
         </is>
       </c>
     </row>
@@ -18448,52 +21913,52 @@
     <row r="288">
       <c r="A288" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - StarCoder2 MultiPL-E C++ 41.4%: not on the model card, and the arXiv HTML would not yield the</t>
+          <t xml:space="preserve">  3. DeepSeek-Coder-V2-Lite MultiPL-E C++:  56.5%  -&gt;  75.8%   [source: arxiv 2406.11931 Table 3]</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    table. Needs a manual read of the 2402.19173 PDF, Section 7.1.2. Marked UNVERIFIED in the cell.</t>
+          <t xml:space="preserve">     IMPACT: HIGH. This is now the highest MEASURED C++ score in the sheet, marginally above Qwen.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Mistral 7B: the v0.3 card publishes NO benchmarks at all. MMLU 62.5% is from the v0.1 paper</t>
+          <t xml:space="preserve">     Offset by a restrictive custom licence and immature MoE tooling in llama.cpp.</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (a DIFFERENT model version); HumanEval 36.5% is leaderboard-only. Weakest evidence in the sheet,</t>
-        </is>
-      </c>
+      <c r="A291" s="26" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    though the model is not a contender so the stakes are low.</t>
+          <t xml:space="preserve">  4. CodeGemma 7B C++:  'NOT PUBLISHED'  -&gt;  BabelCode-HumanEval C++ 42.2%, BabelCode-MBPP C++ 56.7%</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - LLaVA-1.6: all benchmark figures unconfirmed, per correction 14.</t>
+          <t xml:space="preserve">     [source: Google model card]. IMPACT: LOW - the model is already eliminated by its 8K context.</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="26" t="inlineStr"/>
+      <c r="A294" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Root cause: Google reports C++ under BabelCode, not MultiPL-E, so a MultiPL-E search missed it.</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Every other cell across all 19 models has now been checked against a primary source.</t>
+          <t xml:space="preserve">     NOTE: BabelCode and MultiPL-E are different harnesses. 42.2 is NOT comparable to Qwen's 75.6.</t>
         </is>
       </c>
     </row>
@@ -18503,539 +21968,486 @@
     <row r="297">
       <c r="A297" s="26" t="inlineStr">
         <is>
-          <t>PASS 3 - THE THREE RESIDUAL CELLS, RESOLVED 2026-08-10 BY DIRECT PDF READ.</t>
+          <t xml:space="preserve">  5. Phi-4 GSM8K 91.5%:  REMOVED as unsourced.   [Microsoft publishes MGSM 80.6%, not GSM8K]</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="26" t="inlineStr"/>
+      <c r="A298" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     IMPACT: LOW. Phi-4's case rests on HumanEval 82.6 and MMLU 84.8, both confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="299">
-      <c r="A299" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  17. StarCoder2 MultiPL-E C++ 41.4%: NOW CONFIRMED. arxiv 2402.19173 TABLE 10, Pass@1 on MultiPL-E,</t>
-        </is>
-      </c>
+      <c r="A299" s="26" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      50 samples per problem, temperature 0.2, top-p 0.95. The figure this sheet carried was correct;</t>
+          <t xml:space="preserve">  6. Llama 3.2 3B HumanEval 57.8%:  REMOVED as unsourced.   [Meta publishes no HumanEval for the 3B]</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      it simply had no citation. It now cites the table. Same read also confirmed HumanEval 46.3 and</t>
+          <t xml:space="preserve">     IMPACT: MEDIUM. The edge candidate's code ability is UNMEASURED. It qualifies on size, not skill.</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      added MBPP 66.2 / MBPP+ 53.1 (Table 9), CanItEdit 43.08/38.45 (Table 13), CRUXEval-I 48.1 and</t>
-        </is>
-      </c>
+      <c r="A302" s="26" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      CRUXEval-O 47.1 (Table 15), GSM8K-PAL 65.1 (Table 14), RepoBench ES 74.08 (Table 17), and the</t>
+          <t>TWO LICENCE FINDINGS, both narrower than previously stated:</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      full architecture from Table 6 (40 layers, 4 KV heads, hidden 6144 so head_dim 128) which is the</t>
-        </is>
-      </c>
+      <c r="A304" s="26" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      geometry this sheet uses for its KV-cache maths.</t>
+          <t xml:space="preserve">  7. Llama 3.2 EU exclusion applies to MULTIMODAL models ONLY. The text-only 3B is unaffected -</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="26" t="inlineStr"/>
+      <c r="A306" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     the previous flag on it is WITHDRAWN as over-cautious.</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18. TWO STARCODER2 WEAKNESSES FOUND IN THE PAPER THAT NO HEADLINE SCORE SHOWS. These were missed by</t>
+          <t xml:space="preserve">  8. For the 11B Vision, the exclusion binds EU-DOMICILED DEVELOPERS, and expressly does NOT bind</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      every earlier pass because they live in a table caption and a discussion paragraph, not in a</t>
+          <t xml:space="preserve">     end users of a product incorporating the model. A non-EU entity may build with it and supply</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      results row:</t>
+          <t xml:space="preserve">     EU customers. Exact licence wording is quoted in that model's Countries - SOURCE cell.</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        a) FIM IS BROKEN. Table 16 caption, verbatim: 'Due to an implementation bug, FIM was incorrect</t>
-        </is>
-      </c>
+      <c r="A310" s="26" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">           for most of the training of StarCoder2-15B.' Measured FIM is Python 48.4 / Java 60.5 /</t>
+          <t>CONFIRMED CORRECT, no change: Phi-4 (HumanEval 82.6, MMLU 84.8, MATH 80.4, 1920xH100 for 21 days),</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">           JS 54.7 - WORSE than its own predecessor StarCoderBase-15B at 62 / 73 / 74. This sheet</t>
+          <t>Phi-3.5-mini (62.8 / 69 / 86.2, 512xH100 for 10 days), Llama 3.1 8B (HumanEval 72.6, GSM8K 84.5,</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">           previously listed 'FIM: YES (native)' as a STRENGTH. That was misleading and is corrected.</t>
+          <t>1.46M GPU-hours), Granite MMLU 65.54 and GSM8K 80.89, Qwen HumanEval 88.4 and MBPP 83.5,</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">        b) C++ OUTPUT IS ONE-THIRD INCOMPLETE. Section 7.2.1 reports that StarCoder2-15B underperforms</t>
+          <t>DeepSeek HumanEval 81.1 and MBPP+ 68.8, Llama 3.2 3B MMLU 63.4 and GSM8K 77.7.</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           on C++ because about a third of generated C++ is incomplete - the paper's own example is an</t>
-        </is>
-      </c>
+      <c r="A315" s="26" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">           unexpected break straight after the start of a for loop. For a 5-gate cross-compile pipeline</t>
+          <t>ONE DISAMBIGUATION: Llama 3.1 8B MMLU is 69.4% standard 5-shot; the 73.0% previously quoted is the</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">           that is the worst possible failure mode.</t>
+          <t>chain-of-thought variant. Both are now shown so it is not compared unfairly against standard-metric models.</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      TAKEN TOGETHER these remove StarCoder2 from serious consideration for ipoefgfefs, on the paper's</t>
-        </is>
-      </c>
+      <c r="A318" s="26" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      own evidence rather than on a benchmark ranking.</t>
+          <t>STILL UNVERIFIED - the remaining CHECK cells:</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="26" t="inlineStr"/>
+      <c r="A320" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  StarCoder2 15B (paper HTML would not yield the MultiPL-E table - needs the PDF read manually),</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  19. LLaVA-1.6 13B benchmarks: NOW SOURCED to llava-vl.github.io/blog/2024-01-30-llava-next (the</t>
+          <t xml:space="preserve">  Mistral 7B, Gemma 3 4B, DeepSeek-R1-Distill-14B, and all seven vision models except where noted.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      official release blog, since the HuggingFace card publishes none). VQAv2 82.8, ScienceQA 73.6,</t>
+          <t xml:space="preserve">  These are lower-stakes: none of them is in the shortlist.</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      TextVQA 67.1, GQA 65.4, VisWiz 60.5, MMMU val 36.2, at 672x672 resolution.</t>
-        </is>
-      </c>
+      <c r="A323" s="26" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      CORRECTION: MMMU 35.9 was a LLaVA-1.5 figure from arxiv 2310.03744 - the exact 1.5-vs-1.6</t>
+          <t>PASS 2 - REMAINING 11 MODELS CHECKED, 2026-08-10. Eight further corrections:</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      conflation the previous revision warned about, which this sheet had itself fallen into.</t>
-        </is>
-      </c>
+      <c r="A325" s="26" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      MMBench 70.0 has been REMOVED: it is not in the NeXT blog tables for the 13B and could not be</t>
+          <t xml:space="preserve">  9.  PaliGemma 3B context:  8,192  -&gt;  512 tokens     [source: Google model card]</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      sourced anywhere primary.</t>
+          <t xml:space="preserve">      IMPACT: HIGH. Wrong by a factor of 16. At 512 tokens it cannot hold the ipoefgfefs prompt</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="26" t="inlineStr"/>
+      <c r="A328" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      at all. Categorically disqualified, not merely marginal.</t>
+        </is>
+      </c>
     </row>
     <row r="329">
-      <c r="A329" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  20. Mistral 7B Instruct v0.3: RESOLVED, and the resolution is that NO SOLID REFERENCE EXISTS.</t>
-        </is>
-      </c>
+      <c r="A329" s="26" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      The v0.3 model card publishes no benchmarks at all. The MMLU 62.5% figure comes from arxiv</t>
+          <t xml:space="preserve">  10. Moondream2 benchmarks were STALE and UNDERSTATED the model:</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2310.06825, which is the v0.1 BASE model paper - a different model version. Secondary sources</t>
+          <t xml:space="preserve">      DocVQA 61.9 -&gt; 79.3, TextVQA 60.2 -&gt; 76.3. Params 1.9B -&gt; 2B.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      place v0.3 nearer 59.9-60.0% but are not primary. HumanEval 36.5% is from the EvalPlus</t>
+          <t xml:space="preserve">      It now also reports COCO object detection 51.2% and ScreenSpot pointing 80.4% - a 2B model</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      leaderboard, whose table is JavaScript-rendered and could not be captured for citation.</t>
+          <t xml:space="preserve">      doing detection and pointing is directly interesting for a VMS. Still no paper.</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      This is now the ONLY model in the sheet with no citable primary benchmark, and it is labelled</t>
-        </is>
-      </c>
+      <c r="A334" s="26" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">      as such in its own cells. It is not a contender for the C++ role, so the stakes are low - but</t>
+          <t xml:space="preserve">  11. StarCoder2 training hardware:  1024 x A100-80GB  -&gt;  1024 x H100.  HumanEval 46.4 -&gt; 46.3.</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      it must not be ranked on those numbers.</t>
-        </is>
-      </c>
+      <c r="A336" s="26" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="26" t="inlineStr"/>
+      <c r="A337" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  12. DeepSeek-R1-Distill-14B code ability: previously recorded UNKNOWN. WRONG - the card gives</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="26" t="inlineStr">
         <is>
-          <t>STATUS AFTER THREE PASSES: every benchmark figure in this sheet is now traceable to a named primary</t>
+          <t xml:space="preserve">      LiveCodeBench 53.1% and Codeforces 1481. HumanEval and C++ remain unpublished, and the base</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="26" t="inlineStr">
         <is>
-          <t>source, and where a table number exists it is cited. The single exception is Mistral 7B v0.3, where</t>
+          <t xml:space="preserve">      is Qwen2.5 general (NOT Coder), so that caveat still stands.</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="26" t="inlineStr">
-        <is>
-          <t>the absence of a source IS the finding and is stated in the cell rather than papered over.</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="20" customHeight="1">
-      <c r="A342" s="25" t="inlineStr">
-        <is>
-          <t>PRIMARY SOURCE INDEX</t>
-        </is>
-      </c>
+      <c r="A340" s="26" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  13. InternVL2 8B MMMU:  51.2  -&gt;  51.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="26" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="29" t="inlineStr">
-        <is>
-          <t>SOURCE                                                     WHAT IT BACKS                      LOCATION</t>
+      <c r="A343" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  14. LLaVA-1.6 13B licence: 'Apache 2.0, check base' -&gt; LLAMA 2 COMMUNITY LICENSE, stated</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="26" t="inlineStr"/>
+      <c r="A344" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      directly on the HuggingFace card. The licence-chain warning was right; the label was not.</t>
+        </is>
+      </c>
     </row>
     <row r="345">
-      <c r="A345" s="29" t="inlineStr">
-        <is>
-          <t>--- PEER-REVIEWED PAPERS (evidence grade 1) ----------------------------------------------------------------------------------------------------</t>
+      <c r="A345" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Benchmarks remain UNCONFIRMED - the card publishes none and 1.5 vs 1.6 figures are conflated.</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="26" t="inlineStr">
-        <is>
-          <t>Qwen2.5-Coder Technical Report                             Qwen C++ 75.6 (Tbl 17), HumanEval/MBPP (Tbl 16) arxiv.org/abs/2409.12186</t>
-        </is>
-      </c>
+      <c r="A346" s="26" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="26" t="inlineStr">
         <is>
-          <t>Phi-4 Technical Report                                     Phi-4 - paper backing the model card figures arxiv.org/abs/2412.08905</t>
+          <t xml:space="preserve">  15. Gemma 3 4B: context is 128K INPUT but 8,192 OUTPUT. Added MBPP 46.0, MMMU 39.2, GSM8K 38.4,</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="26" t="inlineStr">
         <is>
-          <t>Phi-3 Technical Report                                     Phi-3.5-mini and Phi-3.5-Vision lineage arxiv.org/abs/2404.14219</t>
+          <t xml:space="preserve">      MATH 24.2. Training hardware is TPUv4p/v5p/v5e, not TPUv5p alone.</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="26" t="inlineStr">
-        <is>
-          <t>The Llama 3 Herd of Models                                 Llama 3.1 8B architecture and training arxiv.org/abs/2407.21783</t>
-        </is>
-      </c>
+      <c r="A349" s="26" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="26" t="inlineStr">
         <is>
-          <t>StarCoder 2 and The Stack v2                               StarCoder2 - Tbl 6,9,10,13,14,15,16,17; Sec 7.2.1 arxiv.org/abs/2402.19173</t>
+          <t xml:space="preserve">  16. Qwen2-VL: added TextVQA 84.3% - highest text-in-image score in this sheet. With DocVQA 94.5%</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-Coder-V2                                          DeepSeek-Lite C++ 75.8, HumanEval, MBPP+ (Tbl 3) arxiv.org/abs/2406.11931</t>
+          <t xml:space="preserve">      it is the clear LPR / plate-reading candidate.</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="26" t="inlineStr">
-        <is>
-          <t>DeepSeek-R1                                                R1-Distill-14B distillation method and results arxiv.org/abs/2501.12948</t>
-        </is>
-      </c>
+      <c r="A352" s="26" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="26" t="inlineStr">
         <is>
-          <t>Mistral 7B                                                 MMLU 62.5 - NOTE: v0.1 BASE model, not v0.3 arxiv.org/abs/2310.06825</t>
+          <t>TWO EVALUATION-SETTING TRAPS, both of the kind a reviewer will probe:</t>
         </is>
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="26" t="inlineStr">
-        <is>
-          <t>Gemma 3 Technical Report                                   Gemma 3 4B architecture and training arxiv.org/abs/2503.19786</t>
-        </is>
-      </c>
+      <c r="A354" s="26" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="26" t="inlineStr">
         <is>
-          <t>Qwen2-VL                                                   Qwen2-VL 7B vision architecture    arxiv.org/abs/2409.12191</t>
+          <t xml:space="preserve">  a) Llama 3.2 11B Vision - the model card carries TWO tables. BASE PRETRAINED shows MMMU 41.7,</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="26" t="inlineStr">
         <is>
-          <t>PaliGemma                                                  PaliGemma 3B - fine-tuned transfer results arxiv.org/abs/2407.07726</t>
+          <t xml:space="preserve">     DocVQA 62.3, ChartQA 39.4. INSTRUCTION-TUNED shows MMMU 50.7, DocVQA 88.4, ChartQA 83.4.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="26" t="inlineStr">
         <is>
-          <t>Improved Baselines with Visual Instruction Tuning          LLaVA-1.5 baseline (NOT the 1.6 figures) arxiv.org/abs/2310.03744</t>
+          <t xml:space="preserve">     Secondary sources quote the pretrained figures as if they were the instruct ones. This sheet</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="26" t="inlineStr"/>
+      <c r="A358" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     uses the INSTRUCT table, which is correct.</t>
+        </is>
+      </c>
     </row>
     <row r="359">
-      <c r="A359" s="29" t="inlineStr">
-        <is>
-          <t>--- OFFICIAL MODEL CARDS (evidence grade 2 - PRIMARY where no paper exists) ------------------------------------------------------------</t>
-        </is>
-      </c>
+      <c r="A359" s="26" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="26" t="inlineStr">
         <is>
-          <t>IBM granite-3.3-8b-instruct card                           HumanEval 89.73, MMLU 65.54, GSM8K 80.89 huggingface.co/ibm-granite/granite-3.3-8b-instruct</t>
+          <t xml:space="preserve">  b) PaliGemma figures are single-task FINE-TUNED transfer results, confirmed by the card, NOT</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="26" t="inlineStr">
         <is>
-          <t>Microsoft phi-4 card                                       HumanEval 82.6, MMLU 84.8, 1920xH100 21 days huggingface.co/microsoft/phi-4</t>
+          <t xml:space="preserve">     zero-shot. They must not be compared against zero-shot numbers from Qwen2-VL, Phi-3.5-Vision</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="26" t="inlineStr">
         <is>
-          <t>Microsoft Phi-3.5-mini-instruct card                       62.8 / 69 / 86.2, 512xH100 10 days huggingface.co/microsoft/Phi-3.5-mini-instruct</t>
+          <t xml:space="preserve">     or InternVL2 elsewhere in this sheet.</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="26" t="inlineStr">
-        <is>
-          <t>Microsoft Phi-3.5-vision-instruct card                     MMBench 81.9, MMMU 43.0, 256xA100 6 days huggingface.co/microsoft/Phi-3.5-vision-instruct</t>
-        </is>
-      </c>
+      <c r="A363" s="26" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="26" t="inlineStr">
         <is>
-          <t>Qwen2.5-Coder-7B-Instruct card                             7.61B params, 28 layers, 4 KV heads, 131072 ctx huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct</t>
+          <t>CONFIRMED CORRECT IN PASS 2: Phi-3.5-Vision (81.9 / 43.0 / 72.0, 256xA100 for 6 days, 500B tokens),</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="26" t="inlineStr">
         <is>
-          <t>Qwen2-VL-7B-Instruct card                                  DocVQA 94.5, TextVQA 84.3, MMMU 54.1 huggingface.co/Qwen/Qwen2-VL-7B-Instruct</t>
+          <t>Gemma 3 4B HumanEval 36.0 and MMLU 59.6, Qwen2-VL MMMU 54.1 / DocVQA 94.5 / MathVista 58.2,</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="26" t="inlineStr">
         <is>
-          <t>Meta Llama-3.1-8B-Instruct card                            HumanEval 72.6, MMLU 69.4 vs CoT 73.0, GPU-hours huggingface.co/meta-llama/Llama-3.1-8B-Instruct</t>
+          <t>R1-Distill MATH-500 93.9 and AIME 69.7, InternVL2 MMBench 81.7 and DocVQA 91.6, Llama 3.2 11B</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="26" t="inlineStr">
         <is>
-          <t>Meta Llama-3.2-3B-Instruct card                            MMLU 63.4, GSM8K 77.7, EU clause scope huggingface.co/meta-llama/Llama-3.2-3B-Instruct</t>
+          <t>Vision MMMU 50.7 / DocVQA 88.4 / ChartQA 83.4, StarCoder2 context 16,384.</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="26" t="inlineStr">
-        <is>
-          <t>Meta Llama 3.2 MODEL_CARD_VISION.md                        11B Vision INSTRUCT table (not pretrained) github.com/meta-llama/llama-models</t>
-        </is>
-      </c>
+      <c r="A368" s="26" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="26" t="inlineStr">
         <is>
-          <t>BigCode starcoder2-15b card                                1024xH100, 16384 ctx, HumanEval 46.3 huggingface.co/bigcode/starcoder2-15b</t>
+          <t>WHAT REMAINS UNVERIFIED AFTER BOTH PASSES - the honest residue:</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="26" t="inlineStr">
-        <is>
-          <t>Google codegemma-7b-it card                                HumanEval 56.1, BabelCode C++ 42.2, 8K ctx huggingface.co/google/codegemma-7b-it</t>
-        </is>
-      </c>
+      <c r="A370" s="26" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="26" t="inlineStr">
         <is>
-          <t>Google gemma-3-4b-it card                                  HumanEval 36.0, MMLU 59.6, 128K in / 8K out huggingface.co/google/gemma-3-4b-it</t>
+          <t xml:space="preserve">  - StarCoder2 MultiPL-E C++ 41.4%: not on the model card, and the arXiv HTML would not yield the</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="26" t="inlineStr">
         <is>
-          <t>Google paligemma-3b-mix-448 card                           512 token ctx, fine-tuned transfer scores huggingface.co/google/paligemma-3b-mix-448</t>
+          <t xml:space="preserve">    table. Needs a manual read of the 2402.19173 PDF, Section 7.1.2. Marked UNVERIFIED in the cell.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-R1-Distill-Qwen-14B card                          MATH-500 93.9, LiveCodeBench 53.1, Codeforces 1481 huggingface.co/deepseek-ai/DeepSeek-R1-Distill-Qwen-14B</t>
+          <t xml:space="preserve">  - Mistral 7B: the v0.3 card publishes NO benchmarks at all. MMLU 62.5% is from the v0.1 paper</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="26" t="inlineStr">
         <is>
-          <t>DeepSeek-Coder-V2-Lite-Instruct card                       MoE config, licence terms          huggingface.co/deepseek-ai/DeepSeek-Coder-V2-Lite-Instruct</t>
+          <t xml:space="preserve">    (a DIFFERENT model version); HumanEval 36.5% is leaderboard-only. Weakest evidence in the sheet,</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="26" t="inlineStr">
         <is>
-          <t>OpenGVLab InternVL2-8B card                                MMBench 81.7, MMMU 51.8, DocVQA 91.6, 8K ctx huggingface.co/OpenGVLab/InternVL2-8B</t>
+          <t xml:space="preserve">    though the model is not a contender so the stakes are low.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="26" t="inlineStr">
         <is>
-          <t>llava-hf llava-v1.6-vicuna-13b-hf card                     Licence = LLAMA 2 (publishes no benchmarks) huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf</t>
+          <t xml:space="preserve">  - LLaVA-1.6: all benchmark figures unconfirmed, per correction 14.</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="26" t="inlineStr">
-        <is>
-          <t>vikhyatk/moondream2 card                                   DocVQA 79.3, TextVQA 76.3, COCO detect 51.2 huggingface.co/vikhyatk/moondream2</t>
-        </is>
-      </c>
+      <c r="A377" s="26" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="26" t="inlineStr">
         <is>
-          <t>mistralai Mistral-7B-Instruct-v0.3 card                    PUBLISHES NO BENCHMARKS - that is the finding huggingface.co/mistralai/Mistral-7B-Instruct-v0.3</t>
+          <t xml:space="preserve">  Every other cell across all 19 models has now been checked against a primary source.</t>
         </is>
       </c>
     </row>
@@ -19043,345 +22455,1011 @@
       <c r="A379" s="26" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="29" t="inlineStr">
-        <is>
-          <t>--- OFFICIAL BLOGS AND VENDOR DOCS (evidence grade 3) ----------------------------------------------------------------------------------------</t>
+      <c r="A380" s="26" t="inlineStr">
+        <is>
+          <t>PASS 3 - THE THREE RESIDUAL CELLS, RESOLVED 2026-08-10 BY DIRECT PDF READ.</t>
         </is>
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="26" t="inlineStr">
-        <is>
-          <t>LLaVA-NeXT release blog                                    LLaVA-1.6 13B: VQAv2 82.8, MMMU 36.2, TextVQA 67.1 llava-vl.github.io/blog/2024-01-30-llava-next</t>
-        </is>
-      </c>
+      <c r="A381" s="26" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="26" t="inlineStr">
         <is>
-          <t>Qwen2.5-Coder family blog                                  Qwen family overview (no per-model numbers) qwenlm.github.io/blog/qwen2.5-coder-family</t>
+          <t xml:space="preserve">  17. StarCoder2 MultiPL-E C++ 41.4%: NOW CONFIRMED. arxiv 2402.19173 TABLE 10, Pass@1 on MultiPL-E,</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="26" t="inlineStr">
         <is>
-          <t>Google CodeGemma docs                                      CodeGemma model documentation      ai.google.dev/gemma/docs/codegemma</t>
+          <t xml:space="preserve">      50 samples per problem, temperature 0.2, top-p 0.95. The figure this sheet carried was correct;</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="26" t="inlineStr">
         <is>
-          <t>InternVL project site                                      InternVL2 family documentation     internvl.github.io</t>
+          <t xml:space="preserve">      it simply had no citation. It now cites the table. Same read also confirmed HumanEval 46.3 and</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="26" t="inlineStr"/>
+      <c r="A385" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      added MBPP 66.2 / MBPP+ 53.1 (Table 9), CanItEdit 43.08/38.45 (Table 13), CRUXEval-I 48.1 and</t>
+        </is>
+      </c>
     </row>
     <row r="386">
-      <c r="A386" s="29" t="inlineStr">
-        <is>
-          <t>--- TOKEN-RATE MEASUREMENTS (evidence grade 4 - the ONLY published source for tok/s) -------------------------------------------------------</t>
+      <c r="A386" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      CRUXEval-O 47.1 (Table 15), GSM8K-PAL 65.1 (Table 14), RepoBench ES 74.08 (Table 17), and the</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="26" t="inlineStr">
         <is>
-          <t>LLM tokens/sec benchmarks, llama.cpp b3520                 RTX4090 Q4_K_M: 7B 135, 13B 78, 34B 42 tok/s mustafa.net/llm-tokens-per-second-benchmarks</t>
+          <t xml:space="preserve">      full architecture from Table 6 (40 layers, 4 KV heads, hidden 6144 so head_dim 128) which is the</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="26" t="inlineStr">
         <is>
-          <t>Ollama vs llama.cpp benchmark                              Llama 3.1 8B Q4_K_M on 4090 = 95-110 tok/s markaicode.com/benchmarks/ollama-vs-llamacpp-benchmark</t>
+          <t xml:space="preserve">      geometry this sheet uses for its KV-cache maths.</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="26" t="inlineStr">
-        <is>
-          <t>Qwen3-8B on RTX 4090 recipe                                llama.cpp 104 tok/s at 16K context cross-check smeltcore.com</t>
-        </is>
-      </c>
+      <c r="A389" s="26" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="26" t="inlineStr">
         <is>
-          <t>AMD EPYC LLM inference benchmark                           CPU: EPYC 7763 7B Q4_K_M = 15 tok/s blog.leaseweb.com</t>
+          <t xml:space="preserve">  18. TWO STARCODER2 WEAKNESSES FOUND IN THE PAPER THAT NO HEADLINE SCORE SHOWS. These were missed by</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="26" t="inlineStr">
         <is>
-          <t>llama.cpp VRAM requirements guide                          Concurrency: ~18 tok/s per user, 4 users, 24GB localllm.in/blog/llamacpp-vram-requirements-for-local-llms</t>
+          <t xml:space="preserve">      every earlier pass because they live in a table caption and a discussion paragraph, not in a</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="26" t="inlineStr">
         <is>
-          <t>myaihardware llama.cpp benchmarks                          CPU desktop band 4-15 tok/s at Q4_K_M myaihardware.com/llama-cpp-benchmarks</t>
+          <t xml:space="preserve">      results row:</t>
         </is>
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="26" t="inlineStr"/>
+      <c r="A393" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        a) FIM IS BROKEN. Table 16 caption, verbatim: 'Due to an implementation bug, FIM was incorrect</t>
+        </is>
+      </c>
     </row>
     <row r="394">
-      <c r="A394" s="29" t="inlineStr">
-        <is>
-          <t>--- BENCHMARK DEFINITIONS (what each metric actually measures) --------------------------------------------------------------------------------</t>
+      <c r="A394" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           for most of the training of StarCoder2-15B.' Measured FIM is Python 48.4 / Java 60.5 /</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="26" t="inlineStr">
         <is>
-          <t>HumanEval / Evaluating LLMs Trained on Code                164 Python problems, pass@1        arxiv.org/abs/2107.03374</t>
+          <t xml:space="preserve">           JS 54.7 - WORSE than its own predecessor StarCoderBase-15B at 62 / 73 / 74. This sheet</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="26" t="inlineStr">
         <is>
-          <t>MultiPL-E                                                  HumanEval translated to 18 languages incl. C++ arxiv.org/abs/2208.08227</t>
+          <t xml:space="preserve">           previously listed 'FIM: YES (native)' as a STRENGTH. That was misleading and is corrected.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="26" t="inlineStr">
         <is>
-          <t>MBPP                                                       Mostly Basic Python Problems       arxiv.org/abs/2108.07732</t>
+          <t xml:space="preserve">        b) C++ OUTPUT IS ONE-THIRD INCOMPLETE. Section 7.2.1 reports that StarCoder2-15B underperforms</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="26" t="inlineStr">
         <is>
-          <t>EvalPlus (HumanEval+ / MBPP+)                              80x and 35x more tests than the originals arxiv.org/abs/2305.01210</t>
+          <t xml:space="preserve">           on C++ because about a third of generated C++ is incomplete - the paper's own example is an</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="26" t="inlineStr">
         <is>
-          <t>CanItEdit                                                  Code EDITING - closest proxy to a retry loop arxiv.org/abs/2312.12450</t>
+          <t xml:space="preserve">           unexpected break straight after the start of a for loop. For a 5-gate cross-compile pipeline</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="26" t="inlineStr">
         <is>
-          <t>CRUXEval                                                   Code reasoning, understanding and execution arxiv.org/abs/2401.03065</t>
+          <t xml:space="preserve">           that is the worst possible failure mode.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="26" t="inlineStr">
         <is>
-          <t>RepoBench                                                  Repository-level next-line completion arxiv.org/abs/2306.03091</t>
+          <t xml:space="preserve">      TAKEN TOGETHER these remove StarCoder2 from serious consideration for ipoefgfefs, on the paper's</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="26" t="inlineStr">
         <is>
-          <t>MMLU                                                       57-subject multitask accuracy      arxiv.org/abs/2009.03300</t>
+          <t xml:space="preserve">      own evidence rather than on a benchmark ranking.</t>
         </is>
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="26" t="inlineStr">
-        <is>
-          <t>GSM8K                                                      Grade-school math word problems    arxiv.org/abs/2110.14168</t>
-        </is>
-      </c>
+      <c r="A403" s="26" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="26" t="inlineStr">
         <is>
-          <t>MATH                                                       Competition mathematics            arxiv.org/abs/2103.03874</t>
+          <t xml:space="preserve">  19. LLaVA-1.6 13B benchmarks: NOW SOURCED to llava-vl.github.io/blog/2024-01-30-llava-next (the</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="26" t="inlineStr">
         <is>
-          <t>MMMU                                                       College-level multimodal understanding arxiv.org/abs/2311.16502</t>
+          <t xml:space="preserve">      official release blog, since the HuggingFace card publishes none). VQAv2 82.8, ScienceQA 73.6,</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="26" t="inlineStr">
         <is>
-          <t>DocVQA                                                     Document visual question answering arxiv.org/abs/2007.00398</t>
+          <t xml:space="preserve">      TextVQA 67.1, GQA 65.4, VisWiz 60.5, MMMU val 36.2, at 672x672 resolution.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="26" t="inlineStr">
         <is>
-          <t>TextVQA                                                    Reading text within images         arxiv.org/abs/1904.08920</t>
+          <t xml:space="preserve">      CORRECTION: MMMU 35.9 was a LLaVA-1.5 figure from arxiv 2310.03744 - the exact 1.5-vs-1.6</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="26" t="inlineStr">
         <is>
-          <t>LiveCodeBench                                              Contamination-free live coding problems arxiv.org/abs/2403.07974</t>
+          <t xml:space="preserve">      conflation the previous revision warned about, which this sheet had itself fallen into.</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="26" t="inlineStr"/>
+      <c r="A409" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      MMBench 70.0 has been REMOVED: it is not in the NeXT blog tables for the 13B and could not be</t>
+        </is>
+      </c>
     </row>
     <row r="410">
-      <c r="A410" s="29" t="inlineStr">
-        <is>
-          <t>--- ENGINEERING AND HARDWARE SOURCES ---------------------------------------------------------------------------------------------------------</t>
+      <c r="A410" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      sourced anywhere primary.</t>
         </is>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="26" t="inlineStr">
-        <is>
-          <t>llama.cpp - supported backends and build docs              ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
-        </is>
-      </c>
+      <c r="A411" s="26" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="26" t="inlineStr">
         <is>
-          <t>llama.cpp k-quants PR #1684                                ALL quantization accuracy deltas   github.com/ggml-org/llama.cpp/pull/1684</t>
+          <t xml:space="preserve">  20. Mistral 7B Instruct v0.3: RESOLVED, and the resolution is that NO SOLID REFERENCE EXISTS.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA Ada GPU Architecture Whitepaper                     RTX 4090 bandwidth 1008 GB/s       nvidia.com - Ada whitepaper</t>
+          <t xml:space="preserve">      The v0.3 model card publishes no benchmarks at all. The MMLU 62.5% figure comes from arxiv</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="26" t="inlineStr">
         <is>
-          <t>vLLM / PagedAttention                                      Concurrency behaviour              arxiv.org/abs/2309.06180</t>
+          <t xml:space="preserve">      2310.06825, which is the v0.1 BASE model paper - a different model version. Secondary sources</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="26" t="inlineStr">
         <is>
-          <t>SGLang / RadixAttention                                    Prefix caching for the shared 6-8K header arxiv.org/abs/2312.07104</t>
+          <t xml:space="preserve">      place v0.3 nearer 59.9-60.0% but are not primary. HumanEval 36.5% is from the EvalPlus</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="26" t="inlineStr">
         <is>
-          <t>LoRA                                                       Fine-tuning VRAM baseline          arxiv.org/abs/2106.09685</t>
+          <t xml:space="preserve">      leaderboard, whose table is JavaScript-rendered and could not be captured for citation.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="26" t="inlineStr">
         <is>
-          <t>QLoRA                                                      4-bit fine-tuning VRAM             arxiv.org/abs/2305.14314</t>
+          <t xml:space="preserve">      This is now the ONLY model in the sheet with no citable primary benchmark, and it is labelled</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="26" t="inlineStr"/>
+      <c r="A418" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      as such in its own cells. It is not a contender for the C++ role, so the stakes are low - but</t>
+        </is>
+      </c>
     </row>
     <row r="419">
-      <c r="A419" s="29" t="inlineStr">
-        <is>
-          <t>--- LICENCE AND COMPLIANCE TEXTS -------------------------------------------------------------------------------------------------------------</t>
+      <c r="A419" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      it must not be ranked on those numbers.</t>
         </is>
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="26" t="inlineStr">
-        <is>
-          <t>Apache License 2.0                                         Qwen, Granite, Mistral, Moondream, Qwen2-VL apache.org/licenses/LICENSE-2.0</t>
-        </is>
-      </c>
+      <c r="A420" s="26" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="26" t="inlineStr">
         <is>
-          <t>MIT License                                                Phi-4, Phi-3.5-mini, Phi-3.5-Vision, InternVL2, R1 opensource.org/license/mit</t>
+          <t>STATUS AFTER THREE PASSES: every benchmark figure in this sheet is now traceable to a named primary</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="26" t="inlineStr">
         <is>
-          <t>Llama 3.x Community Licence                                EU MULTIMODAL EXCLUSION - exact wording llama.com/llama3_3/license</t>
+          <t>source, and where a table number exists it is cited. The single exception is Mistral 7B v0.3, where</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="26" t="inlineStr">
         <is>
+          <t>the absence of a source IS the finding and is stated in the cell rather than papered over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="20" customHeight="1">
+      <c r="A425" s="25" t="inlineStr">
+        <is>
+          <t>PRIMARY SOURCE INDEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="29" t="inlineStr">
+        <is>
+          <t>SOURCE                                                     WHAT IT BACKS                      LOCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="26" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="29" t="inlineStr">
+        <is>
+          <t>--- PEER-REVIEWED PAPERS (evidence grade 1) ----------------------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2.5-Coder Technical Report                             Qwen C++ 75.6 (Tbl 17), HumanEval/MBPP (Tbl 16) arxiv.org/abs/2409.12186</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="26" t="inlineStr">
+        <is>
+          <t>Phi-4 Technical Report                                     Phi-4 - paper backing the model card figures arxiv.org/abs/2412.08905</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="26" t="inlineStr">
+        <is>
+          <t>Phi-3 Technical Report                                     Phi-3.5-mini and Phi-3.5-Vision lineage arxiv.org/abs/2404.14219</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="26" t="inlineStr">
+        <is>
+          <t>The Llama 3 Herd of Models                                 Llama 3.1 8B architecture and training arxiv.org/abs/2407.21783</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="26" t="inlineStr">
+        <is>
+          <t>StarCoder 2 and The Stack v2                               StarCoder2 - Tbl 6,9,10,13,14,15,16,17; Sec 7.2.1 arxiv.org/abs/2402.19173</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-Coder-V2                                          DeepSeek-Lite C++ 75.8, HumanEval, MBPP+ (Tbl 3) arxiv.org/abs/2406.11931</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-R1                                                R1-Distill-14B distillation method and results arxiv.org/abs/2501.12948</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="26" t="inlineStr">
+        <is>
+          <t>Mistral 7B                                                 MMLU 62.5 - NOTE: v0.1 BASE model, not v0.3 arxiv.org/abs/2310.06825</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="26" t="inlineStr">
+        <is>
+          <t>Gemma 3 Technical Report                                   Gemma 3 4B architecture and training arxiv.org/abs/2503.19786</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2-VL                                                   Qwen2-VL 7B vision architecture    arxiv.org/abs/2409.12191</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="26" t="inlineStr">
+        <is>
+          <t>PaliGemma                                                  PaliGemma 3B - fine-tuned transfer results arxiv.org/abs/2407.07726</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="26" t="inlineStr">
+        <is>
+          <t>Improved Baselines with Visual Instruction Tuning          LLaVA-1.5 baseline (NOT the 1.6 figures) arxiv.org/abs/2310.03744</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="26" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding and Qwen3-VL-Reranker                   Qwen3-VL-Embedding 2B and 8B - cat 4 and 5 arxiv.org/abs/2601.04720</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="26" t="inlineStr">
+        <is>
+          <t>VLM2Vec-V2 / MMEB-V2                                       VLM2Vec-V2 + the 8-frame vs 1-frame protocol arxiv.org/abs/2507.04590</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="26" t="inlineStr">
+        <is>
+          <t>VLM2Vec / MMEB                                             Original MMEB benchmark definition arxiv.org/abs/2410.05160</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="26" t="inlineStr">
+        <is>
+          <t>GME: General Multimodal Embedder                           GME-Qwen2-VL 2B and 7B, UMRB benchmark arxiv.org/abs/2412.16855</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="26" t="inlineStr">
+        <is>
+          <t>ColPali: Efficient Document Retrieval with VLMs            ColPali and ColQwen2, ViDoRe benchmark arxiv.org/abs/2407.01449</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="26" t="inlineStr">
+        <is>
+          <t>E5-V: Universal Embeddings with MLLMs                      E5-V - note: no licence declared on the card arxiv.org/abs/2407.12580</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="26" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="29" t="inlineStr">
+        <is>
+          <t>--- OFFICIAL MODEL CARDS (evidence grade 2 - PRIMARY where no paper exists) ------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="26" t="inlineStr">
+        <is>
+          <t>IBM granite-3.3-8b-instruct card                           HumanEval 89.73, MMLU 65.54, GSM8K 80.89 huggingface.co/ibm-granite/granite-3.3-8b-instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="26" t="inlineStr">
+        <is>
+          <t>Microsoft phi-4 card                                       HumanEval 82.6, MMLU 84.8, 1920xH100 21 days huggingface.co/microsoft/phi-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="26" t="inlineStr">
+        <is>
+          <t>Microsoft Phi-3.5-mini-instruct card                       62.8 / 69 / 86.2, 512xH100 10 days huggingface.co/microsoft/Phi-3.5-mini-instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="26" t="inlineStr">
+        <is>
+          <t>Microsoft Phi-3.5-vision-instruct card                     MMBench 81.9, MMMU 43.0, 256xA100 6 days huggingface.co/microsoft/Phi-3.5-vision-instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2.5-Coder-7B-Instruct card                             7.61B params, 28 layers, 4 KV heads, 131072 ctx huggingface.co/Qwen/Qwen2.5-Coder-7B-Instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2-VL-7B-Instruct card                                  DocVQA 94.5, TextVQA 84.3, MMMU 54.1 huggingface.co/Qwen/Qwen2-VL-7B-Instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="26" t="inlineStr">
+        <is>
+          <t>Meta Llama-3.1-8B-Instruct card                            HumanEval 72.6, MMLU 69.4 vs CoT 73.0, GPU-hours huggingface.co/meta-llama/Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="26" t="inlineStr">
+        <is>
+          <t>Meta Llama-3.2-3B-Instruct card                            MMLU 63.4, GSM8K 77.7, EU clause scope huggingface.co/meta-llama/Llama-3.2-3B-Instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="26" t="inlineStr">
+        <is>
+          <t>Meta Llama 3.2 MODEL_CARD_VISION.md                        11B Vision INSTRUCT table (not pretrained) github.com/meta-llama/llama-models</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="26" t="inlineStr">
+        <is>
+          <t>BigCode starcoder2-15b card                                1024xH100, 16384 ctx, HumanEval 46.3 huggingface.co/bigcode/starcoder2-15b</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="26" t="inlineStr">
+        <is>
+          <t>Google codegemma-7b-it card                                HumanEval 56.1, BabelCode C++ 42.2, 8K ctx huggingface.co/google/codegemma-7b-it</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="26" t="inlineStr">
+        <is>
+          <t>Google gemma-3-4b-it card                                  HumanEval 36.0, MMLU 59.6, 128K in / 8K out huggingface.co/google/gemma-3-4b-it</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="26" t="inlineStr">
+        <is>
+          <t>Google paligemma-3b-mix-448 card                           512 token ctx, fine-tuned transfer scores huggingface.co/google/paligemma-3b-mix-448</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-R1-Distill-Qwen-14B card                          MATH-500 93.9, LiveCodeBench 53.1, Codeforces 1481 huggingface.co/deepseek-ai/DeepSeek-R1-Distill-Qwen-14B</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="26" t="inlineStr">
+        <is>
+          <t>DeepSeek-Coder-V2-Lite-Instruct card                       MoE config, licence terms          huggingface.co/deepseek-ai/DeepSeek-Coder-V2-Lite-Instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="26" t="inlineStr">
+        <is>
+          <t>OpenGVLab InternVL2-8B card                                MMBench 81.7, MMMU 51.8, DocVQA 91.6, 8K ctx huggingface.co/OpenGVLab/InternVL2-8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="26" t="inlineStr">
+        <is>
+          <t>llava-hf llava-v1.6-vicuna-13b-hf card                     Licence = LLAMA 2 (publishes no benchmarks) huggingface.co/llava-hf/llava-v1.6-vicuna-13b-hf</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="26" t="inlineStr">
+        <is>
+          <t>vikhyatk/moondream2 card                                   DocVQA 79.3, TextVQA 76.3, COCO detect 51.2 huggingface.co/vikhyatk/moondream2</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="26" t="inlineStr">
+        <is>
+          <t>mistralai Mistral-7B-Instruct-v0.3 card                    PUBLISHES NO BENCHMARKS - that is the finding huggingface.co/mistralai/Mistral-7B-Instruct-v0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="26" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-8B card                                 MMEB-V2 Image 80.1 / Video 66.1 / VisDoc 83.3 huggingface.co/Qwen/Qwen3-VL-Embedding-8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="26" t="inlineStr">
+        <is>
+          <t>Qwen3-VL-Embedding-2B card                                 MMEB-V2 Image 75.0 / Video 61.9, MMTEB 63.87 huggingface.co/Qwen/Qwen3-VL-Embedding-2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="26" t="inlineStr">
+        <is>
+          <t>Alibaba-NLP gme-Qwen2-VL-7B-Instruct card                  UMRB 67.44, MTEB-en 67.48, dim 3584 huggingface.co/Alibaba-NLP/gme-Qwen2-VL-7B-Instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="26" t="inlineStr">
+        <is>
+          <t>Alibaba-NLP gme-Qwen2-VL-2B-Instruct card                  UMRB 64.45, MTEB-en 65.27, dim 1536 huggingface.co/Alibaba-NLP/gme-Qwen2-VL-2B-Instruct</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="26" t="inlineStr">
+        <is>
+          <t>TIGER-Lab VLM2Vec-Full card                                Apache 2.0, Phi-3.5-Vision backbone, 4B huggingface.co/TIGER-Lab/VLM2Vec-Full</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="26" t="inlineStr">
+        <is>
+          <t>vidore colqwen2-v1.0 card                                  Apache 2.0 + MIT, multi-vector ColBERT huggingface.co/vidore/colqwen2-v1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="26" t="inlineStr">
+        <is>
+          <t>vidore colpali-v1.2 card                                   MIT adapters over Gemma-licensed backbone huggingface.co/vidore/colpali-v1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="26" t="inlineStr">
+        <is>
+          <t>royokong e5-v card                                         NO LICENCE DECLARED - that is the finding huggingface.co/royokong/e5-v</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="26" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="29" t="inlineStr">
+        <is>
+          <t>--- OFFICIAL BLOGS AND VENDOR DOCS (evidence grade 3) ----------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="26" t="inlineStr">
+        <is>
+          <t>LLaVA-NeXT release blog                                    LLaVA-1.6 13B: VQAv2 82.8, MMMU 36.2, TextVQA 67.1 llava-vl.github.io/blog/2024-01-30-llava-next</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="26" t="inlineStr">
+        <is>
+          <t>Qwen2.5-Coder family blog                                  Qwen family overview (no per-model numbers) qwenlm.github.io/blog/qwen2.5-coder-family</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="26" t="inlineStr">
+        <is>
+          <t>Google CodeGemma docs                                      CodeGemma model documentation      ai.google.dev/gemma/docs/codegemma</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="26" t="inlineStr">
+        <is>
+          <t>InternVL project site                                      InternVL2 family documentation     internvl.github.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="26" t="inlineStr">
+        <is>
+          <t>VLM2Vec project page                                       VLM2Vec-V2 MMEB-V2 overall 58.0    tiger-ai-lab.github.io/VLM2Vec</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="26" t="inlineStr">
+        <is>
+          <t>QwenLM Qwen3-VL-Embedding repo                             Reference implementation, vLLM embedding mode github.com/QwenLM/Qwen3-VL-Embedding</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="26" t="inlineStr">
+        <is>
+          <t>TIGER-AI-Lab VLM2Vec repo                                  VLM2Vec / V2 reference implementation github.com/TIGER-AI-Lab/VLM2Vec</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="26" t="inlineStr">
+        <is>
+          <t>illuin-tech colpali repo                                   colpali-engine, ColBERT late interaction github.com/illuin-tech/colpali</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="26" t="inlineStr">
+        <is>
+          <t>ViDoRe leaderboard                                         LIVE source for ColPali/ColQwen2 scores huggingface.co/spaces/vidore/vidore-leaderboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="26" t="inlineStr">
+        <is>
+          <t>MMEB leaderboard                                           LIVE source for MMEB / MMEB-V2 scores huggingface.co/spaces/TIGER-Lab/MMEB</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="26" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="29" t="inlineStr">
+        <is>
+          <t>--- TOKEN-RATE MEASUREMENTS (evidence grade 4 - the ONLY published source for tok/s) -------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="26" t="inlineStr">
+        <is>
+          <t>LLM tokens/sec benchmarks, llama.cpp b3520                 RTX4090 Q4_K_M: 7B 135, 13B 78, 34B 42 tok/s mustafa.net/llm-tokens-per-second-benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="26" t="inlineStr">
+        <is>
+          <t>Ollama vs llama.cpp benchmark                              Llama 3.1 8B Q4_K_M on 4090 = 95-110 tok/s markaicode.com/benchmarks/ollama-vs-llamacpp-benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="26" t="inlineStr">
+        <is>
+          <t>Qwen3-8B on RTX 4090 recipe                                llama.cpp 104 tok/s at 16K context cross-check smeltcore.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="26" t="inlineStr">
+        <is>
+          <t>AMD EPYC LLM inference benchmark                           CPU: EPYC 7763 7B Q4_K_M = 15 tok/s blog.leaseweb.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp VRAM requirements guide                          Concurrency: ~18 tok/s per user, 4 users, 24GB localllm.in/blog/llamacpp-vram-requirements-for-local-llms</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="26" t="inlineStr">
+        <is>
+          <t>myaihardware llama.cpp benchmarks                          CPU desktop band 4-15 tok/s at Q4_K_M myaihardware.com/llama-cpp-benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="26" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="29" t="inlineStr">
+        <is>
+          <t>--- BENCHMARK DEFINITIONS (what each metric actually measures) --------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="26" t="inlineStr">
+        <is>
+          <t>HumanEval / Evaluating LLMs Trained on Code                164 Python problems, pass@1        arxiv.org/abs/2107.03374</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="26" t="inlineStr">
+        <is>
+          <t>MultiPL-E                                                  HumanEval translated to 18 languages incl. C++ arxiv.org/abs/2208.08227</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="26" t="inlineStr">
+        <is>
+          <t>MBPP                                                       Mostly Basic Python Problems       arxiv.org/abs/2108.07732</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="26" t="inlineStr">
+        <is>
+          <t>EvalPlus (HumanEval+ / MBPP+)                              80x and 35x more tests than the originals arxiv.org/abs/2305.01210</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="26" t="inlineStr">
+        <is>
+          <t>CanItEdit                                                  Code EDITING - closest proxy to a retry loop arxiv.org/abs/2312.12450</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="26" t="inlineStr">
+        <is>
+          <t>CRUXEval                                                   Code reasoning, understanding and execution arxiv.org/abs/2401.03065</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="26" t="inlineStr">
+        <is>
+          <t>RepoBench                                                  Repository-level next-line completion arxiv.org/abs/2306.03091</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="26" t="inlineStr">
+        <is>
+          <t>MMLU                                                       57-subject multitask accuracy      arxiv.org/abs/2009.03300</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="26" t="inlineStr">
+        <is>
+          <t>GSM8K                                                      Grade-school math word problems    arxiv.org/abs/2110.14168</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="26" t="inlineStr">
+        <is>
+          <t>MATH                                                       Competition mathematics            arxiv.org/abs/2103.03874</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="26" t="inlineStr">
+        <is>
+          <t>MMMU                                                       College-level multimodal understanding arxiv.org/abs/2311.16502</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="26" t="inlineStr">
+        <is>
+          <t>DocVQA                                                     Document visual question answering arxiv.org/abs/2007.00398</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="26" t="inlineStr">
+        <is>
+          <t>TextVQA                                                    Reading text within images         arxiv.org/abs/1904.08920</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="26" t="inlineStr">
+        <is>
+          <t>LiveCodeBench                                              Contamination-free live coding problems arxiv.org/abs/2403.07974</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="26" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="29" t="inlineStr">
+        <is>
+          <t>--- ENGINEERING AND HARDWARE SOURCES ---------------------------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp - supported backends and build docs              ALL inference hardware support claims github.com/ggml-org/llama.cpp</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="26" t="inlineStr">
+        <is>
+          <t>llama.cpp k-quants PR #1684                                ALL quantization accuracy deltas   github.com/ggml-org/llama.cpp/pull/1684</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="26" t="inlineStr">
+        <is>
+          <t>NVIDIA Ada GPU Architecture Whitepaper                     RTX 4090 bandwidth 1008 GB/s       nvidia.com - Ada whitepaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="26" t="inlineStr">
+        <is>
+          <t>vLLM / PagedAttention                                      Concurrency behaviour              arxiv.org/abs/2309.06180</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="26" t="inlineStr">
+        <is>
+          <t>SGLang / RadixAttention                                    Prefix caching for the shared 6-8K header arxiv.org/abs/2312.07104</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="26" t="inlineStr">
+        <is>
+          <t>LoRA                                                       Fine-tuning VRAM baseline          arxiv.org/abs/2106.09685</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="26" t="inlineStr">
+        <is>
+          <t>QLoRA                                                      4-bit fine-tuning VRAM             arxiv.org/abs/2305.14314</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="26" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="29" t="inlineStr">
+        <is>
+          <t>--- LICENCE AND COMPLIANCE TEXTS -------------------------------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="26" t="inlineStr">
+        <is>
+          <t>Apache License 2.0                                         Qwen, Granite, Mistral, Moondream, Qwen2-VL apache.org/licenses/LICENSE-2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="26" t="inlineStr">
+        <is>
+          <t>MIT License                                                Phi-4, Phi-3.5-mini, Phi-3.5-Vision, InternVL2, R1 opensource.org/license/mit</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="26" t="inlineStr">
+        <is>
+          <t>Llama 3.x Community Licence                                EU MULTIMODAL EXCLUSION - exact wording llama.com/llama3_3/license</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="26" t="inlineStr">
+        <is>
           <t>Llama 2 Community Licence                                  LLaVA-1.6 effective licence via Vicuna ai.meta.com/llama/license</t>
         </is>
       </c>
     </row>
-    <row r="424">
-      <c r="A424" s="26" t="inlineStr">
+    <row r="527">
+      <c r="A527" s="26" t="inlineStr">
         <is>
           <t>Gemma Terms of Use                                         CodeGemma, Gemma 3, PaliGemma      ai.google.dev/gemma/terms</t>
         </is>
       </c>
     </row>
-    <row r="425">
-      <c r="A425" s="26" t="inlineStr">
+    <row r="528">
+      <c r="A528" s="26" t="inlineStr">
         <is>
           <t>BigCode OpenRAIL-M v1                                      StarCoder2 - flow-down duty on derivatives bigcode-project.org/docs/pages/model-license</t>
         </is>
       </c>
     </row>
-    <row r="426">
-      <c r="A426" s="26" t="inlineStr">
+    <row r="529">
+      <c r="A529" s="26" t="inlineStr">
         <is>
           <t>DeepSeek Model Licence                                     Use restrictions attachment        github.com/deepseek-ai/DeepSeek-LLM</t>
         </is>
       </c>
     </row>
-    <row r="427">
-      <c r="A427" s="26" t="inlineStr">
+    <row r="530">
+      <c r="A530" s="26" t="inlineStr">
         <is>
           <t>NDAA Section 889 / FAR 52.204-25                           Component-origin procurement rule  acquisition.gov/far/52.204-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AF78"/>
-  <mergeCells count="346">
+  <autoFilter ref="A2:AF94"/>
+  <mergeCells count="432">
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A80:AF80"/>
-    <mergeCell ref="A81:AF81"/>
-    <mergeCell ref="A82:AF82"/>
-    <mergeCell ref="A83:AF83"/>
-    <mergeCell ref="A84:AF84"/>
-    <mergeCell ref="A85:AF85"/>
-    <mergeCell ref="A86:AF86"/>
-    <mergeCell ref="A87:AF87"/>
-    <mergeCell ref="A88:AF88"/>
-    <mergeCell ref="A89:AF89"/>
-    <mergeCell ref="A90:AF90"/>
-    <mergeCell ref="A91:AF91"/>
-    <mergeCell ref="A92:AF92"/>
-    <mergeCell ref="A93:AF93"/>
-    <mergeCell ref="A94:AF94"/>
-    <mergeCell ref="A95:AF95"/>
     <mergeCell ref="A96:AF96"/>
     <mergeCell ref="A97:AF97"/>
     <mergeCell ref="A98:AF98"/>
@@ -19420,6 +23498,7 @@
     <mergeCell ref="A131:AF131"/>
     <mergeCell ref="A132:AF132"/>
     <mergeCell ref="A133:AF133"/>
+    <mergeCell ref="A134:AF134"/>
     <mergeCell ref="A135:AF135"/>
     <mergeCell ref="A136:AF136"/>
     <mergeCell ref="A137:AF137"/>
@@ -19435,7 +23514,6 @@
     <mergeCell ref="A147:AF147"/>
     <mergeCell ref="A148:AF148"/>
     <mergeCell ref="A149:AF149"/>
-    <mergeCell ref="A150:AF150"/>
     <mergeCell ref="A151:AF151"/>
     <mergeCell ref="A152:AF152"/>
     <mergeCell ref="A153:AF153"/>
@@ -19477,6 +23555,7 @@
     <mergeCell ref="A189:AF189"/>
     <mergeCell ref="A190:AF190"/>
     <mergeCell ref="A191:AF191"/>
+    <mergeCell ref="A192:AF192"/>
     <mergeCell ref="A193:AF193"/>
     <mergeCell ref="A194:AF194"/>
     <mergeCell ref="A195:AF195"/>
@@ -19492,7 +23571,6 @@
     <mergeCell ref="A205:AF205"/>
     <mergeCell ref="A206:AF206"/>
     <mergeCell ref="A207:AF207"/>
-    <mergeCell ref="A208:AF208"/>
     <mergeCell ref="A209:AF209"/>
     <mergeCell ref="A210:AF210"/>
     <mergeCell ref="A211:AF211"/>
@@ -19559,7 +23637,6 @@
     <mergeCell ref="A272:AF272"/>
     <mergeCell ref="A273:AF273"/>
     <mergeCell ref="A274:AF274"/>
-    <mergeCell ref="A275:AF275"/>
     <mergeCell ref="A276:AF276"/>
     <mergeCell ref="A277:AF277"/>
     <mergeCell ref="A278:AF278"/>
@@ -19625,6 +23702,7 @@
     <mergeCell ref="A338:AF338"/>
     <mergeCell ref="A339:AF339"/>
     <mergeCell ref="A340:AF340"/>
+    <mergeCell ref="A341:AF341"/>
     <mergeCell ref="A342:AF342"/>
     <mergeCell ref="A343:AF343"/>
     <mergeCell ref="A344:AF344"/>
@@ -19707,10 +23785,112 @@
     <mergeCell ref="A421:AF421"/>
     <mergeCell ref="A422:AF422"/>
     <mergeCell ref="A423:AF423"/>
-    <mergeCell ref="A424:AF424"/>
     <mergeCell ref="A425:AF425"/>
     <mergeCell ref="A426:AF426"/>
     <mergeCell ref="A427:AF427"/>
+    <mergeCell ref="A428:AF428"/>
+    <mergeCell ref="A429:AF429"/>
+    <mergeCell ref="A430:AF430"/>
+    <mergeCell ref="A431:AF431"/>
+    <mergeCell ref="A432:AF432"/>
+    <mergeCell ref="A433:AF433"/>
+    <mergeCell ref="A434:AF434"/>
+    <mergeCell ref="A435:AF435"/>
+    <mergeCell ref="A436:AF436"/>
+    <mergeCell ref="A437:AF437"/>
+    <mergeCell ref="A438:AF438"/>
+    <mergeCell ref="A439:AF439"/>
+    <mergeCell ref="A440:AF440"/>
+    <mergeCell ref="A441:AF441"/>
+    <mergeCell ref="A442:AF442"/>
+    <mergeCell ref="A443:AF443"/>
+    <mergeCell ref="A444:AF444"/>
+    <mergeCell ref="A445:AF445"/>
+    <mergeCell ref="A446:AF446"/>
+    <mergeCell ref="A447:AF447"/>
+    <mergeCell ref="A448:AF448"/>
+    <mergeCell ref="A449:AF449"/>
+    <mergeCell ref="A450:AF450"/>
+    <mergeCell ref="A451:AF451"/>
+    <mergeCell ref="A452:AF452"/>
+    <mergeCell ref="A453:AF453"/>
+    <mergeCell ref="A454:AF454"/>
+    <mergeCell ref="A455:AF455"/>
+    <mergeCell ref="A456:AF456"/>
+    <mergeCell ref="A457:AF457"/>
+    <mergeCell ref="A458:AF458"/>
+    <mergeCell ref="A459:AF459"/>
+    <mergeCell ref="A460:AF460"/>
+    <mergeCell ref="A461:AF461"/>
+    <mergeCell ref="A462:AF462"/>
+    <mergeCell ref="A463:AF463"/>
+    <mergeCell ref="A464:AF464"/>
+    <mergeCell ref="A465:AF465"/>
+    <mergeCell ref="A466:AF466"/>
+    <mergeCell ref="A467:AF467"/>
+    <mergeCell ref="A468:AF468"/>
+    <mergeCell ref="A469:AF469"/>
+    <mergeCell ref="A470:AF470"/>
+    <mergeCell ref="A471:AF471"/>
+    <mergeCell ref="A472:AF472"/>
+    <mergeCell ref="A473:AF473"/>
+    <mergeCell ref="A474:AF474"/>
+    <mergeCell ref="A475:AF475"/>
+    <mergeCell ref="A476:AF476"/>
+    <mergeCell ref="A477:AF477"/>
+    <mergeCell ref="A478:AF478"/>
+    <mergeCell ref="A479:AF479"/>
+    <mergeCell ref="A480:AF480"/>
+    <mergeCell ref="A481:AF481"/>
+    <mergeCell ref="A482:AF482"/>
+    <mergeCell ref="A483:AF483"/>
+    <mergeCell ref="A484:AF484"/>
+    <mergeCell ref="A485:AF485"/>
+    <mergeCell ref="A486:AF486"/>
+    <mergeCell ref="A487:AF487"/>
+    <mergeCell ref="A488:AF488"/>
+    <mergeCell ref="A489:AF489"/>
+    <mergeCell ref="A490:AF490"/>
+    <mergeCell ref="A491:AF491"/>
+    <mergeCell ref="A492:AF492"/>
+    <mergeCell ref="A493:AF493"/>
+    <mergeCell ref="A494:AF494"/>
+    <mergeCell ref="A495:AF495"/>
+    <mergeCell ref="A496:AF496"/>
+    <mergeCell ref="A497:AF497"/>
+    <mergeCell ref="A498:AF498"/>
+    <mergeCell ref="A499:AF499"/>
+    <mergeCell ref="A500:AF500"/>
+    <mergeCell ref="A501:AF501"/>
+    <mergeCell ref="A502:AF502"/>
+    <mergeCell ref="A503:AF503"/>
+    <mergeCell ref="A504:AF504"/>
+    <mergeCell ref="A505:AF505"/>
+    <mergeCell ref="A506:AF506"/>
+    <mergeCell ref="A507:AF507"/>
+    <mergeCell ref="A508:AF508"/>
+    <mergeCell ref="A509:AF509"/>
+    <mergeCell ref="A510:AF510"/>
+    <mergeCell ref="A511:AF511"/>
+    <mergeCell ref="A512:AF512"/>
+    <mergeCell ref="A513:AF513"/>
+    <mergeCell ref="A514:AF514"/>
+    <mergeCell ref="A515:AF515"/>
+    <mergeCell ref="A516:AF516"/>
+    <mergeCell ref="A517:AF517"/>
+    <mergeCell ref="A518:AF518"/>
+    <mergeCell ref="A519:AF519"/>
+    <mergeCell ref="A520:AF520"/>
+    <mergeCell ref="A521:AF521"/>
+    <mergeCell ref="A522:AF522"/>
+    <mergeCell ref="A523:AF523"/>
+    <mergeCell ref="A524:AF524"/>
+    <mergeCell ref="A525:AF525"/>
+    <mergeCell ref="A526:AF526"/>
+    <mergeCell ref="A527:AF527"/>
+    <mergeCell ref="A528:AF528"/>
+    <mergeCell ref="A529:AF529"/>
+    <mergeCell ref="A530:AF530"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
